--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -376,8 +376,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N109" headerRowCount="1">
-  <autoFilter ref="A1:N109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N217" headerRowCount="1">
+  <autoFilter ref="A1:N217"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tarih"/>
     <tableColumn id="2" name="Saat"/>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
     </row>
     <row r="5">
@@ -986,7 +986,7 @@
         <v>46262</v>
       </c>
       <c r="B2" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v/>
       </c>
       <c r="H2" s="11" t="n">
-        <v>55.1299</v>
+        <v>55.1391</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>56.7016</v>
+        <v>56.7159</v>
       </c>
       <c r="J2" s="11">
         <f>IF(OR(H2="",I2=""),"",I2-H2)</f>
@@ -1022,10 +1022,10 @@
         <v/>
       </c>
       <c r="L2" s="11" t="n">
-        <v>6943.27</v>
+        <v>6944.15</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>7194.86</v>
+        <v>7195.74</v>
       </c>
       <c r="N2" s="11">
         <f>IF(OR(L2="",M2=""),"",M2-L2)</f>
@@ -1041,7 +1041,7 @@
         <v>46262</v>
       </c>
       <c r="B3" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>47.845</v>
+        <v>47.844</v>
       </c>
       <c r="E3" s="11" t="n">
         <v>48.625</v>
@@ -1063,10 +1063,10 @@
         <v/>
       </c>
       <c r="H3" s="11" t="n">
-        <v>55.696</v>
+        <v>55.714</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>56.61</v>
+        <v>56.634</v>
       </c>
       <c r="J3" s="11">
         <f>IF(OR(H3="",I3=""),"",I3-H3)</f>
@@ -1077,10 +1077,10 @@
         <v/>
       </c>
       <c r="L3" s="11" t="n">
-        <v>7033.82</v>
+        <v>7036.42</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>7178.15</v>
+        <v>7181.67</v>
       </c>
       <c r="N3" s="11">
         <f>IF(OR(L3="",M3=""),"",M3-L3)</f>
@@ -1096,7 +1096,7 @@
         <v>46262</v>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>48.028</v>
+        <v>48.032</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>48.322</v>
+        <v>48.319</v>
       </c>
       <c r="F4" s="11">
         <f>IF(OR(D4="",E4=""),"",E4-D4)</f>
@@ -1118,10 +1118,10 @@
         <v/>
       </c>
       <c r="H4" s="11" t="n">
-        <v>55.742</v>
+        <v>55.76</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>56.26</v>
+        <v>56.268</v>
       </c>
       <c r="J4" s="11">
         <f>IF(OR(H4="",I4=""),"",I4-H4)</f>
@@ -1132,10 +1132,10 @@
         <v/>
       </c>
       <c r="L4" s="11" t="n">
-        <v>7105.59</v>
+        <v>7102.9</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>7177.87</v>
+        <v>7173.72</v>
       </c>
       <c r="N4" s="11">
         <f>IF(OR(L4="",M4=""),"",M4-L4)</f>
@@ -1151,7 +1151,7 @@
         <v>46262</v>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>47.971</v>
+        <v>47.981</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>48.17</v>
+        <v>48.19</v>
       </c>
       <c r="F5" s="11">
         <f>IF(OR(D5="",E5=""),"",E5-D5)</f>
@@ -1173,10 +1173,10 @@
         <v/>
       </c>
       <c r="H5" s="11" t="n">
-        <v>55.731</v>
+        <v>55.765</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>56.075</v>
+        <v>56.12</v>
       </c>
       <c r="J5" s="11">
         <f>IF(OR(H5="",I5=""),"",I5-H5)</f>
@@ -1187,10 +1187,10 @@
         <v/>
       </c>
       <c r="L5" s="11" t="n">
-        <v>6998.3</v>
+        <v>7004.51</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>7175</v>
+        <v>7185</v>
       </c>
       <c r="N5" s="11">
         <f>IF(OR(L5="",M5=""),"",M5-L5)</f>
@@ -1206,7 +1206,7 @@
         <v>46262</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>47.3126</v>
+        <v>47.3123</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>48.5892</v>
+        <v>48.5893</v>
       </c>
       <c r="F6" s="11">
         <f>IF(OR(D6="",E6=""),"",E6-D6)</f>
@@ -1228,10 +1228,10 @@
         <v/>
       </c>
       <c r="H6" s="11" t="n">
-        <v>55.1726</v>
+        <v>55.197</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>56.5438</v>
+        <v>56.5683</v>
       </c>
       <c r="J6" s="11">
         <f>IF(OR(H6="",I6=""),"",I6-H6)</f>
@@ -1242,10 +1242,10 @@
         <v/>
       </c>
       <c r="L6" s="11" t="n">
-        <v>7005.31</v>
+        <v>7009.57</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>7164.08</v>
+        <v>7168.59</v>
       </c>
       <c r="N6" s="11">
         <f>IF(OR(L6="",M6=""),"",M6-L6)</f>
@@ -1261,7 +1261,7 @@
         <v>46262</v>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>47.166</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>49.084</v>
+        <v>49.083</v>
       </c>
       <c r="F7" s="11">
         <f>IF(OR(D7="",E7=""),"",E7-D7)</f>
@@ -1283,10 +1283,10 @@
         <v/>
       </c>
       <c r="H7" s="11" t="n">
-        <v>54.901</v>
+        <v>54.925</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>57.143</v>
+        <v>57.162</v>
       </c>
       <c r="J7" s="11">
         <f>IF(OR(H7="",I7=""),"",I7-H7)</f>
@@ -1297,10 +1297,10 @@
         <v/>
       </c>
       <c r="L7" s="11" t="n">
-        <v>7009.17</v>
+        <v>7012.46</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>7203.12</v>
+        <v>7205.91</v>
       </c>
       <c r="N7" s="11">
         <f>IF(OR(L7="",M7=""),"",M7-L7)</f>
@@ -1316,7 +1316,7 @@
         <v>46262</v>
       </c>
       <c r="B8" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>47.4203</v>
+        <v>47.4194</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>48.8204</v>
+        <v>48.8195</v>
       </c>
       <c r="F8" s="11">
         <f>IF(OR(D8="",E8=""),"",E8-D8)</f>
@@ -1338,10 +1338,10 @@
         <v/>
       </c>
       <c r="H8" s="11" t="n">
-        <v>55.1945</v>
+        <v>55.2124</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>56.8241</v>
+        <v>56.8475</v>
       </c>
       <c r="J8" s="11">
         <f>IF(OR(H8="",I8=""),"",I8-H8)</f>
@@ -1352,10 +1352,10 @@
         <v/>
       </c>
       <c r="L8" s="11" t="n">
-        <v>7019.29</v>
+        <v>7021.23</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>7227.61</v>
+        <v>7229.64</v>
       </c>
       <c r="N8" s="11">
         <f>IF(OR(L8="",M8=""),"",M8-L8)</f>
@@ -1371,7 +1371,7 @@
         <v>46262</v>
       </c>
       <c r="B9" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>48.0771</v>
+        <v>48.077</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>48.1462</v>
+        <v>48.146</v>
       </c>
       <c r="F9" s="11">
         <f>IF(OR(D9="",E9=""),"",E9-D9)</f>
@@ -1393,10 +1393,10 @@
         <v/>
       </c>
       <c r="H9" s="11" t="n">
-        <v>55.9461</v>
+        <v>55.9699</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>56.0434</v>
+        <v>56.0673</v>
       </c>
       <c r="J9" s="11">
         <f>IF(OR(H9="",I9=""),"",I9-H9)</f>
@@ -1407,10 +1407,10 @@
         <v/>
       </c>
       <c r="L9" s="11" t="n">
-        <v>7066.85</v>
+        <v>7071.54</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>7097.86</v>
+        <v>7102.56</v>
       </c>
       <c r="N9" s="11">
         <f>IF(OR(L9="",M9=""),"",M9-L9)</f>
@@ -1426,7 +1426,7 @@
         <v>46262</v>
       </c>
       <c r="B10" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>48.0984</v>
+        <v>48.0978</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>48.1369</v>
+        <v>48.1371</v>
       </c>
       <c r="F10" s="11">
         <f>IF(OR(D10="",E10=""),"",E10-D10)</f>
@@ -1448,10 +1448,10 @@
         <v/>
       </c>
       <c r="H10" s="11" t="n">
-        <v>55.9328</v>
+        <v>55.9561</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>56.0473</v>
+        <v>56.0716</v>
       </c>
       <c r="J10" s="11">
         <f>IF(OR(H10="",I10=""),"",I10-H10)</f>
@@ -1462,10 +1462,10 @@
         <v/>
       </c>
       <c r="L10" s="11" t="n">
-        <v>7068.4</v>
+        <v>7072.86</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>7102.54</v>
+        <v>7107.09</v>
       </c>
       <c r="N10" s="11">
         <f>IF(OR(L10="",M10=""),"",M10-L10)</f>
@@ -1481,7 +1481,7 @@
         <v>46262</v>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>47.7827</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>49.0179</v>
+        <v>49.018</v>
       </c>
       <c r="F11" s="11">
         <f>IF(OR(D11="",E11=""),"",E11-D11)</f>
@@ -1503,10 +1503,10 @@
         <v/>
       </c>
       <c r="H11" s="11" t="n">
-        <v>55.5196</v>
+        <v>55.5387</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>56.7975</v>
+        <v>56.8171</v>
       </c>
       <c r="J11" s="11">
         <f>IF(OR(H11="",I11=""),"",I11-H11)</f>
@@ -1517,10 +1517,10 @@
         <v/>
       </c>
       <c r="L11" s="11" t="n">
-        <v>7039.49</v>
+        <v>7038.55</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>7154.33</v>
+        <v>7153.42</v>
       </c>
       <c r="N11" s="11">
         <f>IF(OR(L11="",M11=""),"",M11-L11)</f>
@@ -1536,7 +1536,7 @@
         <v>46262</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         <v/>
       </c>
       <c r="H12" s="11" t="n">
-        <v>55.5499</v>
+        <v>55.5738</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>56.7126</v>
+        <v>56.7418</v>
       </c>
       <c r="J12" s="11">
         <f>IF(OR(H12="",I12=""),"",I12-H12)</f>
@@ -1572,10 +1572,10 @@
         <v/>
       </c>
       <c r="L12" s="11" t="n">
-        <v>7028.87</v>
+        <v>7032.7</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>7191.97</v>
+        <v>7195.66</v>
       </c>
       <c r="N12" s="11">
         <f>IF(OR(L12="",M12=""),"",M12-L12)</f>
@@ -1591,7 +1591,7 @@
         <v>46262</v>
       </c>
       <c r="B13" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>47.8481</v>
+        <v>47.848</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>48.4682</v>
+        <v>48.468</v>
       </c>
       <c r="F13" s="11">
         <f>IF(OR(D13="",E13=""),"",E13-D13)</f>
@@ -1613,10 +1613,10 @@
         <v/>
       </c>
       <c r="H13" s="11" t="n">
-        <v>55.7163</v>
+        <v>55.7305</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>56.3944</v>
+        <v>56.4086</v>
       </c>
       <c r="J13" s="11">
         <f>IF(OR(H13="",I13=""),"",I13-H13)</f>
@@ -1627,10 +1627,10 @@
         <v/>
       </c>
       <c r="L13" s="11" t="n">
-        <v>7092.53</v>
+        <v>7095.83</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>7149.33</v>
+        <v>7152.33</v>
       </c>
       <c r="N13" s="11">
         <f>IF(OR(L13="",M13=""),"",M13-L13)</f>
@@ -1646,7 +1646,7 @@
         <v>46262</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v/>
       </c>
       <c r="H14" s="11" t="n">
-        <v>55.084</v>
+        <v>55.098</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>56.656</v>
+        <v>56.67</v>
       </c>
       <c r="J14" s="11">
         <f>IF(OR(H14="",I14=""),"",I14-H14)</f>
@@ -1682,10 +1682,10 @@
         <v/>
       </c>
       <c r="L14" s="11" t="n">
-        <v>6986.24</v>
+        <v>6987.18</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>7244.46</v>
+        <v>7245.43</v>
       </c>
       <c r="N14" s="11">
         <f>IF(OR(L14="",M14=""),"",M14-L14)</f>
@@ -1701,7 +1701,7 @@
         <v>46262</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>47.8481</v>
+        <v>47.8479</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>48.4681</v>
+        <v>48.468</v>
       </c>
       <c r="F15" s="11">
         <f>IF(OR(D15="",E15=""),"",E15-D15)</f>
@@ -1723,10 +1723,10 @@
         <v/>
       </c>
       <c r="H15" s="11" t="n">
-        <v>55.71</v>
+        <v>55.7338</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>56.3879</v>
+        <v>56.4115</v>
       </c>
       <c r="J15" s="11">
         <f>IF(OR(H15="",I15=""),"",I15-H15)</f>
@@ -1737,10 +1737,10 @@
         <v/>
       </c>
       <c r="L15" s="11" t="n">
-        <v>7091.41</v>
+        <v>7095.59</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>7147.85</v>
+        <v>7152.46</v>
       </c>
       <c r="N15" s="11">
         <f>IF(OR(L15="",M15=""),"",M15-L15)</f>
@@ -1756,7 +1756,7 @@
         <v>46262</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>47.725</v>
+        <v>47.7247</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>48.705</v>
+        <v>48.7047</v>
       </c>
       <c r="F16" s="11">
         <f>IF(OR(D16="",E16=""),"",E16-D16)</f>
@@ -1778,10 +1778,10 @@
         <v/>
       </c>
       <c r="H16" s="11" t="n">
-        <v>55.5614</v>
+        <v>55.5778</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>56.7024</v>
+        <v>56.7191</v>
       </c>
       <c r="J16" s="11">
         <f>IF(OR(H16="",I16=""),"",I16-H16)</f>
@@ -1792,10 +1792,10 @@
         <v/>
       </c>
       <c r="L16" s="11" t="n">
-        <v>7021.06</v>
+        <v>7022.64</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>7237.17</v>
+        <v>7239.64</v>
       </c>
       <c r="N16" s="11">
         <f>IF(OR(L16="",M16=""),"",M16-L16)</f>
@@ -1811,7 +1811,7 @@
         <v>46262</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>48.0408</v>
+        <v>48.04</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>48.1248</v>
+        <v>48.125</v>
       </c>
       <c r="F17" s="11">
         <f>IF(OR(D17="",E17=""),"",E17-D17)</f>
@@ -1833,10 +1833,10 @@
         <v/>
       </c>
       <c r="H17" s="11" t="n">
-        <v>55.791</v>
+        <v>55.816</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>55.979</v>
+        <v>56.003</v>
       </c>
       <c r="J17" s="11">
         <f>IF(OR(H17="",I17=""),"",I17-H17)</f>
@@ -1847,10 +1847,10 @@
         <v/>
       </c>
       <c r="L17" s="11" t="n">
-        <v>7036.2</v>
+        <v>7040.97</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>7110.18</v>
+        <v>7115</v>
       </c>
       <c r="N17" s="11">
         <f>IF(OR(L17="",M17=""),"",M17-L17)</f>
@@ -1866,7 +1866,7 @@
         <v>46262</v>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>48.0758</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>48.3543</v>
+        <v>48.3544</v>
       </c>
       <c r="F18" s="11">
         <f>IF(OR(D18="",E18=""),"",E18-D18)</f>
@@ -1888,10 +1888,10 @@
         <v/>
       </c>
       <c r="H18" s="11" t="n">
-        <v>55.9603</v>
+        <v>55.9867</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>56.2846</v>
+        <v>56.3113</v>
       </c>
       <c r="J18" s="11">
         <f>IF(OR(H18="",I18=""),"",I18-H18)</f>
@@ -1902,10 +1902,10 @@
         <v/>
       </c>
       <c r="L18" s="11" t="n">
-        <v>7063.03</v>
+        <v>7067.85</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>7202.62</v>
+        <v>7207.59</v>
       </c>
       <c r="N18" s="11">
         <f>IF(OR(L18="",M18=""),"",M18-L18)</f>
@@ -1921,7 +1921,7 @@
         <v>46262</v>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1937,10 +1937,10 @@
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="11" t="n">
-        <v>7043.92</v>
+        <v>7044.02</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>7247.4</v>
+        <v>7247.51</v>
       </c>
       <c r="N19" s="11">
         <f>IF(OR(L19="",M19=""),"",M19-L19)</f>
@@ -1956,7 +1956,7 @@
         <v>46262</v>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>47.6572</v>
+        <v>47.6589</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>48.5572</v>
+        <v>48.5557</v>
       </c>
       <c r="F20" s="11">
         <f>IF(OR(D20="",E20=""),"",E20-D20)</f>
@@ -1978,10 +1978,10 @@
         <v/>
       </c>
       <c r="H20" s="11" t="n">
-        <v>55.4777</v>
+        <v>55.5024</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>56.5449</v>
+        <v>56.5735</v>
       </c>
       <c r="J20" s="11">
         <f>IF(OR(H20="",I20=""),"",I20-H20)</f>
@@ -1992,10 +1992,10 @@
         <v/>
       </c>
       <c r="L20" s="11" t="n">
-        <v>7021.83</v>
+        <v>7026.34</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>7469.98</v>
+        <v>7474.1</v>
       </c>
       <c r="N20" s="11">
         <f>IF(OR(L20="",M20=""),"",M20-L20)</f>
@@ -2011,7 +2011,7 @@
         <v>46262</v>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>47.6091</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>48.6147</v>
+        <v>48.6145</v>
       </c>
       <c r="F21" s="11">
         <f>IF(OR(D21="",E21=""),"",E21-D21)</f>
@@ -2033,10 +2033,10 @@
         <v/>
       </c>
       <c r="H21" s="11" t="n">
-        <v>55.4961</v>
+        <v>55.5153</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>56.5077</v>
+        <v>56.5271</v>
       </c>
       <c r="J21" s="11">
         <f>IF(OR(H21="",I21=""),"",I21-H21)</f>
@@ -2047,10 +2047,10 @@
         <v/>
       </c>
       <c r="L21" s="11" t="n">
-        <v>6993.62</v>
+        <v>6996.56</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>7246.14</v>
+        <v>7249.09</v>
       </c>
       <c r="N21" s="11">
         <f>IF(OR(L21="",M21=""),"",M21-L21)</f>
@@ -2066,7 +2066,7 @@
         <v>46262</v>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>47.535</v>
+        <v>47.5342</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>48.6933</v>
+        <v>48.6934</v>
       </c>
       <c r="F22" s="11">
         <f>IF(OR(D22="",E22=""),"",E22-D22)</f>
@@ -2088,10 +2088,10 @@
         <v/>
       </c>
       <c r="H22" s="11" t="n">
-        <v>55.3259</v>
+        <v>55.344</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>56.6789</v>
+        <v>56.6986</v>
       </c>
       <c r="J22" s="11">
         <f>IF(OR(H22="",I22=""),"",I22-H22)</f>
@@ -2102,10 +2102,10 @@
         <v/>
       </c>
       <c r="L22" s="11" t="n">
-        <v>7013.18</v>
+        <v>7016.31</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>7206.08</v>
+        <v>7209.23</v>
       </c>
       <c r="N22" s="11">
         <f>IF(OR(L22="",M22=""),"",M22-L22)</f>
@@ -2121,7 +2121,7 @@
         <v>46262</v>
       </c>
       <c r="B23" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46262</v>
       </c>
       <c r="B24" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>47.4538</v>
+        <v>47.4536</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>48.4713</v>
+        <v>48.471</v>
       </c>
       <c r="F24" s="11">
         <f>IF(OR(D24="",E24=""),"",E24-D24)</f>
@@ -2198,10 +2198,10 @@
         <v/>
       </c>
       <c r="H24" s="11" t="n">
-        <v>55.2381</v>
+        <v>55.263</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>56.4231</v>
+        <v>56.4483</v>
       </c>
       <c r="J24" s="11">
         <f>IF(OR(H24="",I24=""),"",I24-H24)</f>
@@ -2212,10 +2212,10 @@
         <v/>
       </c>
       <c r="L24" s="11" t="n">
-        <v>6966.83</v>
+        <v>6971.17</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>7151.86</v>
+        <v>7156.37</v>
       </c>
       <c r="N24" s="11">
         <f>IF(OR(L24="",M24=""),"",M24-L24)</f>
@@ -2231,7 +2231,7 @@
         <v>46262</v>
       </c>
       <c r="B25" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>46262</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>48.0811</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>48.1424</v>
+        <v>48.1425</v>
       </c>
       <c r="F26" s="11">
         <f>IF(OR(D26="",E26=""),"",E26-D26)</f>
@@ -2298,10 +2298,10 @@
         <v/>
       </c>
       <c r="H26" s="11" t="n">
-        <v>55.9505</v>
+        <v>55.9747</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>56.0404</v>
+        <v>56.065</v>
       </c>
       <c r="J26" s="11">
         <f>IF(OR(H26="",I26=""),"",I26-H26)</f>
@@ -2312,10 +2312,10 @@
         <v/>
       </c>
       <c r="L26" s="11" t="n">
-        <v>7081.77</v>
+        <v>7085.13</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>7113.29</v>
+        <v>7115.67</v>
       </c>
       <c r="N26" s="11">
         <f>IF(OR(L26="",M26=""),"",M26-L26)</f>
@@ -2331,7 +2331,7 @@
         <v>46262</v>
       </c>
       <c r="B27" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>48.05</v>
+        <v>48.049</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>48.186</v>
@@ -2353,10 +2353,10 @@
         <v/>
       </c>
       <c r="H27" s="11" t="n">
-        <v>55.831</v>
+        <v>55.854</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>56.034</v>
+        <v>56.053</v>
       </c>
       <c r="J27" s="11">
         <f>IF(OR(H27="",I27=""),"",I27-H27)</f>
@@ -2367,10 +2367,10 @@
         <v/>
       </c>
       <c r="L27" s="11" t="n">
-        <v>7054</v>
+        <v>7063</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>7097</v>
+        <v>7104</v>
       </c>
       <c r="N27" s="11">
         <f>IF(OR(L27="",M27=""),"",M27-L27)</f>
@@ -2386,7 +2386,7 @@
         <v>46262</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         <v/>
       </c>
       <c r="H28" s="11" t="n">
-        <v>55.491</v>
+        <v>55.508</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>56.581</v>
+        <v>56.598</v>
       </c>
       <c r="J28" s="11">
         <f>IF(OR(H28="",I28=""),"",I28-H28)</f>
@@ -2422,10 +2422,10 @@
         <v/>
       </c>
       <c r="L28" s="11" t="n">
-        <v>7082.06</v>
+        <v>7076.05</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>7182.06</v>
+        <v>7176.05</v>
       </c>
       <c r="N28" s="11">
         <f>IF(OR(L28="",M28=""),"",M28-L28)</f>
@@ -2441,7 +2441,7 @@
         <v>46262</v>
       </c>
       <c r="B29" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="12" t="n"/>
       <c r="L29" s="11" t="n">
-        <v>7043.92</v>
+        <v>7044.02</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>7232.93</v>
+        <v>7233.04</v>
       </c>
       <c r="N29" s="11">
         <f>IF(OR(L29="",M29=""),"",M29-L29)</f>
@@ -2476,7 +2476,7 @@
         <v>46262</v>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         <v/>
       </c>
       <c r="H30" s="11" t="n">
-        <v>55.1797</v>
+        <v>55.2034</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>56.8399</v>
+        <v>56.8692</v>
       </c>
       <c r="J30" s="11">
         <f>IF(OR(H30="",I30=""),"",I30-H30)</f>
@@ -2512,10 +2512,10 @@
         <v/>
       </c>
       <c r="L30" s="11" t="n">
-        <v>6981.54</v>
+        <v>6986.46</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>7191.96</v>
+        <v>7197.13</v>
       </c>
       <c r="N30" s="11">
         <f>IF(OR(L30="",M30=""),"",M30-L30)</f>
@@ -2531,7 +2531,7 @@
         <v>46262</v>
       </c>
       <c r="B31" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>48.1001</v>
+        <v>48.1003</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>48.3413</v>
+        <v>48.3415</v>
       </c>
       <c r="F31" s="11">
         <f>IF(OR(D31="",E31=""),"",E31-D31)</f>
@@ -2553,10 +2553,10 @@
         <v/>
       </c>
       <c r="H31" s="11" t="n">
-        <v>55.9358</v>
+        <v>55.9595</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>56.2728</v>
+        <v>56.2966</v>
       </c>
       <c r="J31" s="11">
         <f>IF(OR(H31="",I31=""),"",I31-H31)</f>
@@ -2567,10 +2567,10 @@
         <v/>
       </c>
       <c r="L31" s="11" t="n">
-        <v>6981.88</v>
+        <v>6985.71</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>7124.01</v>
+        <v>7127.91</v>
       </c>
       <c r="N31" s="11">
         <f>IF(OR(L31="",M31=""),"",M31-L31)</f>
@@ -2586,7 +2586,7 @@
         <v>46262</v>
       </c>
       <c r="B32" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>47.7074</v>
+        <v>47.7072</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>48.5152</v>
+        <v>48.5151</v>
       </c>
       <c r="F32" s="11">
         <f>IF(OR(D32="",E32=""),"",E32-D32)</f>
@@ -2608,10 +2608,10 @@
         <v/>
       </c>
       <c r="H32" s="11" t="n">
-        <v>55.569</v>
+        <v>55.5874</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>56.4279</v>
+        <v>56.447</v>
       </c>
       <c r="J32" s="11">
         <f>IF(OR(H32="",I32=""),"",I32-H32)</f>
@@ -2622,10 +2622,10 @@
         <v/>
       </c>
       <c r="L32" s="11" t="n">
-        <v>7023.07</v>
+        <v>7022.97</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>7220.82</v>
+        <v>7220.87</v>
       </c>
       <c r="N32" s="11">
         <f>IF(OR(L32="",M32=""),"",M32-L32)</f>
@@ -2641,7 +2641,7 @@
         <v>46262</v>
       </c>
       <c r="B33" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>48.0171</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>48.2197</v>
+        <v>48.2196</v>
       </c>
       <c r="F33" s="11">
         <f>IF(OR(D33="",E33=""),"",E33-D33)</f>
@@ -2663,10 +2663,10 @@
         <v/>
       </c>
       <c r="H33" s="11" t="n">
-        <v>55.8879</v>
+        <v>55.9047</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>56.1131</v>
+        <v>56.1299</v>
       </c>
       <c r="J33" s="11">
         <f>IF(OR(H33="",I33=""),"",I33-H33)</f>
@@ -2677,10 +2677,10 @@
         <v/>
       </c>
       <c r="L33" s="11" t="n">
-        <v>7058.1</v>
+        <v>7063.03</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>7114.79</v>
+        <v>7119.76</v>
       </c>
       <c r="N33" s="11">
         <f>IF(OR(L33="",M33=""),"",M33-L33)</f>
@@ -2696,7 +2696,7 @@
         <v>46262</v>
       </c>
       <c r="B34" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>47.7422</v>
+        <v>47.7421</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>48.7032</v>
+        <v>48.7031</v>
       </c>
       <c r="F34" s="11">
         <f>IF(OR(D34="",E34=""),"",E34-D34)</f>
@@ -2718,10 +2718,10 @@
         <v/>
       </c>
       <c r="H34" s="11" t="n">
-        <v>55.6038</v>
+        <v>55.6208</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>56.7169</v>
+        <v>56.7339</v>
       </c>
       <c r="J34" s="11">
         <f>IF(OR(H34="",I34=""),"",I34-H34)</f>
@@ -2732,10 +2732,10 @@
         <v/>
       </c>
       <c r="L34" s="11" t="n">
-        <v>7041.26</v>
+        <v>7044.4</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>7185.86</v>
+        <v>7189</v>
       </c>
       <c r="N34" s="11">
         <f>IF(OR(L34="",M34=""),"",M34-L34)</f>
@@ -2751,7 +2751,7 @@
         <v>46262</v>
       </c>
       <c r="B35" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>48.042</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>48.115</v>
+        <v>48.116</v>
       </c>
       <c r="F35" s="11">
         <f>IF(OR(D35="",E35=""),"",E35-D35)</f>
@@ -2773,10 +2773,10 @@
         <v/>
       </c>
       <c r="H35" s="11" t="n">
-        <v>55.801</v>
+        <v>55.825</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>55.972</v>
+        <v>55.991</v>
       </c>
       <c r="J35" s="11">
         <f>IF(OR(H35="",I35=""),"",I35-H35)</f>
@@ -2796,7 +2796,7 @@
         <v>46262</v>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v/>
       </c>
       <c r="H36" s="11" t="n">
-        <v>55.38</v>
+        <v>55.39</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>56.52</v>
+        <v>56.53</v>
       </c>
       <c r="J36" s="11">
         <f>IF(OR(H36="",I36=""),"",I36-H36)</f>
@@ -2832,10 +2832,10 @@
         <v/>
       </c>
       <c r="L36" s="11" t="n">
-        <v>7009.19</v>
+        <v>7009.9</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>7215.39</v>
+        <v>7216.46</v>
       </c>
       <c r="N36" s="11">
         <f>IF(OR(L36="",M36=""),"",M36-L36)</f>
@@ -2851,7 +2851,7 @@
         <v>46262</v>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         <v/>
       </c>
       <c r="H37" s="11" t="n">
-        <v>55.5758</v>
+        <v>55.5785</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>56.7001</v>
+        <v>56.7028</v>
       </c>
       <c r="J37" s="11">
         <f>IF(OR(H37="",I37=""),"",I37-H37)</f>
@@ -2887,10 +2887,10 @@
         <v/>
       </c>
       <c r="L37" s="11" t="n">
-        <v>7078.33</v>
+        <v>7071.22</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>7221.25</v>
+        <v>7214</v>
       </c>
       <c r="N37" s="11">
         <f>IF(OR(L37="",M37=""),"",M37-L37)</f>
@@ -2906,7 +2906,7 @@
         <v>46262</v>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>47.8019</v>
+        <v>47.8017</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>48.4521</v>
+        <v>48.4519</v>
       </c>
       <c r="F38" s="11">
         <f>IF(OR(D38="",E38=""),"",E38-D38)</f>
@@ -2928,10 +2928,10 @@
         <v/>
       </c>
       <c r="H38" s="11" t="n">
-        <v>55.5796</v>
+        <v>55.5984</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>56.392</v>
+        <v>56.4112</v>
       </c>
       <c r="J38" s="11">
         <f>IF(OR(H38="",I38=""),"",I38-H38)</f>
@@ -2942,10 +2942,10 @@
         <v/>
       </c>
       <c r="L38" s="11" t="n">
-        <v>7038.97</v>
+        <v>7042.31</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>7181.1</v>
+        <v>7184.5</v>
       </c>
       <c r="N38" s="11">
         <f>IF(OR(L38="",M38=""),"",M38-L38)</f>
@@ -2961,7 +2961,7 @@
         <v>46262</v>
       </c>
       <c r="B39" s="10" t="n">
-        <v>0.5570949074074074</v>
+        <v>0.5665625</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>47.7169</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>48.7128</v>
+        <v>48.713</v>
       </c>
       <c r="F39" s="11">
         <f>IF(OR(D39="",E39=""),"",E39-D39)</f>
@@ -2983,10 +2983,10 @@
         <v/>
       </c>
       <c r="H39" s="11" t="n">
-        <v>55.5095</v>
+        <v>55.5267</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>56.7236</v>
+        <v>56.7413</v>
       </c>
       <c r="J39" s="11">
         <f>IF(OR(H39="",I39=""),"",I39-H39)</f>
@@ -2997,10 +2997,10 @@
         <v/>
       </c>
       <c r="L39" s="11" t="n">
-        <v>7061.18</v>
+        <v>7064.07</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>7285.19</v>
+        <v>7288.24</v>
       </c>
       <c r="N39" s="11">
         <f>IF(OR(L39="",M39=""),"",M39-L39)</f>
@@ -3025,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8730,6 +8730,5622 @@
       <c r="M109" s="15" t="inlineStr"/>
       <c r="N109" s="10" t="n">
         <v>0.5575578703703704</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B110" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>55.1391</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>56.7159</v>
+      </c>
+      <c r="G110" s="11">
+        <f>IF(OR(E110="",F110=""),"",F110-E110)</f>
+        <v/>
+      </c>
+      <c r="H110" s="12">
+        <f>IFERROR(G110/E110,"")</f>
+        <v/>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="n">
+        <v>1.5768</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="M110" s="15" t="inlineStr"/>
+      <c r="N110" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B111" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>47.354</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>48.704</v>
+      </c>
+      <c r="G111" s="11">
+        <f>IF(OR(E111="",F111=""),"",F111-E111)</f>
+        <v/>
+      </c>
+      <c r="H111" s="12">
+        <f>IFERROR(G111/E111,"")</f>
+        <v/>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="M111" s="15" t="inlineStr"/>
+      <c r="N111" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B112" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>6944.15</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>7195.74</v>
+      </c>
+      <c r="G112" s="11">
+        <f>IF(OR(E112="",F112=""),"",F112-E112)</f>
+        <v/>
+      </c>
+      <c r="H112" s="12">
+        <f>IFERROR(G112/E112,"")</f>
+        <v/>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="n">
+        <v>251.59</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M112" s="15" t="inlineStr"/>
+      <c r="N112" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B113" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>55.714</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>56.634</v>
+      </c>
+      <c r="G113" s="11">
+        <f>IF(OR(E113="",F113=""),"",F113-E113)</f>
+        <v/>
+      </c>
+      <c r="H113" s="12">
+        <f>IFERROR(G113/E113,"")</f>
+        <v/>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J113" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M113" s="15" t="inlineStr"/>
+      <c r="N113" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B114" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>47.844</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>48.625</v>
+      </c>
+      <c r="G114" s="11">
+        <f>IF(OR(E114="",F114=""),"",F114-E114)</f>
+        <v/>
+      </c>
+      <c r="H114" s="12">
+        <f>IFERROR(G114/E114,"")</f>
+        <v/>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M114" s="15" t="inlineStr"/>
+      <c r="N114" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B115" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>7036.42</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>7181.67</v>
+      </c>
+      <c r="G115" s="11">
+        <f>IF(OR(E115="",F115=""),"",F115-E115)</f>
+        <v/>
+      </c>
+      <c r="H115" s="12">
+        <f>IFERROR(G115/E115,"")</f>
+        <v/>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>145.26</v>
+      </c>
+      <c r="L115" s="12" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="M115" s="15" t="inlineStr"/>
+      <c r="N115" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B116" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>56.268</v>
+      </c>
+      <c r="G116" s="11">
+        <f>IF(OR(E116="",F116=""),"",F116-E116)</f>
+        <v/>
+      </c>
+      <c r="H116" s="12">
+        <f>IFERROR(G116/E116,"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="L116" s="12" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="M116" s="15" t="inlineStr"/>
+      <c r="N116" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B117" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>48.032</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>48.319</v>
+      </c>
+      <c r="G117" s="11">
+        <f>IF(OR(E117="",F117=""),"",F117-E117)</f>
+        <v/>
+      </c>
+      <c r="H117" s="12">
+        <f>IFERROR(G117/E117,"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M117" s="15" t="inlineStr"/>
+      <c r="N117" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B118" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>7102.9</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>7173.72</v>
+      </c>
+      <c r="G118" s="11">
+        <f>IF(OR(E118="",F118=""),"",F118-E118)</f>
+        <v/>
+      </c>
+      <c r="H118" s="12">
+        <f>IFERROR(G118/E118,"")</f>
+        <v/>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K118" s="11" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M118" s="15" t="inlineStr"/>
+      <c r="N118" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B119" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>55.765</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="G119" s="11">
+        <f>IF(OR(E119="",F119=""),"",F119-E119)</f>
+        <v/>
+      </c>
+      <c r="H119" s="12">
+        <f>IFERROR(G119/E119,"")</f>
+        <v/>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="M119" s="15" t="inlineStr"/>
+      <c r="N119" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B120" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>47.981</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="G120" s="11">
+        <f>IF(OR(E120="",F120=""),"",F120-E120)</f>
+        <v/>
+      </c>
+      <c r="H120" s="12">
+        <f>IFERROR(G120/E120,"")</f>
+        <v/>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="M120" s="15" t="inlineStr"/>
+      <c r="N120" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B121" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>7004.51</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>7185</v>
+      </c>
+      <c r="G121" s="11">
+        <f>IF(OR(E121="",F121=""),"",F121-E121)</f>
+        <v/>
+      </c>
+      <c r="H121" s="12">
+        <f>IFERROR(G121/E121,"")</f>
+        <v/>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>180.49</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="M121" s="15" t="inlineStr"/>
+      <c r="N121" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B122" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>55.197</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>56.5683</v>
+      </c>
+      <c r="G122" s="11">
+        <f>IF(OR(E122="",F122=""),"",F122-E122)</f>
+        <v/>
+      </c>
+      <c r="H122" s="12">
+        <f>IFERROR(G122/E122,"")</f>
+        <v/>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K122" s="11" t="n">
+        <v>1.3713</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="M122" s="15" t="inlineStr"/>
+      <c r="N122" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B123" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>47.3123</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>48.5893</v>
+      </c>
+      <c r="G123" s="11">
+        <f>IF(OR(E123="",F123=""),"",F123-E123)</f>
+        <v/>
+      </c>
+      <c r="H123" s="12">
+        <f>IFERROR(G123/E123,"")</f>
+        <v/>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="M123" s="15" t="inlineStr"/>
+      <c r="N123" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>7009.57</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>7168.59</v>
+      </c>
+      <c r="G124" s="11">
+        <f>IF(OR(E124="",F124=""),"",F124-E124)</f>
+        <v/>
+      </c>
+      <c r="H124" s="12">
+        <f>IFERROR(G124/E124,"")</f>
+        <v/>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="n">
+        <v>159.02</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="M124" s="15" t="inlineStr"/>
+      <c r="N124" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B125" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>54.925</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>57.162</v>
+      </c>
+      <c r="G125" s="11">
+        <f>IF(OR(E125="",F125=""),"",F125-E125)</f>
+        <v/>
+      </c>
+      <c r="H125" s="12">
+        <f>IFERROR(G125/E125,"")</f>
+        <v/>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>2.237</v>
+      </c>
+      <c r="L125" s="12" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="M125" s="15" t="inlineStr"/>
+      <c r="N125" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>47.166</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>49.083</v>
+      </c>
+      <c r="G126" s="11">
+        <f>IF(OR(E126="",F126=""),"",F126-E126)</f>
+        <v/>
+      </c>
+      <c r="H126" s="12">
+        <f>IFERROR(G126/E126,"")</f>
+        <v/>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="L126" s="12" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M126" s="15" t="inlineStr"/>
+      <c r="N126" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B127" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>7012.46</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>7205.91</v>
+      </c>
+      <c r="G127" s="11">
+        <f>IF(OR(E127="",F127=""),"",F127-E127)</f>
+        <v/>
+      </c>
+      <c r="H127" s="12">
+        <f>IFERROR(G127/E127,"")</f>
+        <v/>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J127" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="n">
+        <v>193.45</v>
+      </c>
+      <c r="L127" s="12" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M127" s="15" t="inlineStr"/>
+      <c r="N127" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B128" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>55.2124</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>56.8475</v>
+      </c>
+      <c r="G128" s="11">
+        <f>IF(OR(E128="",F128=""),"",F128-E128)</f>
+        <v/>
+      </c>
+      <c r="H128" s="12">
+        <f>IFERROR(G128/E128,"")</f>
+        <v/>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="n">
+        <v>1.6351</v>
+      </c>
+      <c r="L128" s="12" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="M128" s="15" t="inlineStr"/>
+      <c r="N128" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B129" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>47.4194</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>48.8195</v>
+      </c>
+      <c r="G129" s="11">
+        <f>IF(OR(E129="",F129=""),"",F129-E129)</f>
+        <v/>
+      </c>
+      <c r="H129" s="12">
+        <f>IFERROR(G129/E129,"")</f>
+        <v/>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J129" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="M129" s="15" t="inlineStr"/>
+      <c r="N129" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B130" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>7021.23</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>7229.64</v>
+      </c>
+      <c r="G130" s="11">
+        <f>IF(OR(E130="",F130=""),"",F130-E130)</f>
+        <v/>
+      </c>
+      <c r="H130" s="12">
+        <f>IFERROR(G130/E130,"")</f>
+        <v/>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="n">
+        <v>208.41</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="M130" s="15" t="inlineStr"/>
+      <c r="N130" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B131" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>55.9699</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>56.0673</v>
+      </c>
+      <c r="G131" s="11">
+        <f>IF(OR(E131="",F131=""),"",F131-E131)</f>
+        <v/>
+      </c>
+      <c r="H131" s="12">
+        <f>IFERROR(G131/E131,"")</f>
+        <v/>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="L131" s="12" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="M131" s="15" t="inlineStr"/>
+      <c r="N131" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B132" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>48.077</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>48.146</v>
+      </c>
+      <c r="G132" s="11">
+        <f>IF(OR(E132="",F132=""),"",F132-E132)</f>
+        <v/>
+      </c>
+      <c r="H132" s="12">
+        <f>IFERROR(G132/E132,"")</f>
+        <v/>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="L132" s="12" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="M132" s="15" t="inlineStr"/>
+      <c r="N132" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B133" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>7071.54</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>7102.56</v>
+      </c>
+      <c r="G133" s="11">
+        <f>IF(OR(E133="",F133=""),"",F133-E133)</f>
+        <v/>
+      </c>
+      <c r="H133" s="12">
+        <f>IFERROR(G133/E133,"")</f>
+        <v/>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J133" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="L133" s="12" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="M133" s="15" t="inlineStr"/>
+      <c r="N133" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B134" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>55.9561</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>56.0716</v>
+      </c>
+      <c r="G134" s="11">
+        <f>IF(OR(E134="",F134=""),"",F134-E134)</f>
+        <v/>
+      </c>
+      <c r="H134" s="12">
+        <f>IFERROR(G134/E134,"")</f>
+        <v/>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="L134" s="12" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="M134" s="15" t="inlineStr"/>
+      <c r="N134" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B135" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>48.0978</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>48.1371</v>
+      </c>
+      <c r="G135" s="11">
+        <f>IF(OR(E135="",F135=""),"",F135-E135)</f>
+        <v/>
+      </c>
+      <c r="H135" s="12">
+        <f>IFERROR(G135/E135,"")</f>
+        <v/>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="L135" s="12" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M135" s="15" t="inlineStr"/>
+      <c r="N135" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>7072.86</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>7107.09</v>
+      </c>
+      <c r="G136" s="11">
+        <f>IF(OR(E136="",F136=""),"",F136-E136)</f>
+        <v/>
+      </c>
+      <c r="H136" s="12">
+        <f>IFERROR(G136/E136,"")</f>
+        <v/>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K136" s="11" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="L136" s="12" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="M136" s="15" t="inlineStr"/>
+      <c r="N136" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B137" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>55.5387</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>56.8171</v>
+      </c>
+      <c r="G137" s="11">
+        <f>IF(OR(E137="",F137=""),"",F137-E137)</f>
+        <v/>
+      </c>
+      <c r="H137" s="12">
+        <f>IFERROR(G137/E137,"")</f>
+        <v/>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="n">
+        <v>1.2784</v>
+      </c>
+      <c r="L137" s="12" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="M137" s="15" t="inlineStr"/>
+      <c r="N137" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B138" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>47.7827</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>49.018</v>
+      </c>
+      <c r="G138" s="11">
+        <f>IF(OR(E138="",F138=""),"",F138-E138)</f>
+        <v/>
+      </c>
+      <c r="H138" s="12">
+        <f>IFERROR(G138/E138,"")</f>
+        <v/>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="n">
+        <v>1.2353</v>
+      </c>
+      <c r="L138" s="12" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="M138" s="15" t="inlineStr"/>
+      <c r="N138" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B139" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>7038.55</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>7153.42</v>
+      </c>
+      <c r="G139" s="11">
+        <f>IF(OR(E139="",F139=""),"",F139-E139)</f>
+        <v/>
+      </c>
+      <c r="H139" s="12">
+        <f>IFERROR(G139/E139,"")</f>
+        <v/>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="L139" s="12" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M139" s="15" t="inlineStr"/>
+      <c r="N139" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B140" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>55.5738</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>56.7418</v>
+      </c>
+      <c r="G140" s="11">
+        <f>IF(OR(E140="",F140=""),"",F140-E140)</f>
+        <v/>
+      </c>
+      <c r="H140" s="12">
+        <f>IFERROR(G140/E140,"")</f>
+        <v/>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="L140" s="12" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M140" s="15" t="inlineStr"/>
+      <c r="N140" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B141" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>47.795</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>48.645</v>
+      </c>
+      <c r="G141" s="11">
+        <f>IF(OR(E141="",F141=""),"",F141-E141)</f>
+        <v/>
+      </c>
+      <c r="H141" s="12">
+        <f>IFERROR(G141/E141,"")</f>
+        <v/>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L141" s="12" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="M141" s="15" t="inlineStr"/>
+      <c r="N141" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B142" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>7032.7</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>7195.66</v>
+      </c>
+      <c r="G142" s="11">
+        <f>IF(OR(E142="",F142=""),"",F142-E142)</f>
+        <v/>
+      </c>
+      <c r="H142" s="12">
+        <f>IFERROR(G142/E142,"")</f>
+        <v/>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K142" s="11" t="n">
+        <v>162.96</v>
+      </c>
+      <c r="L142" s="12" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="M142" s="15" t="inlineStr"/>
+      <c r="N142" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B143" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>55.7305</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>56.4086</v>
+      </c>
+      <c r="G143" s="11">
+        <f>IF(OR(E143="",F143=""),"",F143-E143)</f>
+        <v/>
+      </c>
+      <c r="H143" s="12">
+        <f>IFERROR(G143/E143,"")</f>
+        <v/>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="n">
+        <v>0.6781</v>
+      </c>
+      <c r="L143" s="12" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="M143" s="15" t="inlineStr"/>
+      <c r="N143" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B144" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>47.848</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>48.468</v>
+      </c>
+      <c r="G144" s="11">
+        <f>IF(OR(E144="",F144=""),"",F144-E144)</f>
+        <v/>
+      </c>
+      <c r="H144" s="12">
+        <f>IFERROR(G144/E144,"")</f>
+        <v/>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="L144" s="12" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M144" s="15" t="inlineStr"/>
+      <c r="N144" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B145" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>7095.83</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>7152.33</v>
+      </c>
+      <c r="G145" s="11">
+        <f>IF(OR(E145="",F145=""),"",F145-E145)</f>
+        <v/>
+      </c>
+      <c r="H145" s="12">
+        <f>IFERROR(G145/E145,"")</f>
+        <v/>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="L145" s="12" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M145" s="15" t="inlineStr"/>
+      <c r="N145" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B146" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>55.098</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="G146" s="11">
+        <f>IF(OR(E146="",F146=""),"",F146-E146)</f>
+        <v/>
+      </c>
+      <c r="H146" s="12">
+        <f>IFERROR(G146/E146,"")</f>
+        <v/>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K146" s="11" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="L146" s="12" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="M146" s="15" t="inlineStr"/>
+      <c r="N146" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B147" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>47.315</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>48.665</v>
+      </c>
+      <c r="G147" s="11">
+        <f>IF(OR(E147="",F147=""),"",F147-E147)</f>
+        <v/>
+      </c>
+      <c r="H147" s="12">
+        <f>IFERROR(G147/E147,"")</f>
+        <v/>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L147" s="12" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="M147" s="15" t="inlineStr"/>
+      <c r="N147" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B148" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>6987.18</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>7245.43</v>
+      </c>
+      <c r="G148" s="11">
+        <f>IF(OR(E148="",F148=""),"",F148-E148)</f>
+        <v/>
+      </c>
+      <c r="H148" s="12">
+        <f>IFERROR(G148/E148,"")</f>
+        <v/>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K148" s="11" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="L148" s="12" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="M148" s="15" t="inlineStr"/>
+      <c r="N148" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B149" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>55.7338</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>56.4115</v>
+      </c>
+      <c r="G149" s="11">
+        <f>IF(OR(E149="",F149=""),"",F149-E149)</f>
+        <v/>
+      </c>
+      <c r="H149" s="12">
+        <f>IFERROR(G149/E149,"")</f>
+        <v/>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K149" s="11" t="n">
+        <v>0.6777</v>
+      </c>
+      <c r="L149" s="12" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="M149" s="15" t="inlineStr"/>
+      <c r="N149" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B150" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>47.8479</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>48.468</v>
+      </c>
+      <c r="G150" s="11">
+        <f>IF(OR(E150="",F150=""),"",F150-E150)</f>
+        <v/>
+      </c>
+      <c r="H150" s="12">
+        <f>IFERROR(G150/E150,"")</f>
+        <v/>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K150" s="11" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="L150" s="12" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M150" s="15" t="inlineStr"/>
+      <c r="N150" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B151" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v>7095.59</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>7152.46</v>
+      </c>
+      <c r="G151" s="11">
+        <f>IF(OR(E151="",F151=""),"",F151-E151)</f>
+        <v/>
+      </c>
+      <c r="H151" s="12">
+        <f>IFERROR(G151/E151,"")</f>
+        <v/>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K151" s="11" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="L151" s="12" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M151" s="15" t="inlineStr"/>
+      <c r="N151" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B152" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>55.5024</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>56.5735</v>
+      </c>
+      <c r="G152" s="11">
+        <f>IF(OR(E152="",F152=""),"",F152-E152)</f>
+        <v/>
+      </c>
+      <c r="H152" s="12">
+        <f>IFERROR(G152/E152,"")</f>
+        <v/>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K152" s="11" t="n">
+        <v>1.0711</v>
+      </c>
+      <c r="L152" s="12" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="M152" s="15" t="inlineStr"/>
+      <c r="N152" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B153" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>47.6589</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>48.5557</v>
+      </c>
+      <c r="G153" s="11">
+        <f>IF(OR(E153="",F153=""),"",F153-E153)</f>
+        <v/>
+      </c>
+      <c r="H153" s="12">
+        <f>IFERROR(G153/E153,"")</f>
+        <v/>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K153" s="11" t="n">
+        <v>0.8968</v>
+      </c>
+      <c r="L153" s="12" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="M153" s="15" t="inlineStr"/>
+      <c r="N153" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B154" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>7026.34</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>7474.1</v>
+      </c>
+      <c r="G154" s="11">
+        <f>IF(OR(E154="",F154=""),"",F154-E154)</f>
+        <v/>
+      </c>
+      <c r="H154" s="12">
+        <f>IFERROR(G154/E154,"")</f>
+        <v/>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K154" s="11" t="n">
+        <v>447.76</v>
+      </c>
+      <c r="L154" s="12" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="M154" s="15" t="inlineStr"/>
+      <c r="N154" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B155" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="n">
+        <v>55.5778</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>56.7191</v>
+      </c>
+      <c r="G155" s="11">
+        <f>IF(OR(E155="",F155=""),"",F155-E155)</f>
+        <v/>
+      </c>
+      <c r="H155" s="12">
+        <f>IFERROR(G155/E155,"")</f>
+        <v/>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K155" s="11" t="n">
+        <v>1.1413</v>
+      </c>
+      <c r="L155" s="12" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M155" s="15" t="inlineStr"/>
+      <c r="N155" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>47.7247</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>48.7047</v>
+      </c>
+      <c r="G156" s="11">
+        <f>IF(OR(E156="",F156=""),"",F156-E156)</f>
+        <v/>
+      </c>
+      <c r="H156" s="12">
+        <f>IFERROR(G156/E156,"")</f>
+        <v/>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K156" s="11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L156" s="12" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M156" s="15" t="inlineStr"/>
+      <c r="N156" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B157" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v>7022.64</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>7239.64</v>
+      </c>
+      <c r="G157" s="11">
+        <f>IF(OR(E157="",F157=""),"",F157-E157)</f>
+        <v/>
+      </c>
+      <c r="H157" s="12">
+        <f>IFERROR(G157/E157,"")</f>
+        <v/>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K157" s="11" t="n">
+        <v>217</v>
+      </c>
+      <c r="L157" s="12" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="M157" s="15" t="inlineStr"/>
+      <c r="N157" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B158" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>55.816</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>56.003</v>
+      </c>
+      <c r="G158" s="11">
+        <f>IF(OR(E158="",F158=""),"",F158-E158)</f>
+        <v/>
+      </c>
+      <c r="H158" s="12">
+        <f>IFERROR(G158/E158,"")</f>
+        <v/>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K158" s="11" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="L158" s="12" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="M158" s="15" t="inlineStr"/>
+      <c r="N158" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B159" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>48.125</v>
+      </c>
+      <c r="G159" s="11">
+        <f>IF(OR(E159="",F159=""),"",F159-E159)</f>
+        <v/>
+      </c>
+      <c r="H159" s="12">
+        <f>IFERROR(G159/E159,"")</f>
+        <v/>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K159" s="11" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="L159" s="12" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M159" s="15" t="inlineStr"/>
+      <c r="N159" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B160" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>7040.97</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>7115</v>
+      </c>
+      <c r="G160" s="11">
+        <f>IF(OR(E160="",F160=""),"",F160-E160)</f>
+        <v/>
+      </c>
+      <c r="H160" s="12">
+        <f>IFERROR(G160/E160,"")</f>
+        <v/>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K160" s="11" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="L160" s="12" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="M160" s="15" t="inlineStr"/>
+      <c r="N160" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B161" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>55.9867</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>56.3113</v>
+      </c>
+      <c r="G161" s="11">
+        <f>IF(OR(E161="",F161=""),"",F161-E161)</f>
+        <v/>
+      </c>
+      <c r="H161" s="12">
+        <f>IFERROR(G161/E161,"")</f>
+        <v/>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J161" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K161" s="11" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="L161" s="12" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="M161" s="15" t="inlineStr"/>
+      <c r="N161" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B162" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>48.0758</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>48.3544</v>
+      </c>
+      <c r="G162" s="11">
+        <f>IF(OR(E162="",F162=""),"",F162-E162)</f>
+        <v/>
+      </c>
+      <c r="H162" s="12">
+        <f>IFERROR(G162/E162,"")</f>
+        <v/>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K162" s="11" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="L162" s="12" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="M162" s="15" t="inlineStr"/>
+      <c r="N162" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B163" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>7067.85</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>7207.59</v>
+      </c>
+      <c r="G163" s="11">
+        <f>IF(OR(E163="",F163=""),"",F163-E163)</f>
+        <v/>
+      </c>
+      <c r="H163" s="12">
+        <f>IFERROR(G163/E163,"")</f>
+        <v/>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J163" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K163" s="11" t="n">
+        <v>139.74</v>
+      </c>
+      <c r="L163" s="12" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="M163" s="15" t="inlineStr"/>
+      <c r="N163" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hepsipay</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>7044.02</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>7247.51</v>
+      </c>
+      <c r="G164" s="11">
+        <f>IF(OR(E164="",F164=""),"",F164-E164)</f>
+        <v/>
+      </c>
+      <c r="H164" s="12">
+        <f>IFERROR(G164/E164,"")</f>
+        <v/>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K164" s="11" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="L164" s="12" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="M164" s="15" t="inlineStr"/>
+      <c r="N164" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B165" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>55.5153</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>56.5271</v>
+      </c>
+      <c r="G165" s="11">
+        <f>IF(OR(E165="",F165=""),"",F165-E165)</f>
+        <v/>
+      </c>
+      <c r="H165" s="12">
+        <f>IFERROR(G165/E165,"")</f>
+        <v/>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J165" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K165" s="11" t="n">
+        <v>1.0118</v>
+      </c>
+      <c r="L165" s="12" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="M165" s="15" t="inlineStr"/>
+      <c r="N165" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B166" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>47.6091</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>48.6145</v>
+      </c>
+      <c r="G166" s="11">
+        <f>IF(OR(E166="",F166=""),"",F166-E166)</f>
+        <v/>
+      </c>
+      <c r="H166" s="12">
+        <f>IFERROR(G166/E166,"")</f>
+        <v/>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J166" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K166" s="11" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="L166" s="12" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="M166" s="15" t="inlineStr"/>
+      <c r="N166" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B167" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>6996.56</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>7249.09</v>
+      </c>
+      <c r="G167" s="11">
+        <f>IF(OR(E167="",F167=""),"",F167-E167)</f>
+        <v/>
+      </c>
+      <c r="H167" s="12">
+        <f>IFERROR(G167/E167,"")</f>
+        <v/>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J167" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K167" s="11" t="n">
+        <v>252.53</v>
+      </c>
+      <c r="L167" s="12" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="M167" s="15" t="inlineStr"/>
+      <c r="N167" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B168" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="G168" s="11">
+        <f>IF(OR(E168="",F168=""),"",F168-E168)</f>
+        <v/>
+      </c>
+      <c r="H168" s="12">
+        <f>IFERROR(G168/E168,"")</f>
+        <v/>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K168" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L168" s="12" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M168" s="15" t="inlineStr"/>
+      <c r="N168" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B169" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="G169" s="11">
+        <f>IF(OR(E169="",F169=""),"",F169-E169)</f>
+        <v/>
+      </c>
+      <c r="H169" s="12">
+        <f>IFERROR(G169/E169,"")</f>
+        <v/>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J169" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K169" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L169" s="12" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M169" s="15" t="inlineStr"/>
+      <c r="N169" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B170" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>7085.83</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>7092.14</v>
+      </c>
+      <c r="G170" s="11">
+        <f>IF(OR(E170="",F170=""),"",F170-E170)</f>
+        <v/>
+      </c>
+      <c r="H170" s="12">
+        <f>IFERROR(G170/E170,"")</f>
+        <v/>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K170" s="11" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="L170" s="12" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M170" s="15" t="inlineStr"/>
+      <c r="N170" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B171" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>55.263</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>56.4483</v>
+      </c>
+      <c r="G171" s="11">
+        <f>IF(OR(E171="",F171=""),"",F171-E171)</f>
+        <v/>
+      </c>
+      <c r="H171" s="12">
+        <f>IFERROR(G171/E171,"")</f>
+        <v/>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J171" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K171" s="11" t="n">
+        <v>1.1853</v>
+      </c>
+      <c r="L171" s="12" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="M171" s="15" t="inlineStr"/>
+      <c r="N171" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B172" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>47.4536</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>48.471</v>
+      </c>
+      <c r="G172" s="11">
+        <f>IF(OR(E172="",F172=""),"",F172-E172)</f>
+        <v/>
+      </c>
+      <c r="H172" s="12">
+        <f>IFERROR(G172/E172,"")</f>
+        <v/>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J172" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K172" s="11" t="n">
+        <v>1.0174</v>
+      </c>
+      <c r="L172" s="12" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="M172" s="15" t="inlineStr"/>
+      <c r="N172" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B173" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>6971.17</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>7156.37</v>
+      </c>
+      <c r="G173" s="11">
+        <f>IF(OR(E173="",F173=""),"",F173-E173)</f>
+        <v/>
+      </c>
+      <c r="H173" s="12">
+        <f>IFERROR(G173/E173,"")</f>
+        <v/>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J173" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K173" s="11" t="n">
+        <v>185.19</v>
+      </c>
+      <c r="L173" s="12" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="M173" s="15" t="inlineStr"/>
+      <c r="N173" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B174" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>55.9574</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>56.0582</v>
+      </c>
+      <c r="G174" s="11">
+        <f>IF(OR(E174="",F174=""),"",F174-E174)</f>
+        <v/>
+      </c>
+      <c r="H174" s="12">
+        <f>IFERROR(G174/E174,"")</f>
+        <v/>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K174" s="11" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="L174" s="12" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M174" s="15" t="inlineStr"/>
+      <c r="N174" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B175" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>48.0466</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>48.1331</v>
+      </c>
+      <c r="G175" s="11">
+        <f>IF(OR(E175="",F175=""),"",F175-E175)</f>
+        <v/>
+      </c>
+      <c r="H175" s="12">
+        <f>IFERROR(G175/E175,"")</f>
+        <v/>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J175" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K175" s="11" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="L175" s="12" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M175" s="15" t="inlineStr"/>
+      <c r="N175" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B176" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>55.9747</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>56.065</v>
+      </c>
+      <c r="G176" s="11">
+        <f>IF(OR(E176="",F176=""),"",F176-E176)</f>
+        <v/>
+      </c>
+      <c r="H176" s="12">
+        <f>IFERROR(G176/E176,"")</f>
+        <v/>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J176" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K176" s="11" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="L176" s="12" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M176" s="15" t="inlineStr"/>
+      <c r="N176" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B177" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="n">
+        <v>48.0811</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>48.1425</v>
+      </c>
+      <c r="G177" s="11">
+        <f>IF(OR(E177="",F177=""),"",F177-E177)</f>
+        <v/>
+      </c>
+      <c r="H177" s="12">
+        <f>IFERROR(G177/E177,"")</f>
+        <v/>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J177" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K177" s="11" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="L177" s="12" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="M177" s="15" t="inlineStr"/>
+      <c r="N177" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B178" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>7085.13</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>7115.67</v>
+      </c>
+      <c r="G178" s="11">
+        <f>IF(OR(E178="",F178=""),"",F178-E178)</f>
+        <v/>
+      </c>
+      <c r="H178" s="12">
+        <f>IFERROR(G178/E178,"")</f>
+        <v/>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J178" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K178" s="11" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="L178" s="12" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="M178" s="15" t="inlineStr"/>
+      <c r="N178" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B179" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="n">
+        <v>55.854</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>56.053</v>
+      </c>
+      <c r="G179" s="11">
+        <f>IF(OR(E179="",F179=""),"",F179-E179)</f>
+        <v/>
+      </c>
+      <c r="H179" s="12">
+        <f>IFERROR(G179/E179,"")</f>
+        <v/>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J179" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K179" s="11" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="L179" s="12" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="M179" s="15" t="inlineStr"/>
+      <c r="N179" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B180" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>48.049</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>48.186</v>
+      </c>
+      <c r="G180" s="11">
+        <f>IF(OR(E180="",F180=""),"",F180-E180)</f>
+        <v/>
+      </c>
+      <c r="H180" s="12">
+        <f>IFERROR(G180/E180,"")</f>
+        <v/>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J180" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K180" s="11" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="L180" s="12" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="M180" s="15" t="inlineStr"/>
+      <c r="N180" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B181" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>7063</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>7104</v>
+      </c>
+      <c r="G181" s="11">
+        <f>IF(OR(E181="",F181=""),"",F181-E181)</f>
+        <v/>
+      </c>
+      <c r="H181" s="12">
+        <f>IFERROR(G181/E181,"")</f>
+        <v/>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J181" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K181" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="L181" s="12" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="M181" s="15" t="inlineStr"/>
+      <c r="N181" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B182" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>55.508</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>56.598</v>
+      </c>
+      <c r="G182" s="11">
+        <f>IF(OR(E182="",F182=""),"",F182-E182)</f>
+        <v/>
+      </c>
+      <c r="H182" s="12">
+        <f>IFERROR(G182/E182,"")</f>
+        <v/>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K182" s="11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L182" s="12" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="M182" s="15" t="inlineStr"/>
+      <c r="N182" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B183" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="n">
+        <v>47.641</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>48.641</v>
+      </c>
+      <c r="G183" s="11">
+        <f>IF(OR(E183="",F183=""),"",F183-E183)</f>
+        <v/>
+      </c>
+      <c r="H183" s="12">
+        <f>IFERROR(G183/E183,"")</f>
+        <v/>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J183" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K183" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" s="12" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M183" s="15" t="inlineStr"/>
+      <c r="N183" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B184" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>7076.05</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>7176.05</v>
+      </c>
+      <c r="G184" s="11">
+        <f>IF(OR(E184="",F184=""),"",F184-E184)</f>
+        <v/>
+      </c>
+      <c r="H184" s="12">
+        <f>IFERROR(G184/E184,"")</f>
+        <v/>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J184" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K184" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L184" s="12" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="M184" s="15" t="inlineStr"/>
+      <c r="N184" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B185" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Papara</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="n">
+        <v>7044.02</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>7233.04</v>
+      </c>
+      <c r="G185" s="11">
+        <f>IF(OR(E185="",F185=""),"",F185-E185)</f>
+        <v/>
+      </c>
+      <c r="H185" s="12">
+        <f>IFERROR(G185/E185,"")</f>
+        <v/>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J185" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K185" s="11" t="n">
+        <v>189.02</v>
+      </c>
+      <c r="L185" s="12" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="M185" s="15" t="inlineStr"/>
+      <c r="N185" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B186" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="n">
+        <v>55.2034</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>56.8692</v>
+      </c>
+      <c r="G186" s="11">
+        <f>IF(OR(E186="",F186=""),"",F186-E186)</f>
+        <v/>
+      </c>
+      <c r="H186" s="12">
+        <f>IFERROR(G186/E186,"")</f>
+        <v/>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J186" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K186" s="11" t="n">
+        <v>1.6658</v>
+      </c>
+      <c r="L186" s="12" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="M186" s="15" t="inlineStr"/>
+      <c r="N186" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B187" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>47.505</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>48.725</v>
+      </c>
+      <c r="G187" s="11">
+        <f>IF(OR(E187="",F187=""),"",F187-E187)</f>
+        <v/>
+      </c>
+      <c r="H187" s="12">
+        <f>IFERROR(G187/E187,"")</f>
+        <v/>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J187" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K187" s="11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L187" s="12" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="M187" s="15" t="inlineStr"/>
+      <c r="N187" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B188" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="n">
+        <v>6986.46</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>7197.13</v>
+      </c>
+      <c r="G188" s="11">
+        <f>IF(OR(E188="",F188=""),"",F188-E188)</f>
+        <v/>
+      </c>
+      <c r="H188" s="12">
+        <f>IFERROR(G188/E188,"")</f>
+        <v/>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J188" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K188" s="11" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="L188" s="12" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="M188" s="15" t="inlineStr"/>
+      <c r="N188" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B189" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="n">
+        <v>55.9595</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>56.2966</v>
+      </c>
+      <c r="G189" s="11">
+        <f>IF(OR(E189="",F189=""),"",F189-E189)</f>
+        <v/>
+      </c>
+      <c r="H189" s="12">
+        <f>IFERROR(G189/E189,"")</f>
+        <v/>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J189" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K189" s="11" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="L189" s="12" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M189" s="15" t="inlineStr"/>
+      <c r="N189" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B190" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>48.1003</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>48.3415</v>
+      </c>
+      <c r="G190" s="11">
+        <f>IF(OR(E190="",F190=""),"",F190-E190)</f>
+        <v/>
+      </c>
+      <c r="H190" s="12">
+        <f>IFERROR(G190/E190,"")</f>
+        <v/>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J190" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K190" s="11" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="L190" s="12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M190" s="15" t="inlineStr"/>
+      <c r="N190" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B191" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>6985.71</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>7127.91</v>
+      </c>
+      <c r="G191" s="11">
+        <f>IF(OR(E191="",F191=""),"",F191-E191)</f>
+        <v/>
+      </c>
+      <c r="H191" s="12">
+        <f>IFERROR(G191/E191,"")</f>
+        <v/>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J191" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K191" s="11" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="L191" s="12" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="M191" s="15" t="inlineStr"/>
+      <c r="N191" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B192" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="n">
+        <v>55.5874</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>56.447</v>
+      </c>
+      <c r="G192" s="11">
+        <f>IF(OR(E192="",F192=""),"",F192-E192)</f>
+        <v/>
+      </c>
+      <c r="H192" s="12">
+        <f>IFERROR(G192/E192,"")</f>
+        <v/>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K192" s="11" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="L192" s="12" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="M192" s="15" t="inlineStr"/>
+      <c r="N192" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B193" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="n">
+        <v>47.7072</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>48.5151</v>
+      </c>
+      <c r="G193" s="11">
+        <f>IF(OR(E193="",F193=""),"",F193-E193)</f>
+        <v/>
+      </c>
+      <c r="H193" s="12">
+        <f>IFERROR(G193/E193,"")</f>
+        <v/>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J193" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K193" s="11" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="L193" s="12" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M193" s="15" t="inlineStr"/>
+      <c r="N193" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B194" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="n">
+        <v>7022.97</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>7220.87</v>
+      </c>
+      <c r="G194" s="11">
+        <f>IF(OR(E194="",F194=""),"",F194-E194)</f>
+        <v/>
+      </c>
+      <c r="H194" s="12">
+        <f>IFERROR(G194/E194,"")</f>
+        <v/>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K194" s="11" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="L194" s="12" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="M194" s="15" t="inlineStr"/>
+      <c r="N194" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B195" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="n">
+        <v>55.9047</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>56.1299</v>
+      </c>
+      <c r="G195" s="11">
+        <f>IF(OR(E195="",F195=""),"",F195-E195)</f>
+        <v/>
+      </c>
+      <c r="H195" s="12">
+        <f>IFERROR(G195/E195,"")</f>
+        <v/>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J195" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K195" s="11" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="L195" s="12" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M195" s="15" t="inlineStr"/>
+      <c r="N195" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B196" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="n">
+        <v>48.0171</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>48.2196</v>
+      </c>
+      <c r="G196" s="11">
+        <f>IF(OR(E196="",F196=""),"",F196-E196)</f>
+        <v/>
+      </c>
+      <c r="H196" s="12">
+        <f>IFERROR(G196/E196,"")</f>
+        <v/>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J196" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K196" s="11" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="L196" s="12" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M196" s="15" t="inlineStr"/>
+      <c r="N196" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B197" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="n">
+        <v>7063.03</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>7119.76</v>
+      </c>
+      <c r="G197" s="11">
+        <f>IF(OR(E197="",F197=""),"",F197-E197)</f>
+        <v/>
+      </c>
+      <c r="H197" s="12">
+        <f>IFERROR(G197/E197,"")</f>
+        <v/>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J197" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K197" s="11" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="L197" s="12" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M197" s="15" t="inlineStr"/>
+      <c r="N197" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B198" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="n">
+        <v>55.6208</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>56.7339</v>
+      </c>
+      <c r="G198" s="11">
+        <f>IF(OR(E198="",F198=""),"",F198-E198)</f>
+        <v/>
+      </c>
+      <c r="H198" s="12">
+        <f>IFERROR(G198/E198,"")</f>
+        <v/>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J198" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K198" s="11" t="n">
+        <v>1.1131</v>
+      </c>
+      <c r="L198" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M198" s="15" t="inlineStr"/>
+      <c r="N198" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B199" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="n">
+        <v>47.7421</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>48.7031</v>
+      </c>
+      <c r="G199" s="11">
+        <f>IF(OR(E199="",F199=""),"",F199-E199)</f>
+        <v/>
+      </c>
+      <c r="H199" s="12">
+        <f>IFERROR(G199/E199,"")</f>
+        <v/>
+      </c>
+      <c r="I199" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J199" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K199" s="11" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="L199" s="12" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="M199" s="15" t="inlineStr"/>
+      <c r="N199" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B200" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="n">
+        <v>7044.4</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>7189</v>
+      </c>
+      <c r="G200" s="11">
+        <f>IF(OR(E200="",F200=""),"",F200-E200)</f>
+        <v/>
+      </c>
+      <c r="H200" s="12">
+        <f>IFERROR(G200/E200,"")</f>
+        <v/>
+      </c>
+      <c r="I200" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J200" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K200" s="11" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="L200" s="12" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M200" s="15" t="inlineStr"/>
+      <c r="N200" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B201" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="n">
+        <v>55.825</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>55.991</v>
+      </c>
+      <c r="G201" s="11">
+        <f>IF(OR(E201="",F201=""),"",F201-E201)</f>
+        <v/>
+      </c>
+      <c r="H201" s="12">
+        <f>IFERROR(G201/E201,"")</f>
+        <v/>
+      </c>
+      <c r="I201" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J201" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K201" s="11" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="L201" s="12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M201" s="15" t="inlineStr"/>
+      <c r="N201" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B202" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>48.042</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>48.116</v>
+      </c>
+      <c r="G202" s="11">
+        <f>IF(OR(E202="",F202=""),"",F202-E202)</f>
+        <v/>
+      </c>
+      <c r="H202" s="12">
+        <f>IFERROR(G202/E202,"")</f>
+        <v/>
+      </c>
+      <c r="I202" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J202" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K202" s="11" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L202" s="12" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="M202" s="15" t="inlineStr"/>
+      <c r="N202" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B203" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="G203" s="11">
+        <f>IF(OR(E203="",F203=""),"",F203-E203)</f>
+        <v/>
+      </c>
+      <c r="H203" s="12">
+        <f>IFERROR(G203/E203,"")</f>
+        <v/>
+      </c>
+      <c r="I203" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J203" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K203" s="11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L203" s="12" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="M203" s="15" t="inlineStr"/>
+      <c r="N203" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B204" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="G204" s="11">
+        <f>IF(OR(E204="",F204=""),"",F204-E204)</f>
+        <v/>
+      </c>
+      <c r="H204" s="12">
+        <f>IFERROR(G204/E204,"")</f>
+        <v/>
+      </c>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J204" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K204" s="11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L204" s="12" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="M204" s="15" t="inlineStr"/>
+      <c r="N204" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B205" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="n">
+        <v>7009.9</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>7216.46</v>
+      </c>
+      <c r="G205" s="11">
+        <f>IF(OR(E205="",F205=""),"",F205-E205)</f>
+        <v/>
+      </c>
+      <c r="H205" s="12">
+        <f>IFERROR(G205/E205,"")</f>
+        <v/>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J205" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K205" s="11" t="n">
+        <v>206.56</v>
+      </c>
+      <c r="L205" s="12" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="M205" s="15" t="inlineStr"/>
+      <c r="N205" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B206" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="n">
+        <v>55.5785</v>
+      </c>
+      <c r="F206" s="11" t="n">
+        <v>56.7028</v>
+      </c>
+      <c r="G206" s="11">
+        <f>IF(OR(E206="",F206=""),"",F206-E206)</f>
+        <v/>
+      </c>
+      <c r="H206" s="12">
+        <f>IFERROR(G206/E206,"")</f>
+        <v/>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K206" s="11" t="n">
+        <v>1.1243</v>
+      </c>
+      <c r="L206" s="12" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M206" s="15" t="inlineStr"/>
+      <c r="N206" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B207" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="n">
+        <v>47.7541</v>
+      </c>
+      <c r="F207" s="11" t="n">
+        <v>48.7201</v>
+      </c>
+      <c r="G207" s="11">
+        <f>IF(OR(E207="",F207=""),"",F207-E207)</f>
+        <v/>
+      </c>
+      <c r="H207" s="12">
+        <f>IFERROR(G207/E207,"")</f>
+        <v/>
+      </c>
+      <c r="I207" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J207" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K207" s="11" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="L207" s="12" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M207" s="15" t="inlineStr"/>
+      <c r="N207" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B208" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="n">
+        <v>7071.22</v>
+      </c>
+      <c r="F208" s="11" t="n">
+        <v>7214</v>
+      </c>
+      <c r="G208" s="11">
+        <f>IF(OR(E208="",F208=""),"",F208-E208)</f>
+        <v/>
+      </c>
+      <c r="H208" s="12">
+        <f>IFERROR(G208/E208,"")</f>
+        <v/>
+      </c>
+      <c r="I208" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J208" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K208" s="11" t="n">
+        <v>142.78</v>
+      </c>
+      <c r="L208" s="12" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M208" s="15" t="inlineStr"/>
+      <c r="N208" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B209" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="n">
+        <v>55.5984</v>
+      </c>
+      <c r="F209" s="11" t="n">
+        <v>56.4112</v>
+      </c>
+      <c r="G209" s="11">
+        <f>IF(OR(E209="",F209=""),"",F209-E209)</f>
+        <v/>
+      </c>
+      <c r="H209" s="12">
+        <f>IFERROR(G209/E209,"")</f>
+        <v/>
+      </c>
+      <c r="I209" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J209" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K209" s="11" t="n">
+        <v>0.8128</v>
+      </c>
+      <c r="L209" s="12" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="M209" s="15" t="inlineStr"/>
+      <c r="N209" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B210" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="n">
+        <v>47.8017</v>
+      </c>
+      <c r="F210" s="11" t="n">
+        <v>48.4519</v>
+      </c>
+      <c r="G210" s="11">
+        <f>IF(OR(E210="",F210=""),"",F210-E210)</f>
+        <v/>
+      </c>
+      <c r="H210" s="12">
+        <f>IFERROR(G210/E210,"")</f>
+        <v/>
+      </c>
+      <c r="I210" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J210" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K210" s="11" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="L210" s="12" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="M210" s="15" t="inlineStr"/>
+      <c r="N210" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B211" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="n">
+        <v>7042.31</v>
+      </c>
+      <c r="F211" s="11" t="n">
+        <v>7184.5</v>
+      </c>
+      <c r="G211" s="11">
+        <f>IF(OR(E211="",F211=""),"",F211-E211)</f>
+        <v/>
+      </c>
+      <c r="H211" s="12">
+        <f>IFERROR(G211/E211,"")</f>
+        <v/>
+      </c>
+      <c r="I211" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J211" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K211" s="11" t="n">
+        <v>142.19</v>
+      </c>
+      <c r="L211" s="12" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M211" s="15" t="inlineStr"/>
+      <c r="N211" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B212" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="n">
+        <v>55.5267</v>
+      </c>
+      <c r="F212" s="11" t="n">
+        <v>56.7413</v>
+      </c>
+      <c r="G212" s="11">
+        <f>IF(OR(E212="",F212=""),"",F212-E212)</f>
+        <v/>
+      </c>
+      <c r="H212" s="12">
+        <f>IFERROR(G212/E212,"")</f>
+        <v/>
+      </c>
+      <c r="I212" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J212" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K212" s="11" t="n">
+        <v>1.2146</v>
+      </c>
+      <c r="L212" s="12" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="M212" s="15" t="inlineStr"/>
+      <c r="N212" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B213" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="n">
+        <v>47.7169</v>
+      </c>
+      <c r="F213" s="11" t="n">
+        <v>48.713</v>
+      </c>
+      <c r="G213" s="11">
+        <f>IF(OR(E213="",F213=""),"",F213-E213)</f>
+        <v/>
+      </c>
+      <c r="H213" s="12">
+        <f>IFERROR(G213/E213,"")</f>
+        <v/>
+      </c>
+      <c r="I213" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J213" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K213" s="11" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="L213" s="12" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M213" s="15" t="inlineStr"/>
+      <c r="N213" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B214" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="n">
+        <v>7064.07</v>
+      </c>
+      <c r="F214" s="11" t="n">
+        <v>7288.24</v>
+      </c>
+      <c r="G214" s="11">
+        <f>IF(OR(E214="",F214=""),"",F214-E214)</f>
+        <v/>
+      </c>
+      <c r="H214" s="12">
+        <f>IFERROR(G214/E214,"")</f>
+        <v/>
+      </c>
+      <c r="I214" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J214" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K214" s="11" t="n">
+        <v>224.17</v>
+      </c>
+      <c r="L214" s="12" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="M214" s="15" t="inlineStr"/>
+      <c r="N214" s="10" t="n">
+        <v>0.5670601851851852</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B215" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="n">
+        <v>55.344</v>
+      </c>
+      <c r="F215" s="11" t="n">
+        <v>56.6986</v>
+      </c>
+      <c r="G215" s="11">
+        <f>IF(OR(E215="",F215=""),"",F215-E215)</f>
+        <v/>
+      </c>
+      <c r="H215" s="12">
+        <f>IFERROR(G215/E215,"")</f>
+        <v/>
+      </c>
+      <c r="I215" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J215" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K215" s="11" t="n">
+        <v>1.3546</v>
+      </c>
+      <c r="L215" s="12" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="M215" s="15" t="inlineStr"/>
+      <c r="N215" s="10" t="n">
+        <v>0.5669097222222222</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B216" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="n">
+        <v>47.5342</v>
+      </c>
+      <c r="F216" s="11" t="n">
+        <v>48.6934</v>
+      </c>
+      <c r="G216" s="11">
+        <f>IF(OR(E216="",F216=""),"",F216-E216)</f>
+        <v/>
+      </c>
+      <c r="H216" s="12">
+        <f>IFERROR(G216/E216,"")</f>
+        <v/>
+      </c>
+      <c r="I216" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J216" s="14" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K216" s="11" t="n">
+        <v>1.1592</v>
+      </c>
+      <c r="L216" s="12" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="M216" s="15" t="inlineStr"/>
+      <c r="N216" s="10" t="n">
+        <v>0.5667592592592593</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B217" s="10" t="n">
+        <v>0.5665625</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="n">
+        <v>7016.31</v>
+      </c>
+      <c r="F217" s="11" t="n">
+        <v>7209.23</v>
+      </c>
+      <c r="G217" s="11">
+        <f>IF(OR(E217="",F217=""),"",F217-E217)</f>
+        <v/>
+      </c>
+      <c r="H217" s="12">
+        <f>IFERROR(G217/E217,"")</f>
+        <v/>
+      </c>
+      <c r="I217" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J217" s="14" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K217" s="11" t="n">
+        <v>192.92</v>
+      </c>
+      <c r="L217" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M217" s="15" t="inlineStr"/>
+      <c r="N217" s="10" t="n">
+        <v>0.5670601851851852</v>
       </c>
     </row>
   </sheetData>
@@ -8842,10 +14458,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId216"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId109"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId217"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -5427,7 +5427,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5449,7 +5449,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -5471,7 +5471,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -5493,7 +5493,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -5515,7 +5515,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -5537,7 +5537,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -5559,7 +5559,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -5581,7 +5581,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -5603,7 +5603,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -5625,7 +5625,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -5647,7 +5647,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="11" name="Chart 11"/>
@@ -5669,7 +5669,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="12" name="Chart 12"/>
@@ -5691,7 +5691,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="13" name="Chart 13"/>
@@ -5713,7 +5713,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="14" name="Chart 14"/>
@@ -5735,7 +5735,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="15" name="Chart 15"/>
@@ -5757,7 +5757,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="16" name="Chart 16"/>
@@ -5779,7 +5779,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="17" name="Chart 17"/>
@@ -5801,7 +5801,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2880000"/>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="18" name="Chart 18"/>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -5427,7 +5427,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5449,7 +5449,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -5471,7 +5471,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -5493,7 +5493,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -5515,7 +5515,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -5537,7 +5537,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -5559,7 +5559,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -5581,7 +5581,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -5603,7 +5603,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -5625,7 +5625,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -5647,7 +5647,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="11" name="Chart 11"/>
@@ -5669,7 +5669,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="12" name="Chart 12"/>
@@ -5691,7 +5691,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="13" name="Chart 13"/>
@@ -5713,7 +5713,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="14" name="Chart 14"/>
@@ -5735,7 +5735,7 @@
       <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="15" name="Chart 15"/>
@@ -5757,7 +5757,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="16" name="Chart 16"/>
@@ -5779,7 +5779,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="17" name="Chart 17"/>
@@ -5801,7 +5801,7 @@
       <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="6840000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="18" name="Chart 18"/>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -10,6 +10,7 @@
     <sheet name="GUNCEL_KURLAR" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="GECMIS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="OZET" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GRAFIK_VERILERI" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,12 +59,10 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <color rgb="00C65911"/>
     </font>
   </fonts>
   <fills count="51">
@@ -406,58 +405,43 @@
     <xf numFmtId="0" fontId="2" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="48" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -557,7 +541,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AB2</f>
+              <f>'GRAFIK_VERILERI'!B1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -591,7 +575,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -617,7 +601,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AB$3:$AB$8</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -648,7 +632,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AC2</f>
+              <f>'GRAFIK_VERILERI'!C1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -682,7 +666,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -708,7 +692,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AC$3:$AC$8</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -739,7 +723,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AD2</f>
+              <f>'GRAFIK_VERILERI'!D1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -773,7 +757,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -799,7 +783,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AD$3:$AD$8</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -830,7 +814,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AE2</f>
+              <f>'GRAFIK_VERILERI'!E1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -864,7 +848,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -890,7 +874,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AE$3:$AE$8</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -921,7 +905,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AF2</f>
+              <f>'GRAFIK_VERILERI'!F1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -955,7 +939,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -981,7 +965,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AF$3:$AF$8</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1015,8 +999,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -1034,8 +1017,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1043,6 +1024,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1101,7 +1083,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AF200</f>
+              <f>'GRAFIK_VERILERI'!C1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -1135,33 +1117,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AE$201:$AE$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AF$201:$AF$206</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1190,10 +1172,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1203,8 +1182,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -1222,8 +1200,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1233,6 +1209,7 @@
           <min val="0.02255547230137524"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1303,7 +1280,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AG200</f>
+              <f>'GRAFIK_VERILERI'!H1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -1337,33 +1314,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AE$201:$AE$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AG$201:$AG$206</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1392,10 +1369,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1405,8 +1379,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -1424,8 +1397,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1435,6 +1406,7 @@
           <min val="0.02251604918664015"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1505,7 +1477,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AH200</f>
+              <f>'GRAFIK_VERILERI'!M1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -1539,33 +1511,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AE$201:$AE$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AH$201:$AH$206</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1594,10 +1566,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1607,8 +1576,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -1626,8 +1594,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1637,6 +1603,7 @@
           <min val="0.02634377435370254"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1707,7 +1674,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AJ200</f>
+              <f>'GRAFIK_VERILERI'!D1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -1741,33 +1708,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AI$201:$AI$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AJ$201:$AJ$206</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1796,10 +1763,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1809,8 +1773,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -1828,8 +1791,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1839,6 +1800,7 @@
           <min val="0.01394771487950567"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1909,7 +1871,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AK200</f>
+              <f>'GRAFIK_VERILERI'!I1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -1943,33 +1905,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AI$201:$AI$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AK$201:$AK$206</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -1998,10 +1960,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -2011,8 +1970,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -2030,8 +1988,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2041,6 +1997,7 @@
           <min val="0.01451066469310389"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -2111,7 +2068,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AL200</f>
+              <f>'GRAFIK_VERILERI'!N1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -2145,33 +2102,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AI$201:$AI$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AL$201:$AL$206</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -2200,10 +2157,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -2213,8 +2167,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -2232,8 +2185,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2243,6 +2194,7 @@
           <min val="0.0196170269615309"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -2313,7 +2265,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AN200</f>
+              <f>'GRAFIK_VERILERI'!E1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -2347,33 +2299,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AM$201:$AM$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AN$201:$AN$206</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -2402,10 +2354,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -2415,8 +2364,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -2434,8 +2382,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2445,6 +2391,7 @@
           <min val="0.01190344185435327"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -2515,7 +2462,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AO200</f>
+              <f>'GRAFIK_VERILERI'!J1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -2549,33 +2496,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AM$201:$AM$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AO$201:$AO$206</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -2604,10 +2551,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -2617,8 +2561,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -2636,8 +2579,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2647,6 +2588,7 @@
           <min val="0.01190503299558375"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -2717,7 +2659,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AP200</f>
+              <f>'GRAFIK_VERILERI'!O1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -2751,33 +2693,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AM$201:$AM$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AP$201:$AP$206</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -2806,10 +2748,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -2819,8 +2758,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -2838,8 +2776,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2849,6 +2785,7 @@
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -2919,7 +2856,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AR200</f>
+              <f>'GRAFIK_VERILERI'!F1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -2953,33 +2890,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AQ$201:$AQ$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AR$201:$AR$206</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3008,10 +2945,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -3021,8 +2955,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -3040,8 +2973,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3051,6 +2982,7 @@
           <min val="0.01797489899804002"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -3121,7 +3053,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AG2</f>
+              <f>'GRAFIK_VERILERI'!G1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3155,7 +3087,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -3181,7 +3113,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AG$3:$AG$8</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3212,7 +3144,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AH2</f>
+              <f>'GRAFIK_VERILERI'!H1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3246,7 +3178,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -3272,7 +3204,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AH$3:$AH$8</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3303,7 +3235,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AI2</f>
+              <f>'GRAFIK_VERILERI'!I1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3337,7 +3269,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -3363,7 +3295,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AI$3:$AI$8</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3394,7 +3326,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AJ2</f>
+              <f>'GRAFIK_VERILERI'!J1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3428,7 +3360,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -3454,7 +3386,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AJ$3:$AJ$8</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3485,7 +3417,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AK2</f>
+              <f>'GRAFIK_VERILERI'!K1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3519,7 +3451,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -3545,7 +3477,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AK$3:$AK$8</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3579,8 +3511,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -3598,8 +3529,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3607,6 +3536,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -3665,7 +3595,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AS200</f>
+              <f>'GRAFIK_VERILERI'!K1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3699,33 +3629,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AQ$201:$AQ$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AS$201:$AS$206</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3754,10 +3684,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -3767,8 +3694,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -3786,8 +3712,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3797,6 +3721,7 @@
           <min val="0.01791241253707181"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -3867,7 +3792,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AT200</f>
+              <f>'GRAFIK_VERILERI'!P1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -3901,33 +3826,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AQ$201:$AQ$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AT$201:$AT$206</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -3956,10 +3881,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -3969,8 +3891,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -3988,8 +3909,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3999,6 +3918,7 @@
           <min val="0.007620168856054751"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -4069,7 +3989,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AL2</f>
+              <f>'GRAFIK_VERILERI'!L1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4103,7 +4023,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -4129,7 +4049,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AL$3:$AL$8</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -4160,7 +4080,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AM2</f>
+              <f>'GRAFIK_VERILERI'!M1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4194,7 +4114,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -4220,7 +4140,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AM$3:$AM$8</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -4251,7 +4171,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AN2</f>
+              <f>'GRAFIK_VERILERI'!N1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4285,7 +4205,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -4311,7 +4231,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AN$3:$AN$8</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -4342,7 +4262,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AO2</f>
+              <f>'GRAFIK_VERILERI'!O1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4376,7 +4296,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -4402,7 +4322,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AO$3:$AO$8</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -4433,7 +4353,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AP2</f>
+              <f>'GRAFIK_VERILERI'!P1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4467,7 +4387,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$3:$AA$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
@@ -4493,7 +4413,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AP$3:$AP$8</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -4527,8 +4447,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -4546,8 +4465,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4555,6 +4472,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -4613,7 +4531,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AB100</f>
+              <f>'GRAFIK_VERILERI'!U1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4647,7 +4565,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -4661,7 +4579,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AB$101:$AB$102</f>
+              <f>'GRAFIK_VERILERI'!$U$2:$U$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -4680,7 +4598,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AC100</f>
+              <f>'GRAFIK_VERILERI'!V1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4714,7 +4632,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -4728,7 +4646,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AC$101:$AC$102</f>
+              <f>'GRAFIK_VERILERI'!$V$2:$V$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -4747,7 +4665,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AD100</f>
+              <f>'GRAFIK_VERILERI'!W1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4781,7 +4699,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -4795,7 +4713,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AD$101:$AD$102</f>
+              <f>'GRAFIK_VERILERI'!$W$2:$W$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -4814,7 +4732,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AE100</f>
+              <f>'GRAFIK_VERILERI'!X1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4848,7 +4766,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -4862,7 +4780,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AE$101:$AE$102</f>
+              <f>'GRAFIK_VERILERI'!$X$2:$X$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -4881,7 +4799,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AF100</f>
+              <f>'GRAFIK_VERILERI'!Y1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -4915,7 +4833,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -4929,7 +4847,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AF$101:$AF$102</f>
+              <f>'GRAFIK_VERILERI'!$Y$2:$Y$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -4951,8 +4869,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -4970,8 +4887,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4979,6 +4894,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -5037,7 +4953,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AG100</f>
+              <f>'GRAFIK_VERILERI'!Z1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5071,7 +4987,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5085,7 +5001,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AG$101:$AG$102</f>
+              <f>'GRAFIK_VERILERI'!$Z$2:$Z$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5104,7 +5020,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AH100</f>
+              <f>'GRAFIK_VERILERI'!AA1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5138,7 +5054,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5152,7 +5068,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AH$101:$AH$102</f>
+              <f>'GRAFIK_VERILERI'!$AA$2:$AA$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5171,7 +5087,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AI100</f>
+              <f>'GRAFIK_VERILERI'!AB1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5205,7 +5121,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5219,7 +5135,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AI$101:$AI$102</f>
+              <f>'GRAFIK_VERILERI'!$AB$2:$AB$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5238,7 +5154,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AJ100</f>
+              <f>'GRAFIK_VERILERI'!AC1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5272,7 +5188,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5286,7 +5202,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AJ$101:$AJ$102</f>
+              <f>'GRAFIK_VERILERI'!$AC$2:$AC$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5305,7 +5221,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AK100</f>
+              <f>'GRAFIK_VERILERI'!AD1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5339,7 +5255,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5353,7 +5269,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AK$101:$AK$102</f>
+              <f>'GRAFIK_VERILERI'!$AD$2:$AD$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5375,8 +5291,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -5394,8 +5309,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5403,6 +5316,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -5461,7 +5375,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AL100</f>
+              <f>'GRAFIK_VERILERI'!AE1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5495,7 +5409,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5509,7 +5423,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AL$101:$AL$102</f>
+              <f>'GRAFIK_VERILERI'!$AE$2:$AE$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5528,7 +5442,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OZET'!AM100</f>
+              <f>'GRAFIK_VERILERI'!AF1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5562,7 +5476,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5576,7 +5490,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AM$101:$AM$102</f>
+              <f>'GRAFIK_VERILERI'!$AF$2:$AF$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5595,7 +5509,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OZET'!AN100</f>
+              <f>'GRAFIK_VERILERI'!AG1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5629,7 +5543,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5643,7 +5557,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AN$101:$AN$102</f>
+              <f>'GRAFIK_VERILERI'!$AG$2:$AG$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5662,7 +5576,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OZET'!AO100</f>
+              <f>'GRAFIK_VERILERI'!AH1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5696,7 +5610,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5710,7 +5624,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AO$101:$AO$102</f>
+              <f>'GRAFIK_VERILERI'!$AH$2:$AH$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5729,7 +5643,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'OZET'!AP100</f>
+              <f>'GRAFIK_VERILERI'!AI1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5763,7 +5677,7 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$101:$AA$102</f>
+              <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
               <strCache>
                 <ptCount val="2"/>
                 <pt idx="0">
@@ -5777,7 +5691,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AP$101:$AP$102</f>
+              <f>'GRAFIK_VERILERI'!$AI$2:$AI$3</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="2"/>
@@ -5799,8 +5713,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -5818,8 +5731,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5827,6 +5738,7 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -5885,7 +5797,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AB200</f>
+              <f>'GRAFIK_VERILERI'!B1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -5919,33 +5831,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$201:$AA$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AB$201:$AB$206</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -5974,10 +5886,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -5987,8 +5896,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -6006,8 +5914,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6017,6 +5923,7 @@
           <min val="0.02563021945997443"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -6087,7 +5994,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AC200</f>
+              <f>'GRAFIK_VERILERI'!G1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -6121,33 +6028,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$201:$AA$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AC$201:$AC$206</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -6176,10 +6083,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -6189,8 +6093,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -6208,8 +6111,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6219,6 +6120,7 @@
           <min val="0.02562858686951813"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -6289,7 +6191,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'OZET'!AD200</f>
+              <f>'GRAFIK_VERILERI'!L1</f>
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
@@ -6323,33 +6225,33 @@
           </marker>
           <cat>
             <strRef>
-              <f>'OZET'!$AA$201:$AA$206</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
               <strCache>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>28.08 13:22</v>
+                  <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt 10:22</v>
+                  <v>29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz 10:22</v>
+                  <v>30.08 Paz</v>
                 </pt>
                 <pt idx="3">
-                  <v>31.08 08:55</v>
+                  <v>31.08</v>
                 </pt>
                 <pt idx="4">
-                  <v>01.09 11:01</v>
+                  <v>01.09</v>
                 </pt>
                 <pt idx="5">
-                  <v>02.09 09:35</v>
+                  <v>02.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'OZET'!$AD$201:$AD$206</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
                 <ptCount val="6"/>
@@ -6378,10 +6280,7 @@
         <dLbls>
           <numFmt formatCode="0.00%"/>
           <dLblPos val="t"/>
-          <showLegendKey val="0"/>
           <showVal val="1"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -6391,8 +6290,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -6410,8 +6308,6 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6421,6 +6317,7 @@
           <min val="0.03018959592357282"/>
         </scaling>
         <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -6470,10 +6367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -6492,10 +6389,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -6512,12 +6409,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -6536,10 +6433,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -6558,10 +6455,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -6578,12 +6475,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -6602,10 +6499,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -6624,10 +6521,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -6644,12 +6541,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -6668,10 +6565,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -6690,10 +6587,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="11" name="Chart 11"/>
@@ -6710,12 +6607,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="12" name="Chart 12"/>
@@ -6734,10 +6631,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="13" name="Chart 13"/>
@@ -6756,10 +6653,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="14" name="Chart 14"/>
@@ -6776,12 +6673,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="15" name="Chart 15"/>
@@ -6800,10 +6697,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="16" name="Chart 16"/>
@@ -6822,10 +6719,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="17" name="Chart 17"/>
@@ -6842,12 +6739,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="18" name="Chart 18"/>
@@ -6866,10 +6763,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="19" name="Chart 19"/>
@@ -6888,10 +6785,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="20" name="Chart 20"/>
@@ -6908,12 +6805,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3060000"/>
+    <ext cx="6300000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="21" name="Chart 21"/>
@@ -7369,7 +7266,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7389,28 +7286,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9966</v>
+        <v>54.9584</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5645</v>
+        <v>56.5253</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5679</v>
+        <v>1.5669</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02850903510398825</v>
+        <v>0.02851065533203296</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6533.46</v>
+        <v>6526.11</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6769.59</v>
+        <v>6761.93</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.13</v>
+        <v>235.82</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03614164623338936</v>
+        <v>0.03613484909080601</v>
       </c>
     </row>
     <row r="3">
@@ -7418,7 +7315,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7426,40 +7323,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>47.896</v>
+        <v>47.897</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>48.678</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.01632704192416903</v>
+        <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.444</v>
+        <v>55.407</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.36</v>
+        <v>56.331</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.916</v>
+        <v>0.924</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01652117451843301</v>
+        <v>0.01667659321024419</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6604.59</v>
+        <v>6605.19</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6741.06</v>
+        <v>6741.53</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>136.47</v>
+        <v>136.34</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02066290261772495</v>
+        <v>0.0206413441551265</v>
       </c>
     </row>
     <row r="4">
@@ -7467,7 +7364,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7475,40 +7372,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.084</v>
+        <v>48.085</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>48.37</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.286</v>
+        <v>0.285</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.005947924465518676</v>
+        <v>0.005927004263283769</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.5</v>
+        <v>55.468</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.003</v>
+        <v>55.972</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.503</v>
+        <v>0.504</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009063063063063063</v>
+        <v>0.009086320040383645</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6667.4</v>
+        <v>6661.43</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6733.67</v>
+        <v>6727.26</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>66.27</v>
+        <v>65.83</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.00993940666526682</v>
+        <v>0.009882262517207266</v>
       </c>
     </row>
     <row r="5">
@@ -7516,7 +7413,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7536,28 +7433,28 @@
         <v>0.004779618046175266</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.6</v>
+        <v>55.566</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.978</v>
+        <v>55.943</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006798561151079137</v>
+        <v>0.006784724471799302</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6577.17</v>
+        <v>6576.76</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6770</v>
+        <v>6775</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>192.83</v>
+        <v>198.24</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02931808057264751</v>
+        <v>0.03014250177899148</v>
       </c>
     </row>
     <row r="6">
@@ -7565,7 +7462,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7573,40 +7470,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4525</v>
+        <v>47.453</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7293</v>
+        <v>48.7291</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2768</v>
+        <v>1.2761</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02690690690690691</v>
+        <v>0.02689187195751586</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0377</v>
+        <v>54.9958</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.4029</v>
+        <v>56.3607</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3652</v>
+        <v>1.3649</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02480481560821037</v>
+        <v>0.02481825884885755</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6590.4</v>
+        <v>6590.71</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6741.63</v>
+        <v>6741.74</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>151.23</v>
+        <v>151.03</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02294701383831027</v>
+        <v>0.02291558876054325</v>
       </c>
     </row>
     <row r="7">
@@ -7614,7 +7511,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7622,40 +7519,40 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>47.302</v>
+        <v>47.301</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>49.224</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.922</v>
+        <v>1.923</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04063253139402139</v>
+        <v>0.04065453161666772</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.762</v>
+        <v>54.72</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.992</v>
+        <v>56.948</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.23</v>
+        <v>2.228</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04072166831014207</v>
+        <v>0.04071637426900585</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6586.23</v>
+        <v>6586.53</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6779.98</v>
+        <v>6781.37</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>193.75</v>
+        <v>194.84</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02941743607496246</v>
+        <v>0.02958158544787619</v>
       </c>
     </row>
     <row r="8">
@@ -7663,7 +7560,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7671,40 +7568,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5541</v>
+        <v>47.5548</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9542</v>
+        <v>48.9549</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944225629335851</v>
+        <v>0.02944182290746675</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0529</v>
+        <v>55.0205</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6787</v>
+        <v>56.6404</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6258</v>
+        <v>1.6199</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02953159597405405</v>
+        <v>0.02944175352823039</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6603.79</v>
+        <v>6604.17</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6799.37</v>
+        <v>6799.59</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.58</v>
+        <v>195.42</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02961632638227442</v>
+        <v>0.029590395159422</v>
       </c>
     </row>
     <row r="9">
@@ -7712,7 +7609,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7720,40 +7617,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2237</v>
+        <v>48.2234</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2809</v>
+        <v>48.2804</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0572</v>
+        <v>0.057</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001186138765793583</v>
+        <v>0.001181998780674942</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.813</v>
+        <v>55.775</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.8961</v>
+        <v>55.8581</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.08309999999999999</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001488900435382438</v>
+        <v>0.001489914836396235</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6656.12</v>
+        <v>6656.63</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6684.96</v>
+        <v>6685.53</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.84</v>
+        <v>28.9</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004332854575939135</v>
+        <v>0.00434153618272309</v>
       </c>
     </row>
     <row r="10">
@@ -7761,7 +7658,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7769,40 +7666,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2372</v>
+        <v>48.2365</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2763</v>
+        <v>48.2753</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0388</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0008105777283921952</v>
+        <v>0.0008043701346490728</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.7949</v>
+        <v>55.7523</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.9098</v>
+        <v>55.8663</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1149</v>
+        <v>0.114</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002059328003097057</v>
+        <v>0.002044758691569675</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6653.45</v>
+        <v>6653.82</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6685.17</v>
+        <v>6685.41</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.72</v>
+        <v>31.59</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004767451472544319</v>
+        <v>0.00474764871908167</v>
       </c>
     </row>
     <row r="11">
@@ -7810,7 +7707,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7818,40 +7715,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9229</v>
+        <v>47.924</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.162</v>
+        <v>49.1614</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2391</v>
+        <v>1.2374</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02585611471759848</v>
+        <v>0.02582004840998247</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.4011</v>
+        <v>55.3593</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6768</v>
+        <v>56.6372</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2757</v>
+        <v>1.2779</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02302661860504575</v>
+        <v>0.02308374563984732</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6618.66</v>
+        <v>6607.43</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6726.73</v>
+        <v>6715.85</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.07</v>
+        <v>108.42</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01632807849322975</v>
+        <v>0.01640880039591793</v>
       </c>
     </row>
     <row r="12">
@@ -7859,7 +7756,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7879,28 +7776,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.3099</v>
+        <v>55.267</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4666</v>
+        <v>56.4275</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1567</v>
+        <v>1.1605</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.0209130734280843</v>
+        <v>0.02099806394412579</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6601.1</v>
+        <v>6602.21</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6755.91</v>
+        <v>6756.46</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.81</v>
+        <v>154.25</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02345215191407492</v>
+        <v>0.02336338892582938</v>
       </c>
     </row>
     <row r="13">
@@ -7908,7 +7805,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7916,40 +7813,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9981</v>
+        <v>47.9982</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6051</v>
+        <v>48.605</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6068</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264633391738423</v>
+        <v>0.01264214074694468</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5849</v>
+        <v>55.5507</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2454</v>
+        <v>56.2121</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6605</v>
+        <v>0.6614</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01188272354542331</v>
+        <v>0.01190624060542892</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6676.84</v>
+        <v>6675.99</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6731.65</v>
+        <v>6730.28</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.81</v>
+        <v>54.29</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008208973107038659</v>
+        <v>0.008132127220082714</v>
       </c>
     </row>
     <row r="14">
@@ -7957,7 +7854,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7977,28 +7874,28 @@
         <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.942</v>
+        <v>54.909</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.505</v>
+        <v>56.471</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.563</v>
+        <v>1.562</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02844818171890357</v>
+        <v>0.02844706696534266</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6575.5</v>
+        <v>6570.4</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6818.41</v>
+        <v>6813.12</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.91</v>
+        <v>242.72</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694167743897803</v>
+        <v>0.03694143431145745</v>
       </c>
     </row>
     <row r="15">
@@ -8006,7 +7903,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -8014,40 +7911,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9979</v>
+        <v>47.9981</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6051</v>
+        <v>48.6048</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6072</v>
+        <v>0.6067</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01265055346171395</v>
+        <v>0.0126400836699786</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5823</v>
+        <v>55.5477</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2424</v>
+        <v>56.2091</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6601</v>
+        <v>0.6614</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01187608285371422</v>
+        <v>0.01190688363334575</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6674.29</v>
+        <v>6674.85</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6728.79</v>
+        <v>6729.12</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.5</v>
+        <v>54.27</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008165662564857085</v>
+        <v>0.008130519786961504</v>
       </c>
     </row>
     <row r="16">
@@ -8055,7 +7952,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -8063,40 +7960,40 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.867</v>
+        <v>47.8672</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.847</v>
+        <v>48.8472</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0.98</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02047339503206802</v>
+        <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4204</v>
+        <v>55.3847</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5551</v>
+        <v>56.5187</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1347</v>
+        <v>1.134</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047441014500076</v>
+        <v>0.02047496871879779</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6607.75</v>
+        <v>6606.81</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6811.45</v>
+        <v>6809.95</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.7</v>
+        <v>203.14</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03082743747871817</v>
+        <v>0.0307470625006622</v>
       </c>
     </row>
     <row r="17">
@@ -8104,7 +8001,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -8124,28 +8021,28 @@
         <v>0.001723421926910299</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.6</v>
+        <v>55.56</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.805</v>
+        <v>55.764</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.205</v>
+        <v>0.204</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.00368705035971223</v>
+        <v>0.00367170626349892</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6601.61</v>
+        <v>6600.29</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6699.74</v>
+        <v>6698.35</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>98.13</v>
+        <v>98.06</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01486455576745673</v>
+        <v>0.01485692295338538</v>
       </c>
     </row>
     <row r="18">
@@ -8153,7 +8050,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8161,40 +8058,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2175</v>
+        <v>48.2166</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3641</v>
+        <v>48.3636</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1466</v>
+        <v>0.147</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003040389899932597</v>
+        <v>0.003048742549246525</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.8062</v>
+        <v>55.7775</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9772</v>
+        <v>55.9485</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.171</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003064175665069472</v>
+        <v>0.003065752319483663</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6661.42</v>
+        <v>6663.42</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6708.52</v>
+        <v>6710.57</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.1</v>
+        <v>47.15</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007070564534288485</v>
+        <v>0.007075945985695034</v>
       </c>
     </row>
     <row r="19">
@@ -8202,7 +8099,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8218,16 +8115,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6677.06</v>
+        <v>6675.12</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6872.74</v>
+        <v>6870.74</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.68</v>
+        <v>195.62</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02930631146043318</v>
+        <v>0.02930584019463321</v>
       </c>
     </row>
     <row r="20">
@@ -8235,7 +8132,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8243,40 +8140,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8049</v>
+        <v>47.7959</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6896</v>
+        <v>48.6872</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8847</v>
+        <v>0.8913</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01850647109396735</v>
+        <v>0.01864804303297982</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3429</v>
+        <v>55.3145</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.4022</v>
+        <v>56.369</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0593</v>
+        <v>1.0545</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01914066664377906</v>
+        <v>0.01906371747010278</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6604.46</v>
+        <v>6606.29</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7050.71</v>
+        <v>7052.53</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>446.25</v>
+        <v>446.24</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06756797679144094</v>
+        <v>0.06754774616312635</v>
       </c>
     </row>
     <row r="21">
@@ -8284,7 +8181,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8292,40 +8189,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7509</v>
+        <v>47.7513</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7548</v>
+        <v>48.7549</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0039</v>
+        <v>1.0036</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02102368751164899</v>
+        <v>0.02101722885031403</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3566</v>
+        <v>55.3258</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3656</v>
+        <v>56.3323</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.009</v>
+        <v>1.0065</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01822727551908896</v>
+        <v>0.01819223581041756</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6575.3</v>
+        <v>6574.25</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6827.56</v>
+        <v>6826.48</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>252.26</v>
+        <v>252.23</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03836478943926513</v>
+        <v>0.03836635357645359</v>
       </c>
     </row>
     <row r="22">
@@ -8333,7 +8230,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8341,40 +8238,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6781</v>
+        <v>47.6764</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8334</v>
+        <v>48.8332</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1553</v>
+        <v>1.1568</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02423125082585086</v>
+        <v>0.02426357694792392</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.1926</v>
+        <v>55.1593</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5296</v>
+        <v>56.5003</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.337</v>
+        <v>1.341</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02422426194815971</v>
+        <v>0.02431140351672338</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6600.29</v>
+        <v>6593.49</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6781.32</v>
+        <v>6774.94</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.03</v>
+        <v>181.45</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02742758272742561</v>
+        <v>0.02751956854412458</v>
       </c>
     </row>
     <row r="23">
@@ -8382,7 +8279,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8431,7 +8328,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8439,40 +8336,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6863</v>
+        <v>47.6115</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.6725</v>
+        <v>48.5977</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0.9862</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02068099223466698</v>
+        <v>0.0207134830870693</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1204</v>
+        <v>55.09</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2628</v>
+        <v>56.2338</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1424</v>
+        <v>1.1438</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02072553900189403</v>
+        <v>0.02076238881829733</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6554.01</v>
+        <v>6568.72</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6728.02</v>
+        <v>6742.66</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174.01</v>
+        <v>173.94</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02655015784229807</v>
+        <v>0.02648004481847301</v>
       </c>
     </row>
     <row r="25">
@@ -8480,7 +8377,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8521,7 +8418,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8529,40 +8426,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2264</v>
+        <v>48.2256</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2801</v>
+        <v>48.2791</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0537</v>
+        <v>0.0535</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001113498001094836</v>
+        <v>0.001109369297634451</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8154</v>
+        <v>55.7844</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.898</v>
+        <v>55.866</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001479878313153717</v>
+        <v>0.001462774539118463</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6650.2</v>
+        <v>6652.56</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6679.92</v>
+        <v>6681.14</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>29.72</v>
+        <v>28.58</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004469038525157138</v>
+        <v>0.004296090527556309</v>
       </c>
     </row>
     <row r="27">
@@ -8570,7 +8467,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8578,40 +8475,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.18</v>
+        <v>48.184</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.307</v>
+        <v>48.306</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.127</v>
+        <v>0.122</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002635948526359485</v>
+        <v>0.00253196081686867</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.607</v>
+        <v>55.578</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.841</v>
+        <v>55.826</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.234</v>
+        <v>0.248</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004208103296347582</v>
+        <v>0.00446219727230199</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6610</v>
+        <v>6607</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>6687</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.01164901664145235</v>
+        <v>0.01210836991070077</v>
       </c>
     </row>
     <row r="28">
@@ -8619,7 +8516,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8627,40 +8524,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7595</v>
+        <v>47.761</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7595</v>
+        <v>48.761</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093824265329411</v>
+        <v>0.0209375850589393</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.326</v>
+        <v>55.29</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.416</v>
+        <v>56.38</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01970140621046163</v>
+        <v>0.01971423403870501</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6662.5</v>
+        <v>6653.36</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6762.5</v>
+        <v>6753.36</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.0150093808630394</v>
+        <v>0.01502999987976</v>
       </c>
     </row>
     <row r="29">
@@ -8668,7 +8565,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8684,16 +8581,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6677.98</v>
+        <v>6674.12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6859.96</v>
+        <v>6856.01</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>181.98</v>
+        <v>181.89</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02725075546797085</v>
+        <v>0.02725303111121766</v>
       </c>
     </row>
     <row r="30">
@@ -8701,7 +8598,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8721,28 +8618,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0871</v>
+        <v>55.0538</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.744</v>
+        <v>56.7097</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6569</v>
+        <v>1.6559</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.0300778222124599</v>
+        <v>0.03007785112017699</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6573.62</v>
+        <v>6575.87</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6771.74</v>
+        <v>6773.54</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>198.12</v>
+        <v>197.67</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03013864506923126</v>
+        <v>0.03005990081920719</v>
       </c>
     </row>
     <row r="31">
@@ -8750,7 +8647,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8758,40 +8655,40 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1519</v>
+        <v>48.1382</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.3934</v>
+        <v>48.3796</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2415</v>
+        <v>0.2414</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.00501537841705104</v>
+        <v>0.005014728427735145</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.6894</v>
+        <v>55.6258</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.0249</v>
+        <v>55.9609</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3355</v>
+        <v>0.3351</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006024485808789465</v>
+        <v>0.006024183022985737</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6589.37</v>
+        <v>6590.86</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6722.82</v>
+        <v>6724.34</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>133.45</v>
+        <v>133.48</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025231547173706</v>
+        <v>0.02025228877566812</v>
       </c>
     </row>
     <row r="32">
@@ -8799,7 +8696,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8807,40 +8704,40 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8512</v>
+        <v>47.8519</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6534</v>
+        <v>48.6541</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>0.8022</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676446985655532</v>
+        <v>0.01676422461804025</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.433</v>
+        <v>55.4009</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2837</v>
+        <v>56.2522</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8507</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01534645427813757</v>
+        <v>0.01536617636175586</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6608.44</v>
+        <v>6601.06</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6805.02</v>
+        <v>6797.5</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.58</v>
+        <v>196.44</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02974680862654424</v>
+        <v>0.02975885691085977</v>
       </c>
     </row>
     <row r="33">
@@ -8848,7 +8745,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8859,37 +8756,37 @@
         <v>48.1537</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3568</v>
+        <v>48.3569</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.2031</v>
+        <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004217744430853704</v>
+        <v>0.004219821114473031</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7387</v>
+        <v>55.7075</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9633</v>
+        <v>55.932</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2246</v>
+        <v>0.2245</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004029516296576705</v>
+        <v>0.004029978010142261</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6644.27</v>
+        <v>6643.77</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6697.64</v>
+        <v>6697.14</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>53.37</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008032485133807025</v>
+        <v>0.008033089646390528</v>
       </c>
     </row>
     <row r="34">
@@ -8897,7 +8794,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8905,40 +8802,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8942</v>
+        <v>47.8945</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8552</v>
+        <v>48.8555</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006506006990408</v>
+        <v>0.02006493438703818</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4726</v>
+        <v>55.4377</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5747</v>
+        <v>56.5397</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.1021</v>
+        <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986746610038109</v>
+        <v>0.01987816954888099</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6610.91</v>
+        <v>6609.01</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6755.51</v>
+        <v>6753.61</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02187293428590013</v>
+        <v>0.02187922245540557</v>
       </c>
     </row>
     <row r="35">
@@ -8946,7 +8843,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8954,28 +8851,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.174</v>
+        <v>48.178</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.254</v>
+        <v>48.248</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.001660646821937144</v>
+        <v>0.001452945327742953</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.636</v>
+        <v>55.599</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.806</v>
+        <v>55.76</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.17</v>
+        <v>0.161</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.003055575526637429</v>
+        <v>0.002895735534811777</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8987,7 +8884,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -9007,28 +8904,28 @@
         <v>0.02098635886673662</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.18</v>
+        <v>55.14</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.31</v>
+        <v>56.28</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.0204784342152954</v>
+        <v>0.02067464635473341</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6580.52</v>
+        <v>6577.8</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6782.97</v>
+        <v>6780.22</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>202.45</v>
+        <v>202.42</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03076504592342247</v>
+        <v>0.03077320684727416</v>
       </c>
     </row>
     <row r="37">
@@ -9036,7 +8933,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -9044,40 +8941,40 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.8903</v>
+        <v>47.8905</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8591</v>
+        <v>48.8593</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.9688</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02022956632136362</v>
+        <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.454</v>
+        <v>55.4274</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5759</v>
+        <v>56.5487</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1219</v>
+        <v>1.1213</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023118260179608</v>
+        <v>0.02023006671790487</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6648.56</v>
+        <v>6644.74</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6782.81</v>
+        <v>6778.9</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.25</v>
+        <v>134.16</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019234240196374</v>
+        <v>0.02019040624614356</v>
       </c>
     </row>
     <row r="38">
@@ -9085,7 +8982,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9093,40 +8990,40 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9382</v>
+        <v>47.9374</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.5904</v>
+        <v>48.5896</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0.6522</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360501645869056</v>
+        <v>0.0136052435050712</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4351</v>
+        <v>55.4023</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2455</v>
+        <v>56.2122</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8104</v>
+        <v>0.8099</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461889669180718</v>
+        <v>0.01461852666766542</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6610.1</v>
+        <v>6610.75</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6743.57</v>
+        <v>6744.23</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.47</v>
+        <v>133.48</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019182765767537</v>
+        <v>0.02019135498997844</v>
       </c>
     </row>
     <row r="39">
@@ -9134,7 +9031,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.3999189814814815</v>
+        <v>0.4163541666666667</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -9142,58 +9039,43 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7682</v>
+        <v>47.7685</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7652</v>
+        <v>48.7653</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.997</v>
+        <v>0.9968</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02087162589337677</v>
+        <v>0.02086730795398641</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2615</v>
+        <v>55.2295</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4701</v>
+        <v>56.4373</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2086</v>
+        <v>1.2078</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02187056087873112</v>
+        <v>0.02186874768013471</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6631.73</v>
+        <v>6631.3</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6842.3</v>
+        <v>6841.75</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.57</v>
+        <v>210.45</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03175189580999226</v>
+        <v>0.03173585873056565</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G39">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(G2&lt;&gt;"",G2=MIN($G$2:$G$39))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K39">
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(K2&lt;&gt;"",K2=MIN($K$2:$K$39))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O39">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>AND(O2&lt;&gt;"",O2=MIN($O$2:$O$39))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -42362,29 +42244,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT206"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42394,1550 +42282,1665 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="AA2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>AYLIK ORTALAMA MAKAS %</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
+        <is>
+          <t>SON VERİ ÇEKİMİ</t>
+        </is>
+      </c>
+      <c r="L3" s="60" t="inlineStr">
+        <is>
+          <t>5 BANKADA EN DÜŞÜK GÜNCEL MAKAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Ay</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Banka</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Dolar</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Gram Altın</t>
+        </is>
+      </c>
+      <c r="G4" s="61" t="inlineStr">
+        <is>
+          <t>Veri tarihi</t>
+        </is>
+      </c>
+      <c r="H4" s="62" t="n">
+        <v>46267</v>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Banka Sayısı</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>En Düşük %</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>En Avantajlı</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Alış</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>Satış</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="n">
+        <v>0.03553378696044311</v>
+      </c>
+      <c r="D5" s="66" t="n">
+        <v>0.03553642841103422</v>
+      </c>
+      <c r="E5" s="67" t="n">
+        <v>0.05383117747984287</v>
+      </c>
+      <c r="G5" s="61" t="inlineStr">
+        <is>
+          <t>Çekim saati</t>
+        </is>
+      </c>
+      <c r="H5" s="68" t="n">
+        <v>0.4163541666666667</v>
+      </c>
+      <c r="L5" s="69" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="M5" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="70" t="n">
+        <v>0.02022948183877804</v>
+      </c>
+      <c r="O5" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="P5" s="72" t="n">
+        <v>47.8905</v>
+      </c>
+      <c r="Q5" s="72" t="n">
+        <v>48.8593</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="63" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="n">
+        <v>0.04311562150687483</v>
+      </c>
+      <c r="D6" s="66" t="n">
+        <v>0.0432699268677014</v>
+      </c>
+      <c r="E6" s="67" t="n">
+        <v>0.06066925394146307</v>
+      </c>
+      <c r="G6" s="61" t="inlineStr">
+        <is>
+          <t>Sağlayıcı sayısı</t>
+        </is>
+      </c>
+      <c r="H6" s="63" t="n">
+        <v>38</v>
+      </c>
+      <c r="L6" s="74" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="M6" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="70" t="n">
+        <v>0.02023006671790487</v>
+      </c>
+      <c r="O6" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="P6" s="72" t="n">
+        <v>55.4274</v>
+      </c>
+      <c r="Q6" s="72" t="n">
+        <v>56.5487</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="63" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="n">
+        <v>0.03847709584999994</v>
+      </c>
+      <c r="D7" s="66" t="n">
+        <v>0.03535742466332828</v>
+      </c>
+      <c r="E7" s="67" t="n">
+        <v>0.0540849048600331</v>
+      </c>
+      <c r="G7" s="61" t="inlineStr">
+        <is>
+          <t>Ürün kaydı</t>
+        </is>
+      </c>
+      <c r="H7" s="63" t="n">
+        <v>108</v>
+      </c>
+      <c r="L7" s="76" t="inlineStr">
+        <is>
+          <t>GRAM ALTIN</t>
+        </is>
+      </c>
+      <c r="M7" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="70" t="n">
+        <v>0.02019040624614356</v>
+      </c>
+      <c r="O7" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="P7" s="72" t="n">
+        <v>6644.74</v>
+      </c>
+      <c r="Q7" s="72" t="n">
+        <v>6778.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="n">
+        <v>0.04104187506584386</v>
+      </c>
+      <c r="D8" s="66" t="n">
+        <v>0.0514487601107881</v>
+      </c>
+      <c r="E8" s="67" t="n">
+        <v>0.08301204597474589</v>
+      </c>
+      <c r="G8" s="61" t="inlineStr">
+        <is>
+          <t>Hatalı kayıt</t>
+        </is>
+      </c>
+      <c r="H8" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="77" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="C9" s="65" t="n">
+        <v>0.04760750668842017</v>
+      </c>
+      <c r="D9" s="66" t="n">
+        <v>0.04783493387226885</v>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>0.1017248276143379</v>
+      </c>
+      <c r="G9" s="61" t="inlineStr">
+        <is>
+          <t>Kontrol gereken</t>
+        </is>
+      </c>
+      <c r="H9" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="63" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="n">
+        <v>0.02845400039156511</v>
+      </c>
+      <c r="D10" s="66" t="n">
+        <v>0.02846019565754637</v>
+      </c>
+      <c r="E10" s="67" t="n">
+        <v>0.03694321012774233</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="73" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="n">
+        <v>0.0284261405518742</v>
+      </c>
+      <c r="D11" s="66" t="n">
+        <v>0.02847118412784268</v>
+      </c>
+      <c r="E11" s="67" t="n">
+        <v>0.03614313031148214</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="B12" s="75" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="n">
+        <v>0.02109574084424381</v>
+      </c>
+      <c r="D12" s="66" t="n">
+        <v>0.02046731269055863</v>
+      </c>
+      <c r="E12" s="67" t="n">
+        <v>0.03051048704906535</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="n">
+        <v>0.02023029953768716</v>
+      </c>
+      <c r="D13" s="66" t="n">
+        <v>0.02023090916840954</v>
+      </c>
+      <c r="E13" s="67" t="n">
+        <v>0.02019194235075064</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="77" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="n">
+        <v>0.02422333905778681</v>
+      </c>
+      <c r="D14" s="66" t="n">
+        <v>0.02435060197965432</v>
+      </c>
+      <c r="E14" s="67" t="n">
+        <v>0.02742927462036698</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>GÜNLÜK DEĞER DETAYI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Banka</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Dolar Makas %</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Euro Makas %</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Gram Altın Makas %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="C18" s="65" t="n">
+        <v>0.02853217795625066</v>
+      </c>
+      <c r="D18" s="66" t="n">
+        <v>0.02853823251760947</v>
+      </c>
+      <c r="E18" s="67" t="n">
+        <v>0.0369612266397948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="63" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="C19" s="65" t="n">
+        <v>0.02850867930903408</v>
+      </c>
+      <c r="D19" s="66" t="n">
+        <v>0.0285090304898068</v>
+      </c>
+      <c r="E19" s="67" t="n">
+        <v>0.03623508807809576</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B20" s="75" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="C20" s="65" t="n">
+        <v>0.0212363330529857</v>
+      </c>
+      <c r="D20" s="66" t="n">
+        <v>0.02058504875406284</v>
+      </c>
+      <c r="E20" s="67" t="n">
+        <v>0.02941852054231659</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="C21" s="65" t="n">
+        <v>0.02022862958363784</v>
+      </c>
+      <c r="D21" s="66" t="n">
+        <v>0.02023002817773203</v>
+      </c>
+      <c r="E21" s="67" t="n">
+        <v>0.020191203292302</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t>İş Bankası</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="C22" s="65" t="n">
+        <v>0.024367308299148</v>
+      </c>
+      <c r="D22" s="66" t="n">
+        <v>0.02445509246121618</v>
+      </c>
+      <c r="E22" s="67" t="n">
+        <v>0.02750535420451208</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="78" t="inlineStr">
+        <is>
+          <t>29.08.2026 - Cumartesi</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="C23" s="65" t="n">
+        <v>0.04254051984515251</v>
+      </c>
+      <c r="D23" s="66" t="n">
+        <v>0.04254615596583081</v>
+      </c>
+      <c r="E23" s="67" t="n">
+        <v>0.07070208501600407</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>29.08.2026 - Cumartesi</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="C24" s="65" t="n">
+        <v>0.05774536433047458</v>
+      </c>
+      <c r="D24" s="66" t="n">
+        <v>0.05801975297698195</v>
+      </c>
+      <c r="E24" s="67" t="n">
+        <v>0.08513100563182345</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>29.08.2026 - Cumartesi</t>
+        </is>
+      </c>
+      <c r="B25" s="75" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="C25" s="65" t="n">
+        <v>0.05599487069886729</v>
+      </c>
+      <c r="D25" s="66" t="n">
+        <v>0.0500459981600736</v>
+      </c>
+      <c r="E25" s="67" t="n">
+        <v>0.07842598844624503</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="78" t="inlineStr">
+        <is>
+          <t>29.08.2026 - Cumartesi</t>
+        </is>
+      </c>
+      <c r="B26" s="71" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="C26" s="65" t="n">
+        <v>0.06185456823006069</v>
+      </c>
+      <c r="D26" s="66" t="n">
+        <v>0.06185500408847346</v>
+      </c>
+      <c r="E26" s="67" t="n">
+        <v>0.1458328933354655</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="78" t="inlineStr">
+        <is>
+          <t>29.08.2026 - Cumartesi</t>
+        </is>
+      </c>
+      <c r="B27" s="77" t="inlineStr">
         <is>
           <t>İş Bankası</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="C27" s="65" t="n">
+        <v>0.05541806874813648</v>
+      </c>
+      <c r="D27" s="66" t="n">
+        <v>0.05578350900359923</v>
+      </c>
+      <c r="E27" s="67" t="n">
+        <v>0.1264646520842799</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>30.08.2026 - Pazar</t>
+        </is>
+      </c>
+      <c r="B28" s="64" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="C28" s="65" t="n">
+        <v>0.04254051984515251</v>
+      </c>
+      <c r="D28" s="66" t="n">
+        <v>0.04254615596583081</v>
+      </c>
+      <c r="E28" s="67" t="n">
+        <v>0.07070208501600407</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="78" t="inlineStr">
+        <is>
+          <t>30.08.2026 - Pazar</t>
+        </is>
+      </c>
+      <c r="B29" s="73" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="C29" s="65" t="n">
+        <v>0.05774536433047458</v>
+      </c>
+      <c r="D29" s="66" t="n">
+        <v>0.05801975297698195</v>
+      </c>
+      <c r="E29" s="67" t="n">
+        <v>0.08513100563182345</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="78" t="inlineStr">
+        <is>
+          <t>30.08.2026 - Pazar</t>
+        </is>
+      </c>
+      <c r="B30" s="75" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="C30" s="65" t="n">
+        <v>0.05572160546541418</v>
+      </c>
+      <c r="D30" s="66" t="n">
+        <v>0.05018382352941177</v>
+      </c>
+      <c r="E30" s="67" t="n">
+        <v>0.07830678789731968</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="78" t="inlineStr">
+        <is>
+          <t>30.08.2026 - Pazar</t>
+        </is>
+      </c>
+      <c r="B31" s="71" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="C31" s="65" t="n">
+        <v>0.06185456823006069</v>
+      </c>
+      <c r="D31" s="66" t="n">
+        <v>0.06185500408847346</v>
+      </c>
+      <c r="E31" s="67" t="n">
+        <v>0.1458328933354655</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="78" t="inlineStr">
+        <is>
+          <t>30.08.2026 - Pazar</t>
+        </is>
+      </c>
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>İş Bankası</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>28.08</t>
-        </is>
-      </c>
-      <c r="AB3" s="55" t="n">
-        <v>0.02853217795625066</v>
-      </c>
-      <c r="AC3" s="55" t="n">
-        <v>0.02850867930903408</v>
-      </c>
-      <c r="AD3" s="55" t="n">
-        <v>0.0212363330529857</v>
-      </c>
-      <c r="AE3" s="55" t="n">
-        <v>0.02022862958363784</v>
-      </c>
-      <c r="AF3" s="55" t="n">
-        <v>0.024367308299148</v>
-      </c>
-      <c r="AG3" s="55" t="n">
-        <v>0.02853823251760947</v>
-      </c>
-      <c r="AH3" s="55" t="n">
-        <v>0.0285090304898068</v>
-      </c>
-      <c r="AI3" s="55" t="n">
-        <v>0.02058504875406284</v>
-      </c>
-      <c r="AJ3" s="55" t="n">
-        <v>0.02023002817773203</v>
-      </c>
-      <c r="AK3" s="55" t="n">
-        <v>0.02445509246121618</v>
-      </c>
-      <c r="AL3" s="55" t="n">
-        <v>0.0369612266397948</v>
-      </c>
-      <c r="AM3" s="55" t="n">
-        <v>0.03623508807809576</v>
-      </c>
-      <c r="AN3" s="55" t="n">
-        <v>0.02941852054231659</v>
-      </c>
-      <c r="AO3" s="55" t="n">
-        <v>0.020191203292302</v>
-      </c>
-      <c r="AP3" s="55" t="n">
-        <v>0.02750535420451208</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>29.08 Cmt</t>
-        </is>
-      </c>
-      <c r="AB4" s="55" t="n">
-        <v>0.04254051984515251</v>
-      </c>
-      <c r="AC4" s="55" t="n">
-        <v>0.05774536433047458</v>
-      </c>
-      <c r="AD4" s="55" t="n">
-        <v>0.05599487069886729</v>
-      </c>
-      <c r="AE4" s="55" t="n">
-        <v>0.06185456823006069</v>
-      </c>
-      <c r="AF4" s="55" t="n">
+      <c r="C32" s="65" t="n">
         <v>0.05541806874813648</v>
       </c>
-      <c r="AG4" s="55" t="n">
-        <v>0.04254615596583081</v>
-      </c>
-      <c r="AH4" s="55" t="n">
-        <v>0.05801975297698195</v>
-      </c>
-      <c r="AI4" s="55" t="n">
-        <v>0.0500459981600736</v>
-      </c>
-      <c r="AJ4" s="55" t="n">
+      <c r="D32" s="66" t="n">
+        <v>0.05578350900359923</v>
+      </c>
+      <c r="E32" s="67" t="n">
+        <v>0.1264646520842799</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C33" s="65" t="n">
+        <v>0.02852193019521676</v>
+      </c>
+      <c r="D33" s="66" t="n">
+        <v>0.02851516919486581</v>
+      </c>
+      <c r="E33" s="67" t="n">
+        <v>0.03695931324756854</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="63" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="C34" s="65" t="n">
+        <v>0.02846307805751606</v>
+      </c>
+      <c r="D34" s="66" t="n">
+        <v>0.02853117102703489</v>
+      </c>
+      <c r="E34" s="67" t="n">
+        <v>0.0361799164241096</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="63" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B35" s="75" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="C35" s="65" t="n">
+        <v>0.02095557418273261</v>
+      </c>
+      <c r="D35" s="66" t="n">
+        <v>0.02061482820976492</v>
+      </c>
+      <c r="E35" s="67" t="n">
+        <v>0.03018832255425111</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="63" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="C36" s="65" t="n">
+        <v>0.02022973421961622</v>
+      </c>
+      <c r="D36" s="66" t="n">
         <v>0.06185500408847346</v>
       </c>
-      <c r="AK4" s="55" t="n">
-        <v>0.05578350900359923</v>
-      </c>
-      <c r="AL4" s="55" t="n">
-        <v>0.07070208501600407</v>
-      </c>
-      <c r="AM4" s="55" t="n">
-        <v>0.08513100563182345</v>
-      </c>
-      <c r="AN4" s="55" t="n">
-        <v>0.07842598844624503</v>
-      </c>
-      <c r="AO4" s="55" t="n">
-        <v>0.1458328933354655</v>
-      </c>
-      <c r="AP4" s="55" t="n">
+      <c r="E36" s="67" t="n">
+        <v>0.02019119393575063</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B37" s="77" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="C37" s="65" t="n">
+        <v>0.05522658095825972</v>
+      </c>
+      <c r="D37" s="66" t="n">
+        <v>0.05531762502066078</v>
+      </c>
+      <c r="E37" s="67" t="n">
         <v>0.1264646520842799</v>
       </c>
     </row>
-    <row r="5">
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>30.08 Paz</t>
-        </is>
-      </c>
-      <c r="AB5" s="55" t="n">
-        <v>0.04254051984515251</v>
-      </c>
-      <c r="AC5" s="55" t="n">
-        <v>0.05774536433047458</v>
-      </c>
-      <c r="AD5" s="55" t="n">
-        <v>0.05572160546541418</v>
-      </c>
-      <c r="AE5" s="55" t="n">
-        <v>0.06185456823006069</v>
-      </c>
-      <c r="AF5" s="55" t="n">
-        <v>0.05541806874813648</v>
-      </c>
-      <c r="AG5" s="55" t="n">
-        <v>0.04254615596583081</v>
-      </c>
-      <c r="AH5" s="55" t="n">
-        <v>0.05801975297698195</v>
-      </c>
-      <c r="AI5" s="55" t="n">
-        <v>0.05018382352941177</v>
-      </c>
-      <c r="AJ5" s="55" t="n">
-        <v>0.06185500408847346</v>
-      </c>
-      <c r="AK5" s="55" t="n">
-        <v>0.05578350900359923</v>
-      </c>
-      <c r="AL5" s="55" t="n">
-        <v>0.07070208501600407</v>
-      </c>
-      <c r="AM5" s="55" t="n">
-        <v>0.08513100563182345</v>
-      </c>
-      <c r="AN5" s="55" t="n">
-        <v>0.07830678789731968</v>
-      </c>
-      <c r="AO5" s="55" t="n">
-        <v>0.1458328933354655</v>
-      </c>
-      <c r="AP5" s="55" t="n">
-        <v>0.1264646520842799</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>31.08</t>
-        </is>
-      </c>
-      <c r="AB6" s="55" t="n">
-        <v>0.02852193019521676</v>
-      </c>
-      <c r="AC6" s="55" t="n">
-        <v>0.02846307805751606</v>
-      </c>
-      <c r="AD6" s="55" t="n">
-        <v>0.02095557418273261</v>
-      </c>
-      <c r="AE6" s="55" t="n">
-        <v>0.02022973421961622</v>
-      </c>
-      <c r="AF6" s="55" t="n">
-        <v>0.05522658095825972</v>
-      </c>
-      <c r="AG6" s="55" t="n">
-        <v>0.02851516919486581</v>
-      </c>
-      <c r="AH6" s="55" t="n">
-        <v>0.02853117102703489</v>
-      </c>
-      <c r="AI6" s="55" t="n">
-        <v>0.02061482820976492</v>
-      </c>
-      <c r="AJ6" s="55" t="n">
-        <v>0.06185500408847346</v>
-      </c>
-      <c r="AK6" s="55" t="n">
-        <v>0.05531762502066078</v>
-      </c>
-      <c r="AL6" s="55" t="n">
-        <v>0.03695931324756854</v>
-      </c>
-      <c r="AM6" s="55" t="n">
-        <v>0.0361799164241096</v>
-      </c>
-      <c r="AN6" s="55" t="n">
-        <v>0.03018832255425111</v>
-      </c>
-      <c r="AO6" s="55" t="n">
-        <v>0.02019119393575063</v>
-      </c>
-      <c r="AP6" s="55" t="n">
-        <v>0.1264646520842799</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>01.09</t>
-        </is>
-      </c>
-      <c r="AB7" s="55" t="n">
+    <row r="38">
+      <c r="A38" s="63" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C38" s="65" t="n">
         <v>0.02845939792562611</v>
       </c>
-      <c r="AC7" s="55" t="n">
+      <c r="D38" s="66" t="n">
+        <v>0.02847220959618916</v>
+      </c>
+      <c r="E38" s="67" t="n">
+        <v>0.03694474281650664</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="63" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B39" s="73" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="C39" s="65" t="n">
         <v>0.02843182679752327</v>
       </c>
-      <c r="AD7" s="55" t="n">
+      <c r="D39" s="66" t="n">
+        <v>0.02843333315169712</v>
+      </c>
+      <c r="E39" s="67" t="n">
+        <v>0.03614461438957493</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="63" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B40" s="75" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="C40" s="65" t="n">
         <v>0.021205122821751</v>
       </c>
-      <c r="AE7" s="55" t="n">
+      <c r="D40" s="66" t="n">
+        <v>0.02045619116582187</v>
+      </c>
+      <c r="E40" s="67" t="n">
+        <v>0.03025592817470824</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B41" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="C41" s="65" t="n">
         <v>0.02023103275401069</v>
       </c>
-      <c r="AF7" s="55" t="n">
+      <c r="D41" s="66" t="n">
+        <v>0.020230635735023</v>
+      </c>
+      <c r="E41" s="67" t="n">
+        <v>0.02019154229953755</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="C42" s="65" t="n">
         <v>0.02421542728972276</v>
       </c>
-      <c r="AG7" s="55" t="n">
-        <v>0.02847220959618916</v>
-      </c>
-      <c r="AH7" s="55" t="n">
-        <v>0.02843333315169712</v>
-      </c>
-      <c r="AI7" s="55" t="n">
-        <v>0.02045619116582187</v>
-      </c>
-      <c r="AJ7" s="55" t="n">
-        <v>0.020230635735023</v>
-      </c>
-      <c r="AK7" s="55" t="n">
+      <c r="D42" s="66" t="n">
         <v>0.02447694201114892</v>
       </c>
-      <c r="AL7" s="55" t="n">
-        <v>0.03694474281650664</v>
-      </c>
-      <c r="AM7" s="55" t="n">
-        <v>0.03614461438957493</v>
-      </c>
-      <c r="AN7" s="55" t="n">
-        <v>0.03025592817470824</v>
-      </c>
-      <c r="AO7" s="55" t="n">
-        <v>0.02019154229953755</v>
-      </c>
-      <c r="AP7" s="55" t="n">
+      <c r="E42" s="67" t="n">
         <v>0.02743096651330836</v>
       </c>
     </row>
-    <row r="8">
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>02.09</t>
-        </is>
-      </c>
-      <c r="AB8" s="55" t="n">
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C43" s="65" t="n">
         <v>0.02844860285750411</v>
       </c>
-      <c r="AC8" s="55" t="n">
+      <c r="D43" s="66" t="n">
+        <v>0.02844818171890357</v>
+      </c>
+      <c r="E43" s="67" t="n">
+        <v>0.03694167743897803</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B44" s="73" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="C44" s="65" t="n">
         <v>0.02842045430622513</v>
       </c>
-      <c r="AD8" s="55" t="n">
+      <c r="D44" s="66" t="n">
+        <v>0.02850903510398825</v>
+      </c>
+      <c r="E44" s="67" t="n">
+        <v>0.03614164623338936</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B45" s="75" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="C45" s="65" t="n">
         <v>0.02098635886673662</v>
       </c>
-      <c r="AE8" s="55" t="n">
+      <c r="D45" s="66" t="n">
+        <v>0.0204784342152954</v>
+      </c>
+      <c r="E45" s="67" t="n">
+        <v>0.03076504592342247</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B46" s="71" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="C46" s="65" t="n">
         <v>0.02022956632136362</v>
       </c>
-      <c r="AF8" s="55" t="n">
+      <c r="D46" s="66" t="n">
+        <v>0.02023118260179608</v>
+      </c>
+      <c r="E46" s="67" t="n">
+        <v>0.02019234240196374</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="77" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="C47" s="65" t="n">
         <v>0.02423125082585086</v>
       </c>
-      <c r="AG8" s="55" t="n">
-        <v>0.02844818171890357</v>
-      </c>
-      <c r="AH8" s="55" t="n">
-        <v>0.02850903510398825</v>
-      </c>
-      <c r="AI8" s="55" t="n">
-        <v>0.0204784342152954</v>
-      </c>
-      <c r="AJ8" s="55" t="n">
-        <v>0.02023118260179608</v>
-      </c>
-      <c r="AK8" s="55" t="n">
+      <c r="D47" s="66" t="n">
         <v>0.02422426194815971</v>
       </c>
-      <c r="AL8" s="55" t="n">
-        <v>0.03694167743897803</v>
-      </c>
-      <c r="AM8" s="55" t="n">
-        <v>0.03614164623338936</v>
-      </c>
-      <c r="AN8" s="55" t="n">
-        <v>0.03076504592342247</v>
-      </c>
-      <c r="AO8" s="55" t="n">
-        <v>0.02019234240196374</v>
-      </c>
-      <c r="AP8" s="55" t="n">
+      <c r="E47" s="67" t="n">
         <v>0.02742758272742561</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
-          <t>AYLIK ORTALAMA MAKAS %</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Banka</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Dolar Ort. Makas %</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Euro Ort. Makas %</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Gram Altın Ort. Makas %</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="61" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="B28" s="62" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="C28" s="63" t="n">
-        <v>0.03553378696044311</v>
-      </c>
-      <c r="D28" s="64" t="n">
-        <v>0.03553642841103422</v>
-      </c>
-      <c r="E28" s="65" t="n">
-        <v>0.05383117747984287</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="61" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="B29" s="66" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="C29" s="63" t="n">
-        <v>0.04311562150687483</v>
-      </c>
-      <c r="D29" s="64" t="n">
-        <v>0.0432699268677014</v>
-      </c>
-      <c r="E29" s="65" t="n">
-        <v>0.06066925394146307</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="61" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="C30" s="63" t="n">
-        <v>0.03847709584999994</v>
-      </c>
-      <c r="D30" s="64" t="n">
-        <v>0.03535742466332828</v>
-      </c>
-      <c r="E30" s="65" t="n">
-        <v>0.0540849048600331</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="61" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="C31" s="63" t="n">
-        <v>0.04104187506584386</v>
-      </c>
-      <c r="D31" s="64" t="n">
-        <v>0.0514487601107881</v>
-      </c>
-      <c r="E31" s="65" t="n">
-        <v>0.08301204597474589</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="61" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="B32" s="69" t="inlineStr">
-        <is>
-          <t>İş Bankası</t>
-        </is>
-      </c>
-      <c r="C32" s="63" t="n">
-        <v>0.04760750668842017</v>
-      </c>
-      <c r="D32" s="64" t="n">
-        <v>0.04783493387226885</v>
-      </c>
-      <c r="E32" s="65" t="n">
-        <v>0.1017248276143379</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="61" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="B33" s="62" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="C33" s="63" t="n">
-        <v>0.02845400039156511</v>
-      </c>
-      <c r="D33" s="64" t="n">
-        <v>0.02846019565754637</v>
-      </c>
-      <c r="E33" s="65" t="n">
-        <v>0.03694321012774233</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="61" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="B34" s="66" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="C34" s="63" t="n">
-        <v>0.0284261405518742</v>
-      </c>
-      <c r="D34" s="64" t="n">
-        <v>0.02847118412784268</v>
-      </c>
-      <c r="E34" s="65" t="n">
-        <v>0.03614313031148214</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="61" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="B35" s="67" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="C35" s="63" t="n">
-        <v>0.02109574084424381</v>
-      </c>
-      <c r="D35" s="64" t="n">
-        <v>0.02046731269055863</v>
-      </c>
-      <c r="E35" s="65" t="n">
-        <v>0.03051048704906535</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="61" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="C36" s="63" t="n">
-        <v>0.02023029953768716</v>
-      </c>
-      <c r="D36" s="64" t="n">
-        <v>0.02023090916840954</v>
-      </c>
-      <c r="E36" s="65" t="n">
-        <v>0.02019194235075064</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="61" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="B37" s="69" t="inlineStr">
-        <is>
-          <t>İş Bankası</t>
-        </is>
-      </c>
-      <c r="C37" s="63" t="n">
-        <v>0.02422333905778681</v>
-      </c>
-      <c r="D37" s="64" t="n">
-        <v>0.02435060197965432</v>
-      </c>
-      <c r="E37" s="65" t="n">
-        <v>0.02742927462036698</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>İş Bankası</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>İş Bankası</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="AP100" t="inlineStr">
-        <is>
-          <t>İş Bankası</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>Ağustos 2026</t>
-        </is>
-      </c>
-      <c r="AB101" s="55" t="n">
-        <v>0.03553378696044311</v>
-      </c>
-      <c r="AC101" s="55" t="n">
-        <v>0.04311562150687483</v>
-      </c>
-      <c r="AD101" s="55" t="n">
-        <v>0.03847709584999994</v>
-      </c>
-      <c r="AE101" s="55" t="n">
-        <v>0.04104187506584386</v>
-      </c>
-      <c r="AF101" s="55" t="n">
-        <v>0.04760750668842017</v>
-      </c>
-      <c r="AG101" s="55" t="n">
-        <v>0.03553642841103422</v>
-      </c>
-      <c r="AH101" s="55" t="n">
-        <v>0.0432699268677014</v>
-      </c>
-      <c r="AI101" s="55" t="n">
-        <v>0.03535742466332828</v>
-      </c>
-      <c r="AJ101" s="55" t="n">
-        <v>0.0514487601107881</v>
-      </c>
-      <c r="AK101" s="55" t="n">
-        <v>0.04783493387226885</v>
-      </c>
-      <c r="AL101" s="55" t="n">
-        <v>0.05383117747984287</v>
-      </c>
-      <c r="AM101" s="55" t="n">
-        <v>0.06066925394146307</v>
-      </c>
-      <c r="AN101" s="55" t="n">
-        <v>0.0540849048600331</v>
-      </c>
-      <c r="AO101" s="55" t="n">
-        <v>0.08301204597474589</v>
-      </c>
-      <c r="AP101" s="55" t="n">
-        <v>0.1017248276143379</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Eylül 2026</t>
-        </is>
-      </c>
-      <c r="AB102" s="55" t="n">
-        <v>0.02845400039156511</v>
-      </c>
-      <c r="AC102" s="55" t="n">
-        <v>0.0284261405518742</v>
-      </c>
-      <c r="AD102" s="55" t="n">
-        <v>0.02109574084424381</v>
-      </c>
-      <c r="AE102" s="55" t="n">
-        <v>0.02023029953768716</v>
-      </c>
-      <c r="AF102" s="55" t="n">
-        <v>0.02422333905778681</v>
-      </c>
-      <c r="AG102" s="55" t="n">
-        <v>0.02846019565754637</v>
-      </c>
-      <c r="AH102" s="55" t="n">
-        <v>0.02847118412784268</v>
-      </c>
-      <c r="AI102" s="55" t="n">
-        <v>0.02046731269055863</v>
-      </c>
-      <c r="AJ102" s="55" t="n">
-        <v>0.02023090916840954</v>
-      </c>
-      <c r="AK102" s="55" t="n">
-        <v>0.02435060197965432</v>
-      </c>
-      <c r="AL102" s="55" t="n">
-        <v>0.03694321012774233</v>
-      </c>
-      <c r="AM102" s="55" t="n">
-        <v>0.03614313031148214</v>
-      </c>
-      <c r="AN102" s="55" t="n">
-        <v>0.03051048704906535</v>
-      </c>
-      <c r="AO102" s="55" t="n">
-        <v>0.02019194235075064</v>
-      </c>
-      <c r="AP102" s="55" t="n">
-        <v>0.02742927462036698</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="70" t="inlineStr">
-        <is>
-          <t>SON VERİ ÇEKİMİ ÖZETİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="71" t="inlineStr">
-        <is>
-          <t>Veri tarihi</t>
-        </is>
-      </c>
-      <c r="B184" s="72" t="n">
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="71" t="inlineStr">
-        <is>
-          <t>Veri çekim saati</t>
-        </is>
-      </c>
-      <c r="B185" s="73" t="n">
-        <v>0.3999189814814815</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="71" t="inlineStr">
-        <is>
-          <t>Son çekimde bulunan sağlayıcı sayısı</t>
-        </is>
-      </c>
-      <c r="B186" s="61" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="71" t="inlineStr">
-        <is>
-          <t>Son çekimde alınan toplam ürün kaydı</t>
-        </is>
-      </c>
-      <c r="B187" s="61" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="71" t="inlineStr">
-        <is>
-          <t>Hatalı kayıt sayısı</t>
-        </is>
-      </c>
-      <c r="B188" s="61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="71" t="inlineStr">
-        <is>
-          <t>Kontrol gereken kayıt sayısı</t>
-        </is>
-      </c>
-      <c r="B189" s="61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="70" t="inlineStr">
-        <is>
-          <t>5 BANKA ARASINDA EN DÜŞÜK GÜNCEL MAKAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr">
-        <is>
-          <t>Ürün</t>
-        </is>
-      </c>
-      <c r="B192" s="1" t="inlineStr">
-        <is>
-          <t>Verisi Bulunan Banka Sayısı</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>En Düşük Makas %</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t>En Avantajlı Banka</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t>Alış</t>
-        </is>
-      </c>
-      <c r="F192" s="1" t="inlineStr">
-        <is>
-          <t>Satış</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="74" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="B193" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="C193" s="75" t="n">
-        <v>0.02022956632136362</v>
-      </c>
-      <c r="D193" s="68" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="E193" s="76" t="n">
-        <v>47.8903</v>
-      </c>
-      <c r="F193" s="76" t="n">
-        <v>48.8591</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="77" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="B194" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="C194" s="75" t="n">
-        <v>0.02023118260179608</v>
-      </c>
-      <c r="D194" s="68" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="E194" s="76" t="n">
-        <v>55.454</v>
-      </c>
-      <c r="F194" s="76" t="n">
-        <v>56.5759</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="78" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-      <c r="B195" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="C195" s="75" t="n">
-        <v>0.02019234240196374</v>
-      </c>
-      <c r="D195" s="68" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="E195" s="76" t="n">
-        <v>6648.56</v>
-      </c>
-      <c r="F195" s="76" t="n">
-        <v>6782.81</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>Garanti BBVA Tarih</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>Akbank Tarih</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>Yapıkredi Tarih</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası Tarih</t>
-        </is>
-      </c>
-      <c r="AN200" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>İş Bankası Tarih</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>DOLAR</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="AT200" t="inlineStr">
-        <is>
-          <t>GRAM ALTIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>28.08 13:22</t>
-        </is>
-      </c>
-      <c r="AB201" s="55" t="n">
-        <v>0.02853217795625066</v>
-      </c>
-      <c r="AC201" s="55" t="n">
-        <v>0.02853823251760947</v>
-      </c>
-      <c r="AD201" s="55" t="n">
-        <v>0.0369612266397948</v>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>28.08 13:22</t>
-        </is>
-      </c>
-      <c r="AF201" s="55" t="n">
-        <v>0.02850867930903408</v>
-      </c>
-      <c r="AG201" s="55" t="n">
-        <v>0.0285090304898068</v>
-      </c>
-      <c r="AH201" s="55" t="n">
-        <v>0.03623508807809576</v>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>28.08 13:22</t>
-        </is>
-      </c>
-      <c r="AJ201" s="55" t="n">
-        <v>0.0212363330529857</v>
-      </c>
-      <c r="AK201" s="55" t="n">
-        <v>0.02058504875406284</v>
-      </c>
-      <c r="AL201" s="55" t="n">
-        <v>0.02941852054231659</v>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>28.08 13:22</t>
-        </is>
-      </c>
-      <c r="AN201" s="55" t="n">
-        <v>0.02022862958363784</v>
-      </c>
-      <c r="AO201" s="55" t="n">
-        <v>0.02023002817773203</v>
-      </c>
-      <c r="AP201" s="55" t="n">
-        <v>0.020191203292302</v>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>28.08 13:22</t>
-        </is>
-      </c>
-      <c r="AR201" s="55" t="n">
-        <v>0.024367308299148</v>
-      </c>
-      <c r="AS201" s="55" t="n">
-        <v>0.02445509246121618</v>
-      </c>
-      <c r="AT201" s="55" t="n">
-        <v>0.02750535420451208</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>29.08 Cmt 10:22</t>
-        </is>
-      </c>
-      <c r="AB202" s="55" t="n">
-        <v>0.04254051984515251</v>
-      </c>
-      <c r="AC202" s="55" t="n">
-        <v>0.04254615596583081</v>
-      </c>
-      <c r="AD202" s="55" t="n">
-        <v>0.07070208501600407</v>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>29.08 Cmt 10:22</t>
-        </is>
-      </c>
-      <c r="AF202" s="55" t="n">
-        <v>0.05774536433047458</v>
-      </c>
-      <c r="AG202" s="55" t="n">
-        <v>0.05801975297698195</v>
-      </c>
-      <c r="AH202" s="55" t="n">
-        <v>0.08513100563182345</v>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>29.08 Cmt 10:22</t>
-        </is>
-      </c>
-      <c r="AJ202" s="55" t="n">
-        <v>0.05599487069886729</v>
-      </c>
-      <c r="AK202" s="55" t="n">
-        <v>0.0500459981600736</v>
-      </c>
-      <c r="AL202" s="55" t="n">
-        <v>0.07842598844624503</v>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>29.08 Cmt 10:22</t>
-        </is>
-      </c>
-      <c r="AN202" s="55" t="n">
-        <v>0.06185456823006069</v>
-      </c>
-      <c r="AO202" s="55" t="n">
-        <v>0.06185500408847346</v>
-      </c>
-      <c r="AP202" s="55" t="n">
-        <v>0.1458328933354655</v>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>29.08 Cmt 10:22</t>
-        </is>
-      </c>
-      <c r="AR202" s="55" t="n">
-        <v>0.05541806874813648</v>
-      </c>
-      <c r="AS202" s="55" t="n">
-        <v>0.05578350900359923</v>
-      </c>
-      <c r="AT202" s="55" t="n">
-        <v>0.1264646520842799</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>30.08 Paz 10:22</t>
-        </is>
-      </c>
-      <c r="AB203" s="55" t="n">
-        <v>0.04254051984515251</v>
-      </c>
-      <c r="AC203" s="55" t="n">
-        <v>0.04254615596583081</v>
-      </c>
-      <c r="AD203" s="55" t="n">
-        <v>0.07070208501600407</v>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>30.08 Paz 10:22</t>
-        </is>
-      </c>
-      <c r="AF203" s="55" t="n">
-        <v>0.05774536433047458</v>
-      </c>
-      <c r="AG203" s="55" t="n">
-        <v>0.05801975297698195</v>
-      </c>
-      <c r="AH203" s="55" t="n">
-        <v>0.08513100563182345</v>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>30.08 Paz 10:22</t>
-        </is>
-      </c>
-      <c r="AJ203" s="55" t="n">
-        <v>0.05572160546541418</v>
-      </c>
-      <c r="AK203" s="55" t="n">
-        <v>0.05018382352941177</v>
-      </c>
-      <c r="AL203" s="55" t="n">
-        <v>0.07830678789731968</v>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>30.08 Paz 10:22</t>
-        </is>
-      </c>
-      <c r="AN203" s="55" t="n">
-        <v>0.06185456823006069</v>
-      </c>
-      <c r="AO203" s="55" t="n">
-        <v>0.06185500408847346</v>
-      </c>
-      <c r="AP203" s="55" t="n">
-        <v>0.1458328933354655</v>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>30.08 Paz 10:22</t>
-        </is>
-      </c>
-      <c r="AR203" s="55" t="n">
-        <v>0.05541806874813648</v>
-      </c>
-      <c r="AS203" s="55" t="n">
-        <v>0.05578350900359923</v>
-      </c>
-      <c r="AT203" s="55" t="n">
-        <v>0.1264646520842799</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>31.08 08:55</t>
-        </is>
-      </c>
-      <c r="AB204" s="55" t="n">
-        <v>0.02852193019521676</v>
-      </c>
-      <c r="AC204" s="55" t="n">
-        <v>0.02851516919486581</v>
-      </c>
-      <c r="AD204" s="55" t="n">
-        <v>0.03695931324756854</v>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>31.08 08:55</t>
-        </is>
-      </c>
-      <c r="AF204" s="55" t="n">
-        <v>0.02846307805751606</v>
-      </c>
-      <c r="AG204" s="55" t="n">
-        <v>0.02853117102703489</v>
-      </c>
-      <c r="AH204" s="55" t="n">
-        <v>0.0361799164241096</v>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>31.08 08:55</t>
-        </is>
-      </c>
-      <c r="AJ204" s="55" t="n">
-        <v>0.02095557418273261</v>
-      </c>
-      <c r="AK204" s="55" t="n">
-        <v>0.02061482820976492</v>
-      </c>
-      <c r="AL204" s="55" t="n">
-        <v>0.03018832255425111</v>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>31.08 08:55</t>
-        </is>
-      </c>
-      <c r="AN204" s="55" t="n">
-        <v>0.02022973421961622</v>
-      </c>
-      <c r="AO204" s="55" t="n">
-        <v>0.06185500408847346</v>
-      </c>
-      <c r="AP204" s="55" t="n">
-        <v>0.02019119393575063</v>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>31.08 08:55</t>
-        </is>
-      </c>
-      <c r="AR204" s="55" t="n">
-        <v>0.05522658095825972</v>
-      </c>
-      <c r="AS204" s="55" t="n">
-        <v>0.05531762502066078</v>
-      </c>
-      <c r="AT204" s="55" t="n">
-        <v>0.1264646520842799</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>01.09 11:01</t>
-        </is>
-      </c>
-      <c r="AB205" s="55" t="n">
-        <v>0.02845939792562611</v>
-      </c>
-      <c r="AC205" s="55" t="n">
-        <v>0.02847220959618916</v>
-      </c>
-      <c r="AD205" s="55" t="n">
-        <v>0.03694474281650664</v>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>01.09 11:01</t>
-        </is>
-      </c>
-      <c r="AF205" s="55" t="n">
-        <v>0.02843182679752327</v>
-      </c>
-      <c r="AG205" s="55" t="n">
-        <v>0.02843333315169712</v>
-      </c>
-      <c r="AH205" s="55" t="n">
-        <v>0.03614461438957493</v>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>01.09 11:01</t>
-        </is>
-      </c>
-      <c r="AJ205" s="55" t="n">
-        <v>0.021205122821751</v>
-      </c>
-      <c r="AK205" s="55" t="n">
-        <v>0.02045619116582187</v>
-      </c>
-      <c r="AL205" s="55" t="n">
-        <v>0.03025592817470824</v>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>01.09 11:01</t>
-        </is>
-      </c>
-      <c r="AN205" s="55" t="n">
-        <v>0.02023103275401069</v>
-      </c>
-      <c r="AO205" s="55" t="n">
-        <v>0.020230635735023</v>
-      </c>
-      <c r="AP205" s="55" t="n">
-        <v>0.02019154229953755</v>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>01.09 11:01</t>
-        </is>
-      </c>
-      <c r="AR205" s="55" t="n">
-        <v>0.02421542728972276</v>
-      </c>
-      <c r="AS205" s="55" t="n">
-        <v>0.02447694201114892</v>
-      </c>
-      <c r="AT205" s="55" t="n">
-        <v>0.02743096651330836</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>02.09 09:35</t>
-        </is>
-      </c>
-      <c r="AB206" s="55" t="n">
-        <v>0.02844860285750411</v>
-      </c>
-      <c r="AC206" s="55" t="n">
-        <v>0.02844818171890357</v>
-      </c>
-      <c r="AD206" s="55" t="n">
-        <v>0.03694167743897803</v>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>02.09 09:35</t>
-        </is>
-      </c>
-      <c r="AF206" s="55" t="n">
-        <v>0.02842045430622513</v>
-      </c>
-      <c r="AG206" s="55" t="n">
-        <v>0.02850903510398825</v>
-      </c>
-      <c r="AH206" s="55" t="n">
-        <v>0.03614164623338936</v>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>02.09 09:35</t>
-        </is>
-      </c>
-      <c r="AJ206" s="55" t="n">
-        <v>0.02098635886673662</v>
-      </c>
-      <c r="AK206" s="55" t="n">
-        <v>0.0204784342152954</v>
-      </c>
-      <c r="AL206" s="55" t="n">
-        <v>0.03076504592342247</v>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>02.09 09:35</t>
-        </is>
-      </c>
-      <c r="AN206" s="55" t="n">
-        <v>0.02022956632136362</v>
-      </c>
-      <c r="AO206" s="55" t="n">
-        <v>0.02023118260179608</v>
-      </c>
-      <c r="AP206" s="55" t="n">
-        <v>0.02019234240196374</v>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>02.09 09:35</t>
-        </is>
-      </c>
-      <c r="AR206" s="55" t="n">
-        <v>0.02423125082585086</v>
-      </c>
-      <c r="AS206" s="55" t="n">
-        <v>0.02422426194815971</v>
-      </c>
-      <c r="AT206" s="55" t="n">
-        <v>0.02742758272742561</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A26:E26"/>
+  <mergeCells count="5">
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>USD - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>USD - Akbank</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>USD - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>USD - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>USD - İş Bankası</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EUR - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>EUR - Akbank</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>EUR - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>EUR - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>EUR - İş Bankası</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>XAU - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>XAU - Akbank</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>XAU - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>XAU - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>XAU - İş Bankası</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Ay</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>USD - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>USD - Akbank</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>USD - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>USD - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>USD - İş Bankası</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>EUR - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>EUR - Akbank</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>EUR - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>EUR - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>EUR - İş Bankası</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>XAU - Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>XAU - Akbank</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>XAU - Yapıkredi</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>XAU - Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>XAU - İş Bankası</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>28.08</t>
+        </is>
+      </c>
+      <c r="B2" s="55" t="n">
+        <v>0.02853217795625066</v>
+      </c>
+      <c r="C2" s="55" t="n">
+        <v>0.02850867930903408</v>
+      </c>
+      <c r="D2" s="55" t="n">
+        <v>0.0212363330529857</v>
+      </c>
+      <c r="E2" s="55" t="n">
+        <v>0.02022862958363784</v>
+      </c>
+      <c r="F2" s="55" t="n">
+        <v>0.024367308299148</v>
+      </c>
+      <c r="G2" s="55" t="n">
+        <v>0.02853823251760947</v>
+      </c>
+      <c r="H2" s="55" t="n">
+        <v>0.0285090304898068</v>
+      </c>
+      <c r="I2" s="55" t="n">
+        <v>0.02058504875406284</v>
+      </c>
+      <c r="J2" s="55" t="n">
+        <v>0.02023002817773203</v>
+      </c>
+      <c r="K2" s="55" t="n">
+        <v>0.02445509246121618</v>
+      </c>
+      <c r="L2" s="55" t="n">
+        <v>0.0369612266397948</v>
+      </c>
+      <c r="M2" s="55" t="n">
+        <v>0.03623508807809576</v>
+      </c>
+      <c r="N2" s="55" t="n">
+        <v>0.02941852054231659</v>
+      </c>
+      <c r="O2" s="55" t="n">
+        <v>0.020191203292302</v>
+      </c>
+      <c r="P2" s="55" t="n">
+        <v>0.02750535420451208</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Ağustos 2026</t>
+        </is>
+      </c>
+      <c r="U2" s="55" t="n">
+        <v>0.03553378696044311</v>
+      </c>
+      <c r="V2" s="55" t="n">
+        <v>0.04311562150687483</v>
+      </c>
+      <c r="W2" s="55" t="n">
+        <v>0.03847709584999994</v>
+      </c>
+      <c r="X2" s="55" t="n">
+        <v>0.04104187506584386</v>
+      </c>
+      <c r="Y2" s="55" t="n">
+        <v>0.04760750668842017</v>
+      </c>
+      <c r="Z2" s="55" t="n">
+        <v>0.03553642841103422</v>
+      </c>
+      <c r="AA2" s="55" t="n">
+        <v>0.0432699268677014</v>
+      </c>
+      <c r="AB2" s="55" t="n">
+        <v>0.03535742466332828</v>
+      </c>
+      <c r="AC2" s="55" t="n">
+        <v>0.0514487601107881</v>
+      </c>
+      <c r="AD2" s="55" t="n">
+        <v>0.04783493387226885</v>
+      </c>
+      <c r="AE2" s="55" t="n">
+        <v>0.05383117747984287</v>
+      </c>
+      <c r="AF2" s="55" t="n">
+        <v>0.06066925394146307</v>
+      </c>
+      <c r="AG2" s="55" t="n">
+        <v>0.0540849048600331</v>
+      </c>
+      <c r="AH2" s="55" t="n">
+        <v>0.08301204597474589</v>
+      </c>
+      <c r="AI2" s="55" t="n">
+        <v>0.1017248276143379</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>29.08 Cmt</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="n">
+        <v>0.04254051984515251</v>
+      </c>
+      <c r="C3" s="55" t="n">
+        <v>0.05774536433047458</v>
+      </c>
+      <c r="D3" s="55" t="n">
+        <v>0.05599487069886729</v>
+      </c>
+      <c r="E3" s="55" t="n">
+        <v>0.06185456823006069</v>
+      </c>
+      <c r="F3" s="55" t="n">
+        <v>0.05541806874813648</v>
+      </c>
+      <c r="G3" s="55" t="n">
+        <v>0.04254615596583081</v>
+      </c>
+      <c r="H3" s="55" t="n">
+        <v>0.05801975297698195</v>
+      </c>
+      <c r="I3" s="55" t="n">
+        <v>0.0500459981600736</v>
+      </c>
+      <c r="J3" s="55" t="n">
+        <v>0.06185500408847346</v>
+      </c>
+      <c r="K3" s="55" t="n">
+        <v>0.05578350900359923</v>
+      </c>
+      <c r="L3" s="55" t="n">
+        <v>0.07070208501600407</v>
+      </c>
+      <c r="M3" s="55" t="n">
+        <v>0.08513100563182345</v>
+      </c>
+      <c r="N3" s="55" t="n">
+        <v>0.07842598844624503</v>
+      </c>
+      <c r="O3" s="55" t="n">
+        <v>0.1458328933354655</v>
+      </c>
+      <c r="P3" s="55" t="n">
+        <v>0.1264646520842799</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Eylül 2026</t>
+        </is>
+      </c>
+      <c r="U3" s="55" t="n">
+        <v>0.02845400039156511</v>
+      </c>
+      <c r="V3" s="55" t="n">
+        <v>0.0284261405518742</v>
+      </c>
+      <c r="W3" s="55" t="n">
+        <v>0.02109574084424381</v>
+      </c>
+      <c r="X3" s="55" t="n">
+        <v>0.02023029953768716</v>
+      </c>
+      <c r="Y3" s="55" t="n">
+        <v>0.02422333905778681</v>
+      </c>
+      <c r="Z3" s="55" t="n">
+        <v>0.02846019565754637</v>
+      </c>
+      <c r="AA3" s="55" t="n">
+        <v>0.02847118412784268</v>
+      </c>
+      <c r="AB3" s="55" t="n">
+        <v>0.02046731269055863</v>
+      </c>
+      <c r="AC3" s="55" t="n">
+        <v>0.02023090916840954</v>
+      </c>
+      <c r="AD3" s="55" t="n">
+        <v>0.02435060197965432</v>
+      </c>
+      <c r="AE3" s="55" t="n">
+        <v>0.03694321012774233</v>
+      </c>
+      <c r="AF3" s="55" t="n">
+        <v>0.03614313031148214</v>
+      </c>
+      <c r="AG3" s="55" t="n">
+        <v>0.03051048704906535</v>
+      </c>
+      <c r="AH3" s="55" t="n">
+        <v>0.02019194235075064</v>
+      </c>
+      <c r="AI3" s="55" t="n">
+        <v>0.02742927462036698</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30.08 Paz</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="n">
+        <v>0.04254051984515251</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>0.05774536433047458</v>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>0.05572160546541418</v>
+      </c>
+      <c r="E4" s="55" t="n">
+        <v>0.06185456823006069</v>
+      </c>
+      <c r="F4" s="55" t="n">
+        <v>0.05541806874813648</v>
+      </c>
+      <c r="G4" s="55" t="n">
+        <v>0.04254615596583081</v>
+      </c>
+      <c r="H4" s="55" t="n">
+        <v>0.05801975297698195</v>
+      </c>
+      <c r="I4" s="55" t="n">
+        <v>0.05018382352941177</v>
+      </c>
+      <c r="J4" s="55" t="n">
+        <v>0.06185500408847346</v>
+      </c>
+      <c r="K4" s="55" t="n">
+        <v>0.05578350900359923</v>
+      </c>
+      <c r="L4" s="55" t="n">
+        <v>0.07070208501600407</v>
+      </c>
+      <c r="M4" s="55" t="n">
+        <v>0.08513100563182345</v>
+      </c>
+      <c r="N4" s="55" t="n">
+        <v>0.07830678789731968</v>
+      </c>
+      <c r="O4" s="55" t="n">
+        <v>0.1458328933354655</v>
+      </c>
+      <c r="P4" s="55" t="n">
+        <v>0.1264646520842799</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>31.08</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="n">
+        <v>0.02852193019521676</v>
+      </c>
+      <c r="C5" s="55" t="n">
+        <v>0.02846307805751606</v>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>0.02095557418273261</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>0.02022973421961622</v>
+      </c>
+      <c r="F5" s="55" t="n">
+        <v>0.05522658095825972</v>
+      </c>
+      <c r="G5" s="55" t="n">
+        <v>0.02851516919486581</v>
+      </c>
+      <c r="H5" s="55" t="n">
+        <v>0.02853117102703489</v>
+      </c>
+      <c r="I5" s="55" t="n">
+        <v>0.02061482820976492</v>
+      </c>
+      <c r="J5" s="55" t="n">
+        <v>0.06185500408847346</v>
+      </c>
+      <c r="K5" s="55" t="n">
+        <v>0.05531762502066078</v>
+      </c>
+      <c r="L5" s="55" t="n">
+        <v>0.03695931324756854</v>
+      </c>
+      <c r="M5" s="55" t="n">
+        <v>0.0361799164241096</v>
+      </c>
+      <c r="N5" s="55" t="n">
+        <v>0.03018832255425111</v>
+      </c>
+      <c r="O5" s="55" t="n">
+        <v>0.02019119393575063</v>
+      </c>
+      <c r="P5" s="55" t="n">
+        <v>0.1264646520842799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01.09</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>0.02845939792562611</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>0.02843182679752327</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>0.021205122821751</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>0.02023103275401069</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>0.02421542728972276</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>0.02847220959618916</v>
+      </c>
+      <c r="H6" s="55" t="n">
+        <v>0.02843333315169712</v>
+      </c>
+      <c r="I6" s="55" t="n">
+        <v>0.02045619116582187</v>
+      </c>
+      <c r="J6" s="55" t="n">
+        <v>0.020230635735023</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>0.02447694201114892</v>
+      </c>
+      <c r="L6" s="55" t="n">
+        <v>0.03694474281650664</v>
+      </c>
+      <c r="M6" s="55" t="n">
+        <v>0.03614461438957493</v>
+      </c>
+      <c r="N6" s="55" t="n">
+        <v>0.03025592817470824</v>
+      </c>
+      <c r="O6" s="55" t="n">
+        <v>0.02019154229953755</v>
+      </c>
+      <c r="P6" s="55" t="n">
+        <v>0.02743096651330836</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02.09</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>0.02844860285750411</v>
+      </c>
+      <c r="C7" s="55" t="n">
+        <v>0.02842045430622513</v>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>0.02098635886673662</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>0.02022956632136362</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>0.02423125082585086</v>
+      </c>
+      <c r="G7" s="55" t="n">
+        <v>0.02844818171890357</v>
+      </c>
+      <c r="H7" s="55" t="n">
+        <v>0.02850903510398825</v>
+      </c>
+      <c r="I7" s="55" t="n">
+        <v>0.0204784342152954</v>
+      </c>
+      <c r="J7" s="55" t="n">
+        <v>0.02023118260179608</v>
+      </c>
+      <c r="K7" s="55" t="n">
+        <v>0.02422426194815971</v>
+      </c>
+      <c r="L7" s="55" t="n">
+        <v>0.03694167743897803</v>
+      </c>
+      <c r="M7" s="55" t="n">
+        <v>0.03614164623338936</v>
+      </c>
+      <c r="N7" s="55" t="n">
+        <v>0.03076504592342247</v>
+      </c>
+      <c r="O7" s="55" t="n">
+        <v>0.02019234240196374</v>
+      </c>
+      <c r="P7" s="55" t="n">
+        <v>0.02742758272742561</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="GUNCEL_KURLAR" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +49,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C65911"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
@@ -415,16 +415,16 @@
     <xf numFmtId="0" fontId="6" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -433,7 +433,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -545,6 +545,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!B1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -571,13 +577,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02853217795625066</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.04254051984515251</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.04254051984515251</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02852193019521676</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02845939792562611</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02844860285750411</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -588,6 +637,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!C1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -614,13 +669,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02850867930903408</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05774536433047458</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05774536433047458</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02846307805751606</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02843182679752327</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02842045430622513</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -631,6 +729,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!D1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -657,13 +761,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0212363330529857</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05599487069886729</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05572160546541418</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02095557418273261</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.021205122821751</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02098635886673662</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -674,6 +821,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!E1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -700,13 +853,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02022862958363784</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.06185456823006069</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.06185456823006069</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02022973421961622</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02023103275401069</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02022956632136362</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -717,6 +913,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!F1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -743,13 +945,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.024367308299148</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05541806874813648</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05541806874813648</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.05522658095825972</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02421542728972276</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02423125082585086</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -770,12 +1015,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -785,8 +1030,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.07017975595934527"/>
-          <min val="0.01190344185435327"/>
+          <max val="0.06809845902702412"/>
+          <min val="0.01398473878667442"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -814,15 +1059,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -853,6 +1092,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!C1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>DOLAR</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -879,13 +1124,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02850867930903408</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05774536433047458</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05774536433047458</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02846307805751606</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02843182679752327</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02842045430622513</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -906,12 +1194,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -947,18 +1235,20 @@
       </valAx>
       <spPr>
         <a:solidFill>
-          <a:srgbClr val="FCE4E4"/>
+          <a:srgbClr val="FDE2E2"/>
         </a:solidFill>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FDE2E2"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -993,6 +1283,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!H1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>EURO</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1004,7 +1300,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="square"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1019,13 +1315,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0285090304898068</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05801975297698195</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05801975297698195</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02853117102703489</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02843333315169712</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02850903510398825</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1046,12 +1385,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1087,18 +1426,20 @@
       </valAx>
       <spPr>
         <a:solidFill>
-          <a:srgbClr val="FCE4E4"/>
+          <a:srgbClr val="FDE2E2"/>
         </a:solidFill>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FDE2E2"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1133,6 +1474,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!M1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>GRAM ALTIN</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1144,7 +1491,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1159,13 +1506,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.03623508807809576</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.08513100563182345</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.08513100563182345</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.0361799164241096</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03614461438957493</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03614164623338936</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1186,12 +1576,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1227,18 +1617,20 @@
       </valAx>
       <spPr>
         <a:solidFill>
-          <a:srgbClr val="FCE4E4"/>
+          <a:srgbClr val="FDE2E2"/>
         </a:solidFill>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FDE2E2"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1273,6 +1665,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!D1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>DOLAR</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1299,13 +1697,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0212363330529857</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05599487069886729</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05572160546541418</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02095557418273261</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.021205122821751</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02098635886673662</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1326,12 +1767,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1374,11 +1815,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E4D7F5"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1413,6 +1856,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!I1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>EURO</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1424,7 +1873,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="square"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1439,13 +1888,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02058504875406284</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.0500459981600736</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05018382352941177</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02061482820976492</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02045619116582187</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.0204784342152954</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1466,12 +1958,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1514,11 +2006,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E4D7F5"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1553,6 +2047,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!N1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>GRAM ALTIN</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1564,7 +2064,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1579,13 +2079,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02941852054231659</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.07842598844624503</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.07830678789731968</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.03018832255425111</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03025592817470824</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03076504592342247</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1606,12 +2149,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1654,11 +2197,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E4D7F5"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1693,6 +2238,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!E1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>DOLAR</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1719,13 +2270,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02022862958363784</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.06185456823006069</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.06185456823006069</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02022973421961622</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02023103275401069</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02022956632136362</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1746,12 +2340,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1794,11 +2388,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FFF2CC"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1833,6 +2429,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!J1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>EURO</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1844,7 +2446,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="square"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1859,13 +2461,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02023002817773203</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.020230635735023</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02023118260179608</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1886,12 +2531,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -1934,11 +2579,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FFF2CC"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1973,6 +2620,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!O1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>GRAM ALTIN</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -1984,7 +2637,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -1999,13 +2652,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.020191203292302</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.1458328933354655</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.1458328933354655</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02019119393575063</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02019154229953755</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02019234240196374</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2026,12 +2722,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -2074,11 +2770,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="FFF2CC"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2113,6 +2811,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!F1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>DOLAR</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2139,13 +2843,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.024367308299148</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05541806874813648</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05541806874813648</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.05522658095825972</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02421542728972276</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02423125082585086</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2166,12 +2913,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -2214,11 +2961,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="DDEBF7"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2253,6 +3002,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!G1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2279,13 +3034,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02853823251760947</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.04254615596583081</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.04254615596583081</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02851516919486581</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02847220959618916</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02844818171890357</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2296,6 +3094,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!H1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2322,13 +3126,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0285090304898068</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05801975297698195</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05801975297698195</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02853117102703489</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02843333315169712</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02850903510398825</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2339,6 +3186,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!I1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2365,13 +3218,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02058504875406284</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.0500459981600736</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05018382352941177</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02061482820976492</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02045619116582187</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.0204784342152954</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2382,6 +3278,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!J1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2408,13 +3310,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02023002817773203</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.06185500408847346</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.020230635735023</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02023118260179608</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2425,6 +3370,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!K1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2451,13 +3402,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02445509246121618</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05578350900359923</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05578350900359923</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.05531762502066078</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02447694201114892</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02422426194815971</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2478,12 +3472,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -2493,8 +3487,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.07017999927062174"/>
-          <min val="0.01190503299558375"/>
+          <max val="0.06809875047508467"/>
+          <min val="0.01398628179112082"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -2522,15 +3516,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -2561,6 +3549,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!K1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>EURO</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2572,7 +3566,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="square"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -2587,13 +3581,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02445509246121618</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.05578350900359923</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.05578350900359923</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.05531762502066078</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02447694201114892</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02422426194815971</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2614,12 +3651,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -2662,11 +3699,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="DDEBF7"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2701,6 +3740,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!P1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>GRAM ALTIN</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2712,7 +3757,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -2727,13 +3772,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02750535420451208</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02743096651330836</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02742758272742561</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2754,12 +3842,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -2802,11 +3890,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="DDEBF7"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2841,6 +3931,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!L1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2867,13 +3963,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0369612266397948</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.07070208501600407</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.07070208501600407</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.03695931324756854</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03694474281650664</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03694167743897803</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2884,6 +4023,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!M1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2910,13 +4055,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.03623508807809576</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.08513100563182345</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.08513100563182345</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.0361799164241096</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03614461438957493</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03614164623338936</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2927,6 +4115,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!N1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2953,13 +4147,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02941852054231659</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.07842598844624503</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.07830678789731968</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.03018832255425111</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03025592817470824</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03076504592342247</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2970,6 +4207,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!O1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -2996,13 +4239,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.020191203292302</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.1458328933354655</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.1458328933354655</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02019119393575063</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02019154229953755</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02019234240196374</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3013,6 +4299,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!P1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3039,13 +4331,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02750535420451208</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.1264646520842799</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02743096651330836</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02742758272742561</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3066,12 +4401,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -3081,8 +4416,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1709612332154084"/>
-          <min val="0"/>
+          <max val="0.1646791482454227"/>
+          <min val="0.001344939025793405"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -3110,15 +4445,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -3149,6 +4478,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!U1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3161,7 +4496,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="70AD47"/>
@@ -3175,13 +4510,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$U$2:$U$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.03553378696044311</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02845400039156511</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3192,6 +4546,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!V1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3204,7 +4564,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="C00000"/>
@@ -3218,13 +4578,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$V$2:$V$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.04311562150687483</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.0284261405518742</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3235,6 +4614,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!W1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3247,7 +4632,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
@@ -3261,13 +4646,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$W$2:$W$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.03847709584999994</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02109574084424381</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3278,6 +4682,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!X1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3290,7 +4700,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="FFC000"/>
@@ -3304,13 +4714,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$X$2:$X$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.04104187506584386</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02023029953768716</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3321,6 +4750,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!Y1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3333,7 +4768,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="4472C4"/>
@@ -3347,13 +4782,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$Y$2:$Y$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.04760750668842017</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02422333905778681</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3374,12 +4828,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -3389,8 +4843,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05308294811856677"/>
-          <min val="0.01475485810754055"/>
+          <max val="0.05171408776103012"/>
+          <min val="0.0161237184650772"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -3418,15 +4872,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -3457,6 +4905,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!Z1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3469,7 +4923,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="70AD47"/>
@@ -3483,13 +4937,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$Z$2:$Z$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.03553642841103422</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02846019565754637</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3500,6 +4973,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AA1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3512,7 +4991,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="C00000"/>
@@ -3526,13 +5005,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AA$2:$AA$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.0432699268677014</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02847118412784268</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3543,6 +5041,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AB1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3555,7 +5059,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
@@ -3569,13 +5073,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AB$2:$AB$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.03535742466332828</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02046731269055863</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3586,6 +5109,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AC1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3598,7 +5127,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="FFC000"/>
@@ -3612,13 +5141,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AC$2:$AC$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.0514487601107881</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02023090916840954</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3629,6 +5177,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AD1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3641,7 +5195,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="4472C4"/>
@@ -3655,13 +5209,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AD$2:$AD$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.04783493387226885</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02435060197965432</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3682,12 +5255,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -3697,8 +5270,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05769233029926381"/>
-          <min val="0.01398733897993383"/>
+          <max val="0.05613143775214488"/>
+          <min val="0.01554823152705276"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -3726,15 +5299,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -3765,6 +5332,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AE1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Garanti BBVA</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3777,7 +5350,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="70AD47"/>
@@ -3791,13 +5364,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AE$2:$AE$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.05383117747984287</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.03694321012774233</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3808,6 +5400,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AF1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Akbank</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3820,7 +5418,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="C00000"/>
@@ -3834,13 +5432,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AF$2:$AF$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.06066925394146307</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.03614313031148214</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3851,6 +5468,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AG1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Yapıkredi</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3863,7 +5486,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
@@ -3877,13 +5500,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AG$2:$AG$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.0540849048600331</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.03051048704906535</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3894,6 +5536,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AH1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ziraat Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3906,7 +5554,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="FFC000"/>
@@ -3920,13 +5568,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AH$2:$AH$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.08301204597474589</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02019194235075064</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3937,6 +5604,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!AI1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>İş Bankası</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -3949,7 +5622,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="7"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="4472C4"/>
@@ -3963,13 +5636,32 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$T$2:$T$3</f>
-            </numRef>
+              <strCache>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>Ağustos 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Eylül 2026</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$AI$2:$AI$3</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="2"/>
+                <pt idx="0">
+                  <v>0.1017248276143379</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.02742927462036698</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3990,12 +5682,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -4005,8 +5697,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1180314046670554"/>
-          <min val="0.00388536529803318"/>
+          <max val="0.113954760403876"/>
+          <min val="0.007962009561212546"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -4034,15 +5726,9 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
@@ -4073,6 +5759,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!B1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>DOLAR</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -4099,13 +5791,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02853217795625066</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.04254051984515251</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.04254051984515251</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02852193019521676</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02845939792562611</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02844860285750411</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -4126,12 +5861,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -4174,11 +5909,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E2F0D9"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -4213,6 +5950,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!G1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>EURO</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -4224,7 +5967,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="square"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -4239,13 +5982,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.02853823251760947</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.04254615596583081</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.04254615596583081</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.02851516919486581</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.02847220959618916</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.02844818171890357</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -4266,12 +6052,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -4314,11 +6100,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E2F0D9"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -4353,6 +6141,12 @@
           <tx>
             <strRef>
               <f>'GRAFIK_VERILERI'!L1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>GRAM ALTIN</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -4364,7 +6158,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="6"/>
             <spPr>
               <a:solidFill>
@@ -4379,13 +6173,56 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>28.08</v>
+                </pt>
+                <pt idx="1">
+                  <v>29.08 Cmt</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.08 Paz</v>
+                </pt>
+                <pt idx="3">
+                  <v>31.08</v>
+                </pt>
+                <pt idx="4">
+                  <v>01.09</v>
+                </pt>
+                <pt idx="5">
+                  <v>02.09</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
+              <numCache>
+                <formatCode>0.00%</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>0.0369612266397948</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.07070208501600407</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.07070208501600407</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.03695931324756854</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.03694474281650664</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.03694167743897803</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -4406,12 +6243,12 @@
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="650"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="650"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
@@ -4454,11 +6291,13 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill/>
+    <a:solidFill>
+      <a:srgbClr val="E2F0D9"/>
+    </a:solidFill>
     <a:ln>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -4475,7 +6314,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -4492,12 +6331,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -4514,12 +6353,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -4538,10 +6377,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -4558,12 +6397,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -4580,12 +6419,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -4604,10 +6443,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -4624,12 +6463,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -4646,12 +6485,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -4670,10 +6509,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -4690,12 +6529,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="11" name="Chart 11"/>
@@ -4712,12 +6551,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="12" name="Chart 12"/>
@@ -4736,10 +6575,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="13" name="Chart 13"/>
@@ -4756,12 +6595,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="14" name="Chart 14"/>
@@ -4778,12 +6617,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="15" name="Chart 15"/>
@@ -4802,10 +6641,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="16" name="Chart 16"/>
@@ -4822,12 +6661,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="17" name="Chart 17"/>
@@ -4844,12 +6683,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="18" name="Chart 18"/>
@@ -4868,10 +6707,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="19" name="Chart 19"/>
@@ -4888,12 +6727,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="20" name="Chart 20"/>
@@ -4910,12 +6749,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6048000" cy="2951999"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="21" name="Chart 21"/>
@@ -5274,7 +7113,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -5371,7 +7210,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -5391,28 +7230,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9536</v>
+        <v>54.9918</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5203</v>
+        <v>56.5547</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5667</v>
+        <v>1.5629</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02850950620159553</v>
+        <v>0.02842060088958717</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6541</v>
+        <v>6532.97</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6777.5</v>
+        <v>6769.14</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.5</v>
+        <v>236.17</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03615655098608775</v>
+        <v>0.03615047979709076</v>
       </c>
     </row>
     <row r="3">
@@ -5420,7 +7259,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -5428,40 +7267,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>47.896</v>
+        <v>47.897</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>48.678</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.01632704192416903</v>
+        <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.42</v>
+        <v>55.445</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.336</v>
+        <v>56.355</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.916</v>
+        <v>0.91</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01652832912306027</v>
+        <v>0.0164126611957796</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6621.42</v>
+        <v>6607.29</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6757.92</v>
+        <v>6743.19</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>136.5</v>
+        <v>135.9</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02061491341736365</v>
+        <v>0.02056819058948525</v>
       </c>
     </row>
     <row r="4">
@@ -5469,7 +7308,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -5477,40 +7316,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.078</v>
+        <v>48.079</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.377</v>
+        <v>48.375</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.299</v>
+        <v>0.296</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006219060693040476</v>
+        <v>0.006156534037729569</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.446</v>
+        <v>55.49</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>55.966</v>
+        <v>56.006</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.52</v>
+        <v>0.516</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009378494390938932</v>
+        <v>0.009298972787889709</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6676.2</v>
+        <v>6673.09</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6744.35</v>
+        <v>6740.67</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>68.15000000000001</v>
+        <v>67.58</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01020790269914023</v>
+        <v>0.01012724240194573</v>
       </c>
     </row>
     <row r="5">
@@ -5518,7 +7357,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -5526,40 +7365,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.121</v>
+        <v>48.122</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.351</v>
+        <v>48.352</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0.23</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.004779618046175266</v>
+        <v>0.004779518723245085</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.577</v>
+        <v>55.594</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.955</v>
+        <v>55.972</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>0.378</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.00680137466937762</v>
+        <v>0.006799294887937547</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6593.74</v>
+        <v>6581.32</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6790</v>
+        <v>6775</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>196.26</v>
+        <v>193.68</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02976459490365104</v>
+        <v>0.02942874681674801</v>
       </c>
     </row>
     <row r="6">
@@ -5567,7 +7406,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -5575,40 +7414,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4522</v>
+        <v>47.4529</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7286</v>
+        <v>48.7293</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>1.2764</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02689864748104408</v>
+        <v>0.02689825068647016</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0116</v>
+        <v>55.0337</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.3766</v>
+        <v>56.3992</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.365</v>
+        <v>1.3655</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.0248129485417621</v>
+        <v>0.0248120696954775</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6605.19</v>
+        <v>6593.7</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6756.28</v>
+        <v>6744.8</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>151.09</v>
+        <v>151.1</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02287443661726612</v>
+        <v>0.02291581357962904</v>
       </c>
     </row>
     <row r="7">
@@ -5616,7 +7455,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -5627,37 +7466,37 @@
         <v>47.302</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.224</v>
+        <v>49.225</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.922</v>
+        <v>1.923</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04063253139402139</v>
+        <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.733</v>
+        <v>54.753</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.967</v>
+        <v>56.987</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>2.234</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04081632653061225</v>
+        <v>0.04080141727393933</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6602.94</v>
+        <v>6591.68</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6797.45</v>
+        <v>6785.81</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.51</v>
+        <v>194.13</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02945808988117414</v>
+        <v>0.02945076217292102</v>
       </c>
     </row>
     <row r="8">
@@ -5665,7 +7504,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -5673,40 +7512,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5543</v>
+        <v>47.555</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9544</v>
+        <v>48.9551</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944213246751608</v>
+        <v>0.02944169908526969</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0294</v>
+        <v>55.049</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6496</v>
+        <v>56.6746</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6202</v>
+        <v>1.6256</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02944244349384147</v>
+        <v>0.02953005504187179</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6620.33</v>
+        <v>6607.51</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6816.27</v>
+        <v>6803.13</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.94</v>
+        <v>195.62</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02959671194638334</v>
+        <v>0.02960570623426979</v>
       </c>
     </row>
     <row r="9">
@@ -5714,7 +7553,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -5722,40 +7561,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2238</v>
+        <v>48.2244</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2807</v>
+        <v>48.2813</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>0.0569</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001179915311526674</v>
+        <v>0.001179900631215733</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.7935</v>
+        <v>55.8136</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.8766</v>
+        <v>55.8969</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001489420810667909</v>
+        <v>0.001492467785629309</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6672.37</v>
+        <v>6660.19</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6701.25</v>
+        <v>6689.09</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004328297141795195</v>
+        <v>0.00433921554790479</v>
       </c>
     </row>
     <row r="10">
@@ -5763,7 +7602,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -5771,40 +7610,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2372</v>
+        <v>48.238</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2753</v>
+        <v>48.2763</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0383</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007898468401980215</v>
+        <v>0.0007939798499108587</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.7708</v>
+        <v>55.7909</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.8845</v>
+        <v>55.9004</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1137</v>
+        <v>0.1095</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002038701255854318</v>
+        <v>0.001962685670960676</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6668.78</v>
+        <v>6656.67</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6700.67</v>
+        <v>6688.4</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.89</v>
+        <v>31.73</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004781984111036801</v>
+        <v>0.004766647588058293</v>
       </c>
     </row>
     <row r="11">
@@ -5812,7 +7651,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -5820,40 +7659,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9236</v>
+        <v>47.9241</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1613</v>
+        <v>49.1615</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2377</v>
+        <v>1.2374</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02582652388384846</v>
+        <v>0.02581999453302201</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3446</v>
+        <v>55.3834</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6222</v>
+        <v>56.6615</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2776</v>
+        <v>1.2781</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02308445629745269</v>
+        <v>0.0230773119743461</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6616.79</v>
+        <v>6610.38</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6725.39</v>
+        <v>6718.58</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.6</v>
+        <v>108.2</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.0164127923056346</v>
+        <v>0.01636819668460815</v>
       </c>
     </row>
     <row r="12">
@@ -5861,7 +7700,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -5869,40 +7708,40 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>47.847</v>
+        <v>47.8475</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>48.697</v>
+        <v>48.6975</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>0.85</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.01776495914059398</v>
+        <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.2855</v>
+        <v>55.3004</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4416</v>
+        <v>56.4617</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1561</v>
+        <v>1.1613</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02091145056117789</v>
+        <v>0.02099984810236454</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6616.18</v>
+        <v>6605.45</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6771.27</v>
+        <v>6759.84</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>155.09</v>
+        <v>154.39</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02344101883564232</v>
+        <v>0.02337312370845287</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +7749,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -5918,40 +7757,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9974</v>
+        <v>47.998</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6044</v>
+        <v>48.605</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0.607</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264651835307746</v>
+        <v>0.01264636026501104</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5537</v>
+        <v>55.5757</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2145</v>
+        <v>56.2369</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6612</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01189479728622936</v>
+        <v>0.01189728604408042</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6689.72</v>
+        <v>6677.86</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6744.06</v>
+        <v>6732.18</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.34</v>
+        <v>54.32</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008122910973852419</v>
+        <v>0.008134342439044843</v>
       </c>
     </row>
     <row r="14">
@@ -5959,7 +7798,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -5979,28 +7818,28 @@
         <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.913</v>
+        <v>54.938</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.476</v>
+        <v>56.501</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02846320543405022</v>
+        <v>0.0284502530124868</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6585.26</v>
+        <v>6576.27</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6828.53</v>
+        <v>6819.21</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>243.27</v>
+        <v>242.94</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694159380191519</v>
+        <v>0.03694191388127312</v>
       </c>
     </row>
     <row r="15">
@@ -6008,7 +7847,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -6016,40 +7855,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9973</v>
+        <v>47.9982</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6044</v>
+        <v>48.6056</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6071</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264862815200022</v>
+        <v>0.01265464121571226</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5587</v>
+        <v>55.5771</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2198</v>
+        <v>56.2382</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.6611</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01189912650943957</v>
+        <v>0.01189518704646338</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6688.84</v>
+        <v>6677.96</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6743.19</v>
+        <v>6732.29</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.35</v>
+        <v>54.33</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008125474671243445</v>
+        <v>0.008135718093549526</v>
       </c>
     </row>
     <row r="16">
@@ -6057,7 +7896,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -6077,28 +7916,28 @@
         <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.3895</v>
+        <v>55.4159</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5235</v>
+        <v>56.5504</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.134</v>
+        <v>1.1345</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047319437799583</v>
+        <v>0.02047246367919676</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6620.19</v>
+        <v>6612.09</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6824.45</v>
+        <v>6815.15</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>204.26</v>
+        <v>203.06</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03085409935364393</v>
+        <v>0.03071041077783273</v>
       </c>
     </row>
     <row r="17">
@@ -6106,7 +7945,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -6114,40 +7953,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.161</v>
+        <v>48.162</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>48.243</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001702622453852702</v>
+        <v>0.001681823844524729</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.576</v>
+        <v>55.594</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.781</v>
+        <v>55.804</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003688642579530733</v>
+        <v>0.003777386048854193</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6612.89</v>
+        <v>6602.23</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6711.04</v>
+        <v>6701.08</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>98.15000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01484222480640083</v>
+        <v>0.01497221393377692</v>
       </c>
     </row>
     <row r="18">
@@ -6155,7 +7994,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -6163,40 +8002,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2175</v>
+        <v>48.2184</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3634</v>
+        <v>48.3646</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1459</v>
+        <v>0.1462</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.00302587234925079</v>
+        <v>0.003032037562424303</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.7839</v>
+        <v>55.8018</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9545</v>
+        <v>55.973</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1706</v>
+        <v>0.1712</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003058230062795896</v>
+        <v>0.003068001390636144</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6678.34</v>
+        <v>6666.77</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6725.45</v>
+        <v>6713.86</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.11</v>
+        <v>47.09</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007054148186525394</v>
+        <v>0.007063390517446979</v>
       </c>
     </row>
     <row r="19">
@@ -6204,7 +8043,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -6220,16 +8059,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6689.16</v>
+        <v>6682.86</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6885.09</v>
+        <v>6878.68</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.93</v>
+        <v>195.82</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02929067326839244</v>
+        <v>0.02930182586497397</v>
       </c>
     </row>
     <row r="20">
@@ -6237,7 +8076,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -6245,40 +8084,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8034</v>
+        <v>47.8045</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.69</v>
+        <v>48.6911</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0.8866000000000001</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01854679792650732</v>
+        <v>0.01854637115752701</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3181</v>
+        <v>55.2457</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.3773</v>
+        <v>56.3859</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0592</v>
+        <v>1.1402</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01914743998799669</v>
+        <v>0.02063871034306743</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6620.89</v>
+        <v>6610.02</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7066.08</v>
+        <v>7055.57</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.19</v>
+        <v>445.55</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06724020486671732</v>
+        <v>0.06740524234419866</v>
       </c>
     </row>
     <row r="21">
@@ -6286,7 +8125,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -6294,40 +8133,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.751</v>
+        <v>47.7513</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7543</v>
+        <v>48.7549</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0033</v>
+        <v>1.0036</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02101107830202509</v>
+        <v>0.02101722885031403</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.332</v>
+        <v>55.3574</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3418</v>
+        <v>56.3663</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0098</v>
+        <v>1.0089</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.0182498373454782</v>
+        <v>0.01822520566356079</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6590.78</v>
+        <v>6576.42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6842.75</v>
+        <v>6828.38</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.97</v>
+        <v>251.96</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03823067982848768</v>
+        <v>0.03831263818308441</v>
       </c>
     </row>
     <row r="22">
@@ -6335,7 +8174,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -6343,40 +8182,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6773</v>
+        <v>47.6786</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8332</v>
+        <v>48.8338</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1559</v>
+        <v>1.1552</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02424424201873848</v>
+        <v>0.02422889933848728</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.1627</v>
+        <v>55.188</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5097</v>
+        <v>56.5349</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.347</v>
+        <v>1.3469</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.0244186742128286</v>
+        <v>0.02440566789881858</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6612.14</v>
+        <v>6600.05</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6793.93</v>
+        <v>6781.04</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.79</v>
+        <v>180.99</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02749336825899028</v>
+        <v>0.02742251952636722</v>
       </c>
     </row>
     <row r="23">
@@ -6384,7 +8223,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -6433,7 +8272,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -6441,40 +8280,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.612</v>
+        <v>47.6128</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5982</v>
+        <v>48.5991</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9862</v>
+        <v>0.9863</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02071326556330337</v>
+        <v>0.02071501781033672</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.0966</v>
+        <v>55.2029</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2418</v>
+        <v>56.3452</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1452</v>
+        <v>1.1423</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02078531161632478</v>
+        <v>0.02069275346041603</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6569.34</v>
+        <v>6558.81</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6743.7</v>
+        <v>6732.89</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174.36</v>
+        <v>174.08</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02654147905269022</v>
+        <v>0.02654140004055613</v>
       </c>
     </row>
     <row r="25">
@@ -6482,7 +8321,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -6523,7 +8362,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -6531,40 +8370,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2261</v>
+        <v>48.2272</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2795</v>
+        <v>48.2801</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0534</v>
+        <v>0.0529</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001107284229908701</v>
+        <v>0.001096891380797558</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.7892</v>
+        <v>55.8142</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.8696</v>
+        <v>55.8918</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0804</v>
+        <v>0.0776</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001441139145210901</v>
+        <v>0.001390327192721565</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6667.06</v>
+        <v>6655.48</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6695.93</v>
+        <v>6684.33</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.87</v>
+        <v>28.85</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004330244515573582</v>
+        <v>0.004334773750353092</v>
       </c>
     </row>
     <row r="27">
@@ -6572,7 +8411,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -6580,40 +8419,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.186</v>
+        <v>48.163</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.298</v>
+        <v>48.275</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>0.112</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002324326567882787</v>
+        <v>0.00232543653842161</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.59</v>
+        <v>55.613</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.849</v>
+        <v>55.86</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.259</v>
+        <v>0.247</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004659111350962403</v>
+        <v>0.004441407584557567</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6622</v>
+        <v>6614</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6703</v>
+        <v>6690</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.01223195409241921</v>
+        <v>0.01149077713940127</v>
       </c>
     </row>
     <row r="28">
@@ -6621,7 +8460,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -6629,40 +8468,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7605</v>
+        <v>47.7615</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7605</v>
+        <v>48.7615</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093780425246804</v>
+        <v>0.02093736586999989</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.295</v>
+        <v>55.323</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.385</v>
+        <v>56.413</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01971245139705217</v>
+        <v>0.01970247455850189</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6662.96</v>
+        <v>6662.49</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6762.96</v>
+        <v>6762.49</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01500834463961963</v>
+        <v>0.0150094033912246</v>
       </c>
     </row>
     <row r="29">
@@ -6670,7 +8509,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -6686,16 +8525,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6687.89</v>
+        <v>6682.33</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6870.05</v>
+        <v>6864.41</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>182.16</v>
+        <v>182.08</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02723729008700801</v>
+        <v>0.0272479808689484</v>
       </c>
     </row>
     <row r="30">
@@ -6703,7 +8542,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -6711,40 +8550,40 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>47.687</v>
+        <v>47.6875</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>48.907</v>
+        <v>48.9075</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.0255834923564074</v>
+        <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0676</v>
+        <v>55.0871</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7239</v>
+        <v>56.7391</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6563</v>
+        <v>1.652</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03007757737762314</v>
+        <v>0.02998887216789412</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6591.35</v>
+        <v>6579.39</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6789.23</v>
+        <v>6776.91</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>197.88</v>
+        <v>197.52</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03002116410143597</v>
+        <v>0.0300210201857619</v>
       </c>
     </row>
     <row r="31">
@@ -6752,7 +8591,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -6760,40 +8599,40 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1338</v>
+        <v>48.1513</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.3752</v>
+        <v>48.3928</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2414</v>
+        <v>0.2415</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.005015186833368651</v>
+        <v>0.005015440912291049</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.645</v>
+        <v>55.6838</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>55.9802</v>
+        <v>56.0193</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3352</v>
+        <v>0.3355</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006023901518555126</v>
+        <v>0.006025091678369652</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6604.8</v>
+        <v>6591.43</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6738.56</v>
+        <v>6724.93</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>133.76</v>
+        <v>133.5</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025193798449612</v>
+        <v>0.02025357168323111</v>
       </c>
     </row>
     <row r="32">
@@ -6801,7 +8640,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -6812,37 +8651,37 @@
         <v>47.8519</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6541</v>
+        <v>48.654</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8022</v>
+        <v>0.8021</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676422461804025</v>
+        <v>0.01676213483686123</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.397</v>
+        <v>55.4313</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2478</v>
+        <v>56.282</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8508</v>
+        <v>0.8507</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01535823239525606</v>
+        <v>0.01534692493230359</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6612.92</v>
+        <v>6608.49</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6809.26</v>
+        <v>6804.84</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.34</v>
+        <v>196.35</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02969036371224814</v>
+        <v>0.02971177984683339</v>
       </c>
     </row>
     <row r="33">
@@ -6850,7 +8689,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -6858,40 +8697,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1531</v>
+        <v>48.1538</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3562</v>
+        <v>48.3569</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2031</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004217796985033155</v>
+        <v>0.004217735671951123</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7116</v>
+        <v>55.7318</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.936</v>
+        <v>55.9564</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2244</v>
+        <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004027886472476109</v>
+        <v>0.004030015179843464</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6652.04</v>
+        <v>6645.43</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6705.47</v>
+        <v>6698.81</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.43</v>
+        <v>53.38</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008032122476713911</v>
+        <v>0.008032587808463861</v>
       </c>
     </row>
     <row r="34">
@@ -6899,7 +8738,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -6907,40 +8746,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8942</v>
+        <v>47.8945</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8552</v>
+        <v>48.8555</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006506006990408</v>
+        <v>0.02006493438703818</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4462</v>
+        <v>55.4714</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5482</v>
+        <v>56.5735</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.102</v>
+        <v>1.1021</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01987512219051982</v>
+        <v>0.01986789588869219</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6622.55</v>
+        <v>6614.34</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6767.15</v>
+        <v>6758.94</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02183448973582683</v>
+        <v>0.02186159163272526</v>
       </c>
     </row>
     <row r="35">
@@ -6948,7 +8787,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -6956,28 +8795,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.178</v>
+        <v>48.186</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.248</v>
+        <v>48.24</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.001452945327742953</v>
+        <v>0.001120657452372058</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.617</v>
+        <v>55.64</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.78</v>
+        <v>55.785</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.163</v>
+        <v>0.145</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002930758581009403</v>
+        <v>0.002606038820992092</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -6989,7 +8828,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -7009,28 +8848,28 @@
         <v>0.02098635886673662</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.14</v>
+        <v>55.17</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.28</v>
+        <v>56.31</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02067464635473341</v>
+        <v>0.02066340402392605</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6587.03</v>
+        <v>6581.19</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6789.52</v>
+        <v>6783.18</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>202.49</v>
+        <v>201.99</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03074071318940403</v>
+        <v>0.03069201770500472</v>
       </c>
     </row>
     <row r="37">
@@ -7038,7 +8877,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -7046,40 +8885,40 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.89</v>
+        <v>47.8905</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8588</v>
+        <v>48.8593</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.9688</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02022969304656505</v>
+        <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4011</v>
+        <v>55.4352</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5219</v>
+        <v>56.5567</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1208</v>
+        <v>1.1215</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023064523989596</v>
+        <v>0.02023082806592201</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6646.34</v>
+        <v>6647.74</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6780.54</v>
+        <v>6781.97</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.2</v>
+        <v>134.23</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.0201915640788765</v>
+        <v>0.02019182459001104</v>
       </c>
     </row>
     <row r="38">
@@ -7087,7 +8926,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -7095,40 +8934,40 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9378</v>
+        <v>47.9384</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.59</v>
+        <v>48.5906</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0.6522</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360512998093363</v>
+        <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4081</v>
+        <v>55.4338</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2181</v>
+        <v>56.2441</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8103</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461880122220397</v>
+        <v>0.01461743557179915</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6625.2</v>
+        <v>6614.38</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6758.97</v>
+        <v>6747.93</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.77</v>
+        <v>133.55</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019108857091107</v>
+        <v>0.02019085689059292</v>
       </c>
     </row>
     <row r="39">
@@ -7136,7 +8975,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4255671296296296</v>
+        <v>0.4528240740740741</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -7144,40 +8983,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7679</v>
+        <v>47.7684</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7655</v>
+        <v>48.7652</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9976</v>
+        <v>0.9968</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02088431771126635</v>
+        <v>0.02086735163832157</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2328</v>
+        <v>55.2611</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.442</v>
+        <v>56.4695</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2092</v>
+        <v>1.2084</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02189278834315841</v>
+        <v>0.02186710000343823</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6645.46</v>
+        <v>6632.7</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6856.51</v>
+        <v>6843.25</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>211.05</v>
+        <v>210.55</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.0317585238644127</v>
+        <v>0.03174423688693895</v>
       </c>
     </row>
   </sheetData>
@@ -7199,7 +9038,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -7209,7 +9048,7 @@
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -7399,7 +9238,7 @@
       </c>
       <c r="D4" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E4" s="12" t="n">
@@ -7549,7 +9388,7 @@
       </c>
       <c r="D7" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -7699,7 +9538,7 @@
       </c>
       <c r="D10" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -7849,7 +9688,7 @@
       </c>
       <c r="D13" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -7999,7 +9838,7 @@
       </c>
       <c r="D16" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
@@ -8149,7 +9988,7 @@
       </c>
       <c r="D19" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
@@ -8299,7 +10138,7 @@
       </c>
       <c r="D22" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
@@ -8449,7 +10288,7 @@
       </c>
       <c r="D25" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
@@ -8599,7 +10438,7 @@
       </c>
       <c r="D28" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
@@ -8749,7 +10588,7 @@
       </c>
       <c r="D31" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
@@ -8899,7 +10738,7 @@
       </c>
       <c r="D34" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
@@ -9049,7 +10888,7 @@
       </c>
       <c r="D37" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
@@ -9199,7 +11038,7 @@
       </c>
       <c r="D40" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
@@ -9349,7 +11188,7 @@
       </c>
       <c r="D43" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
@@ -9499,7 +11338,7 @@
       </c>
       <c r="D46" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
@@ -9649,7 +11488,7 @@
       </c>
       <c r="D49" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
@@ -9799,7 +11638,7 @@
       </c>
       <c r="D52" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
@@ -9849,7 +11688,7 @@
       </c>
       <c r="D53" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
@@ -9999,7 +11838,7 @@
       </c>
       <c r="D56" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
@@ -10149,7 +11988,7 @@
       </c>
       <c r="D59" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
@@ -10299,7 +12138,7 @@
       </c>
       <c r="D62" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
@@ -10449,7 +12288,7 @@
       </c>
       <c r="D65" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
@@ -10599,7 +12438,7 @@
       </c>
       <c r="D68" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
@@ -10849,7 +12688,7 @@
       </c>
       <c r="D73" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
@@ -10999,7 +12838,7 @@
       </c>
       <c r="D76" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
@@ -11149,7 +12988,7 @@
       </c>
       <c r="D79" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
@@ -11199,7 +13038,7 @@
       </c>
       <c r="D80" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
@@ -11349,7 +13188,7 @@
       </c>
       <c r="D83" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
@@ -11499,7 +13338,7 @@
       </c>
       <c r="D86" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
@@ -11649,7 +13488,7 @@
       </c>
       <c r="D89" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
@@ -11799,7 +13638,7 @@
       </c>
       <c r="D92" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
@@ -11949,7 +13788,7 @@
       </c>
       <c r="D95" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
@@ -12199,7 +14038,7 @@
       </c>
       <c r="D100" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
@@ -12349,7 +14188,7 @@
       </c>
       <c r="D103" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
@@ -12499,7 +14338,7 @@
       </c>
       <c r="D106" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
@@ -12649,7 +14488,7 @@
       </c>
       <c r="D109" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
@@ -12799,7 +14638,7 @@
       </c>
       <c r="D112" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
@@ -12949,7 +14788,7 @@
       </c>
       <c r="D115" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -13099,7 +14938,7 @@
       </c>
       <c r="D118" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
@@ -13249,7 +15088,7 @@
       </c>
       <c r="D121" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -13399,7 +15238,7 @@
       </c>
       <c r="D124" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
@@ -13549,7 +15388,7 @@
       </c>
       <c r="D127" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -13699,7 +15538,7 @@
       </c>
       <c r="D130" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
@@ -13849,7 +15688,7 @@
       </c>
       <c r="D133" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -13999,7 +15838,7 @@
       </c>
       <c r="D136" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
@@ -14149,7 +15988,7 @@
       </c>
       <c r="D139" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -14299,7 +16138,7 @@
       </c>
       <c r="D142" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
@@ -14449,7 +16288,7 @@
       </c>
       <c r="D145" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -14599,7 +16438,7 @@
       </c>
       <c r="D148" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
@@ -14749,7 +16588,7 @@
       </c>
       <c r="D151" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -14899,7 +16738,7 @@
       </c>
       <c r="D154" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
@@ -15049,7 +16888,7 @@
       </c>
       <c r="D157" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -15199,7 +17038,7 @@
       </c>
       <c r="D160" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
@@ -15249,7 +17088,7 @@
       </c>
       <c r="D161" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -15399,7 +17238,7 @@
       </c>
       <c r="D164" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
@@ -15549,7 +17388,7 @@
       </c>
       <c r="D167" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -15699,7 +17538,7 @@
       </c>
       <c r="D170" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
@@ -15849,7 +17688,7 @@
       </c>
       <c r="D173" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -15999,7 +17838,7 @@
       </c>
       <c r="D176" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
@@ -16249,7 +18088,7 @@
       </c>
       <c r="D181" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E181" s="12" t="n">
@@ -16399,7 +18238,7 @@
       </c>
       <c r="D184" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
@@ -16549,7 +18388,7 @@
       </c>
       <c r="D187" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E187" s="12" t="n">
@@ -16599,7 +18438,7 @@
       </c>
       <c r="D188" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E188" s="12" t="n">
@@ -16749,7 +18588,7 @@
       </c>
       <c r="D191" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E191" s="12" t="n">
@@ -16899,7 +18738,7 @@
       </c>
       <c r="D194" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E194" s="12" t="n">
@@ -17049,7 +18888,7 @@
       </c>
       <c r="D197" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E197" s="12" t="n">
@@ -17199,7 +19038,7 @@
       </c>
       <c r="D200" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E200" s="12" t="n">
@@ -17349,7 +19188,7 @@
       </c>
       <c r="D203" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E203" s="12" t="n">
@@ -17599,7 +19438,7 @@
       </c>
       <c r="D208" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E208" s="12" t="n">
@@ -17749,7 +19588,7 @@
       </c>
       <c r="D211" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E211" s="12" t="n">
@@ -17899,7 +19738,7 @@
       </c>
       <c r="D214" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E214" s="12" t="n">
@@ -18049,7 +19888,7 @@
       </c>
       <c r="D217" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E217" s="12" t="n">
@@ -18199,7 +20038,7 @@
       </c>
       <c r="D220" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E220" s="12" t="n">
@@ -18349,7 +20188,7 @@
       </c>
       <c r="D223" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E223" s="12" t="n">
@@ -18499,7 +20338,7 @@
       </c>
       <c r="D226" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E226" s="12" t="n">
@@ -18649,7 +20488,7 @@
       </c>
       <c r="D229" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E229" s="12" t="n">
@@ -18799,7 +20638,7 @@
       </c>
       <c r="D232" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E232" s="12" t="n">
@@ -18949,7 +20788,7 @@
       </c>
       <c r="D235" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E235" s="12" t="n">
@@ -19099,7 +20938,7 @@
       </c>
       <c r="D238" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E238" s="12" t="n">
@@ -19249,7 +21088,7 @@
       </c>
       <c r="D241" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E241" s="12" t="n">
@@ -19399,7 +21238,7 @@
       </c>
       <c r="D244" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E244" s="12" t="n">
@@ -19549,7 +21388,7 @@
       </c>
       <c r="D247" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E247" s="12" t="n">
@@ -19699,7 +21538,7 @@
       </c>
       <c r="D250" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E250" s="12" t="n">
@@ -19849,7 +21688,7 @@
       </c>
       <c r="D253" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E253" s="12" t="n">
@@ -19999,7 +21838,7 @@
       </c>
       <c r="D256" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E256" s="12" t="n">
@@ -20149,7 +21988,7 @@
       </c>
       <c r="D259" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E259" s="12" t="n">
@@ -20299,7 +22138,7 @@
       </c>
       <c r="D262" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E262" s="12" t="n">
@@ -20449,7 +22288,7 @@
       </c>
       <c r="D265" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E265" s="12" t="n">
@@ -20599,7 +22438,7 @@
       </c>
       <c r="D268" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E268" s="12" t="n">
@@ -20649,7 +22488,7 @@
       </c>
       <c r="D269" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E269" s="12" t="n">
@@ -20799,7 +22638,7 @@
       </c>
       <c r="D272" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E272" s="12" t="n">
@@ -20949,7 +22788,7 @@
       </c>
       <c r="D275" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E275" s="12" t="n">
@@ -21099,7 +22938,7 @@
       </c>
       <c r="D278" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E278" s="12" t="n">
@@ -21249,7 +23088,7 @@
       </c>
       <c r="D281" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E281" s="12" t="n">
@@ -21399,7 +23238,7 @@
       </c>
       <c r="D284" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E284" s="12" t="n">
@@ -21649,7 +23488,7 @@
       </c>
       <c r="D289" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E289" s="12" t="n">
@@ -21799,7 +23638,7 @@
       </c>
       <c r="D292" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E292" s="12" t="n">
@@ -21949,7 +23788,7 @@
       </c>
       <c r="D295" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E295" s="12" t="n">
@@ -21999,7 +23838,7 @@
       </c>
       <c r="D296" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E296" s="12" t="n">
@@ -22149,7 +23988,7 @@
       </c>
       <c r="D299" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E299" s="12" t="n">
@@ -22299,7 +24138,7 @@
       </c>
       <c r="D302" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E302" s="12" t="n">
@@ -22449,7 +24288,7 @@
       </c>
       <c r="D305" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E305" s="12" t="n">
@@ -22599,7 +24438,7 @@
       </c>
       <c r="D308" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E308" s="12" t="n">
@@ -22749,7 +24588,7 @@
       </c>
       <c r="D311" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E311" s="12" t="n">
@@ -22999,7 +24838,7 @@
       </c>
       <c r="D316" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E316" s="12" t="n">
@@ -23149,7 +24988,7 @@
       </c>
       <c r="D319" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E319" s="12" t="n">
@@ -23299,7 +25138,7 @@
       </c>
       <c r="D322" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E322" s="12" t="n">
@@ -23449,7 +25288,7 @@
       </c>
       <c r="D325" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E325" s="12" t="n">
@@ -23599,7 +25438,7 @@
       </c>
       <c r="D328" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E328" s="12" t="n">
@@ -23749,7 +25588,7 @@
       </c>
       <c r="D331" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E331" s="12" t="n">
@@ -23899,7 +25738,7 @@
       </c>
       <c r="D334" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E334" s="12" t="n">
@@ -24049,7 +25888,7 @@
       </c>
       <c r="D337" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E337" s="12" t="n">
@@ -24199,7 +26038,7 @@
       </c>
       <c r="D340" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E340" s="12" t="n">
@@ -24349,7 +26188,7 @@
       </c>
       <c r="D343" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E343" s="12" t="n">
@@ -24499,7 +26338,7 @@
       </c>
       <c r="D346" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E346" s="12" t="n">
@@ -24649,7 +26488,7 @@
       </c>
       <c r="D349" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E349" s="12" t="n">
@@ -24799,7 +26638,7 @@
       </c>
       <c r="D352" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E352" s="12" t="n">
@@ -24949,7 +26788,7 @@
       </c>
       <c r="D355" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E355" s="12" t="n">
@@ -25099,7 +26938,7 @@
       </c>
       <c r="D358" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E358" s="12" t="n">
@@ -25249,7 +27088,7 @@
       </c>
       <c r="D361" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E361" s="12" t="n">
@@ -25399,7 +27238,7 @@
       </c>
       <c r="D364" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E364" s="12" t="n">
@@ -25549,7 +27388,7 @@
       </c>
       <c r="D367" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E367" s="12" t="n">
@@ -25699,7 +27538,7 @@
       </c>
       <c r="D370" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E370" s="12" t="n">
@@ -25849,7 +27688,7 @@
       </c>
       <c r="D373" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E373" s="12" t="n">
@@ -25999,7 +27838,7 @@
       </c>
       <c r="D376" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E376" s="12" t="n">
@@ -26049,7 +27888,7 @@
       </c>
       <c r="D377" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E377" s="12" t="n">
@@ -26199,7 +28038,7 @@
       </c>
       <c r="D380" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E380" s="12" t="n">
@@ -26349,7 +28188,7 @@
       </c>
       <c r="D383" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E383" s="12" t="n">
@@ -26499,7 +28338,7 @@
       </c>
       <c r="D386" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E386" s="12" t="n">
@@ -26649,7 +28488,7 @@
       </c>
       <c r="D389" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E389" s="12" t="n">
@@ -26799,7 +28638,7 @@
       </c>
       <c r="D392" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E392" s="12" t="n">
@@ -27049,7 +28888,7 @@
       </c>
       <c r="D397" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E397" s="12" t="n">
@@ -27199,7 +29038,7 @@
       </c>
       <c r="D400" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E400" s="12" t="n">
@@ -27349,7 +29188,7 @@
       </c>
       <c r="D403" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E403" s="12" t="n">
@@ -27399,7 +29238,7 @@
       </c>
       <c r="D404" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E404" s="12" t="n">
@@ -27549,7 +29388,7 @@
       </c>
       <c r="D407" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E407" s="12" t="n">
@@ -27699,7 +29538,7 @@
       </c>
       <c r="D410" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E410" s="12" t="n">
@@ -27849,7 +29688,7 @@
       </c>
       <c r="D413" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E413" s="12" t="n">
@@ -27999,7 +29838,7 @@
       </c>
       <c r="D416" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E416" s="12" t="n">
@@ -28149,7 +29988,7 @@
       </c>
       <c r="D419" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E419" s="12" t="n">
@@ -28399,7 +30238,7 @@
       </c>
       <c r="D424" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E424" s="12" t="n">
@@ -28549,7 +30388,7 @@
       </c>
       <c r="D427" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E427" s="12" t="n">
@@ -28699,7 +30538,7 @@
       </c>
       <c r="D430" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E430" s="12" t="n">
@@ -28849,7 +30688,7 @@
       </c>
       <c r="D433" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E433" s="12" t="n">
@@ -28999,7 +30838,7 @@
       </c>
       <c r="D436" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E436" s="12" t="n">
@@ -29149,7 +30988,7 @@
       </c>
       <c r="D439" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E439" s="12" t="n">
@@ -29299,7 +31138,7 @@
       </c>
       <c r="D442" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E442" s="12" t="n">
@@ -29449,7 +31288,7 @@
       </c>
       <c r="D445" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E445" s="12" t="n">
@@ -29599,7 +31438,7 @@
       </c>
       <c r="D448" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E448" s="12" t="n">
@@ -29749,7 +31588,7 @@
       </c>
       <c r="D451" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E451" s="12" t="n">
@@ -29899,7 +31738,7 @@
       </c>
       <c r="D454" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E454" s="12" t="n">
@@ -30049,7 +31888,7 @@
       </c>
       <c r="D457" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E457" s="12" t="n">
@@ -30199,7 +32038,7 @@
       </c>
       <c r="D460" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E460" s="12" t="n">
@@ -30349,7 +32188,7 @@
       </c>
       <c r="D463" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E463" s="12" t="n">
@@ -30499,7 +32338,7 @@
       </c>
       <c r="D466" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E466" s="12" t="n">
@@ -30649,7 +32488,7 @@
       </c>
       <c r="D469" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E469" s="12" t="n">
@@ -30799,7 +32638,7 @@
       </c>
       <c r="D472" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E472" s="12" t="n">
@@ -30949,7 +32788,7 @@
       </c>
       <c r="D475" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E475" s="12" t="n">
@@ -31099,7 +32938,7 @@
       </c>
       <c r="D478" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E478" s="12" t="n">
@@ -31249,7 +33088,7 @@
       </c>
       <c r="D481" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E481" s="12" t="n">
@@ -31399,7 +33238,7 @@
       </c>
       <c r="D484" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E484" s="12" t="n">
@@ -31449,7 +33288,7 @@
       </c>
       <c r="D485" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E485" s="12" t="n">
@@ -31599,7 +33438,7 @@
       </c>
       <c r="D488" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E488" s="12" t="n">
@@ -31749,7 +33588,7 @@
       </c>
       <c r="D491" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E491" s="12" t="n">
@@ -31899,7 +33738,7 @@
       </c>
       <c r="D494" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E494" s="12" t="n">
@@ -32049,7 +33888,7 @@
       </c>
       <c r="D497" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E497" s="12" t="n">
@@ -32199,7 +34038,7 @@
       </c>
       <c r="D500" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E500" s="12" t="n">
@@ -32449,7 +34288,7 @@
       </c>
       <c r="D505" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E505" s="12" t="n">
@@ -32599,7 +34438,7 @@
       </c>
       <c r="D508" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E508" s="12" t="n">
@@ -32749,7 +34588,7 @@
       </c>
       <c r="D511" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E511" s="12" t="n">
@@ -32799,7 +34638,7 @@
       </c>
       <c r="D512" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E512" s="12" t="n">
@@ -32949,7 +34788,7 @@
       </c>
       <c r="D515" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E515" s="12" t="n">
@@ -33099,7 +34938,7 @@
       </c>
       <c r="D518" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E518" s="12" t="n">
@@ -33249,7 +35088,7 @@
       </c>
       <c r="D521" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E521" s="12" t="n">
@@ -33399,7 +35238,7 @@
       </c>
       <c r="D524" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E524" s="12" t="n">
@@ -33549,7 +35388,7 @@
       </c>
       <c r="D527" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E527" s="12" t="n">
@@ -33799,7 +35638,7 @@
       </c>
       <c r="D532" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E532" s="12" t="n">
@@ -33949,7 +35788,7 @@
       </c>
       <c r="D535" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E535" s="12" t="n">
@@ -34099,7 +35938,7 @@
       </c>
       <c r="D538" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E538" s="12" t="n">
@@ -34249,7 +36088,7 @@
       </c>
       <c r="D541" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E541" s="12" t="n">
@@ -34399,7 +36238,7 @@
       </c>
       <c r="D544" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E544" s="12" t="n">
@@ -34549,7 +36388,7 @@
       </c>
       <c r="D547" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E547" s="12" t="n">
@@ -34699,7 +36538,7 @@
       </c>
       <c r="D550" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E550" s="12" t="n">
@@ -34849,7 +36688,7 @@
       </c>
       <c r="D553" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E553" s="12" t="n">
@@ -34999,7 +36838,7 @@
       </c>
       <c r="D556" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E556" s="12" t="n">
@@ -35149,7 +36988,7 @@
       </c>
       <c r="D559" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E559" s="12" t="n">
@@ -35299,7 +37138,7 @@
       </c>
       <c r="D562" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E562" s="12" t="n">
@@ -35449,7 +37288,7 @@
       </c>
       <c r="D565" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E565" s="12" t="n">
@@ -35599,7 +37438,7 @@
       </c>
       <c r="D568" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E568" s="12" t="n">
@@ -35749,7 +37588,7 @@
       </c>
       <c r="D571" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E571" s="12" t="n">
@@ -35899,7 +37738,7 @@
       </c>
       <c r="D574" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E574" s="12" t="n">
@@ -36049,7 +37888,7 @@
       </c>
       <c r="D577" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E577" s="12" t="n">
@@ -36199,7 +38038,7 @@
       </c>
       <c r="D580" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E580" s="12" t="n">
@@ -36349,7 +38188,7 @@
       </c>
       <c r="D583" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E583" s="12" t="n">
@@ -36499,7 +38338,7 @@
       </c>
       <c r="D586" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E586" s="12" t="n">
@@ -36649,7 +38488,7 @@
       </c>
       <c r="D589" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E589" s="12" t="n">
@@ -36799,7 +38638,7 @@
       </c>
       <c r="D592" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E592" s="12" t="n">
@@ -36849,7 +38688,7 @@
       </c>
       <c r="D593" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E593" s="12" t="n">
@@ -36999,7 +38838,7 @@
       </c>
       <c r="D596" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E596" s="12" t="n">
@@ -37149,7 +38988,7 @@
       </c>
       <c r="D599" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E599" s="12" t="n">
@@ -37299,7 +39138,7 @@
       </c>
       <c r="D602" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E602" s="12" t="n">
@@ -37449,7 +39288,7 @@
       </c>
       <c r="D605" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E605" s="12" t="n">
@@ -37599,7 +39438,7 @@
       </c>
       <c r="D608" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E608" s="12" t="n">
@@ -37849,7 +39688,7 @@
       </c>
       <c r="D613" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E613" s="12" t="n">
@@ -37999,7 +39838,7 @@
       </c>
       <c r="D616" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E616" s="12" t="n">
@@ -38149,7 +39988,7 @@
       </c>
       <c r="D619" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E619" s="12" t="n">
@@ -38199,7 +40038,7 @@
       </c>
       <c r="D620" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E620" s="12" t="n">
@@ -38349,7 +40188,7 @@
       </c>
       <c r="D623" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E623" s="12" t="n">
@@ -38499,7 +40338,7 @@
       </c>
       <c r="D626" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E626" s="12" t="n">
@@ -38649,7 +40488,7 @@
       </c>
       <c r="D629" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E629" s="12" t="n">
@@ -38799,7 +40638,7 @@
       </c>
       <c r="D632" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E632" s="12" t="n">
@@ -38949,7 +40788,7 @@
       </c>
       <c r="D635" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E635" s="12" t="n">
@@ -39199,7 +41038,7 @@
       </c>
       <c r="D640" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E640" s="12" t="n">
@@ -39349,7 +41188,7 @@
       </c>
       <c r="D643" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E643" s="12" t="n">
@@ -39499,7 +41338,7 @@
       </c>
       <c r="D646" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E646" s="12" t="n">
@@ -39649,7 +41488,7 @@
       </c>
       <c r="D649" s="57" t="inlineStr">
         <is>
-          <t>GRAM ALTIN</t>
+          <t>GRAM_ALTIN</t>
         </is>
       </c>
       <c r="E649" s="12" t="n">
@@ -40352,15 +42191,15 @@
   <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="3" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -40370,15 +42209,17 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="3" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Döviz ve Altın Kur Takip Özeti</t>
@@ -40408,9 +42249,11 @@
           <t>Veri tarihi</t>
         </is>
       </c>
-      <c r="C4" s="62" t="n">
+      <c r="B4" s="62" t="n"/>
+      <c r="C4" s="63" t="n">
         <v>46267</v>
       </c>
+      <c r="D4" s="62" t="n"/>
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Ay</t>
@@ -40473,10 +42316,12 @@
           <t>Çekim saati</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
-        <v>0.4255671296296296</v>
-      </c>
-      <c r="F5" s="64" t="inlineStr">
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="64" t="n">
+        <v>0.4528240740740741</v>
+      </c>
+      <c r="D5" s="62" t="n"/>
+      <c r="F5" s="62" t="inlineStr">
         <is>
           <t>Ağustos 2026</t>
         </is>
@@ -40500,11 +42345,11 @@
           <t>DOLAR</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="62" t="n">
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.02022969304656505</v>
+        <v>0.02022948183877804</v>
       </c>
       <c r="O5" s="71" t="inlineStr">
         <is>
@@ -40512,10 +42357,10 @@
         </is>
       </c>
       <c r="P5" s="72" t="n">
-        <v>47.89</v>
+        <v>47.8905</v>
       </c>
       <c r="Q5" s="72" t="n">
-        <v>48.8588</v>
+        <v>48.8593</v>
       </c>
     </row>
     <row r="6">
@@ -40524,10 +42369,12 @@
           <t>Sağlayıcı sayısı</t>
         </is>
       </c>
+      <c r="B6" s="62" t="n"/>
       <c r="C6" s="73" t="n">
         <v>38</v>
       </c>
-      <c r="F6" s="64" t="inlineStr">
+      <c r="D6" s="62" t="n"/>
+      <c r="F6" s="62" t="inlineStr">
         <is>
           <t>Ağustos 2026</t>
         </is>
@@ -40551,11 +42398,11 @@
           <t>EURO</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="62" t="n">
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023064523989596</v>
+        <v>0.02023082806592201</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -40563,10 +42410,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4011</v>
+        <v>55.4352</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5219</v>
+        <v>56.5567</v>
       </c>
     </row>
     <row r="7">
@@ -40575,10 +42422,12 @@
           <t>Ürün kaydı</t>
         </is>
       </c>
+      <c r="B7" s="62" t="n"/>
       <c r="C7" s="73" t="n">
         <v>108</v>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="D7" s="62" t="n"/>
+      <c r="F7" s="62" t="inlineStr">
         <is>
           <t>Ağustos 2026</t>
         </is>
@@ -40602,11 +42451,11 @@
           <t>GRAM ALTIN</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="62" t="n">
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.0201915640788765</v>
+        <v>0.02019182459001104</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -40614,10 +42463,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6646.34</v>
+        <v>6647.74</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6780.54</v>
+        <v>6781.97</v>
       </c>
     </row>
     <row r="8">
@@ -40626,10 +42475,12 @@
           <t>Hatalı kayıt</t>
         </is>
       </c>
+      <c r="B8" s="62" t="n"/>
       <c r="C8" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="64" t="inlineStr">
+      <c r="D8" s="62" t="n"/>
+      <c r="F8" s="62" t="inlineStr">
         <is>
           <t>Ağustos 2026</t>
         </is>
@@ -40655,10 +42506,12 @@
           <t>Kontrol gereken</t>
         </is>
       </c>
+      <c r="B9" s="62" t="n"/>
       <c r="C9" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="64" t="inlineStr">
+      <c r="D9" s="62" t="n"/>
+      <c r="F9" s="62" t="inlineStr">
         <is>
           <t>Ağustos 2026</t>
         </is>
@@ -40679,7 +42532,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="F10" s="64" t="inlineStr">
+      <c r="F10" s="62" t="inlineStr">
         <is>
           <t>Eylül 2026</t>
         </is>
@@ -40700,7 +42553,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="64" t="inlineStr">
+      <c r="F11" s="62" t="inlineStr">
         <is>
           <t>Eylül 2026</t>
         </is>
@@ -40721,7 +42574,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="F12" s="64" t="inlineStr">
+      <c r="F12" s="62" t="inlineStr">
         <is>
           <t>Eylül 2026</t>
         </is>
@@ -40742,7 +42595,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="64" t="inlineStr">
+      <c r="F13" s="62" t="inlineStr">
         <is>
           <t>Eylül 2026</t>
         </is>
@@ -40763,7 +42616,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="F14" s="64" t="inlineStr">
+      <c r="F14" s="62" t="inlineStr">
         <is>
           <t>Eylül 2026</t>
         </is>
@@ -40783,6 +42636,179 @@
         <v>0.02742927462036698</v>
       </c>
     </row>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1"/>
+    <row r="61" ht="20" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1"/>
+    <row r="68" ht="20" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1"/>
+    <row r="83" ht="20" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1"/>
+    <row r="86" ht="20" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1"/>
+    <row r="91" ht="20" customHeight="1"/>
+    <row r="92" ht="20" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1"/>
+    <row r="94" ht="20" customHeight="1"/>
+    <row r="95" ht="20" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1"/>
+    <row r="98" ht="20" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1"/>
+    <row r="101" ht="20" customHeight="1"/>
+    <row r="102" ht="20" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1"/>
+    <row r="105" ht="20" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1"/>
+    <row r="107" ht="20" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1"/>
+    <row r="109" ht="20" customHeight="1"/>
+    <row r="110" ht="20" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1"/>
+    <row r="112" ht="20" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1"/>
+    <row r="114" ht="20" customHeight="1"/>
+    <row r="115" ht="20" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1"/>
+    <row r="119" ht="20" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1"/>
+    <row r="122" ht="20" customHeight="1"/>
+    <row r="123" ht="20" customHeight="1"/>
+    <row r="124" ht="20" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1"/>
+    <row r="126" ht="20" customHeight="1"/>
+    <row r="127" ht="20" customHeight="1"/>
+    <row r="128" ht="20" customHeight="1"/>
+    <row r="129" ht="20" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1"/>
+    <row r="132" ht="20" customHeight="1"/>
+    <row r="133" ht="20" customHeight="1"/>
+    <row r="134" ht="20" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1"/>
+    <row r="136" ht="20" customHeight="1"/>
+    <row r="137" ht="20" customHeight="1"/>
+    <row r="138" ht="20" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1"/>
+    <row r="140" ht="20" customHeight="1"/>
+    <row r="141" ht="20" customHeight="1"/>
+    <row r="142" ht="20" customHeight="1"/>
+    <row r="143" ht="20" customHeight="1"/>
+    <row r="144" ht="20" customHeight="1"/>
+    <row r="145" ht="20" customHeight="1"/>
+    <row r="146" ht="20" customHeight="1"/>
+    <row r="147" ht="20" customHeight="1"/>
+    <row r="148" ht="20" customHeight="1"/>
+    <row r="149" ht="20" customHeight="1"/>
+    <row r="150" ht="20" customHeight="1"/>
+    <row r="151" ht="20" customHeight="1"/>
+    <row r="152" ht="20" customHeight="1"/>
+    <row r="153" ht="20" customHeight="1"/>
+    <row r="154" ht="20" customHeight="1"/>
+    <row r="155" ht="20" customHeight="1"/>
+    <row r="156" ht="20" customHeight="1"/>
+    <row r="157" ht="20" customHeight="1"/>
+    <row r="158" ht="20" customHeight="1"/>
+    <row r="159" ht="20" customHeight="1"/>
+    <row r="160" ht="20" customHeight="1"/>
+    <row r="161" ht="20" customHeight="1"/>
+    <row r="162" ht="20" customHeight="1"/>
+    <row r="163" ht="20" customHeight="1"/>
+    <row r="164" ht="20" customHeight="1"/>
+    <row r="165" ht="20" customHeight="1"/>
+    <row r="166" ht="20" customHeight="1"/>
+    <row r="167" ht="20" customHeight="1"/>
+    <row r="168" ht="20" customHeight="1"/>
+    <row r="169" ht="20" customHeight="1"/>
+    <row r="170" ht="20" customHeight="1"/>
+    <row r="171" ht="20" customHeight="1"/>
+    <row r="172" ht="20" customHeight="1"/>
+    <row r="173" ht="20" customHeight="1"/>
+    <row r="174" ht="20" customHeight="1"/>
+    <row r="175" ht="20" customHeight="1"/>
+    <row r="176" ht="20" customHeight="1"/>
+    <row r="177" ht="20" customHeight="1"/>
+    <row r="178" ht="20" customHeight="1"/>
+    <row r="179" ht="20" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1"/>
+    <row r="181" ht="20" customHeight="1"/>
+    <row r="182" ht="20" customHeight="1"/>
+    <row r="183" ht="20" customHeight="1"/>
+    <row r="184" ht="20" customHeight="1"/>
+    <row r="185" ht="20" customHeight="1"/>
+    <row r="186" ht="20" customHeight="1"/>
+    <row r="187" ht="20" customHeight="1"/>
+    <row r="188" ht="20" customHeight="1"/>
+    <row r="189" ht="20" customHeight="1"/>
+    <row r="190" ht="20" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A4:B4"/>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -7210,7 +7210,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7230,28 +7230,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9918</v>
+        <v>55.0015</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5547</v>
+        <v>56.5696</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5629</v>
+        <v>1.5681</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02842060088958717</v>
+        <v>0.02851013154186704</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6532.97</v>
+        <v>6536.54</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6769.14</v>
+        <v>6772.6</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.17</v>
+        <v>236.06</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03615047979709076</v>
+        <v>0.03611390735771524</v>
       </c>
     </row>
     <row r="3">
@@ -7259,7 +7259,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7279,28 +7279,28 @@
         <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.445</v>
+        <v>55.459</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.355</v>
+        <v>56.374</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.91</v>
+        <v>0.915</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.0164126611957796</v>
+        <v>0.01649867469662273</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6607.29</v>
+        <v>6614.61</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6743.19</v>
+        <v>6750.58</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>135.9</v>
+        <v>135.97</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02056819058948525</v>
+        <v>0.02055601161670907</v>
       </c>
     </row>
     <row r="4">
@@ -7308,7 +7308,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7316,40 +7316,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.079</v>
+        <v>48.083</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.375</v>
+        <v>48.373</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.296</v>
+        <v>0.29</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006156534037729569</v>
+        <v>0.006031237651560843</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.49</v>
+        <v>55.501</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.006</v>
+        <v>56.009</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009298972787889709</v>
+        <v>0.009152988234446227</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6673.09</v>
+        <v>6675.22</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6740.67</v>
+        <v>6742.94</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>67.58</v>
+        <v>67.72</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01012724240194573</v>
+        <v>0.01014498398554654</v>
       </c>
     </row>
     <row r="5">
@@ -7357,7 +7357,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7365,40 +7365,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.122</v>
+        <v>48.13</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.352</v>
+        <v>48.34</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.004779518723245085</v>
+        <v>0.004363183045917307</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.594</v>
+        <v>55.625</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.972</v>
+        <v>55.98</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.378</v>
+        <v>0.355</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006799294887937547</v>
+        <v>0.006382022471910113</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6581.32</v>
+        <v>6588.87</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>6775</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>193.68</v>
+        <v>186.13</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02942874681674801</v>
+        <v>0.02824915349673009</v>
       </c>
     </row>
     <row r="6">
@@ -7406,7 +7406,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7414,40 +7414,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4529</v>
+        <v>47.4531</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7293</v>
+        <v>48.7294</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2764</v>
+        <v>1.2763</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02689825068647016</v>
+        <v>0.02689602997485939</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0337</v>
+        <v>55.0539</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.3992</v>
+        <v>56.4187</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3655</v>
+        <v>1.3648</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.0248120696954775</v>
+        <v>0.02479025100855707</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6593.7</v>
+        <v>6601.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6744.8</v>
+        <v>6752.76</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>151.1</v>
+        <v>150.83</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02291581357962904</v>
+        <v>0.02284634947659245</v>
       </c>
     </row>
     <row r="7">
@@ -7455,7 +7455,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7475,28 +7475,28 @@
         <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.753</v>
+        <v>54.776</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.987</v>
+        <v>57.007</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.234</v>
+        <v>2.231</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04080141727393933</v>
+        <v>0.0407295165766029</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6591.68</v>
+        <v>6598.78</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6785.81</v>
+        <v>6793</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.13</v>
+        <v>194.22</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02945076217292102</v>
+        <v>0.02943271331973486</v>
       </c>
     </row>
     <row r="8">
@@ -7504,7 +7504,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7512,40 +7512,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.555</v>
+        <v>47.5548</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9551</v>
+        <v>48.9549</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944169908526969</v>
+        <v>0.02944182290746675</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.049</v>
+        <v>55.068</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6746</v>
+        <v>56.6893</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6256</v>
+        <v>1.6213</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02953005504187179</v>
+        <v>0.02944178107067625</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6607.51</v>
+        <v>6612.92</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6803.13</v>
+        <v>6808.61</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.62</v>
+        <v>195.69</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02960570623426979</v>
+        <v>0.02959207127864846</v>
       </c>
     </row>
     <row r="9">
@@ -7553,7 +7553,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7561,40 +7561,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2244</v>
+        <v>48.2243</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>48.2813</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0569</v>
+        <v>0.057</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001179900631215733</v>
+        <v>0.001181976721279521</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.8136</v>
+        <v>55.8328</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.8969</v>
+        <v>55.9159</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001492467785629309</v>
+        <v>0.001488372426244071</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6660.19</v>
+        <v>6666.72</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6689.09</v>
+        <v>6695.46</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.9</v>
+        <v>28.74</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.00433921554790479</v>
+        <v>0.004310965512275901</v>
       </c>
     </row>
     <row r="10">
@@ -7602,7 +7602,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7610,40 +7610,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.238</v>
+        <v>48.2379</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2763</v>
+        <v>48.2761</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0382</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007939798499108587</v>
+        <v>0.0007919084371417495</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.7909</v>
+        <v>55.8102</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.9004</v>
+        <v>55.924</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1095</v>
+        <v>0.1138</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.001962685670960676</v>
+        <v>0.002039053793034248</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6656.67</v>
+        <v>6664.59</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6688.4</v>
+        <v>6696.21</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.73</v>
+        <v>31.62</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004766647588058293</v>
+        <v>0.004744477904867366</v>
       </c>
     </row>
     <row r="11">
@@ -7651,7 +7651,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7662,37 +7662,37 @@
         <v>47.9241</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1615</v>
+        <v>49.1617</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2374</v>
+        <v>1.2376</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02581999453302201</v>
+        <v>0.02582416779866497</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3834</v>
+        <v>55.3879</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6615</v>
+        <v>56.6664</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2781</v>
+        <v>1.2785</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.0230773119743461</v>
+        <v>0.02308265884787111</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6610.38</v>
+        <v>6612.91</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6718.58</v>
+        <v>6721.13</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.2</v>
+        <v>108.22</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01636819668460815</v>
+        <v>0.01636495884565191</v>
       </c>
     </row>
     <row r="12">
@@ -7700,7 +7700,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7720,28 +7720,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.3004</v>
+        <v>55.3243</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4617</v>
+        <v>56.4812</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1613</v>
+        <v>1.1569</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02099984810236454</v>
+        <v>0.02091124514905747</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6605.45</v>
+        <v>6613.01</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6759.84</v>
+        <v>6767.11</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.39</v>
+        <v>154.1</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02337312370845287</v>
+        <v>0.02330255057832969</v>
       </c>
     </row>
     <row r="13">
@@ -7749,7 +7749,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7757,40 +7757,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.998</v>
+        <v>47.9983</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.605</v>
+        <v>48.6051</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6068</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264636026501104</v>
+        <v>0.01264211440821863</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5757</v>
+        <v>55.595</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2369</v>
+        <v>56.2555</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6612</v>
+        <v>0.6605</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01189728604408042</v>
+        <v>0.01188056479899271</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6677.86</v>
+        <v>6683.49</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6732.18</v>
+        <v>6737.85</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.32</v>
+        <v>54.36</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008134342439044843</v>
+        <v>0.008133475175394891</v>
       </c>
     </row>
     <row r="14">
@@ -7798,7 +7798,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7818,28 +7818,28 @@
         <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.938</v>
+        <v>54.947</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.501</v>
+        <v>56.51</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.0284502530124868</v>
+        <v>0.02844559302600688</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6576.27</v>
+        <v>6577.51</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6819.21</v>
+        <v>6820.5</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.94</v>
+        <v>242.99</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694191388127312</v>
+        <v>0.03694255120858805</v>
       </c>
     </row>
     <row r="15">
@@ -7847,7 +7847,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7858,37 +7858,37 @@
         <v>47.9982</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6056</v>
+        <v>48.6051</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6069</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01265464121571226</v>
+        <v>0.01264422415840594</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5771</v>
+        <v>55.5975</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2382</v>
+        <v>56.258</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6611</v>
+        <v>0.6605</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01189518704646338</v>
+        <v>0.01188003057691443</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6677.96</v>
+        <v>6685.81</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6732.29</v>
+        <v>6740.05</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.33</v>
+        <v>54.24</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008135718093549526</v>
+        <v>0.008112704369403258</v>
       </c>
     </row>
     <row r="16">
@@ -7896,7 +7896,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7916,28 +7916,28 @@
         <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4159</v>
+        <v>55.4326</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5504</v>
+        <v>56.5675</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1345</v>
+        <v>1.1349</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047246367919676</v>
+        <v>0.02047351197670685</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6612.09</v>
+        <v>6613.09</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6815.15</v>
+        <v>6816.65</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.06</v>
+        <v>203.56</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03071041077783273</v>
+        <v>0.03078137451630025</v>
       </c>
     </row>
     <row r="17">
@@ -7945,7 +7945,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7953,40 +7953,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.162</v>
+        <v>48.16</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.243</v>
+        <v>48.245</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.081</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001681823844524729</v>
+        <v>0.001764950166112957</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.594</v>
+        <v>55.614</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.804</v>
+        <v>55.822</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003777386048854193</v>
+        <v>0.003740065451145395</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6602.23</v>
+        <v>6610.34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6701.08</v>
+        <v>6708.05</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>98.84999999999999</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01497221393377692</v>
+        <v>0.01478138794676219</v>
       </c>
     </row>
     <row r="18">
@@ -7994,7 +7994,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8002,40 +8002,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2184</v>
+        <v>48.2181</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3646</v>
+        <v>48.3642</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1462</v>
+        <v>0.1461</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003032037562424303</v>
+        <v>0.00302998251693866</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.8018</v>
+        <v>55.8231</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.973</v>
+        <v>55.9942</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1712</v>
+        <v>0.1711</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003068001390636144</v>
+        <v>0.003065039383337722</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6666.77</v>
+        <v>6672.61</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6713.86</v>
+        <v>6719.79</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.09</v>
+        <v>47.18</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007063390517446979</v>
+        <v>0.007070696474093346</v>
       </c>
     </row>
     <row r="19">
@@ -8043,7 +8043,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8059,16 +8059,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6682.86</v>
+        <v>6685.7</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6878.68</v>
+        <v>6881.57</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.82</v>
+        <v>195.87</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02930182586497397</v>
+        <v>0.02929685747191768</v>
       </c>
     </row>
     <row r="20">
@@ -8076,7 +8076,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8084,40 +8084,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8045</v>
+        <v>47.7241</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6911</v>
+        <v>48.6807</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.9566</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01854637115752701</v>
+        <v>0.02004438009307666</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.2457</v>
+        <v>55.265</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.3859</v>
+        <v>56.4052</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>1.1402</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.02063871034306743</v>
+        <v>0.02063150275943183</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6610.02</v>
+        <v>6615.9</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7055.57</v>
+        <v>7061.4</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.55</v>
+        <v>445.5</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06740524234419866</v>
+        <v>0.06733777717317371</v>
       </c>
     </row>
     <row r="21">
@@ -8125,7 +8125,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8133,40 +8133,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7513</v>
+        <v>47.7514</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7549</v>
+        <v>48.7548</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0036</v>
+        <v>1.0034</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02101722885031403</v>
+        <v>0.02101299647759019</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3574</v>
+        <v>55.3736</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3663</v>
+        <v>56.3809</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0089</v>
+        <v>1.0073</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01822520566356079</v>
+        <v>0.01819097909473106</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6576.42</v>
+        <v>6580.09</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6828.38</v>
+        <v>6832</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.96</v>
+        <v>251.91</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03831263818308441</v>
+        <v>0.03828367089203947</v>
       </c>
     </row>
     <row r="22">
@@ -8174,7 +8174,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8182,40 +8182,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6786</v>
+        <v>47.6784</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8338</v>
+        <v>48.8334</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1552</v>
+        <v>1.155</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02422889933848728</v>
+        <v>0.02422480620155039</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.188</v>
+        <v>55.2069</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5349</v>
+        <v>56.549</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3469</v>
+        <v>1.3421</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02440566789881858</v>
+        <v>0.02431036700122629</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6600.05</v>
+        <v>6602.95</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6781.04</v>
+        <v>6784.64</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>180.99</v>
+        <v>181.69</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02742251952636722</v>
+        <v>0.02751648884210845</v>
       </c>
     </row>
     <row r="23">
@@ -8223,7 +8223,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8283,37 +8283,37 @@
         <v>47.6128</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5991</v>
+        <v>48.5988</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9863</v>
+        <v>0.986</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02071501781033672</v>
+        <v>0.02070871698366826</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.2029</v>
+        <v>55.1375</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.3452</v>
+        <v>56.2799</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1423</v>
+        <v>1.1424</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02069275346041603</v>
+        <v>0.02071911131262752</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6558.81</v>
+        <v>6561.59</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6732.89</v>
+        <v>6735.59</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174.08</v>
+        <v>174</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02654140004055613</v>
+        <v>0.02651796287180394</v>
       </c>
     </row>
     <row r="25">
@@ -8321,7 +8321,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8370,40 +8370,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2272</v>
+        <v>48.227</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2801</v>
+        <v>48.28</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0529</v>
+        <v>0.053</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001096891380797558</v>
+        <v>0.001098969456943206</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8142</v>
+        <v>55.8335</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.8918</v>
+        <v>55.9105</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0776</v>
+        <v>0.077</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001390327192721565</v>
+        <v>0.001379100360894445</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6655.48</v>
+        <v>6661.11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6684.33</v>
+        <v>6689.87</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.85</v>
+        <v>28.76</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004334773750353092</v>
+        <v>0.004317598718531896</v>
       </c>
     </row>
     <row r="27">
@@ -8411,7 +8411,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8419,40 +8419,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.163</v>
+        <v>48.162</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>48.275</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.00232543653842161</v>
+        <v>0.002346248079398696</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.613</v>
+        <v>55.639</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.86</v>
+        <v>55.885</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004441407584557567</v>
+        <v>0.004421359118603857</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6614</v>
+        <v>6622</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6690</v>
+        <v>6689</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.01149077713940127</v>
+        <v>0.01011778918755663</v>
       </c>
     </row>
     <row r="28">
@@ -8460,7 +8460,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8468,40 +8468,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7615</v>
+        <v>47.761</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7615</v>
+        <v>48.761</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093736586999989</v>
+        <v>0.0209375850589393</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.323</v>
+        <v>55.337</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.413</v>
+        <v>56.427</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01970247455850189</v>
+        <v>0.01969748992536639</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6662.49</v>
+        <v>6658.82</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6762.49</v>
+        <v>6758.82</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.0150094033912246</v>
+        <v>0.0150176758044218</v>
       </c>
     </row>
     <row r="29">
@@ -8509,7 +8509,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8525,16 +8525,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6682.33</v>
+        <v>6684.14</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6864.41</v>
+        <v>6866.24</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>182.08</v>
+        <v>182.1</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.0272479808689484</v>
+        <v>0.02724359453871403</v>
       </c>
     </row>
     <row r="30">
@@ -8542,7 +8542,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8562,28 +8562,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0871</v>
+        <v>55.1061</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7391</v>
+        <v>56.7636</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.652</v>
+        <v>1.6575</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.02998887216789412</v>
+        <v>0.03007833978452476</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6579.39</v>
+        <v>6585.25</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6776.91</v>
+        <v>6783.56</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>197.52</v>
+        <v>198.31</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.0300210201857619</v>
+        <v>0.03011427052883337</v>
       </c>
     </row>
     <row r="31">
@@ -8591,7 +8591,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8599,40 +8599,40 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1513</v>
+        <v>48.2974</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.3928</v>
+        <v>48.2974</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2415</v>
+        <v>0</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.005015440912291049</v>
+        <v>0</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.6838</v>
+        <v>55.9313</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.0193</v>
+        <v>55.9313</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3355</v>
+        <v>0</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006025091678369652</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6591.43</v>
+        <v>6681.5</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6724.93</v>
+        <v>6681.5</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>133.5</v>
+        <v>0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025357168323111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -8640,7 +8640,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8660,28 +8660,28 @@
         <v>0.01676213483686123</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4313</v>
+        <v>55.4468</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.282</v>
+        <v>56.2975</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>0.8507</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01534692493230359</v>
+        <v>0.01534263474177049</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6608.49</v>
+        <v>6610.55</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6804.84</v>
+        <v>6806.97</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.35</v>
+        <v>196.42</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02971177984683339</v>
+        <v>0.02971311010430297</v>
       </c>
     </row>
     <row r="33">
@@ -8689,7 +8689,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8697,40 +8697,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1538</v>
+        <v>48.1537</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3569</v>
+        <v>48.3568</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2031</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004217735671951123</v>
+        <v>0.004217744430853704</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7318</v>
+        <v>55.7532</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9564</v>
+        <v>55.9778</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004030015179843464</v>
+        <v>0.004028468321100851</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6645.43</v>
+        <v>6651.71</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6698.81</v>
+        <v>6705.14</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.38</v>
+        <v>53.43</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008032587808463861</v>
+        <v>0.0080325209607755</v>
       </c>
     </row>
     <row r="34">
@@ -8738,7 +8738,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8758,28 +8758,28 @@
         <v>0.02006493438703818</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4714</v>
+        <v>55.4695</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5735</v>
+        <v>56.5715</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.1021</v>
+        <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986789588869219</v>
+        <v>0.01986677363235652</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6614.34</v>
+        <v>6611.87</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6758.94</v>
+        <v>6756.47</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02186159163272526</v>
+        <v>0.02186975847982492</v>
       </c>
     </row>
     <row r="35">
@@ -8787,7 +8787,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8798,25 +8798,25 @@
         <v>48.186</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.24</v>
+        <v>48.239</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.001120657452372058</v>
+        <v>0.00109990453658739</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.64</v>
+        <v>55.655</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.785</v>
+        <v>55.803</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.145</v>
+        <v>0.148</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002606038820992092</v>
+        <v>0.002659239960470757</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8828,7 +8828,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8848,28 +8848,28 @@
         <v>0.02098635886673662</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.17</v>
+        <v>55.19</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.31</v>
+        <v>56.32</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02066340402392605</v>
+        <v>0.02047472368182642</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6581.19</v>
+        <v>6582.59</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6783.18</v>
+        <v>6784.52</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>201.99</v>
+        <v>201.93</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03069201770500472</v>
+        <v>0.03067637510463207</v>
       </c>
     </row>
     <row r="37">
@@ -8877,7 +8877,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8897,28 +8897,28 @@
         <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4352</v>
+        <v>55.4359</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5567</v>
+        <v>56.5574</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>1.1215</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023082806592201</v>
+        <v>0.02023057260728156</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6647.74</v>
+        <v>6649.04</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6781.97</v>
+        <v>6783.29</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.23</v>
+        <v>134.25</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019182459001104</v>
+        <v>0.02019088469914454</v>
       </c>
     </row>
     <row r="38">
@@ -8926,7 +8926,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8946,28 +8946,28 @@
         <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4338</v>
+        <v>55.4499</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2441</v>
+        <v>56.2606</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8103</v>
+        <v>0.8107</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461743557179915</v>
+        <v>0.0146204050863933</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6614.38</v>
+        <v>6619.46</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6747.93</v>
+        <v>6753.11</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.55</v>
+        <v>133.65</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019085689059292</v>
+        <v>0.02019046870892792</v>
       </c>
     </row>
     <row r="39">
@@ -8975,7 +8975,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8986,37 +8986,37 @@
         <v>47.7684</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7652</v>
+        <v>48.7651</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9968</v>
+        <v>0.9967</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02086735163832157</v>
+        <v>0.02086525820416845</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2611</v>
+        <v>55.2759</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4695</v>
+        <v>56.485</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2084</v>
+        <v>1.2091</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02186710000343823</v>
+        <v>0.02187390888253289</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6632.7</v>
+        <v>6637.93</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6843.25</v>
+        <v>6848.63</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.55</v>
+        <v>210.7</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03174423688693895</v>
+        <v>0.03174182312859582</v>
       </c>
     </row>
   </sheetData>
@@ -42318,7 +42318,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.4528240740740741</v>
+        <v>0.4614699074074074</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42402,7 +42402,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023082806592201</v>
+        <v>0.02023057260728156</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42410,10 +42410,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4352</v>
+        <v>55.4359</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5567</v>
+        <v>56.5574</v>
       </c>
     </row>
     <row r="7">
@@ -42455,7 +42455,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019182459001104</v>
+        <v>0.02019088469914454</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42463,10 +42463,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6647.74</v>
+        <v>6649.04</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6781.97</v>
+        <v>6783.29</v>
       </c>
     </row>
     <row r="8">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -1007,24 +1007,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1033,6 +1037,7 @@
           <max val="0.06809845902702412"/>
           <min val="0.01398473878667442"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1050,9 +1055,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -1178,6 +1197,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1186,24 +1213,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1212,6 +1243,7 @@
           <max val="0.06361034633532447"/>
           <min val="0.02255547230137524"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1229,9 +1261,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1369,6 +1415,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1377,24 +1431,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1403,6 +1461,7 @@
           <max val="0.06393703694203891"/>
           <min val="0.02251604918664015"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1420,9 +1479,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1560,6 +1633,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1568,24 +1649,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1594,6 +1679,7 @@
           <max val="0.09492887751151027"/>
           <min val="0.02634377435370254"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1611,9 +1697,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1751,6 +1851,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1759,24 +1867,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1785,6 +1897,7 @@
           <max val="0.06300273000209422"/>
           <min val="0.01394771487950567"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1802,9 +1915,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1942,6 +2069,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1950,24 +2085,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1976,6 +2115,7 @@
           <max val="0.05612935000212975"/>
           <min val="0.01451066469310389"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1993,9 +2133,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2133,6 +2287,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -2141,24 +2303,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2167,6 +2333,7 @@
           <max val="0.08822748202703072"/>
           <min val="0.0196170269615309"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -2184,9 +2351,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2324,6 +2505,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -2332,24 +2521,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2358,6 +2551,7 @@
           <max val="0.07017975595934527"/>
           <min val="0.01190344185435327"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -2375,9 +2569,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2515,6 +2723,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -2523,24 +2739,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2549,6 +2769,7 @@
           <max val="0.07017999927062174"/>
           <min val="0.01190503299558375"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -2566,9 +2787,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2706,6 +2941,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -2714,24 +2957,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2740,6 +2987,7 @@
           <max val="0.1709612332154084"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -2757,9 +3005,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2897,6 +3159,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -2905,24 +3175,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2931,6 +3205,7 @@
           <max val="0.06165859703981922"/>
           <min val="0.01797489899804002"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -2948,9 +3223,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -3464,24 +3753,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3490,6 +3783,7 @@
           <max val="0.06809875047508467"/>
           <min val="0.01398628179112082"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -3507,9 +3801,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -3635,6 +3943,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -3643,24 +3959,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3669,6 +3989,7 @@
           <max val="0.06209535841468713"/>
           <min val="0.01791241253707181"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -3686,9 +4007,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -3826,6 +4161,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -3834,24 +4177,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3860,6 +4207,7 @@
           <max val="0.1462720659556508"/>
           <min val="0.007620168856054751"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -3877,9 +4225,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -4393,24 +4755,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4419,6 +4785,7 @@
           <max val="0.1646791482454227"/>
           <min val="0.001344939025793405"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -4436,9 +4803,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -4820,24 +5201,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -4846,6 +5231,7 @@
           <max val="0.05171408776103012"/>
           <min val="0.0161237184650772"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -4863,9 +5249,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -5247,24 +5647,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5273,6 +5677,7 @@
           <max val="0.05613143775214488"/>
           <min val="0.01554823152705276"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -5290,9 +5695,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -5674,24 +6093,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5700,6 +6123,7 @@
           <max val="0.113954760403876"/>
           <min val="0.007962009561212546"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -5717,9 +6141,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -5845,6 +6283,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -5853,24 +6299,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -5879,6 +6329,7 @@
           <max val="0.04535890324268219"/>
           <min val="0.02563021945997443"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -5896,9 +6347,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -6036,6 +6501,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -6044,24 +6517,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6070,6 +6547,7 @@
           <max val="0.04536575081521625"/>
           <min val="0.02562858686951813"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -6087,9 +6565,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -6227,6 +6719,14 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <numFmt formatCode="0.00%"/>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -6235,24 +6735,28 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="650"/>
+              <a:defRPr sz="700"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="650"/>
+            <a:endParaRPr sz="700"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -6261,6 +6765,7 @@
           <max val="0.07745416653140928"/>
           <min val="0.03018959592357282"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -6278,9 +6783,23 @@
           </tx>
         </title>
         <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="700"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -7210,7 +7729,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7230,28 +7749,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>55.0015</v>
+        <v>55.006</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5696</v>
+        <v>56.5693</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5681</v>
+        <v>1.5633</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02851013154186704</v>
+        <v>0.02842053594153365</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6536.54</v>
+        <v>6539.92</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6772.6</v>
+        <v>6776.25</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.06</v>
+        <v>236.33</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03611390735771524</v>
+        <v>0.03613652766394695</v>
       </c>
     </row>
     <row r="3">
@@ -7259,7 +7778,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7279,28 +7798,28 @@
         <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.459</v>
+        <v>55.464</v>
       </c>
       <c r="I3" s="10" t="n">
         <v>56.374</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.915</v>
+        <v>0.91</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01649867469662273</v>
+        <v>0.01640703879994231</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6614.61</v>
+        <v>6613.3</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6750.58</v>
+        <v>6749.32</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>135.97</v>
+        <v>136.02</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02055601161670907</v>
+        <v>0.02056764399014108</v>
       </c>
     </row>
     <row r="4">
@@ -7308,7 +7827,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7316,40 +7835,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.083</v>
+        <v>48.079</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.373</v>
+        <v>48.376</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.29</v>
+        <v>0.297</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006031237651560843</v>
+        <v>0.006177333139208386</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.501</v>
+        <v>55.504</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.009</v>
+        <v>56.022</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.508</v>
+        <v>0.518</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009152988234446227</v>
+        <v>0.009332660709138079</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6675.22</v>
+        <v>6674.93</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6742.94</v>
+        <v>6742.97</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>67.72</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01014498398554654</v>
+        <v>0.0101933653236813</v>
       </c>
     </row>
     <row r="5">
@@ -7357,7 +7876,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7377,28 +7896,28 @@
         <v>0.004363183045917307</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.625</v>
+        <v>55.621</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.98</v>
+        <v>55.976</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>0.355</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006382022471910113</v>
+        <v>0.00638248143686737</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6588.87</v>
+        <v>6583.96</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>6775</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>186.13</v>
+        <v>191.04</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02824915349673009</v>
+        <v>0.02901597215049909</v>
       </c>
     </row>
     <row r="6">
@@ -7406,7 +7925,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7414,40 +7933,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4531</v>
+        <v>47.4528</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7294</v>
+        <v>48.7293</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2763</v>
+        <v>1.2765</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02689602997485939</v>
+        <v>0.02690041472789804</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0539</v>
+        <v>55.0511</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.4187</v>
+        <v>56.4161</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3648</v>
+        <v>1.365</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02479025100855707</v>
+        <v>0.02479514487448934</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6601.93</v>
+        <v>6596.32</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6752.76</v>
+        <v>6747.3</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>150.83</v>
+        <v>150.98</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02284634947659245</v>
+        <v>0.02288851965944648</v>
       </c>
     </row>
     <row r="7">
@@ -7455,7 +7974,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7475,28 +7994,28 @@
         <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.776</v>
+        <v>54.772</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>57.007</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.231</v>
+        <v>2.235</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.0407295165766029</v>
+        <v>0.04080552106915943</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6598.78</v>
+        <v>6593.35</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6793</v>
+        <v>6787.56</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.22</v>
+        <v>194.21</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02943271331973486</v>
+        <v>0.02945543615916037</v>
       </c>
     </row>
     <row r="8">
@@ -7504,7 +8023,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7536,16 +8055,16 @@
         <v>0.02944178107067625</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6612.92</v>
+        <v>6610.78</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6808.61</v>
+        <v>6806.45</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.69</v>
+        <v>195.67</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02959207127864846</v>
+        <v>0.02959862527568608</v>
       </c>
     </row>
     <row r="9">
@@ -7553,7 +8072,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7561,40 +8080,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2243</v>
+        <v>48.2242</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2813</v>
+        <v>48.2817</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.057</v>
+        <v>0.0575</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001181976721279521</v>
+        <v>0.001192347410636154</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.8328</v>
+        <v>55.8326</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.9159</v>
+        <v>55.9161</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001488372426244071</v>
+        <v>0.00149554203099981</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6666.72</v>
+        <v>6662.85</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6695.46</v>
+        <v>6691.74</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.74</v>
+        <v>28.89</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004310965512275901</v>
+        <v>0.004335982349895314</v>
       </c>
     </row>
     <row r="10">
@@ -7602,7 +8121,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7610,40 +8129,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2379</v>
+        <v>48.2377</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2761</v>
+        <v>48.2759</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>0.0382</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007919084371417495</v>
+        <v>0.0007919117205007701</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.8102</v>
+        <v>55.8099</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.924</v>
+        <v>55.919</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1138</v>
+        <v>0.1091</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002039053793034248</v>
+        <v>0.001954850304336686</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6664.59</v>
+        <v>6659.12</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6696.21</v>
+        <v>6690.78</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.62</v>
+        <v>31.66</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004744477904867366</v>
+        <v>0.00475438196037915</v>
       </c>
     </row>
     <row r="11">
@@ -7651,7 +8170,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7659,40 +8178,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9241</v>
+        <v>47.9239</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1617</v>
+        <v>49.1614</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2376</v>
+        <v>1.2375</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02582416779866497</v>
+        <v>0.02582218892869738</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>55.3879</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6664</v>
+        <v>56.6663</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2785</v>
+        <v>1.2784</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02308265884787111</v>
+        <v>0.02308085339938867</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6612.91</v>
+        <v>6614.87</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6721.13</v>
+        <v>6723.1</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.22</v>
+        <v>108.23</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01636495884565191</v>
+        <v>0.01636162161917014</v>
       </c>
     </row>
     <row r="12">
@@ -7700,7 +8219,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7720,28 +8239,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.3243</v>
+        <v>55.3195</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>56.4812</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1569</v>
+        <v>1.1617</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02091124514905747</v>
+        <v>0.02099982827032059</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6613.01</v>
+        <v>6607.97</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6767.11</v>
+        <v>6762.41</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.1</v>
+        <v>154.44</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02330255057832969</v>
+        <v>0.02337177680891408</v>
       </c>
     </row>
     <row r="13">
@@ -7749,7 +8268,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7757,40 +8276,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9983</v>
+        <v>47.9981</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6051</v>
+        <v>48.6053</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6068</v>
+        <v>0.6072</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264211440821863</v>
+        <v>0.01265050074898798</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.595</v>
+        <v>55.5975</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2555</v>
+        <v>56.2586</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6605</v>
+        <v>0.6611</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01188056479899271</v>
+        <v>0.01189082242906605</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6683.49</v>
+        <v>6683.82</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6737.85</v>
+        <v>6738.14</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.36</v>
+        <v>54.32</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008133475175394891</v>
+        <v>0.008127089000002993</v>
       </c>
     </row>
     <row r="14">
@@ -7798,7 +8317,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7818,28 +8337,28 @@
         <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.947</v>
+        <v>54.952</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.51</v>
+        <v>56.515</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02844559302600688</v>
+        <v>0.02844300480419275</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6577.51</v>
+        <v>6577.16</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6820.5</v>
+        <v>6820.13</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.99</v>
+        <v>242.97</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694255120858805</v>
+        <v>0.03694147626027039</v>
       </c>
     </row>
     <row r="15">
@@ -7847,7 +8366,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7855,40 +8374,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9982</v>
+        <v>47.998</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>48.6051</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6069</v>
+        <v>0.6071</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264422415840594</v>
+        <v>0.01264844368515355</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5975</v>
+        <v>55.5959</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.258</v>
+        <v>56.2564</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.6605</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01188003057691443</v>
+        <v>0.01188037247350974</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6685.81</v>
+        <v>6680.4</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6740.05</v>
+        <v>6734.79</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.24</v>
+        <v>54.39</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008112704369403258</v>
+        <v>0.008141728040237111</v>
       </c>
     </row>
     <row r="16">
@@ -7896,7 +8415,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7916,28 +8435,28 @@
         <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4326</v>
+        <v>55.4302</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5675</v>
+        <v>56.5651</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>1.1349</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047351197670685</v>
+        <v>0.02047439843262337</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6613.09</v>
+        <v>6613.91</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6816.65</v>
+        <v>6817.49</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.56</v>
+        <v>203.58</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03078137451630025</v>
+        <v>0.03078058213673908</v>
       </c>
     </row>
     <row r="17">
@@ -7945,7 +8464,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7953,40 +8472,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.16</v>
+        <v>48.183</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.245</v>
+        <v>48.242</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001764950166112957</v>
+        <v>0.001224498267023639</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.614</v>
+        <v>55.643</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.822</v>
+        <v>55.811</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.208</v>
+        <v>0.168</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003740065451145395</v>
+        <v>0.003019247704113725</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6610.34</v>
+        <v>6610.07</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6708.05</v>
+        <v>6705</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>97.70999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01478138794676219</v>
+        <v>0.01436142128600756</v>
       </c>
     </row>
     <row r="18">
@@ -7994,7 +8513,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8005,37 +8524,37 @@
         <v>48.2181</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3642</v>
+        <v>48.3643</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1461</v>
+        <v>0.1462</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.00302998251693866</v>
+        <v>0.003032056426943409</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>55.8231</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9942</v>
+        <v>55.9943</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1711</v>
+        <v>0.1712</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003065039383337722</v>
+        <v>0.003066830756443121</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6672.61</v>
+        <v>6669.56</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6719.79</v>
+        <v>6716.68</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.18</v>
+        <v>47.12</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007070696474093346</v>
+        <v>0.007064933818722674</v>
       </c>
     </row>
     <row r="19">
@@ -8043,7 +8562,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8059,16 +8578,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6685.7</v>
+        <v>6685.53</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6881.57</v>
+        <v>6881.39</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.87</v>
+        <v>195.86</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02929685747191768</v>
+        <v>0.02929610666618802</v>
       </c>
     </row>
     <row r="20">
@@ -8076,7 +8595,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8084,40 +8603,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.7241</v>
+        <v>47.8071</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6807</v>
+        <v>48.6877</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.9566</v>
+        <v>0.8806</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.02004438009307666</v>
+        <v>0.01841985813822633</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.265</v>
+        <v>55.3609</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.4052</v>
+        <v>56.4133</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.1402</v>
+        <v>1.0524</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.02063150275943183</v>
+        <v>0.01900980656022572</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6615.9</v>
+        <v>6613.08</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7061.4</v>
+        <v>7057.74</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.5</v>
+        <v>444.66</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06733777717317371</v>
+        <v>0.06723947086682756</v>
       </c>
     </row>
     <row r="21">
@@ -8125,7 +8644,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8136,37 +8655,37 @@
         <v>47.7514</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7548</v>
+        <v>48.7543</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0034</v>
+        <v>1.0029</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02101299647759019</v>
+        <v>0.02100252558040183</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3736</v>
+        <v>55.3718</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3809</v>
+        <v>56.3808</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0073</v>
+        <v>1.009</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01819097909473106</v>
+        <v>0.01822227198682362</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6580.09</v>
+        <v>6581.47</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6832</v>
+        <v>6833.43</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.91</v>
+        <v>251.96</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03828367089203947</v>
+        <v>0.03828324067419588</v>
       </c>
     </row>
     <row r="22">
@@ -8174,7 +8693,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8182,40 +8701,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6784</v>
+        <v>47.6783</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8334</v>
+        <v>48.8332</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.155</v>
+        <v>1.1549</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02422480620155039</v>
+        <v>0.02422275962020458</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.2069</v>
+        <v>55.202</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.549</v>
+        <v>56.5488</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3421</v>
+        <v>1.3468</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02431036700122629</v>
+        <v>0.02439766675120467</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6602.95</v>
+        <v>6604.18</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6784.64</v>
+        <v>6785.28</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.69</v>
+        <v>181.1</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02751648884210845</v>
+        <v>0.02742202665584524</v>
       </c>
     </row>
     <row r="23">
@@ -8223,7 +8742,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8231,28 +8750,28 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.17</v>
+        <v>48.22</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>48.18</v>
+        <v>48.23</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002075980900975711</v>
+        <v>0.0002073828287017835</v>
       </c>
       <c r="H23" s="10" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>55.75</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>55.8</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0008968609865470851</v>
+        <v>0.0008976660682226212</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>6722.02</v>
@@ -8272,7 +8791,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8280,40 +8799,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6128</v>
+        <v>47.6129</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5988</v>
+        <v>48.5986</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.986</v>
+        <v>0.9857</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02070871698366826</v>
+        <v>0.02070237267631251</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1375</v>
+        <v>55.1334</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2799</v>
+        <v>56.2772</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1424</v>
+        <v>1.1438</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02071911131262752</v>
+        <v>0.02074604504710393</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6561.59</v>
+        <v>6561.48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6735.59</v>
+        <v>6735.43</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174</v>
+        <v>173.95</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02651796287180394</v>
+        <v>0.02651078720044868</v>
       </c>
     </row>
     <row r="25">
@@ -8321,7 +8840,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8362,7 +8881,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8373,37 +8892,37 @@
         <v>48.227</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.28</v>
+        <v>48.2796</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.053</v>
+        <v>0.0526</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001098969456943206</v>
+        <v>0.001090675347834201</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8335</v>
+        <v>55.8305</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.9105</v>
+        <v>55.9073</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.077</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001379100360894445</v>
+        <v>0.001375592194230752</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6661.11</v>
+        <v>6658.35</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6689.87</v>
+        <v>6687.13</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.76</v>
+        <v>28.78</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004317598718531896</v>
+        <v>0.004322392184249852</v>
       </c>
     </row>
     <row r="27">
@@ -8411,7 +8930,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8419,40 +8938,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.162</v>
+        <v>48.182</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.275</v>
+        <v>48.285</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.113</v>
+        <v>0.103</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002346248079398696</v>
+        <v>0.002137727782159313</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.639</v>
+        <v>55.652</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.885</v>
+        <v>55.883</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.246</v>
+        <v>0.231</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004421359118603857</v>
+        <v>0.004150794221231942</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6622</v>
+        <v>6623</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6689</v>
+        <v>6683</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.01011778918755663</v>
+        <v>0.009059338668277217</v>
       </c>
     </row>
     <row r="28">
@@ -8460,7 +8979,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8492,16 +9011,16 @@
         <v>0.01969748992536639</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6658.82</v>
+        <v>6662.57</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6758.82</v>
+        <v>6762.57</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.0150176758044218</v>
+        <v>0.01500922316763651</v>
       </c>
     </row>
     <row r="29">
@@ -8509,7 +9028,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8525,16 +9044,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6684.14</v>
+        <v>6686.42</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6866.24</v>
+        <v>6868.55</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>182.1</v>
+        <v>182.13</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02724359453871403</v>
+        <v>0.02723879146090135</v>
       </c>
     </row>
     <row r="30">
@@ -8542,7 +9061,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8562,28 +9081,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.1061</v>
+        <v>55.1014</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7636</v>
+        <v>56.7587</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6575</v>
+        <v>1.6573</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03007833978452476</v>
+        <v>0.03007727571350274</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6585.25</v>
+        <v>6581.7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6783.56</v>
+        <v>6779.29</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>198.31</v>
+        <v>197.59</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03011427052883337</v>
+        <v>0.03002111916374189</v>
       </c>
     </row>
     <row r="31">
@@ -8591,7 +9110,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8599,10 +9118,10 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.2974</v>
+        <v>48.2768</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.2974</v>
+        <v>48.2768</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0</v>
@@ -8611,10 +9130,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.9313</v>
+        <v>55.9056</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>55.9313</v>
+        <v>55.9056</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0</v>
@@ -8623,10 +9142,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6681.5</v>
+        <v>6677.96</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6681.5</v>
+        <v>6677.96</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -8640,7 +9159,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8651,37 +9170,37 @@
         <v>47.8519</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.654</v>
+        <v>48.6538</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8021</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676213483686123</v>
+        <v>0.01675795527450321</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4468</v>
+        <v>55.4453</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2975</v>
+        <v>56.2957</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8507</v>
+        <v>0.8504</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01534263474177049</v>
+        <v>0.01533763907851522</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6610.55</v>
+        <v>6610.7</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6806.97</v>
+        <v>6807.01</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.42</v>
+        <v>196.31</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02971311010430297</v>
+        <v>0.02969579620917603</v>
       </c>
     </row>
     <row r="33">
@@ -8689,7 +9208,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8697,40 +9216,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1537</v>
+        <v>48.1536</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>48.3568</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.2031</v>
+        <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004217744430853704</v>
+        <v>0.004219829877724615</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7532</v>
+        <v>55.7495</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9778</v>
+        <v>55.9741</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004028468321100851</v>
+        <v>0.004028735683728105</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6651.71</v>
+        <v>6650.95</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6705.14</v>
+        <v>6704.37</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.43</v>
+        <v>53.42</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.0080325209607755</v>
+        <v>0.00803193528744014</v>
       </c>
     </row>
     <row r="34">
@@ -8738,7 +9257,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8746,40 +9265,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8945</v>
+        <v>47.8944</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8555</v>
+        <v>48.8554</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006493438703818</v>
+        <v>0.02006497628115187</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4695</v>
+        <v>55.4805</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5715</v>
+        <v>56.5825</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986677363235652</v>
+        <v>0.01986283468966574</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6611.87</v>
+        <v>6616.12</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6756.47</v>
+        <v>6760.72</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02186975847982492</v>
+        <v>0.0218557099931682</v>
       </c>
     </row>
     <row r="35">
@@ -8787,7 +9306,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8795,28 +9314,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.186</v>
+        <v>48.194</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>48.239</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.053</v>
+        <v>0.045</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.00109990453658739</v>
+        <v>0.0009337261899821554</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.655</v>
+        <v>55.664</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.803</v>
+        <v>55.798</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.148</v>
+        <v>0.134</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002659239960470757</v>
+        <v>0.002407300948548434</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8828,7 +9347,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8860,16 +9379,16 @@
         <v>0.02047472368182642</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6582.59</v>
+        <v>6585.46</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6784.52</v>
+        <v>6787.98</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>201.93</v>
+        <v>202.52</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03067637510463207</v>
+        <v>0.03075259738879289</v>
       </c>
     </row>
     <row r="37">
@@ -8877,7 +9396,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8897,28 +9416,28 @@
         <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4359</v>
+        <v>55.4491</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5574</v>
+        <v>56.5709</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1215</v>
+        <v>1.1218</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023057260728156</v>
+        <v>0.02023116696213284</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6649.04</v>
+        <v>6652.77</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6783.29</v>
+        <v>6787.1</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.25</v>
+        <v>134.33</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019088469914454</v>
+        <v>0.02019158936803768</v>
       </c>
     </row>
     <row r="38">
@@ -8926,7 +9445,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8946,28 +9465,28 @@
         <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4499</v>
+        <v>55.4475</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2606</v>
+        <v>56.2582</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>0.8107</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.0146204050863933</v>
+        <v>0.01462103791875197</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6619.46</v>
+        <v>6616.73</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6753.11</v>
+        <v>6750.33</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.65</v>
+        <v>133.6</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019046870892792</v>
+        <v>0.02019124250196094</v>
       </c>
     </row>
     <row r="39">
@@ -8975,7 +9494,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8983,40 +9502,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7684</v>
+        <v>47.7683</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7651</v>
+        <v>48.7652</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9967</v>
+        <v>0.9969</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02086525820416845</v>
+        <v>0.02086948876137522</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2759</v>
+        <v>55.2729</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.485</v>
+        <v>56.4822</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2091</v>
+        <v>1.2093</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02187390888253289</v>
+        <v>0.02187871452375396</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6637.93</v>
+        <v>6638.17</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6848.63</v>
+        <v>6848.85</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.7</v>
+        <v>210.68</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03174182312859582</v>
+        <v>0.03173766263895019</v>
       </c>
     </row>
   </sheetData>
@@ -42318,7 +42837,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.4614699074074074</v>
+        <v>0.4783564814814815</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42402,7 +42921,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023057260728156</v>
+        <v>0.02023116696213284</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42410,10 +42929,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4359</v>
+        <v>55.4491</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5574</v>
+        <v>56.5709</v>
       </c>
     </row>
     <row r="7">
@@ -42455,7 +42974,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019088469914454</v>
+        <v>0.02019158936803768</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42463,10 +42982,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6649.04</v>
+        <v>6652.77</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6783.29</v>
+        <v>6787.1</v>
       </c>
     </row>
     <row r="8">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -1009,23 +1009,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -1037,41 +1036,11 @@
           <max val="0.06809845902702412"/>
           <min val="0.01398473878667442"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -1215,23 +1184,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -1243,41 +1211,11 @@
           <max val="0.06361034633532447"/>
           <min val="0.02255547230137524"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1433,23 +1371,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -1461,41 +1398,11 @@
           <max val="0.06393703694203891"/>
           <min val="0.02251604918664015"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1651,23 +1558,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -1679,41 +1585,11 @@
           <max val="0.09492887751151027"/>
           <min val="0.02634377435370254"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -1869,23 +1745,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -1897,41 +1772,11 @@
           <max val="0.06300273000209422"/>
           <min val="0.01394771487950567"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2087,23 +1932,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -2115,41 +1959,11 @@
           <max val="0.05612935000212975"/>
           <min val="0.01451066469310389"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2305,23 +2119,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -2333,41 +2146,11 @@
           <max val="0.08822748202703072"/>
           <min val="0.0196170269615309"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2523,23 +2306,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -2551,41 +2333,11 @@
           <max val="0.07017975595934527"/>
           <min val="0.01190344185435327"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2741,23 +2493,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -2769,41 +2520,11 @@
           <max val="0.07017999927062174"/>
           <min val="0.01190503299558375"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -2959,23 +2680,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -2987,41 +2707,11 @@
           <max val="0.1709612332154084"/>
           <min val="0"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -3177,23 +2867,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -3205,41 +2894,11 @@
           <max val="0.06165859703981922"/>
           <min val="0.01797489899804002"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -3755,23 +3414,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -3783,41 +3441,11 @@
           <max val="0.06809875047508467"/>
           <min val="0.01398628179112082"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -3961,23 +3589,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -3989,41 +3616,11 @@
           <max val="0.06209535841468713"/>
           <min val="0.01791241253707181"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -4179,23 +3776,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -4207,41 +3803,11 @@
           <max val="0.1462720659556508"/>
           <min val="0.007620168856054751"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -4757,23 +4323,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -4785,41 +4350,11 @@
           <max val="0.1646791482454227"/>
           <min val="0.001344939025793405"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -5203,23 +4738,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -5231,41 +4765,11 @@
           <max val="0.05171408776103012"/>
           <min val="0.0161237184650772"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -5649,23 +5153,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -5677,41 +5180,11 @@
           <max val="0.05613143775214488"/>
           <min val="0.01554823152705276"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -6095,23 +5568,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -6123,41 +5595,11 @@
           <max val="0.113954760403876"/>
           <min val="0.007962009561212546"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -6301,23 +5743,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -6329,41 +5770,11 @@
           <max val="0.04535890324268219"/>
           <min val="0.02563021945997443"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -6519,23 +5930,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -6547,41 +5957,11 @@
           <max val="0.04536575081521625"/>
           <min val="0.02562858686951813"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -6737,23 +6117,22 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
           <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700"/>
+              <a:defRPr sz="700" b="1"/>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="700"/>
+            <a:endParaRPr sz="700" b="1"/>
           </a:p>
         </txPr>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
         <tickMarkSkip val="1"/>
@@ -6765,41 +6144,11 @@
           <max val="0.07745416653140928"/>
           <min val="0.03018959592357282"/>
         </scaling>
-        <delete val="0"/>
+        <delete val="1"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Makas %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
-        <majorTickMark val="out"/>
+        <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="700"/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="700"/>
-          </a:p>
-        </txPr>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
       <spPr>
         <a:solidFill>
@@ -7729,7 +7078,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7749,28 +7098,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>55.006</v>
+        <v>55.0059</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5693</v>
+        <v>56.5692</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>1.5633</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02842053594153365</v>
+        <v>0.02842058760969278</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6539.92</v>
+        <v>6536.37</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6776.25</v>
+        <v>6772.41</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.33</v>
+        <v>236.04</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03613652766394695</v>
+        <v>0.03611178681745372</v>
       </c>
     </row>
     <row r="3">
@@ -7778,7 +7127,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7798,28 +7147,28 @@
         <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.464</v>
+        <v>55.469</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.374</v>
+        <v>56.384</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.91</v>
+        <v>0.915</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01640703879994231</v>
+        <v>0.01649570030106906</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6613.3</v>
+        <v>6614.98</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6749.32</v>
+        <v>6751.04</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>136.02</v>
+        <v>136.06</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02056764399014108</v>
+        <v>0.02056846732718769</v>
       </c>
     </row>
     <row r="4">
@@ -7827,7 +7176,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7835,40 +7184,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.079</v>
+        <v>48.078</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>48.376</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006177333139208386</v>
+        <v>0.006198261158950039</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.504</v>
+        <v>55.509</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.022</v>
+        <v>56.023</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.518</v>
+        <v>0.514</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009332660709138079</v>
+        <v>0.009259759678610676</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6674.93</v>
+        <v>6673.88</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6742.97</v>
+        <v>6741.22</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>68.04000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.0101933653236813</v>
+        <v>0.01009008253070178</v>
       </c>
     </row>
     <row r="5">
@@ -7876,7 +7225,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7896,28 +7245,28 @@
         <v>0.004363183045917307</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.621</v>
+        <v>55.63</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.976</v>
+        <v>55.984</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.00638248143686737</v>
+        <v>0.006363472946252022</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6583.96</v>
+        <v>6588.32</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>6775</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>191.04</v>
+        <v>186.68</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02901597215049909</v>
+        <v>0.0283349928358064</v>
       </c>
     </row>
     <row r="6">
@@ -7925,7 +7274,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7936,37 +7285,37 @@
         <v>47.4528</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7293</v>
+        <v>48.729</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2765</v>
+        <v>1.2762</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02690041472789804</v>
+        <v>0.02689409265628161</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0511</v>
+        <v>55.0575</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.4161</v>
+        <v>56.422</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.365</v>
+        <v>1.3645</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02479514487448934</v>
+        <v>0.02478318121963402</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6596.32</v>
+        <v>6598.14</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6747.3</v>
+        <v>6749.04</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>150.98</v>
+        <v>150.9</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02288851965944648</v>
+        <v>0.02287008156844201</v>
       </c>
     </row>
     <row r="7">
@@ -7974,7 +7323,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7994,28 +7343,28 @@
         <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.772</v>
+        <v>54.781</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>57.007</v>
+        <v>57.012</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.235</v>
+        <v>2.231</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04080552106915943</v>
+        <v>0.04072579909092568</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6593.35</v>
+        <v>6594.98</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6787.56</v>
+        <v>6789.19</v>
       </c>
       <c r="N7" s="12" t="n">
         <v>194.21</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02945543615916037</v>
+        <v>0.02944815602170135</v>
       </c>
     </row>
     <row r="8">
@@ -8023,7 +7372,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -8043,28 +7392,28 @@
         <v>0.02944182290746675</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.068</v>
+        <v>55.0775</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6893</v>
+        <v>56.6991</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6213</v>
+        <v>1.6216</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02944178107067625</v>
+        <v>0.0294421496981526</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6610.78</v>
+        <v>6611.71</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6806.45</v>
+        <v>6807.36</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.67</v>
+        <v>195.65</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02959862527568608</v>
+        <v>0.02959143701100018</v>
       </c>
     </row>
     <row r="9">
@@ -8072,7 +7421,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -8080,40 +7429,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2242</v>
+        <v>48.2241</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2817</v>
+        <v>48.281</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0575</v>
+        <v>0.0569</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001192347410636154</v>
+        <v>0.001179907971325541</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.8326</v>
+        <v>55.8376</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.9161</v>
+        <v>55.9206</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.0835</v>
+        <v>0.083</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.00149554203099981</v>
+        <v>0.001486453572503116</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6662.85</v>
+        <v>6665.67</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6691.74</v>
+        <v>6694.52</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.89</v>
+        <v>28.85</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004335982349895314</v>
+        <v>0.004328147057985169</v>
       </c>
     </row>
     <row r="10">
@@ -8121,7 +7470,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -8129,40 +7478,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2377</v>
+        <v>48.2378</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2759</v>
+        <v>48.2758</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007919117205007701</v>
+        <v>0.0007877639527507474</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.8099</v>
+        <v>55.815</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.919</v>
+        <v>55.9286</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1091</v>
+        <v>0.1136</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.001954850304336686</v>
+        <v>0.002035295171548867</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6659.12</v>
+        <v>6661.29</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6690.78</v>
+        <v>6692.94</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.66</v>
+        <v>31.65</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.00475438196037915</v>
+        <v>0.004751331949217044</v>
       </c>
     </row>
     <row r="11">
@@ -8170,7 +7519,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -8178,40 +7527,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9239</v>
+        <v>47.924</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>49.1614</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2375</v>
+        <v>1.2374</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02582218892869738</v>
+        <v>0.02582004840998247</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3879</v>
+        <v>55.4024</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6663</v>
+        <v>56.681</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2784</v>
+        <v>1.2786</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02308085339938867</v>
+        <v>0.02307842259541103</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6614.87</v>
+        <v>6614.85</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6723.1</v>
+        <v>6723.08</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>108.23</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01636162161917014</v>
+        <v>0.01636167108853564</v>
       </c>
     </row>
     <row r="12">
@@ -8219,7 +7568,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -8242,25 +7591,25 @@
         <v>55.3195</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4812</v>
+        <v>56.4909</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1617</v>
+        <v>1.1714</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02099982827032059</v>
+        <v>0.02117517331140014</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6607.97</v>
+        <v>6609.94</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6762.41</v>
+        <v>6764.43</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.44</v>
+        <v>154.49</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02337177680891408</v>
+        <v>0.02337237554349964</v>
       </c>
     </row>
     <row r="13">
@@ -8268,7 +7617,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -8276,40 +7625,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9981</v>
+        <v>47.9979</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6053</v>
+        <v>48.6049</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6072</v>
+        <v>0.607</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01265050074898798</v>
+        <v>0.01264638661274764</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5975</v>
+        <v>55.5966</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2586</v>
+        <v>56.2577</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.6611</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01189082242906605</v>
+        <v>0.01189101491817845</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6683.82</v>
+        <v>6678.06</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6738.14</v>
+        <v>6732.35</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.32</v>
+        <v>54.29</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008127089000002993</v>
+        <v>0.008129606502487249</v>
       </c>
     </row>
     <row r="14">
@@ -8317,7 +7666,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -8349,16 +7698,16 @@
         <v>0.02844300480419275</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6577.16</v>
+        <v>6573.4</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6820.13</v>
+        <v>6816.24</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.97</v>
+        <v>242.84</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694147626027039</v>
+        <v>0.03694283019441993</v>
       </c>
     </row>
     <row r="15">
@@ -8366,7 +7715,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -8374,40 +7723,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.998</v>
+        <v>47.9979</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6051</v>
+        <v>48.6049</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6071</v>
+        <v>0.607</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264844368515355</v>
+        <v>0.01264638661274764</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5959</v>
+        <v>55.6023</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2564</v>
+        <v>56.2623</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6605</v>
+        <v>0.66</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01188037247350974</v>
+        <v>0.01187001257142241</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6680.4</v>
+        <v>6681.92</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6734.79</v>
+        <v>6736.04</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.39</v>
+        <v>54.12</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008141728040237111</v>
+        <v>0.008099468416263588</v>
       </c>
     </row>
     <row r="16">
@@ -8415,7 +7764,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -8435,28 +7784,28 @@
         <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4302</v>
+        <v>55.4422</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5651</v>
+        <v>56.5773</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1349</v>
+        <v>1.1351</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047439843262337</v>
+        <v>0.02047357428096288</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6613.91</v>
+        <v>6614.91</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6817.49</v>
+        <v>6818.07</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.58</v>
+        <v>203.16</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03078058213673908</v>
+        <v>0.03071243599686163</v>
       </c>
     </row>
     <row r="17">
@@ -8464,7 +7813,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -8472,40 +7821,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.183</v>
+        <v>48.1928</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.242</v>
+        <v>48.2518</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>0.059</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001224498267023639</v>
+        <v>0.001224249265450441</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.643</v>
+        <v>55.672</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.811</v>
+        <v>55.839</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003019247704113725</v>
+        <v>0.002999712602385401</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6610.07</v>
+        <v>6611.85</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6705</v>
+        <v>6706.82</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>94.93000000000001</v>
+        <v>94.97</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01436142128600756</v>
+        <v>0.01436360473997444</v>
       </c>
     </row>
     <row r="18">
@@ -8513,7 +7862,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8521,40 +7870,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2181</v>
+        <v>48.2178</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3643</v>
+        <v>48.364</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0.1462</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003032056426943409</v>
+        <v>0.003032075291697257</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.8231</v>
+        <v>55.828</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9943</v>
+        <v>55.999</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1712</v>
+        <v>0.171</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003066830756443121</v>
+        <v>0.003062979150247187</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6669.56</v>
+        <v>6672.81</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6716.68</v>
+        <v>6719.89</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.12</v>
+        <v>47.08</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007064933818722674</v>
+        <v>0.007055498358262861</v>
       </c>
     </row>
     <row r="19">
@@ -8562,7 +7911,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8578,16 +7927,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6685.53</v>
+        <v>6684.59</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6881.39</v>
+        <v>6880.44</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.86</v>
+        <v>195.85</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02929610666618802</v>
+        <v>0.02929873036341795</v>
       </c>
     </row>
     <row r="20">
@@ -8595,7 +7944,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8603,40 +7952,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8071</v>
+        <v>47.8064</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6877</v>
+        <v>48.6889</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8806</v>
+        <v>0.8825</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01841985813822633</v>
+        <v>0.01845987148164262</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3609</v>
+        <v>55.3698</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.4133</v>
+        <v>56.4197</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0524</v>
+        <v>1.0499</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01900980656022572</v>
+        <v>0.01896160000577932</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6613.08</v>
+        <v>6614.8</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7057.74</v>
+        <v>7060.2</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>444.66</v>
+        <v>445.4</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06723947086682756</v>
+        <v>0.0673338574106549</v>
       </c>
     </row>
     <row r="21">
@@ -8644,7 +7993,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8652,40 +8001,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7514</v>
+        <v>47.7513</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>48.7543</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0029</v>
+        <v>1.003</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02100252558040183</v>
+        <v>0.02100466374737442</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3718</v>
+        <v>55.3789</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3808</v>
+        <v>56.3854</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.009</v>
+        <v>1.0065</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01822227198682362</v>
+        <v>0.01817479220425108</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6581.47</v>
+        <v>6582.5</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6833.43</v>
+        <v>6834.42</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.96</v>
+        <v>251.92</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03828324067419588</v>
+        <v>0.03827117356627421</v>
       </c>
     </row>
     <row r="22">
@@ -8693,7 +8042,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8713,28 +8062,28 @@
         <v>0.02422275962020458</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.202</v>
+        <v>55.2115</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>56.5488</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3468</v>
+        <v>1.3373</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02439766675120467</v>
+        <v>0.02422140314970613</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6604.18</v>
+        <v>6601.95</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6785.28</v>
+        <v>6783.02</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.1</v>
+        <v>181.07</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02742202665584524</v>
+        <v>0.0274267451283333</v>
       </c>
     </row>
     <row r="23">
@@ -8742,7 +8091,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8791,7 +8140,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8799,40 +8148,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6129</v>
+        <v>47.6865</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5986</v>
+        <v>48.6724</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9857</v>
+        <v>0.9859</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02070237267631251</v>
+        <v>0.02067461440869009</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1334</v>
+        <v>55.1413</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2772</v>
+        <v>56.2835</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1438</v>
+        <v>1.1422</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02074604504710393</v>
+        <v>0.0207140564331998</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6561.48</v>
+        <v>6563.64</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6735.43</v>
+        <v>6737.46</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>173.95</v>
+        <v>173.82</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02651078720044868</v>
+        <v>0.02648225679653363</v>
       </c>
     </row>
     <row r="25">
@@ -8840,7 +8189,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8881,7 +8230,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8889,40 +8238,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.227</v>
+        <v>48.2269</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2796</v>
+        <v>48.2797</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.0528</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001090675347834201</v>
+        <v>0.001094824672537526</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8305</v>
+        <v>55.8388</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.9073</v>
+        <v>55.9157</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001375592194230752</v>
+        <v>0.001377178592663166</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6658.35</v>
+        <v>6661.79</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6687.13</v>
+        <v>6690.54</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.78</v>
+        <v>28.75</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004322392184249852</v>
+        <v>0.004315656903024562</v>
       </c>
     </row>
     <row r="27">
@@ -8930,7 +8279,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8938,40 +8287,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.182</v>
+        <v>48.192</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.285</v>
+        <v>48.291</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.103</v>
+        <v>0.099</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002137727782159313</v>
+        <v>0.002054282868525896</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.652</v>
+        <v>55.665</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.883</v>
+        <v>55.904</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.231</v>
+        <v>0.239</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004150794221231942</v>
+        <v>0.004293541722806072</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6623</v>
+        <v>6624</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6683</v>
+        <v>6686</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.009059338668277217</v>
+        <v>0.009359903381642512</v>
       </c>
     </row>
     <row r="28">
@@ -8979,7 +8328,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8999,28 +8348,28 @@
         <v>0.0209375850589393</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.337</v>
+        <v>55.344</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.427</v>
+        <v>56.434</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01969748992536639</v>
+        <v>0.01969499855449552</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6662.57</v>
+        <v>6655.57</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6762.57</v>
+        <v>6755.57</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01500922316763651</v>
+        <v>0.01502500912769305</v>
       </c>
     </row>
     <row r="29">
@@ -9028,7 +8377,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -9044,16 +8393,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6686.42</v>
+        <v>6684.49</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6868.55</v>
+        <v>6866.61</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>182.13</v>
+        <v>182.12</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02723879146090135</v>
+        <v>0.02724516006456738</v>
       </c>
     </row>
     <row r="30">
@@ -9061,7 +8410,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -9081,28 +8430,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.1014</v>
+        <v>55.1109</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7587</v>
+        <v>56.7636</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6573</v>
+        <v>1.6527</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03007727571350274</v>
+        <v>0.02998862294028949</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6581.7</v>
+        <v>6584.82</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6779.29</v>
+        <v>6782.96</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>197.59</v>
+        <v>198.14</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03002111916374189</v>
+        <v>0.03009042008741317</v>
       </c>
     </row>
     <row r="31">
@@ -9110,7 +8459,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -9118,10 +8467,10 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.2768</v>
+        <v>48.297</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.2768</v>
+        <v>48.297</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0</v>
@@ -9130,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.9056</v>
+        <v>55.9351</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>55.9056</v>
+        <v>55.9351</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0</v>
@@ -9142,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6677.96</v>
+        <v>6682.99</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6677.96</v>
+        <v>6682.99</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -9159,7 +8508,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -9170,37 +8519,37 @@
         <v>47.8519</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6538</v>
+        <v>48.6536</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8017</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01675795527450321</v>
+        <v>0.01675377571214518</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4453</v>
+        <v>55.4553</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2957</v>
+        <v>56.3054</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8504</v>
+        <v>0.8501</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01533763907851522</v>
+        <v>0.01532946354992219</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6610.7</v>
+        <v>6614.04</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6807.01</v>
+        <v>6810.1</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.31</v>
+        <v>196.06</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02969579620917603</v>
+        <v>0.02964300185665645</v>
       </c>
     </row>
     <row r="33">
@@ -9208,7 +8557,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -9228,28 +8577,28 @@
         <v>0.004219829877724615</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7495</v>
+        <v>55.759</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9741</v>
+        <v>55.9836</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004028735683728105</v>
+        <v>0.004028049283523735</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6650.95</v>
+        <v>6649.89</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6704.37</v>
+        <v>6703.31</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>53.42</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.00803193528744014</v>
+        <v>0.008033215587024748</v>
       </c>
     </row>
     <row r="34">
@@ -9257,7 +8606,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -9265,40 +8614,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8944</v>
+        <v>47.8942</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8554</v>
+        <v>48.8552</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006497628115187</v>
+        <v>0.02006506006990408</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4805</v>
+        <v>55.4892</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5825</v>
+        <v>56.5913</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.102</v>
+        <v>1.1021</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986283468966574</v>
+        <v>0.01986152260259654</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6616.12</v>
+        <v>6615.97</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6760.72</v>
+        <v>6760.57</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.0218557099931682</v>
+        <v>0.02185620551483758</v>
       </c>
     </row>
     <row r="35">
@@ -9306,7 +8655,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -9314,28 +8663,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.194</v>
+        <v>48.199</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.239</v>
+        <v>48.25</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.0009337261899821554</v>
+        <v>0.001058113238863877</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.664</v>
+        <v>55.69</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.798</v>
+        <v>55.819</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.134</v>
+        <v>0.129</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002407300948548434</v>
+        <v>0.002316394325731729</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -9347,7 +8696,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -9370,25 +8719,25 @@
         <v>55.19</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.32</v>
+        <v>56.33</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02047472368182642</v>
+        <v>0.02065591592679833</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6585.46</v>
+        <v>6584.14</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6787.98</v>
+        <v>6786.1</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>202.52</v>
+        <v>201.96</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03075259738879289</v>
+        <v>0.03067370985428621</v>
       </c>
     </row>
     <row r="37">
@@ -9396,7 +8745,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -9416,28 +8765,28 @@
         <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4491</v>
+        <v>55.4447</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5709</v>
+        <v>56.5664</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1218</v>
+        <v>1.1217</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023116696213284</v>
+        <v>0.02023096887529376</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6652.77</v>
+        <v>6646.78</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6787.1</v>
+        <v>6780.98</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.33</v>
+        <v>134.2</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019158936803768</v>
+        <v>0.02019022744847881</v>
       </c>
     </row>
     <row r="38">
@@ -9445,7 +8794,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9465,28 +8814,28 @@
         <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4475</v>
+        <v>55.4571</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2582</v>
+        <v>56.2678</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>0.8107</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01462103791875197</v>
+        <v>0.01461850691796001</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6616.73</v>
+        <v>6618.5</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6750.33</v>
+        <v>6752.13</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.6</v>
+        <v>133.63</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019124250196094</v>
+        <v>0.02019037546271814</v>
       </c>
     </row>
     <row r="39">
@@ -9494,7 +8843,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -9505,37 +8854,37 @@
         <v>47.7683</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7652</v>
+        <v>48.7651</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02086948876137522</v>
+        <v>0.02086739532283962</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2729</v>
+        <v>55.2806</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4822</v>
+        <v>56.4894</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2093</v>
+        <v>1.2088</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02187871452375396</v>
+        <v>0.02186662228702293</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6638.17</v>
+        <v>6639.21</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6848.85</v>
+        <v>6850.01</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.68</v>
+        <v>210.8</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03173766263895019</v>
+        <v>0.03175076552782635</v>
       </c>
     </row>
   </sheetData>
@@ -42837,7 +42186,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.4783564814814815</v>
+        <v>0.4871875</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42921,7 +42270,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023116696213284</v>
+        <v>0.02023096887529376</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42929,10 +42278,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4491</v>
+        <v>55.4447</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5709</v>
+        <v>56.5664</v>
       </c>
     </row>
     <row r="7">
@@ -42974,7 +42323,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019158936803768</v>
+        <v>0.02019022744847881</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42982,10 +42331,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6652.77</v>
+        <v>6646.78</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6787.1</v>
+        <v>6780.98</v>
       </c>
     </row>
     <row r="8">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -585,10 +585,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -677,10 +677,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -769,10 +769,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -861,10 +861,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -953,10 +953,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -1120,10 +1120,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -1307,10 +1307,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -1494,10 +1494,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -1681,10 +1681,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -1868,10 +1868,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2055,10 +2055,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2242,10 +2242,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2429,10 +2429,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2616,10 +2616,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2803,10 +2803,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -2990,10 +2990,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3082,10 +3082,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3174,10 +3174,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3266,10 +3266,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3358,10 +3358,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3525,10 +3525,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3712,10 +3712,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3899,10 +3899,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -3991,10 +3991,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -4083,10 +4083,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -4175,10 +4175,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -4267,10 +4267,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -5679,10 +5679,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -5866,10 +5866,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -6053,10 +6053,10 @@
                   <v>28.08</v>
                 </pt>
                 <pt idx="1">
-                  <v>29.08 Cmt</v>
+                  <v>🔵 29.08 Cmt</v>
                 </pt>
                 <pt idx="2">
-                  <v>30.08 Paz</v>
+                  <v>🔴 30.08 Paz</v>
                 </pt>
                 <pt idx="3">
                   <v>31.08</v>
@@ -7078,7 +7078,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7098,28 +7098,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>55.0059</v>
+        <v>54.9729</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5692</v>
+        <v>56.5401</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5633</v>
+        <v>1.5672</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02842058760969278</v>
+        <v>0.02850859241553565</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6536.37</v>
+        <v>6523.14</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6772.41</v>
+        <v>6758.76</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.04</v>
+        <v>235.62</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03611178681745372</v>
+        <v>0.03612064128625171</v>
       </c>
     </row>
     <row r="3">
@@ -7127,7 +7127,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7147,28 +7147,28 @@
         <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.469</v>
+        <v>55.426</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.384</v>
+        <v>56.34</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.915</v>
+        <v>0.914</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01649570030106906</v>
+        <v>0.01649045574279219</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6614.98</v>
+        <v>6598.1</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6751.04</v>
+        <v>6733.81</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>136.06</v>
+        <v>135.71</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02056846732718769</v>
+        <v>0.02056804231521196</v>
       </c>
     </row>
     <row r="4">
@@ -7176,7 +7176,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7184,40 +7184,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.078</v>
+        <v>48.081</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.376</v>
+        <v>48.374</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.298</v>
+        <v>0.293</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006198261158950039</v>
+        <v>0.006093883238701359</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.509</v>
+        <v>55.476</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.023</v>
+        <v>55.988</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.514</v>
+        <v>0.512</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009259759678610676</v>
+        <v>0.009229216237652318</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6673.88</v>
+        <v>6663.21</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6741.22</v>
+        <v>6729.36</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>67.34</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01009008253070178</v>
+        <v>0.009927647485221087</v>
       </c>
     </row>
     <row r="5">
@@ -7225,7 +7225,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7236,37 +7236,37 @@
         <v>48.13</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.34</v>
+        <v>48.33</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.004363183045917307</v>
+        <v>0.00415541242468315</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.63</v>
+        <v>55.594</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.984</v>
+        <v>55.938</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.354</v>
+        <v>0.344</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006363472946252022</v>
+        <v>0.00618771809907544</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6588.32</v>
+        <v>6572.1</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6775</v>
+        <v>6755</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>186.68</v>
+        <v>182.9</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.0283349928358064</v>
+        <v>0.0278297652196406</v>
       </c>
     </row>
     <row r="6">
@@ -7274,7 +7274,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7282,40 +7282,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4528</v>
+        <v>47.4534</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.729</v>
+        <v>48.7297</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2762</v>
+        <v>1.2763</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02689409265628161</v>
+        <v>0.02689585993838166</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0575</v>
+        <v>55.0203</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.422</v>
+        <v>56.3848</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>1.3645</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02478318121963402</v>
+        <v>0.02479993747762189</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6598.14</v>
+        <v>6581.24</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6749.04</v>
+        <v>6732.31</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>150.9</v>
+        <v>151.07</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02287008156844201</v>
+        <v>0.02295464076678559</v>
       </c>
     </row>
     <row r="7">
@@ -7323,7 +7323,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7343,28 +7343,28 @@
         <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.781</v>
+        <v>54.743</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>57.012</v>
+        <v>56.973</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.231</v>
+        <v>2.23</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04072579909092568</v>
+        <v>0.04073580183767787</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6594.98</v>
+        <v>6578.25</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6789.19</v>
+        <v>6772.46</v>
       </c>
       <c r="N7" s="12" t="n">
         <v>194.21</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02944815602170135</v>
+        <v>0.02952304944324098</v>
       </c>
     </row>
     <row r="8">
@@ -7372,7 +7372,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7380,40 +7380,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5548</v>
+        <v>47.5551</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9549</v>
+        <v>48.9552</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944182290746675</v>
+        <v>0.02944163717456172</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0775</v>
+        <v>55.0398</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6991</v>
+        <v>56.6603</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6216</v>
+        <v>1.6205</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.0294421496981526</v>
+        <v>0.02944233082242305</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6611.71</v>
+        <v>6595.09</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6807.36</v>
+        <v>6790.33</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.65</v>
+        <v>195.24</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02959143701100018</v>
+        <v>0.02960384164583046</v>
       </c>
     </row>
     <row r="9">
@@ -7421,7 +7421,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7429,40 +7429,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2241</v>
+        <v>48.2247</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.281</v>
+        <v>48.2816</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>0.0569</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001179907971325541</v>
+        <v>0.001179893291197249</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.8376</v>
+        <v>55.7992</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.9206</v>
+        <v>55.8824</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.083</v>
+        <v>0.0832</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001486453572503116</v>
+        <v>0.001491060803739122</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6665.67</v>
+        <v>6648.06</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6694.52</v>
+        <v>6676.93</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.85</v>
+        <v>28.87</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004328147057985169</v>
+        <v>0.004342620253126477</v>
       </c>
     </row>
     <row r="10">
@@ -7470,7 +7470,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7478,40 +7478,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2378</v>
+        <v>48.2382</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2758</v>
+        <v>48.2764</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0382</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007877639527507474</v>
+        <v>0.0007919035121542678</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.815</v>
+        <v>55.7767</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.9286</v>
+        <v>55.8904</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1136</v>
+        <v>0.1137</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002035295171548867</v>
+        <v>0.002038485604203906</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6661.29</v>
+        <v>6644.07</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6692.94</v>
+        <v>6675.7</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.65</v>
+        <v>31.63</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004751331949217044</v>
+        <v>0.004760636176319635</v>
       </c>
     </row>
     <row r="11">
@@ -7519,7 +7519,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7527,40 +7527,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.924</v>
+        <v>47.9238</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1614</v>
+        <v>49.162</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2374</v>
+        <v>1.2382</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02582004840998247</v>
+        <v>0.02583684933164733</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.4024</v>
+        <v>55.3929</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.681</v>
+        <v>56.6712</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2786</v>
+        <v>1.2783</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02307842259541103</v>
+        <v>0.02307696473735804</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6614.85</v>
+        <v>6603.89</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6723.08</v>
+        <v>6712.04</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.23</v>
+        <v>108.15</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01636167108853564</v>
+        <v>0.01637671130197505</v>
       </c>
     </row>
     <row r="12">
@@ -7568,7 +7568,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7588,28 +7588,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.3195</v>
+        <v>55.2908</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4909</v>
+        <v>56.447</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1714</v>
+        <v>1.1562</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02117517331140014</v>
+        <v>0.02091125467528052</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6609.94</v>
+        <v>6593.27</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6764.43</v>
+        <v>6747.42</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.49</v>
+        <v>154.15</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02337237554349964</v>
+        <v>0.0233799010202828</v>
       </c>
     </row>
     <row r="13">
@@ -7617,7 +7617,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7625,40 +7625,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9979</v>
+        <v>47.9984</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6049</v>
+        <v>48.6053</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6069</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264638661274764</v>
+        <v>0.01264417147238241</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5966</v>
+        <v>55.563</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2577</v>
+        <v>56.223</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6611</v>
+        <v>0.66</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01189101491817845</v>
+        <v>0.0118784082932887</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6678.06</v>
+        <v>6667.55</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6732.35</v>
+        <v>6721.57</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.29</v>
+        <v>54.02</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008129606502487249</v>
+        <v>0.008101926494739446</v>
       </c>
     </row>
     <row r="14">
@@ -7666,7 +7666,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7686,28 +7686,28 @@
         <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.952</v>
+        <v>54.928</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.515</v>
+        <v>56.491</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02844300480419275</v>
+        <v>0.02845543256626857</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6573.4</v>
+        <v>6565.63</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6816.24</v>
+        <v>6808.18</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.84</v>
+        <v>242.55</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694283019441993</v>
+        <v>0.03694238024378468</v>
       </c>
     </row>
     <row r="15">
@@ -7715,7 +7715,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7723,40 +7723,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9979</v>
+        <v>47.9984</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6049</v>
+        <v>48.6054</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>0.607</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264638661274764</v>
+        <v>0.01264625487516251</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.6023</v>
+        <v>55.5645</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2623</v>
+        <v>56.2243</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.66</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01187001257142241</v>
+        <v>0.01187448820739861</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6681.92</v>
+        <v>6665.24</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6736.04</v>
+        <v>6719.66</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.12</v>
+        <v>54.42</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008099468416263588</v>
+        <v>0.008164747255912765</v>
       </c>
     </row>
     <row r="16">
@@ -7764,7 +7764,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7784,28 +7784,28 @@
         <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4422</v>
+        <v>55.4063</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5773</v>
+        <v>56.5406</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1351</v>
+        <v>1.1343</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047357428096288</v>
+        <v>0.02047240115293748</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6614.91</v>
+        <v>6600.43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6818.07</v>
+        <v>6803.15</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.16</v>
+        <v>202.72</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03071243599686163</v>
+        <v>0.03071315050686092</v>
       </c>
     </row>
     <row r="17">
@@ -7813,7 +7813,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7821,40 +7821,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.1928</v>
+        <v>48.2001</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.2518</v>
+        <v>48.262</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.059</v>
+        <v>0.0619</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001224249265450441</v>
+        <v>0.001284229700768256</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.672</v>
+        <v>55.648</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.839</v>
+        <v>55.819</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.002999712602385401</v>
+        <v>0.003072886716503738</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6611.85</v>
+        <v>6596.45</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6706.82</v>
+        <v>6691.71</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>94.97</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01436360473997444</v>
+        <v>0.01444110089517847</v>
       </c>
     </row>
     <row r="18">
@@ -7862,7 +7862,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2178</v>
+        <v>48.2184</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.364</v>
+        <v>48.3646</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0.1462</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003032075291697257</v>
+        <v>0.003032037562424303</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.828</v>
+        <v>55.7922</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.999</v>
+        <v>55.9632</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.171</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003062979150247187</v>
+        <v>0.003064944562143096</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6672.81</v>
+        <v>6654.79</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6719.89</v>
+        <v>6701.75</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.08</v>
+        <v>46.96</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007055498358262861</v>
+        <v>0.007056571281738418</v>
       </c>
     </row>
     <row r="19">
@@ -7911,7 +7911,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -7927,16 +7927,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6684.59</v>
+        <v>6672.01</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6880.44</v>
+        <v>6867.62</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.85</v>
+        <v>195.61</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02929873036341795</v>
+        <v>0.02931800162170021</v>
       </c>
     </row>
     <row r="20">
@@ -7944,7 +7944,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -7952,40 +7952,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8064</v>
+        <v>47.7241</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6889</v>
+        <v>48.6807</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8825</v>
+        <v>0.9566</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01845987148164262</v>
+        <v>0.02004438009307666</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3698</v>
+        <v>55.2361</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.4197</v>
+        <v>56.3714</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0499</v>
+        <v>1.1353</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01896160000577932</v>
+        <v>0.02055358723733211</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6614.8</v>
+        <v>6597.45</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7060.2</v>
+        <v>7042.64</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.4</v>
+        <v>445.19</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.0673338574106549</v>
+        <v>0.06747910177417032</v>
       </c>
     </row>
     <row r="21">
@@ -7993,7 +7993,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8001,40 +8001,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7513</v>
+        <v>47.7516</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7543</v>
+        <v>48.7545</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.003</v>
+        <v>1.0029</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02100466374737442</v>
+        <v>0.02100243761465584</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3789</v>
+        <v>55.3406</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3854</v>
+        <v>56.347</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0065</v>
+        <v>1.0064</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01817479220425108</v>
+        <v>0.01818556358261385</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6582.5</v>
+        <v>6566.33</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6834.42</v>
+        <v>6818.24</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.92</v>
+        <v>251.91</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03827117356627421</v>
+        <v>0.03836389581394782</v>
       </c>
     </row>
     <row r="22">
@@ -8042,7 +8042,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8050,40 +8050,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6783</v>
+        <v>47.6787</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8332</v>
+        <v>48.8337</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1549</v>
+        <v>1.155</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02422275962020458</v>
+        <v>0.02422465377621454</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.2115</v>
+        <v>55.1737</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5488</v>
+        <v>56.5151</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3373</v>
+        <v>1.3414</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02422140314970613</v>
+        <v>0.02431230821931464</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6601.95</v>
+        <v>6592.4</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6783.02</v>
+        <v>6774.4</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.07</v>
+        <v>182</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.0274267451283333</v>
+        <v>0.02760754808567441</v>
       </c>
     </row>
     <row r="23">
@@ -8091,7 +8091,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8099,16 +8099,16 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.22</v>
+        <v>48.24</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>48.23</v>
+        <v>48.25</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002073828287017835</v>
+        <v>0.0002072968490878939</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>55.7</v>
@@ -8140,7 +8140,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8148,40 +8148,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6865</v>
+        <v>47.6131</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.6724</v>
+        <v>48.5992</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9859</v>
+        <v>0.9861</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02067461440869009</v>
+        <v>0.02071068676477692</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1413</v>
+        <v>55.105</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2835</v>
+        <v>56.2468</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1422</v>
+        <v>1.1418</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.0207140564331998</v>
+        <v>0.02072044279103529</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6563.64</v>
+        <v>6547.71</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6737.46</v>
+        <v>6721.33</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>173.82</v>
+        <v>173.62</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02648225679653363</v>
+        <v>0.02651614075760838</v>
       </c>
     </row>
     <row r="25">
@@ -8189,7 +8189,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8238,40 +8238,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2269</v>
+        <v>48.2272</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2797</v>
+        <v>48.2802</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0528</v>
+        <v>0.053</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001094824672537526</v>
+        <v>0.001098964899475814</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8388</v>
+        <v>55.8012</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.9157</v>
+        <v>55.8776</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0769</v>
+        <v>0.0764</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001377178592663166</v>
+        <v>0.001369146183236203</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6661.79</v>
+        <v>6643.48</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6690.54</v>
+        <v>6672.33</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.75</v>
+        <v>28.85</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004315656903024562</v>
+        <v>0.004342603575234667</v>
       </c>
     </row>
     <row r="27">
@@ -8279,7 +8279,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8287,40 +8287,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.192</v>
+        <v>48.194</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>48.291</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002054282868525896</v>
+        <v>0.002012698676183757</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>55.665</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.904</v>
+        <v>55.866</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.239</v>
+        <v>0.201</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004293541722806072</v>
+        <v>0.003610886553489625</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6624</v>
+        <v>6620</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6686</v>
+        <v>6668</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.009359903381642512</v>
+        <v>0.007250755287009063</v>
       </c>
     </row>
     <row r="28">
@@ -8328,7 +8328,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8336,40 +8336,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.761</v>
+        <v>47.7615</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.761</v>
+        <v>48.7615</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.0209375850589393</v>
+        <v>0.02093736586999989</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.344</v>
+        <v>55.31</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.434</v>
+        <v>56.4</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01969499855449552</v>
+        <v>0.01970710540589405</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6655.57</v>
+        <v>6646.28</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6755.57</v>
+        <v>6746.28</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01502500912769305</v>
+        <v>0.01504601070072281</v>
       </c>
     </row>
     <row r="29">
@@ -8377,7 +8377,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8393,16 +8393,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6684.49</v>
+        <v>6672.01</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6866.61</v>
+        <v>6853.91</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>182.12</v>
+        <v>181.9</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02724516006456738</v>
+        <v>0.02726314858640799</v>
       </c>
     </row>
     <row r="30">
@@ -8410,7 +8410,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8430,28 +8430,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.1109</v>
+        <v>55.0776</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7636</v>
+        <v>56.7293</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6527</v>
+        <v>1.6517</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.02998862294028949</v>
+        <v>0.0299885979055006</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6584.82</v>
+        <v>6567.5</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6782.96</v>
+        <v>6765.12</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>198.14</v>
+        <v>197.62</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03009042008741317</v>
+        <v>0.03009059763989341</v>
       </c>
     </row>
     <row r="31">
@@ -8459,7 +8459,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.297</v>
+        <v>48.2964</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.297</v>
+        <v>48.2964</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0</v>
@@ -8479,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.9351</v>
+        <v>55.8988</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>55.9351</v>
+        <v>55.8988</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0</v>
@@ -8491,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6682.99</v>
+        <v>6664.82</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6682.99</v>
+        <v>6664.82</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -8508,7 +8508,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8519,37 +8519,37 @@
         <v>47.8519</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6536</v>
+        <v>48.6539</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8017</v>
+        <v>0.802</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01675377571214518</v>
+        <v>0.01676004505568222</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4553</v>
+        <v>55.4265</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.3054</v>
+        <v>56.277</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8501</v>
+        <v>0.8505</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01532946354992219</v>
+        <v>0.01534464561175611</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6614.04</v>
+        <v>6599.48</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6810.1</v>
+        <v>6795.93</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.06</v>
+        <v>196.45</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02964300185665645</v>
+        <v>0.02976749683308382</v>
       </c>
     </row>
     <row r="33">
@@ -8557,7 +8557,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8565,40 +8565,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1536</v>
+        <v>48.1539</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3568</v>
+        <v>48.3571</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004219829877724615</v>
+        <v>0.004219803588079054</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.759</v>
+        <v>55.7173</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9836</v>
+        <v>55.9418</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2246</v>
+        <v>0.2245</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004028049283523735</v>
+        <v>0.004029269185692774</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6649.89</v>
+        <v>6632.87</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6703.31</v>
+        <v>6686.15</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.42</v>
+        <v>53.28</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008033215587024748</v>
+        <v>0.008032721883588854</v>
       </c>
     </row>
     <row r="34">
@@ -8606,7 +8606,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8614,40 +8614,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8942</v>
+        <v>47.8943</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8552</v>
+        <v>48.8553</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006506006990408</v>
+        <v>0.0200650181754405</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4892</v>
+        <v>55.4732</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5913</v>
+        <v>56.5752</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.1021</v>
+        <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986152260259654</v>
+        <v>0.01986544854091706</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6615.97</v>
+        <v>6600.33</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6760.57</v>
+        <v>6744.93</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02185620551483758</v>
+        <v>0.02190799550931545</v>
       </c>
     </row>
     <row r="35">
@@ -8655,7 +8655,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8663,28 +8663,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.199</v>
+        <v>48.224</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.25</v>
+        <v>48.265</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.051</v>
+        <v>0.041</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.001058113238863877</v>
+        <v>0.0008501990710019908</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.69</v>
+        <v>55.689</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.819</v>
+        <v>55.799</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.129</v>
+        <v>0.11</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002316394325731729</v>
+        <v>0.001975255436441667</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8696,7 +8696,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8716,28 +8716,28 @@
         <v>0.02098635886673662</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.19</v>
+        <v>55.16</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.33</v>
+        <v>56.29</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02065591592679833</v>
+        <v>0.02048585931834663</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6584.14</v>
+        <v>6570.03</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6786.1</v>
+        <v>6772.25</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>201.96</v>
+        <v>202.22</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03067370985428621</v>
+        <v>0.03077915930368659</v>
       </c>
     </row>
     <row r="37">
@@ -8745,7 +8745,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8765,28 +8765,28 @@
         <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4447</v>
+        <v>55.4349</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5664</v>
+        <v>56.5564</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1217</v>
+        <v>1.1215</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023096887529376</v>
+        <v>0.02023093755017146</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6646.78</v>
+        <v>6647.04</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6780.98</v>
+        <v>6781.26</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.2</v>
+        <v>134.22</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019022744847881</v>
+        <v>0.02019244656268053</v>
       </c>
     </row>
     <row r="38">
@@ -8794,7 +8794,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8814,28 +8814,28 @@
         <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4571</v>
+        <v>55.4161</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2678</v>
+        <v>56.2262</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8107</v>
+        <v>0.8101</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461850691796001</v>
+        <v>0.01461849534702009</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6618.5</v>
+        <v>6601.38</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6752.13</v>
+        <v>6734.67</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.63</v>
+        <v>133.29</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019037546271814</v>
+        <v>0.0201912327422448</v>
       </c>
     </row>
     <row r="39">
@@ -8843,7 +8843,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8851,40 +8851,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7683</v>
+        <v>47.7687</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7651</v>
+        <v>48.7655</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>0.9968</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02086739532283962</v>
+        <v>0.0208672205858648</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2806</v>
+        <v>55.2409</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4894</v>
+        <v>56.4493</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2088</v>
+        <v>1.2084</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02186662228702293</v>
+        <v>0.02187509616968587</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6639.21</v>
+        <v>6621.58</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6850.01</v>
+        <v>6831.73</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.8</v>
+        <v>210.15</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03175076552782635</v>
+        <v>0.03173713826609359</v>
       </c>
     </row>
   </sheetData>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.4871875</v>
+        <v>0.4999768518518519</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42270,7 +42270,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023096887529376</v>
+        <v>0.02023093755017146</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42278,10 +42278,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4447</v>
+        <v>55.4349</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5664</v>
+        <v>56.5564</v>
       </c>
     </row>
     <row r="7">
@@ -42323,7 +42323,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019022744847881</v>
+        <v>0.02019244656268053</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42331,10 +42331,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6646.78</v>
+        <v>6647.04</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6780.98</v>
+        <v>6781.26</v>
       </c>
     </row>
     <row r="8">
@@ -42376,7 +42376,7 @@
       </c>
       <c r="B9" s="62" t="n"/>
       <c r="C9" s="73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="62" t="n"/>
       <c r="F9" s="62" t="inlineStr">
@@ -42977,7 +42977,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29.08 Cmt</t>
+          <t>🔵 29.08 Cmt</t>
         </is>
       </c>
       <c r="B3" s="55" t="n">
@@ -43079,7 +43079,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30.08 Paz</t>
+          <t>🔴 30.08 Paz</t>
         </is>
       </c>
       <c r="B4" s="55" t="n">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -7078,7 +7078,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7098,28 +7098,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9729</v>
+        <v>54.9733</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5401</v>
+        <v>56.5405</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>1.5672</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02850859241553565</v>
+        <v>0.02850838497961737</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6523.14</v>
+        <v>6522.09</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6758.76</v>
+        <v>6757.84</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>235.62</v>
+        <v>235.75</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03612064128625171</v>
+        <v>0.03614638865762355</v>
       </c>
     </row>
     <row r="3">
@@ -7127,7 +7127,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7159,16 +7159,16 @@
         <v>0.01649045574279219</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6598.1</v>
+        <v>6599.06</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6733.81</v>
+        <v>6734.34</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>135.71</v>
+        <v>135.28</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02056804231521196</v>
+        <v>0.02049988937818416</v>
       </c>
     </row>
     <row r="4">
@@ -7176,7 +7176,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7196,28 +7196,28 @@
         <v>0.006093883238701359</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.476</v>
+        <v>55.473</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>55.988</v>
+        <v>55.983</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.512</v>
+        <v>0.51</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009229216237652318</v>
+        <v>0.00919366178140717</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6663.21</v>
+        <v>6663.18</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6729.36</v>
+        <v>6730.38</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>66.15000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.009927647485221087</v>
+        <v>0.01008527459861507</v>
       </c>
     </row>
     <row r="5">
@@ -7225,7 +7225,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7233,40 +7233,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.13</v>
+        <v>48.18</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.33</v>
+        <v>48.37</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.00415541242468315</v>
+        <v>0.00394354503943545</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.594</v>
+        <v>55.658</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.938</v>
+        <v>55.978</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.344</v>
+        <v>0.32</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.00618771809907544</v>
+        <v>0.005749398109885372</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6572.1</v>
+        <v>6600.17</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6755</v>
+        <v>6770</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>182.9</v>
+        <v>169.83</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.0278297652196406</v>
+        <v>0.02573115540963338</v>
       </c>
     </row>
     <row r="6">
@@ -7274,7 +7274,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7282,40 +7282,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4534</v>
+        <v>47.4536</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7297</v>
+        <v>48.7303</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2763</v>
+        <v>1.2767</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02689585993838166</v>
+        <v>0.02690417586863799</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0203</v>
+        <v>55.0165</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.3848</v>
+        <v>56.3818</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3645</v>
+        <v>1.3653</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02479993747762189</v>
+        <v>0.02481619150618451</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6581.24</v>
+        <v>6595.52</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6732.31</v>
+        <v>6746.54</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>151.07</v>
+        <v>151.02</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02295464076678559</v>
+        <v>0.02289736063267188</v>
       </c>
     </row>
     <row r="7">
@@ -7323,7 +7323,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7334,37 +7334,37 @@
         <v>47.302</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.225</v>
+        <v>49.226</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.923</v>
+        <v>1.924</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04065367214916916</v>
+        <v>0.04067481290431695</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.743</v>
+        <v>54.738</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.973</v>
+        <v>56.974</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.23</v>
+        <v>2.236</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04073580183767787</v>
+        <v>0.040849135883664</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6578.25</v>
+        <v>6589.45</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6772.46</v>
+        <v>6783.97</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.21</v>
+        <v>194.52</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02952304944324098</v>
+        <v>0.02951991440863805</v>
       </c>
     </row>
     <row r="8">
@@ -7372,7 +7372,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7380,40 +7380,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5551</v>
+        <v>47.555</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9552</v>
+        <v>48.9551</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944163717456172</v>
+        <v>0.02944169908526969</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0398</v>
+        <v>55.0301</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6603</v>
+        <v>56.6552</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6205</v>
+        <v>1.6251</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02944233082242305</v>
+        <v>0.02953111115553125</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6595.09</v>
+        <v>6600.75</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6790.33</v>
+        <v>6796.06</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.24</v>
+        <v>195.31</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02960384164583046</v>
+        <v>0.02958906184903231</v>
       </c>
     </row>
     <row r="9">
@@ -7421,7 +7421,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7429,40 +7429,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2247</v>
+        <v>48.2245</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2816</v>
+        <v>48.2821</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0569</v>
+        <v>0.0576</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001179893291197249</v>
+        <v>0.001194413627927713</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.7992</v>
+        <v>55.7996</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.8824</v>
+        <v>55.8827</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.0832</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001491060803739122</v>
+        <v>0.001489257987512455</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6648.06</v>
+        <v>6659.64</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6676.93</v>
+        <v>6688.18</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.87</v>
+        <v>28.54</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004342620253126477</v>
+        <v>0.004285516934849331</v>
       </c>
     </row>
     <row r="10">
@@ -7470,7 +7470,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7478,40 +7478,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2382</v>
+        <v>48.2381</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2764</v>
+        <v>48.2772</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0391</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007919035121542678</v>
+        <v>0.0008105626050777289</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>55.7767</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.8904</v>
+        <v>55.8867</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1137</v>
+        <v>0.11</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002038485604203906</v>
+        <v>0.001972149661059188</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6644.07</v>
+        <v>6655.84</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6675.7</v>
+        <v>6687.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.63</v>
+        <v>31.81</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004760636176319635</v>
+        <v>0.004779261520709632</v>
       </c>
     </row>
     <row r="11">
@@ -7519,7 +7519,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7527,40 +7527,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9238</v>
+        <v>47.9241</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.162</v>
+        <v>49.1615</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2382</v>
+        <v>1.2374</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02583684933164733</v>
+        <v>0.02581999453302201</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3929</v>
+        <v>55.3594</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6712</v>
+        <v>56.6321</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2783</v>
+        <v>1.2727</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02307696473735804</v>
+        <v>0.02298977228799445</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6603.89</v>
+        <v>6601.47</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6712.04</v>
+        <v>6709.49</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.15</v>
+        <v>108.02</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01637671130197505</v>
+        <v>0.01636302217536397</v>
       </c>
     </row>
     <row r="12">
@@ -7568,7 +7568,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7588,28 +7588,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.2908</v>
+        <v>55.2861</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>56.447</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1562</v>
+        <v>1.1609</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02091125467528052</v>
+        <v>0.02099804471648389</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6593.27</v>
+        <v>6606.01</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6747.42</v>
+        <v>6760.81</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.15</v>
+        <v>154.8</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.0233799010202828</v>
+        <v>0.02343320703420067</v>
       </c>
     </row>
     <row r="13">
@@ -7617,7 +7617,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7625,40 +7625,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9984</v>
+        <v>47.9985</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6053</v>
+        <v>48.606</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6069</v>
+        <v>0.6075</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264417147238241</v>
+        <v>0.01265664552017251</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.563</v>
+        <v>55.5613</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.223</v>
+        <v>56.2222</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.66</v>
+        <v>0.6609</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.0118784082932887</v>
+        <v>0.01189497006009579</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6667.55</v>
+        <v>6670.14</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6721.57</v>
+        <v>6724.29</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.02</v>
+        <v>54.15</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008101926494739446</v>
+        <v>0.008118270381131431</v>
       </c>
     </row>
     <row r="14">
@@ -7666,7 +7666,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7674,40 +7674,40 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.454</v>
+        <v>47.455</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>48.804</v>
+        <v>48.805</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02844860285750411</v>
+        <v>0.02844800337161522</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.928</v>
+        <v>54.914</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.491</v>
+        <v>56.477</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02845543256626857</v>
+        <v>0.028462687110755</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6565.63</v>
+        <v>6562.01</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6808.18</v>
+        <v>6804.43</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.55</v>
+        <v>242.42</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694238024378468</v>
+        <v>0.03694294888304041</v>
       </c>
     </row>
     <row r="15">
@@ -7715,7 +7715,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7723,40 +7723,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9984</v>
+        <v>47.9988</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6054</v>
+        <v>48.6058</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>0.607</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264625487516251</v>
+        <v>0.01264614948707051</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5645</v>
+        <v>55.5608</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2243</v>
+        <v>56.2216</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01187448820739861</v>
+        <v>0.01189327727462528</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6665.24</v>
+        <v>6679.6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6719.66</v>
+        <v>6734.63</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.42</v>
+        <v>55.03</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008164747255912765</v>
+        <v>0.008238517276483621</v>
       </c>
     </row>
     <row r="16">
@@ -7764,7 +7764,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7772,40 +7772,40 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.8672</v>
+        <v>47.8675</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.8472</v>
+        <v>48.8475</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0.98</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02047330948958786</v>
+        <v>0.02047318117720792</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4063</v>
+        <v>55.3947</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5406</v>
+        <v>56.5288</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1343</v>
+        <v>1.1341</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047240115293748</v>
+        <v>0.02047307774931537</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6600.43</v>
+        <v>6596.25</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6803.15</v>
+        <v>6798.84</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>202.72</v>
+        <v>202.59</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03071315050686092</v>
+        <v>0.03071290505969301</v>
       </c>
     </row>
     <row r="17">
@@ -7813,7 +7813,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7821,40 +7821,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.2001</v>
+        <v>48.24</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.262</v>
+        <v>48.309</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.0619</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001284229700768256</v>
+        <v>0.001430348258706468</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.648</v>
+        <v>55.682</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.819</v>
+        <v>55.86</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.171</v>
+        <v>0.178</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003072886716503738</v>
+        <v>0.003196724255594268</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6596.45</v>
+        <v>6616.79</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6691.71</v>
+        <v>6705.79</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>95.26000000000001</v>
+        <v>89</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01444110089517847</v>
+        <v>0.01345063089504125</v>
       </c>
     </row>
     <row r="18">
@@ -7862,7 +7862,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2184</v>
+        <v>48.2187</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3646</v>
+        <v>48.3651</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1462</v>
+        <v>0.1464</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003032037562424303</v>
+        <v>0.003036166466536842</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.7922</v>
+        <v>55.7901</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9632</v>
+        <v>55.9613</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.171</v>
+        <v>0.1712</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003064944562143096</v>
+        <v>0.003068644795402769</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6654.79</v>
+        <v>6666</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6701.75</v>
+        <v>6713.15</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>46.96</v>
+        <v>47.15</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007056571281738418</v>
+        <v>0.007073207320732073</v>
       </c>
     </row>
     <row r="19">
@@ -7911,7 +7911,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -7927,16 +7927,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6672.01</v>
+        <v>6669.35</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6867.62</v>
+        <v>6864.8</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.61</v>
+        <v>195.45</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02931800162170021</v>
+        <v>0.02930570445395728</v>
       </c>
     </row>
     <row r="20">
@@ -7944,7 +7944,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -7952,40 +7952,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.7241</v>
+        <v>47.8049</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6807</v>
+        <v>48.6915</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.9566</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.02004438009307666</v>
+        <v>0.01854621597367634</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.2361</v>
+        <v>55.3246</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.3714</v>
+        <v>56.3839</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.1353</v>
+        <v>1.0593</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.02055358723733211</v>
+        <v>0.0191469978996685</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6597.45</v>
+        <v>6610.81</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7042.64</v>
+        <v>7056.88</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.19</v>
+        <v>446.07</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06747910177417032</v>
+        <v>0.06747584637888548</v>
       </c>
     </row>
     <row r="21">
@@ -7993,7 +7993,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8001,40 +8001,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7516</v>
+        <v>47.7518</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7545</v>
+        <v>48.7551</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0029</v>
+        <v>1.0033</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02100243761465584</v>
+        <v>0.02101072629722859</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3406</v>
+        <v>55.3409</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.347</v>
+        <v>56.3476</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0064</v>
+        <v>1.0067</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01818556358261385</v>
+        <v>0.01819088594511473</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6566.33</v>
+        <v>6571.18</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6818.24</v>
+        <v>6823.01</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.91</v>
+        <v>251.83</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03836389581394782</v>
+        <v>0.03832340614623249</v>
       </c>
     </row>
     <row r="22">
@@ -8042,7 +8042,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8050,40 +8050,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6787</v>
+        <v>47.6776</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8337</v>
+        <v>48.8354</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.155</v>
+        <v>1.1578</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02422465377621454</v>
+        <v>0.02428394046680202</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.1737</v>
+        <v>55.1678</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5151</v>
+        <v>56.5123</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3414</v>
+        <v>1.3445</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02431230821931464</v>
+        <v>0.0243711005332821</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6592.4</v>
+        <v>6595.24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6774.4</v>
+        <v>6776.85</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>182</v>
+        <v>181.61</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02760754808567441</v>
+        <v>0.02753652634324149</v>
       </c>
     </row>
     <row r="23">
@@ -8091,7 +8091,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8099,40 +8099,40 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.24</v>
+        <v>48.28</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>48.25</v>
+        <v>48.29</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002072968490878939</v>
+        <v>0.0002071251035625518</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>55.7</v>
+        <v>55.75</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>55.75</v>
+        <v>55.8</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0008976660682226212</v>
+        <v>0.0008968609865470851</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6722.02</v>
+        <v>6669.43</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6728.25</v>
+        <v>6675.67</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.0009268047402417725</v>
+        <v>0.0009356121887477641</v>
       </c>
     </row>
     <row r="24">
@@ -8140,7 +8140,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8148,40 +8148,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6131</v>
+        <v>47.6134</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5992</v>
+        <v>48.5996</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9861</v>
+        <v>0.9862</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02071068676477692</v>
+        <v>0.0207126565210634</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.105</v>
+        <v>55.1015</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2468</v>
+        <v>56.2432</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1418</v>
+        <v>1.1417</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02072044279103529</v>
+        <v>0.02071994410315509</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6547.71</v>
+        <v>6557.78</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6721.33</v>
+        <v>6731.8</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>173.62</v>
+        <v>174.02</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02651614075760838</v>
+        <v>0.02653641933703174</v>
       </c>
     </row>
     <row r="25">
@@ -8189,7 +8189,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8238,40 +8238,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2272</v>
+        <v>48.2274</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2802</v>
+        <v>48.2805</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.053</v>
+        <v>0.0531</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001098964899475814</v>
+        <v>0.001101033852125555</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8012</v>
+        <v>55.798</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>55.8776</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0764</v>
+        <v>0.0796</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001369146183236203</v>
+        <v>0.00142657442919101</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6643.48</v>
+        <v>6658.48</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6672.33</v>
+        <v>6686.88</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.85</v>
+        <v>28.4</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004342603575234667</v>
+        <v>0.004265237711910226</v>
       </c>
     </row>
     <row r="27">
@@ -8279,7 +8279,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8287,40 +8287,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.194</v>
+        <v>48.256</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.291</v>
+        <v>48.355</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.097</v>
+        <v>0.099</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002012698676183757</v>
+        <v>0.002051558355437666</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.665</v>
+        <v>55.697</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.866</v>
+        <v>55.918</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.201</v>
+        <v>0.221</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.003610886553489625</v>
+        <v>0.003967897732373377</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6620</v>
+        <v>6636</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6668</v>
+        <v>6687</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.007250755287009063</v>
+        <v>0.007685352622061483</v>
       </c>
     </row>
     <row r="28">
@@ -8328,7 +8328,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8336,40 +8336,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7615</v>
+        <v>47.762</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7615</v>
+        <v>48.762</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093736586999989</v>
+        <v>0.02093714668564968</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.31</v>
+        <v>55.301</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.4</v>
+        <v>56.391</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01970710540589405</v>
+        <v>0.01971031265257409</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6646.28</v>
+        <v>6644.9</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6746.28</v>
+        <v>6744.9</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01504601070072281</v>
+        <v>0.01504913542716971</v>
       </c>
     </row>
     <row r="29">
@@ -8377,7 +8377,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8393,16 +8393,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6672.01</v>
+        <v>6667.97</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6853.91</v>
+        <v>6849.7</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>181.9</v>
+        <v>181.73</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02726314858640799</v>
+        <v>0.02725417180941126</v>
       </c>
     </row>
     <row r="30">
@@ -8410,7 +8410,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8430,28 +8430,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0776</v>
+        <v>55.0681</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7293</v>
+        <v>56.7244</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6517</v>
+        <v>1.6563</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.0299885979055006</v>
+        <v>0.03007730428324202</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6567.5</v>
+        <v>6578.08</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6765.12</v>
+        <v>6776.19</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>197.62</v>
+        <v>198.11</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03009059763989341</v>
+        <v>0.03011669058448666</v>
       </c>
     </row>
     <row r="31">
@@ -8459,7 +8459,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.2964</v>
+        <v>48.153</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.2964</v>
+        <v>48.3944</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0</v>
+        <v>0.2414</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0</v>
+        <v>0.005013187132681245</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.8988</v>
+        <v>55.6683</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>55.8988</v>
+        <v>56.0036</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0</v>
+        <v>0.3353</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.006023176565478019</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6664.82</v>
+        <v>6593.08</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6664.82</v>
+        <v>6726.61</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>133.53</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0</v>
+        <v>0.02025305320123524</v>
       </c>
     </row>
     <row r="32">
@@ -8508,7 +8508,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8516,40 +8516,40 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8519</v>
+        <v>47.8522</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6539</v>
+        <v>48.6544</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.802</v>
+        <v>0.8022</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676004505568222</v>
+        <v>0.01676411951801589</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4265</v>
+        <v>55.4133</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.277</v>
+        <v>56.2636</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8505</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01534464561175611</v>
+        <v>0.0153446916173554</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6599.48</v>
+        <v>6595.3</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6795.93</v>
+        <v>6791.42</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.45</v>
+        <v>196.12</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02976749683308382</v>
+        <v>0.02973632738465271</v>
       </c>
     </row>
     <row r="33">
@@ -8557,7 +8557,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8565,40 +8565,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1539</v>
+        <v>48.1543</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3571</v>
+        <v>48.3575</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004219803588079054</v>
+        <v>0.004219768535727858</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7173</v>
+        <v>55.7174</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9418</v>
+        <v>55.942</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2245</v>
+        <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004029269185692774</v>
+        <v>0.004031056725547136</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6632.87</v>
+        <v>6638.6</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6686.15</v>
+        <v>6691.93</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.28</v>
+        <v>53.33</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008032721883588854</v>
+        <v>0.008033320278371945</v>
       </c>
     </row>
     <row r="34">
@@ -8606,7 +8606,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8614,40 +8614,40 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8943</v>
+        <v>47.8946</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8553</v>
+        <v>48.8556</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.0200650181754405</v>
+        <v>0.02006489249309943</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4732</v>
+        <v>55.4497</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5752</v>
+        <v>56.5517</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986544854091706</v>
+        <v>0.01987386766745357</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6600.33</v>
+        <v>6594.99</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6744.93</v>
+        <v>6739.59</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02190799550931545</v>
+        <v>0.02192573453485146</v>
       </c>
     </row>
     <row r="35">
@@ -8655,7 +8655,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8663,28 +8663,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.224</v>
+        <v>48.255</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.265</v>
+        <v>48.3</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.0008501990710019908</v>
+        <v>0.0009325458501709667</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.689</v>
+        <v>55.73</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.799</v>
+        <v>55.824</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.11</v>
+        <v>0.094</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.001975255436441667</v>
+        <v>0.001686703750224296</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8696,7 +8696,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8707,37 +8707,37 @@
         <v>47.65</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>48.65</v>
+        <v>48.66</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.02098635886673662</v>
+        <v>0.02119622245540399</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.16</v>
+        <v>55.15</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>56.29</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02048585931834663</v>
+        <v>0.02067089755213055</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6570.03</v>
+        <v>6569.54</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6772.25</v>
+        <v>6771.48</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>202.22</v>
+        <v>201.94</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03077915930368659</v>
+        <v>0.03073883407361855</v>
       </c>
     </row>
     <row r="37">
@@ -8745,7 +8745,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8753,40 +8753,40 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.8905</v>
+        <v>47.8908</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8593</v>
+        <v>48.8596</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.9688</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02022948183877804</v>
+        <v>0.02022935511622274</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4349</v>
+        <v>55.4124</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5564</v>
+        <v>56.5334</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1215</v>
+        <v>1.121</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023093755017146</v>
+        <v>0.02023012899639792</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6647.04</v>
+        <v>6629.01</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6781.26</v>
+        <v>6762.86</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.22</v>
+        <v>133.85</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019244656268053</v>
+        <v>0.02019155198136675</v>
       </c>
     </row>
     <row r="38">
@@ -8794,7 +8794,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8802,40 +8802,40 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9384</v>
+        <v>47.9387</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.5906</v>
+        <v>48.5909</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0.6522</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360495969827946</v>
+        <v>0.01360487455855082</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4161</v>
+        <v>55.4124</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2262</v>
+        <v>56.2225</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>0.8101</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461849534702009</v>
+        <v>0.01461947145404278</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6601.38</v>
+        <v>6607.06</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6734.67</v>
+        <v>6740.46</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.29</v>
+        <v>133.4</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.0201912327422448</v>
+        <v>0.02019052347034838</v>
       </c>
     </row>
     <row r="39">
@@ -8843,7 +8843,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8851,40 +8851,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7687</v>
+        <v>47.769</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7655</v>
+        <v>48.766</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.0208672205858648</v>
+        <v>0.02087127635077142</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2409</v>
+        <v>55.2408</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4493</v>
+        <v>56.4494</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2084</v>
+        <v>1.2086</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02187509616968587</v>
+        <v>0.02187875628158897</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6621.58</v>
+        <v>6627.03</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6831.73</v>
+        <v>6837.43</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.15</v>
+        <v>210.4</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03173713826609359</v>
+        <v>0.03174876226605282</v>
       </c>
     </row>
   </sheetData>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.4999768518518519</v>
+        <v>0.5944791666666667</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42217,7 +42217,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.02022948183877804</v>
+        <v>0.02022935511622274</v>
       </c>
       <c r="O5" s="71" t="inlineStr">
         <is>
@@ -42225,10 +42225,10 @@
         </is>
       </c>
       <c r="P5" s="72" t="n">
-        <v>47.8905</v>
+        <v>47.8908</v>
       </c>
       <c r="Q5" s="72" t="n">
-        <v>48.8593</v>
+        <v>48.8596</v>
       </c>
     </row>
     <row r="6">
@@ -42270,7 +42270,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023093755017146</v>
+        <v>0.02023012899639792</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42278,10 +42278,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4349</v>
+        <v>55.4124</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5564</v>
+        <v>56.5334</v>
       </c>
     </row>
     <row r="7">
@@ -42323,7 +42323,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019244656268053</v>
+        <v>0.02019155198136675</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42331,10 +42331,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6647.04</v>
+        <v>6629.01</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6781.26</v>
+        <v>6762.86</v>
       </c>
     </row>
     <row r="8">
@@ -42376,7 +42376,7 @@
       </c>
       <c r="B9" s="62" t="n"/>
       <c r="C9" s="73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="62" t="n"/>
       <c r="F9" s="62" t="inlineStr">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -7078,7 +7078,7 @@
         <v>46267</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7098,28 +7098,28 @@
         <v>0.02842045430622513</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9733</v>
+        <v>54.9873</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5405</v>
+        <v>56.5501</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5672</v>
+        <v>1.5628</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02850838497961737</v>
+        <v>0.02842110814679026</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6522.09</v>
+        <v>6538.87</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6757.84</v>
+        <v>6775.12</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>235.75</v>
+        <v>236.25</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03614638865762355</v>
+        <v>0.0361300958728343</v>
       </c>
     </row>
     <row r="3">
@@ -7127,7 +7127,7 @@
         <v>46267</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7147,28 +7147,28 @@
         <v>0.01630582291166461</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.426</v>
+        <v>55.44</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.34</v>
+        <v>56.355</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.914</v>
+        <v>0.915</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01649045574279219</v>
+        <v>0.016504329004329</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6599.06</v>
+        <v>6611.61</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6734.34</v>
+        <v>6747.97</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>135.28</v>
+        <v>136.36</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02049988937818416</v>
+        <v>0.02062432599623995</v>
       </c>
     </row>
     <row r="4">
@@ -7176,7 +7176,7 @@
         <v>46267</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7184,40 +7184,40 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.081</v>
+        <v>48.085</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.374</v>
+        <v>48.37</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.293</v>
+        <v>0.285</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.006093883238701359</v>
+        <v>0.005927004263283769</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.473</v>
+        <v>55.498</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>55.983</v>
+        <v>56.001</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.51</v>
+        <v>0.503</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.00919366178140717</v>
+        <v>0.009063389671699881</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6663.18</v>
+        <v>6677.77</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6730.38</v>
+        <v>6744.08</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>67.2</v>
+        <v>66.31</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01008527459861507</v>
+        <v>0.009929961648873801</v>
       </c>
     </row>
     <row r="5">
@@ -7225,7 +7225,7 @@
         <v>46267</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7233,40 +7233,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.18</v>
+        <v>48.209</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.37</v>
+        <v>48.399</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0.19</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.00394354503943545</v>
+        <v>0.003941172810056214</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.658</v>
+        <v>55.718</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>55.978</v>
+        <v>56.039</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.005749398109885372</v>
+        <v>0.00576115438457949</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6600.17</v>
+        <v>6605.81</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6770</v>
+        <v>6780</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>169.83</v>
+        <v>174.19</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02573115540963338</v>
+        <v>0.02636921134576986</v>
       </c>
     </row>
     <row r="6">
@@ -7274,7 +7274,7 @@
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7282,40 +7282,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4536</v>
+        <v>47.4531</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7303</v>
+        <v>48.7296</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2767</v>
+        <v>1.2765</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02690417586863799</v>
+        <v>0.02690024466262478</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0165</v>
+        <v>55.0428</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.3818</v>
+        <v>56.4077</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3653</v>
+        <v>1.3649</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02481619150618451</v>
+        <v>0.02479706700967247</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6595.52</v>
+        <v>6601.16</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6746.54</v>
+        <v>6752.06</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>151.02</v>
+        <v>150.9</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02289736063267188</v>
+        <v>0.02285961861248629</v>
       </c>
     </row>
     <row r="7">
@@ -7323,7 +7323,7 @@
         <v>46267</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7334,37 +7334,37 @@
         <v>47.302</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.226</v>
+        <v>49.225</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.924</v>
+        <v>1.923</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04067481290431695</v>
+        <v>0.04065367214916916</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.738</v>
+        <v>54.762</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.974</v>
+        <v>56.997</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.236</v>
+        <v>2.235</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.040849135883664</v>
+        <v>0.04081297249917826</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6589.45</v>
+        <v>6597.34</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6783.97</v>
+        <v>6791.54</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.52</v>
+        <v>194.2</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02951991440863805</v>
+        <v>0.02943610606699064</v>
       </c>
     </row>
     <row r="8">
@@ -7372,7 +7372,7 @@
         <v>46267</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7380,40 +7380,40 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.555</v>
+        <v>47.5549</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9551</v>
+        <v>48.955</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944169908526969</v>
+        <v>0.02944176099623803</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0301</v>
+        <v>55.0586</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6552</v>
+        <v>56.6845</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6251</v>
+        <v>1.6259</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02953111115553125</v>
+        <v>0.02953035493092814</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6600.75</v>
+        <v>6612.89</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6796.06</v>
+        <v>6808.62</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.31</v>
+        <v>195.73</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02958906184903231</v>
+        <v>0.02959825431845986</v>
       </c>
     </row>
     <row r="9">
@@ -7421,7 +7421,7 @@
         <v>46267</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7429,40 +7429,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2245</v>
+        <v>48.2242</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2821</v>
+        <v>48.2813</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0576</v>
+        <v>0.0571</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001194413627927713</v>
+        <v>0.001184052819953467</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.7996</v>
+        <v>55.8185</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.8827</v>
+        <v>55.9017</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0832</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001489257987512455</v>
+        <v>0.001490545249334898</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6659.64</v>
+        <v>6667.12</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6688.18</v>
+        <v>6695.98</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.54</v>
+        <v>28.86</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004285516934849331</v>
+        <v>0.004328705648015935</v>
       </c>
     </row>
     <row r="10">
@@ -7470,7 +7470,7 @@
         <v>46267</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7478,40 +7478,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2381</v>
+        <v>48.238</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2772</v>
+        <v>48.2765</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0385</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0008105626050777289</v>
+        <v>0.0007981259587876778</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.7767</v>
+        <v>55.7958</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.8867</v>
+        <v>55.91</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.11</v>
+        <v>0.1142</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.001972149661059188</v>
+        <v>0.002046749038458092</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6655.84</v>
+        <v>6664.2</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6687.65</v>
+        <v>6695.84</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.81</v>
+        <v>31.64</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004779261520709632</v>
+        <v>0.004747756669967888</v>
       </c>
     </row>
     <row r="11">
@@ -7519,7 +7519,7 @@
         <v>46267</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7527,40 +7527,40 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9241</v>
+        <v>47.9238</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1615</v>
+        <v>49.1621</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2374</v>
+        <v>1.2383</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02581999453302201</v>
+        <v>0.025838935977531</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3594</v>
+        <v>55.3734</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6321</v>
+        <v>56.6524</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2727</v>
+        <v>1.279</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02298977228799445</v>
+        <v>0.02309773284645696</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6601.47</v>
+        <v>6616.09</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6709.49</v>
+        <v>6724.63</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.02</v>
+        <v>108.54</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01636302217536397</v>
+        <v>0.01640546002246039</v>
       </c>
     </row>
     <row r="12">
@@ -7568,7 +7568,7 @@
         <v>46267</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7588,28 +7588,28 @@
         <v>0.01776477349913789</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.2861</v>
+        <v>55.3099</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.447</v>
+        <v>56.4666</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1609</v>
+        <v>1.1567</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02099804471648389</v>
+        <v>0.0209130734280843</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6606.01</v>
+        <v>6612.1</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6760.81</v>
+        <v>6766.77</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.8</v>
+        <v>154.67</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02343320703420067</v>
+        <v>0.02339196321894708</v>
       </c>
     </row>
     <row r="13">
@@ -7617,7 +7617,7 @@
         <v>46267</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7625,40 +7625,40 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9985</v>
+        <v>47.9982</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.606</v>
+        <v>48.6054</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6075</v>
+        <v>0.6072</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01265664552017251</v>
+        <v>0.01265047439278973</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5613</v>
+        <v>55.5764</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.2222</v>
+        <v>56.237</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6609</v>
+        <v>0.6606</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01189497006009579</v>
+        <v>0.01188634024514002</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6670.14</v>
+        <v>6683.15</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6724.29</v>
+        <v>6737.49</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.15</v>
+        <v>54.34</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008118270381131431</v>
+        <v>0.008130896358752984</v>
       </c>
     </row>
     <row r="14">
@@ -7666,7 +7666,7 @@
         <v>46267</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7674,40 +7674,40 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.455</v>
+        <v>47.454</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>48.805</v>
+        <v>48.804</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02844800337161522</v>
+        <v>0.02844860285750411</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.914</v>
+        <v>54.935</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.477</v>
+        <v>56.498</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1.563</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.028462687110755</v>
+        <v>0.02845180668062255</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6562.01</v>
+        <v>6580.71</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6804.43</v>
+        <v>6823.81</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>242.42</v>
+        <v>243.1</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694294888304041</v>
+        <v>0.03694130268618432</v>
       </c>
     </row>
     <row r="15">
@@ -7715,7 +7715,7 @@
         <v>46267</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7723,40 +7723,40 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9988</v>
+        <v>47.9984</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6058</v>
+        <v>48.6053</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6069</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264614948707051</v>
+        <v>0.01264417147238241</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5608</v>
+        <v>55.5861</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2216</v>
+        <v>56.2467</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6606</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01189327727462528</v>
+        <v>0.01188426603053641</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6679.6</v>
+        <v>6685.19</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6734.63</v>
+        <v>6739.53</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>55.03</v>
+        <v>54.34</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008238517276483621</v>
+        <v>0.008128415198371325</v>
       </c>
     </row>
     <row r="16">
@@ -7764,7 +7764,7 @@
         <v>46267</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7772,40 +7772,40 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.8675</v>
+        <v>47.8672</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.8475</v>
+        <v>48.8472</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0.98</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02047318117720792</v>
+        <v>0.02047330948958786</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.3947</v>
+        <v>55.4111</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5288</v>
+        <v>56.5455</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1341</v>
+        <v>1.1344</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02047307774931537</v>
+        <v>0.0204724324187753</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6596.25</v>
+        <v>6611.86</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6798.84</v>
+        <v>6814.92</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>202.59</v>
+        <v>203.06</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03071290505969301</v>
+        <v>0.03071147906942978</v>
       </c>
     </row>
     <row r="17">
@@ -7813,7 +7813,7 @@
         <v>46267</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7821,40 +7821,40 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.24</v>
+        <v>48.25</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.309</v>
+        <v>48.31</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001430348258706468</v>
+        <v>0.001243523316062176</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.682</v>
+        <v>55.718</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.86</v>
+        <v>55.887</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.178</v>
+        <v>0.169</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003196724255594268</v>
+        <v>0.003033131124591694</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6616.79</v>
+        <v>6628.13</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6705.79</v>
+        <v>6713.71</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>89</v>
+        <v>85.58</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01345063089504125</v>
+        <v>0.01291163571022294</v>
       </c>
     </row>
     <row r="18">
@@ -7862,7 +7862,7 @@
         <v>46267</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2187</v>
+        <v>48.218</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3651</v>
+        <v>48.3648</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1464</v>
+        <v>0.1468</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003036166466536842</v>
+        <v>0.003044506201003774</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.7901</v>
+        <v>55.8086</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9613</v>
+        <v>55.9803</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1712</v>
+        <v>0.1717</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003068644795402769</v>
+        <v>0.003076586762613647</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6666</v>
+        <v>6673.84</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6713.15</v>
+        <v>6721.1</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.15</v>
+        <v>47.26</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007073207320732073</v>
+        <v>0.007081380434652315</v>
       </c>
     </row>
     <row r="19">
@@ -7911,7 +7911,7 @@
         <v>46267</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -7927,16 +7927,16 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6669.35</v>
+        <v>6681.95</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6864.8</v>
+        <v>6877.67</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.45</v>
+        <v>195.72</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02930570445395728</v>
+        <v>0.02929085072471359</v>
       </c>
     </row>
     <row r="20">
@@ -7944,7 +7944,7 @@
         <v>46267</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -7952,40 +7952,40 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8049</v>
+        <v>47.7933</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6915</v>
+        <v>48.6799</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0.8866000000000001</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01854621597367634</v>
+        <v>0.01855071735996468</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3246</v>
+        <v>55.3353</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.3839</v>
+        <v>56.3898</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0593</v>
+        <v>1.0545</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.0191469978996685</v>
+        <v>0.01905655160449117</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6610.81</v>
+        <v>6617.13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7056.88</v>
+        <v>7063.22</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>446.07</v>
+        <v>446.09</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06747584637888548</v>
+        <v>0.06741442286912906</v>
       </c>
     </row>
     <row r="21">
@@ -7993,7 +7993,7 @@
         <v>46267</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8001,40 +8001,40 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7518</v>
+        <v>47.7514</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7551</v>
+        <v>48.7549</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0033</v>
+        <v>1.0035</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02101072629722859</v>
+        <v>0.02101509065702786</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.3409</v>
+        <v>55.357</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.3476</v>
+        <v>56.367</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0067</v>
+        <v>1.01</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01819088594511473</v>
+        <v>0.01824520837473129</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6571.18</v>
+        <v>6583.01</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6823.01</v>
+        <v>6835.05</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>251.83</v>
+        <v>252.04</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03832340614623249</v>
+        <v>0.03828643735920195</v>
       </c>
     </row>
     <row r="22">
@@ -8042,7 +8042,7 @@
         <v>46267</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8050,40 +8050,40 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6776</v>
+        <v>47.6786</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8354</v>
+        <v>48.8336</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1578</v>
+        <v>1.155</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02428394046680202</v>
+        <v>0.02422470458444669</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.1678</v>
+        <v>55.1928</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5123</v>
+        <v>56.5298</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3445</v>
+        <v>1.337</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.0243711005332821</v>
+        <v>0.02422417416764506</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6595.24</v>
+        <v>6604.6</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6776.85</v>
+        <v>6785.71</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.61</v>
+        <v>181.11</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02753652634324149</v>
+        <v>0.02742179692941283</v>
       </c>
     </row>
     <row r="23">
@@ -8091,7 +8091,7 @@
         <v>46267</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8099,16 +8099,16 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.28</v>
+        <v>48.27</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>48.29</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002071251035625518</v>
+        <v>0.0004143360265175057</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>55.75</v>
@@ -8123,16 +8123,16 @@
         <v>0.0008968609865470851</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6669.43</v>
+        <v>6682.61</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6675.67</v>
+        <v>6690.23</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6.24</v>
+        <v>7.62</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.0009356121887477641</v>
+        <v>0.001140273037031938</v>
       </c>
     </row>
     <row r="24">
@@ -8140,7 +8140,7 @@
         <v>46267</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8148,40 +8148,40 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6134</v>
+        <v>47.613</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5996</v>
+        <v>48.5991</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9862</v>
+        <v>0.9861</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.0207126565210634</v>
+        <v>0.02071073026274337</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1015</v>
+        <v>55.1196</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2432</v>
+        <v>56.2617</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1417</v>
+        <v>1.1421</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02071994410315509</v>
+        <v>0.02072039710012409</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6557.78</v>
+        <v>6578.23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6731.8</v>
+        <v>6752.43</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174.02</v>
+        <v>174.2</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02653641933703174</v>
+        <v>0.02648128751959113</v>
       </c>
     </row>
     <row r="25">
@@ -8189,7 +8189,7 @@
         <v>46267</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>46267</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8238,40 +8238,40 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2274</v>
+        <v>48.227</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2805</v>
+        <v>48.2804</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0531</v>
+        <v>0.0534</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001101033852125555</v>
+        <v>0.001107263566052211</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.798</v>
+        <v>55.8172</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.8776</v>
+        <v>55.8979</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0796</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.00142657442919101</v>
+        <v>0.001445790903162466</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6658.48</v>
+        <v>6662.57</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6686.88</v>
+        <v>6690.94</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.4</v>
+        <v>28.37</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004265237711910226</v>
+        <v>0.004258116612658479</v>
       </c>
     </row>
     <row r="27">
@@ -8279,7 +8279,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8287,40 +8287,40 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.256</v>
+        <v>48.265</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.355</v>
+        <v>48.366</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002051558355437666</v>
+        <v>0.002092613695224283</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.697</v>
+        <v>55.733</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.918</v>
+        <v>55.962</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.221</v>
+        <v>0.229</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.003967897732373377</v>
+        <v>0.004108876249259864</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6636</v>
+        <v>6638</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6687</v>
+        <v>6693</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.007685352622061483</v>
+        <v>0.008285628201265442</v>
       </c>
     </row>
     <row r="28">
@@ -8328,7 +8328,7 @@
         <v>46267</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8336,40 +8336,40 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.762</v>
+        <v>47.7615</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.762</v>
+        <v>48.7615</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093714668564968</v>
+        <v>0.02093736586999989</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.301</v>
+        <v>55.318</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.391</v>
+        <v>56.408</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01971031265257409</v>
+        <v>0.01970425539607361</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6644.9</v>
+        <v>6663.22</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6744.9</v>
+        <v>6763.22</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01504913542716971</v>
+        <v>0.0150077590114089</v>
       </c>
     </row>
     <row r="29">
@@ -8377,7 +8377,7 @@
         <v>46267</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8393,16 +8393,16 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6667.97</v>
+        <v>6681.95</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6849.7</v>
+        <v>6863.94</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>181.73</v>
+        <v>181.99</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02725417180941126</v>
+        <v>0.02723606132940234</v>
       </c>
     </row>
     <row r="30">
@@ -8410,7 +8410,7 @@
         <v>46267</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8430,28 +8430,28 @@
         <v>0.02558322411533421</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0681</v>
+        <v>55.0919</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7244</v>
+        <v>56.7489</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6563</v>
+        <v>1.657</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03007730428324202</v>
+        <v>0.03007701676653011</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6578.08</v>
+        <v>6586.13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6776.19</v>
+        <v>6784.36</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>198.11</v>
+        <v>198.23</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03011669058448666</v>
+        <v>0.03009810009823675</v>
       </c>
     </row>
     <row r="31">
@@ -8459,7 +8459,7 @@
         <v>46267</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.153</v>
+        <v>48.1413</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.3944</v>
+        <v>48.3827</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0.2414</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.005013187132681245</v>
+        <v>0.005014405510445293</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.6683</v>
+        <v>55.6806</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.0036</v>
+        <v>56.016</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3353</v>
+        <v>0.3354</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006023176565478019</v>
+        <v>0.006023641986616523</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6593.08</v>
+        <v>6598.67</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6726.61</v>
+        <v>6732.31</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>133.53</v>
+        <v>133.64</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025305320123524</v>
+        <v>0.02025256604740046</v>
       </c>
     </row>
     <row r="32">
@@ -8508,7 +8508,7 @@
         <v>46267</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8516,40 +8516,40 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8522</v>
+        <v>47.8518</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6544</v>
+        <v>48.6541</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8022</v>
+        <v>0.8023</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676411951801589</v>
+        <v>0.01676634943722075</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4133</v>
+        <v>55.4245</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2636</v>
+        <v>56.2748</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>0.8502999999999999</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.0153446916173554</v>
+        <v>0.01534159081272722</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6595.3</v>
+        <v>6611.43</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6791.42</v>
+        <v>6807.72</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.12</v>
+        <v>196.29</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02973632738465271</v>
+        <v>0.02968949228835517</v>
       </c>
     </row>
     <row r="33">
@@ -8557,7 +8557,7 @@
         <v>46267</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8565,40 +8565,40 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1543</v>
+        <v>48.1538</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3575</v>
+        <v>48.357</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004219768535727858</v>
+        <v>0.004219812351257845</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7174</v>
+        <v>55.7353</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.942</v>
+        <v>55.9599</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.2246</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004031056725547136</v>
+        <v>0.004029762107676822</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6638.6</v>
+        <v>6650.43</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6691.93</v>
+        <v>6703.85</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.33</v>
+        <v>53.42</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008033320278371945</v>
+        <v>0.00803256330793648</v>
       </c>
     </row>
     <row r="34">
@@ -8606,7 +8606,7 @@
         <v>46267</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8626,28 +8626,28 @@
         <v>0.02006489249309943</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4497</v>
+        <v>55.4653</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5517</v>
+        <v>56.5673</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>1.102</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01987386766745357</v>
+        <v>0.01986827800444602</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6594.99</v>
+        <v>6617.75</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6739.59</v>
+        <v>6762.35</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02192573453485146</v>
+        <v>0.02185032677269465</v>
       </c>
     </row>
     <row r="35">
@@ -8655,7 +8655,7 @@
         <v>46267</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8663,28 +8663,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.255</v>
+        <v>48.271</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.3</v>
+        <v>48.31</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.0009325458501709667</v>
+        <v>0.000807938513807462</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.73</v>
+        <v>55.772</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.824</v>
+        <v>55.875</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.001686703750224296</v>
+        <v>0.00184680484831098</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8696,7 +8696,7 @@
         <v>46267</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8707,37 +8707,37 @@
         <v>47.65</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>48.66</v>
+        <v>48.65</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.02119622245540399</v>
+        <v>0.02098635886673662</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.15</v>
+        <v>55.17</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.29</v>
+        <v>56.31</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02067089755213055</v>
+        <v>0.02066340402392605</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6569.54</v>
+        <v>6584.64</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6771.48</v>
+        <v>6786.98</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>201.94</v>
+        <v>202.34</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03073883407361855</v>
+        <v>0.03072909073237109</v>
       </c>
     </row>
     <row r="37">
@@ -8745,7 +8745,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8753,40 +8753,40 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.8908</v>
+        <v>47.8905</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8596</v>
+        <v>48.8593</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.9688</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02022935511622274</v>
+        <v>0.02022948183877804</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4124</v>
+        <v>55.4241</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5334</v>
+        <v>56.5454</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.121</v>
+        <v>1.1213</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023012899639792</v>
+        <v>0.02023127123399388</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6629.01</v>
+        <v>6650.94</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6762.86</v>
+        <v>6785.23</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>133.85</v>
+        <v>134.29</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019155198136675</v>
+        <v>0.02019113087774059</v>
       </c>
     </row>
     <row r="38">
@@ -8794,7 +8794,7 @@
         <v>46267</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8802,40 +8802,40 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9387</v>
+        <v>47.9384</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.5909</v>
+        <v>48.5906</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0.6522</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360487455855082</v>
+        <v>0.01360495969827946</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4124</v>
+        <v>55.4326</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.2225</v>
+        <v>56.243</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8101</v>
+        <v>0.8104</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461947145404278</v>
+        <v>0.01461955600134217</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6607.06</v>
+        <v>6620.42</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6740.46</v>
+        <v>6754.09</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.4</v>
+        <v>133.67</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019052347034838</v>
+        <v>0.02019056192809519</v>
       </c>
     </row>
     <row r="39">
@@ -8843,7 +8843,7 @@
         <v>46267</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8851,40 +8851,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.769</v>
+        <v>47.7683</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>48.766</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.997</v>
+        <v>0.9977</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02087127635077142</v>
+        <v>0.02088623626966001</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2408</v>
+        <v>55.2548</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4494</v>
+        <v>56.4646</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2086</v>
+        <v>1.2098</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02187875628158897</v>
+        <v>0.02189493039518739</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6627.03</v>
+        <v>6640.01</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6837.43</v>
+        <v>6850.92</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.4</v>
+        <v>210.91</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03174876226605282</v>
+        <v>0.03176350638026148</v>
       </c>
     </row>
   </sheetData>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.5944791666666667</v>
+        <v>0.6215046296296296</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42217,7 +42217,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.02022935511622274</v>
+        <v>0.02022948183877804</v>
       </c>
       <c r="O5" s="71" t="inlineStr">
         <is>
@@ -42225,10 +42225,10 @@
         </is>
       </c>
       <c r="P5" s="72" t="n">
-        <v>47.8908</v>
+        <v>47.8905</v>
       </c>
       <c r="Q5" s="72" t="n">
-        <v>48.8596</v>
+        <v>48.8593</v>
       </c>
     </row>
     <row r="6">
@@ -42270,7 +42270,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023012899639792</v>
+        <v>0.02023127123399388</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -42278,10 +42278,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4124</v>
+        <v>55.4241</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5334</v>
+        <v>56.5454</v>
       </c>
     </row>
     <row r="7">
@@ -42323,7 +42323,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019155198136675</v>
+        <v>0.02019113087774059</v>
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
@@ -42331,10 +42331,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6629.01</v>
+        <v>6650.94</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6762.86</v>
+        <v>6785.23</v>
       </c>
     </row>
     <row r="8">

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -431,15 +431,15 @@
     <xf numFmtId="10" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -578,9 +578,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -598,16 +598,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -625,6 +628,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02844860285750411</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02843781597573306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -670,9 +676,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -690,16 +696,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -717,6 +726,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02842045430622513</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02840968875607652</v>
                 </pt>
               </numCache>
             </numRef>
@@ -762,9 +774,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -782,16 +794,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -809,6 +824,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02098635886673662</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.01886001676445935</v>
                 </pt>
               </numCache>
             </numRef>
@@ -854,9 +872,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -874,16 +892,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -901,6 +922,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02022956632136362</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02023052613561883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -946,9 +970,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -966,16 +990,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -993,6 +1020,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02423125082585086</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02421591793005269</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1033,8 +1063,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06809845902702412"/>
-          <min val="0.01398473878667442"/>
+          <max val="0.06830375094990089"/>
+          <min val="0.01241083404461915"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1113,9 +1143,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1133,16 +1163,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$7</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -1160,6 +1193,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02842045430622513</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02840968875607652</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1208,8 +1244,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06361034633532447"/>
-          <min val="0.02255547230137524"/>
+          <max val="0.06361249944535419"/>
+          <min val="0.02254255364119691"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1300,9 +1336,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1320,16 +1356,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -1347,6 +1386,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02850903510398825</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02840991553220516</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1395,8 +1437,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06393703694203891"/>
-          <min val="0.02251604918664015"/>
+          <max val="0.06394172046593731"/>
+          <min val="0.0224879480432498"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1487,9 +1529,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1507,16 +1549,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -1534,6 +1579,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03614164623338936</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.03611897381942306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1582,8 +1630,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.09492887751151027"/>
-          <min val="0.02634377435370254"/>
+          <max val="0.09493341199430352"/>
+          <min val="0.02631656745694298"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1674,9 +1722,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1694,16 +1742,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$7</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -1721,6 +1772,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02098635886673662</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.01886001676445935</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1769,8 +1823,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06300273000209422"/>
-          <min val="0.01394771487950567"/>
+          <max val="0.06342184148574888"/>
+          <min val="0.01143304597757776"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1861,9 +1915,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1881,16 +1935,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -1908,6 +1965,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.0204784342152954</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.01842485549132948</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1956,8 +2016,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05612935000212975"/>
-          <min val="0.01451066469310389"/>
+          <max val="0.05653561713702823"/>
+          <min val="0.01207306188371302"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -2048,9 +2108,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2068,16 +2128,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -2095,6 +2158,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03076504592342247</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02810535581445664</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2143,8 +2209,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.08822748202703072"/>
-          <min val="0.0196170269615309"/>
+          <max val="0.0884901149726027"/>
+          <min val="0.01804122928809896"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -2235,9 +2301,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2255,16 +2321,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$7</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -2282,6 +2351,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02022956632136362</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02023052613561883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2422,9 +2494,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2442,16 +2514,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -2469,6 +2544,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02023118260179608</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02023022023022023</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2609,9 +2687,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2629,16 +2707,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -2656,6 +2737,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02019234240196374</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02019112818516369</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2704,7 +2788,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1709612332154084"/>
+          <max val="0.1709612463655258"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2796,9 +2880,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2816,16 +2900,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$7</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -2843,6 +2930,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02423125082585086</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02421591793005269</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2983,9 +3073,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3003,16 +3093,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -3030,6 +3123,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02844818171890357</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02843808451522691</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3075,9 +3171,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3095,16 +3191,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$7</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -3122,6 +3221,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02850903510398825</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02840991553220516</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3167,9 +3269,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3187,16 +3289,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$7</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -3214,6 +3319,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.0204784342152954</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.01842485549132948</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3259,9 +3367,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3279,16 +3387,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$7</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -3306,6 +3417,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02023118260179608</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02023022023022023</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3351,9 +3465,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3371,16 +3485,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3398,6 +3515,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02422426194815971</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02447887476723374</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3438,8 +3558,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06809875047508467"/>
-          <min val="0.01398628179112082"/>
+          <max val="0.06836952637804505"/>
+          <min val="0.01191033320175789"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -3518,9 +3638,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3538,16 +3658,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$7</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3565,6 +3688,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02422426194815971</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02447887476723374</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3705,9 +3831,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3725,16 +3851,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -3752,6 +3881,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02742758272742561</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02741964100895999</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3800,8 +3932,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1462720659556508"/>
-          <min val="0.007620168856054751"/>
+          <max val="0.1462736542993439"/>
+          <min val="0.007610638793896007"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -3892,9 +4024,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3912,16 +4044,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -3939,6 +4074,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03694167743897803</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.03693992900335979</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3984,9 +4122,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4004,16 +4142,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$7</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -4031,6 +4172,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03614164623338936</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.03611897381942306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4076,9 +4220,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4096,16 +4240,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$7</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -4123,6 +4270,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03076504592342247</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02810535581445664</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4168,9 +4318,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4188,16 +4338,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$7</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -4215,6 +4368,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02019234240196374</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02019112818516369</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4260,9 +4416,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4280,16 +4436,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$7</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4307,6 +4466,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02742758272742561</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02741964100895999</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4347,8 +4509,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1646791482454227"/>
-          <min val="0.001344939025793405"/>
+          <max val="0.1646791581080107"/>
+          <min val="0.001344863412618431"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -4449,7 +4611,7 @@
                   <v>0.03553378696044311</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02845400039156511</v>
+                  <v>0.02844860558628776</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4517,7 +4679,7 @@
                   <v>0.04311562150687483</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.0284261405518742</v>
+                  <v>0.02842065661994164</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4585,7 +4747,7 @@
                   <v>0.03847709584999994</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02109574084424381</v>
+                  <v>0.02035049948431565</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4653,7 +4815,7 @@
                   <v>0.04104187506584386</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023029953768716</v>
+                  <v>0.02023037507033105</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4721,7 +4883,7 @@
                   <v>0.04760750668842017</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02422333905778681</v>
+                  <v>0.0242208653485421</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4762,8 +4924,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05171408776103012"/>
-          <min val="0.0161237184650772"/>
+          <max val="0.05171407643113354"/>
+          <min val="0.01612380532761768"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -4864,7 +5026,7 @@
                   <v>0.03553642841103422</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02846019565754637</v>
+                  <v>0.02845282527677321</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4932,7 +5094,7 @@
                   <v>0.0432699268677014</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02847118412784268</v>
+                  <v>0.02845076126263018</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5000,7 +5162,7 @@
                   <v>0.03535742466332828</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02046731269055863</v>
+                  <v>0.01978649362414892</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5068,7 +5230,7 @@
                   <v>0.0514487601107881</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023090916840954</v>
+                  <v>0.02023067952234644</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5136,7 +5298,7 @@
                   <v>0.04783493387226885</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02435060197965432</v>
+                  <v>0.02439335957551413</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5177,8 +5339,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05613143775214488"/>
-          <min val="0.01554823152705276"/>
+          <max val="0.05619810008378397"/>
+          <min val="0.01503715365115304"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5279,7 +5441,7 @@
                   <v>0.05383117747984287</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03694321012774233</v>
+                  <v>0.03694211641961482</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5347,7 +5509,7 @@
                   <v>0.06066925394146307</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03614313031148214</v>
+                  <v>0.03613507814746245</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5415,7 +5577,7 @@
                   <v>0.0540849048600331</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03051048704906535</v>
+                  <v>0.02970877663752912</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5483,7 +5645,7 @@
                   <v>0.08301204597474589</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02019194235075064</v>
+                  <v>0.02019167096222166</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5551,7 +5713,7 @@
                   <v>0.1017248276143379</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02742927462036698</v>
+                  <v>0.02742606341656465</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5592,8 +5754,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.113954760403876"/>
-          <min val="0.007962009561212546"/>
+          <max val="0.1139548011121554"/>
+          <min val="0.007961697464404215"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5672,9 +5834,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -5692,16 +5854,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$7</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -5719,6 +5884,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02844860285750411</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02843781597573306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5767,8 +5935,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.04535890324268219"/>
-          <min val="0.02563021945997443"/>
+          <max val="0.0453610606190364"/>
+          <min val="0.02561727520184917"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5859,9 +6027,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -5879,16 +6047,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$7</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -5906,6 +6077,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.02844818171890357</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.02843808451522691</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5954,8 +6128,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.04536575081521625"/>
-          <min val="0.02562858686951813"/>
+          <max val="0.04536777025595159"/>
+          <min val="0.02561647022510612"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -6046,9 +6220,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$7</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
               <strCache>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6066,16 +6240,19 @@
                 </pt>
                 <pt idx="5">
                   <v>02.09</v>
+                </pt>
+                <pt idx="6">
+                  <v>03.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$7</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$8</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="6"/>
+                <ptCount val="7"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -6093,6 +6270,9 @@
                 </pt>
                 <pt idx="5">
                   <v>0.03694167743897803</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.03693992900335979</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6141,8 +6321,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.07745416653140928"/>
-          <min val="0.03018959592357282"/>
+          <max val="0.07745451621853293"/>
+          <min val="0.03018749780083094"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -6665,8 +6845,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N649" headerRowCount="1">
-  <autoFilter ref="A1:N649"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N757" headerRowCount="1">
+  <autoFilter ref="A1:N757"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tarih"/>
     <tableColumn id="2" name="Saat"/>
@@ -7075,10 +7255,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7086,48 +7266,48 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>47.501</v>
+        <v>47.519</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>48.851</v>
+        <v>48.869</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.02842045430622513</v>
+        <v>0.02840968875607652</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>54.9873</v>
+        <v>55.1216</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.5501</v>
+        <v>56.6876</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5628</v>
+        <v>1.566</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02842110814679026</v>
+        <v>0.02840991553220516</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6538.87</v>
+        <v>6691.22</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6775.12</v>
+        <v>6932.9</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>236.25</v>
+        <v>241.68</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.0361300958728343</v>
+        <v>0.03611897381942306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7135,48 +7315,48 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>47.897</v>
+        <v>47.914</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>48.678</v>
+        <v>48.695</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>0.781</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.01630582291166461</v>
+        <v>0.01630003756730809</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.44</v>
+        <v>55.58</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.355</v>
+        <v>56.496</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.915</v>
+        <v>0.916</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.016504329004329</v>
+        <v>0.0164807484706729</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6611.61</v>
+        <v>6772.16</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6747.97</v>
+        <v>6911.34</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>136.36</v>
+        <v>139.18</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02062432599623995</v>
+        <v>0.02055178849879507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7184,48 +7364,48 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.085</v>
+        <v>48.101</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.37</v>
+        <v>48.389</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.285</v>
+        <v>0.288</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.005927004263283769</v>
+        <v>0.00598740150932413</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.498</v>
+        <v>55.634</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.001</v>
+        <v>56.142</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.503</v>
+        <v>0.508</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.009063389671699881</v>
+        <v>0.00913110687708955</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6677.77</v>
+        <v>6831.41</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6744.08</v>
+        <v>6899.34</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>66.31</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.009929961648873801</v>
+        <v>0.009943774418458269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7233,48 +7413,48 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.209</v>
+        <v>48.26</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.399</v>
+        <v>48.45</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0.19</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.003941172810056214</v>
+        <v>0.003937007874015748</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.718</v>
+        <v>55.865</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>56.039</v>
+        <v>56.209</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.321</v>
+        <v>0.344</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.00576115438457949</v>
+        <v>0.006157701602076435</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6605.81</v>
+        <v>6773.24</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6780</v>
+        <v>6935</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>174.19</v>
+        <v>161.76</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02636921134576986</v>
+        <v>0.02388221884947233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7282,48 +7462,48 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4531</v>
+        <v>47.4706</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7296</v>
+        <v>48.747</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2765</v>
+        <v>1.2764</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02690024466262478</v>
+        <v>0.02688822134120909</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.0428</v>
+        <v>55.1632</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.4077</v>
+        <v>56.5354</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3649</v>
+        <v>1.3722</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02479706700967247</v>
+        <v>0.02487527917162166</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6601.16</v>
+        <v>6755.31</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6752.06</v>
+        <v>6913.93</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>150.9</v>
+        <v>158.62</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02285961861248629</v>
+        <v>0.02348078770626367</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7331,48 +7511,48 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>47.302</v>
+        <v>47.32</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.225</v>
+        <v>49.243</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>1.923</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04065367214916916</v>
+        <v>0.04063820794590026</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.762</v>
+        <v>54.896</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>56.997</v>
+        <v>57.131</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>2.235</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04081297249917826</v>
+        <v>0.04071334887787817</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6597.34</v>
+        <v>6756.65</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6791.54</v>
+        <v>6950.96</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.2</v>
+        <v>194.31</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02943610606699064</v>
+        <v>0.02875833438168323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7380,48 +7560,48 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5549</v>
+        <v>47.5724</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.955</v>
+        <v>48.9725</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02944176099623803</v>
+        <v>0.02943093053955655</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.0586</v>
+        <v>55.1922</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.6845</v>
+        <v>56.8215</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6259</v>
+        <v>1.6293</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02953035493092814</v>
+        <v>0.02952047571939513</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6612.89</v>
+        <v>6771.17</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6808.62</v>
+        <v>6971.44</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>195.73</v>
+        <v>200.27</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02959825431845986</v>
+        <v>0.02957686780866527</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7429,48 +7609,48 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2242</v>
+        <v>48.2418</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2813</v>
+        <v>48.2988</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0571</v>
+        <v>0.057</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001184052819953467</v>
+        <v>0.001181547952190839</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.8185</v>
+        <v>55.9447</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>55.9017</v>
+        <v>56.0327</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.0832</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001490545249334898</v>
+        <v>0.001572981891045979</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6667.12</v>
+        <v>6822.67</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6695.98</v>
+        <v>6851.87</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004328705648015935</v>
+        <v>0.00427984938447851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7478,48 +7658,48 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.238</v>
+        <v>48.2554</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2765</v>
+        <v>48.2942</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0388</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007981259587876778</v>
+        <v>0.0008040550902075208</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.7958</v>
+        <v>55.9297</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>55.91</v>
+        <v>56.0396</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1142</v>
+        <v>0.1099</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.002046749038458092</v>
+        <v>0.001964966735026292</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6664.2</v>
+        <v>6819.54</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6695.84</v>
+        <v>6852.53</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>31.64</v>
+        <v>32.99</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004747756669967888</v>
+        <v>0.004837569689451195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7527,48 +7707,48 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9238</v>
+        <v>47.941</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1621</v>
+        <v>49.1797</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2383</v>
+        <v>1.2387</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.025838935977531</v>
+        <v>0.02583800921966584</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3734</v>
+        <v>55.4817</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.6524</v>
+        <v>56.772</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.279</v>
+        <v>1.2903</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02309773284645696</v>
+        <v>0.02325631694775034</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6616.09</v>
+        <v>6771.98</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6724.63</v>
+        <v>6882.41</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>108.54</v>
+        <v>110.43</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01640546002246039</v>
+        <v>0.01630689990224425</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7576,48 +7756,48 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>47.8475</v>
+        <v>47.8645</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>48.6975</v>
+        <v>48.7145</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>0.85</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.01776477349913789</v>
+        <v>0.01775846399732578</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.3099</v>
+        <v>55.4443</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.4666</v>
+        <v>56.6033</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.1567</v>
+        <v>1.159</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.0209130734280843</v>
+        <v>0.02090386207418977</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6612.1</v>
+        <v>6768.67</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6766.77</v>
+        <v>6926.84</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154.67</v>
+        <v>158.17</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02339196321894708</v>
+        <v>0.02336795855020262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7625,48 +7805,48 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9982</v>
+        <v>48.0158</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6054</v>
+        <v>48.6228</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6072</v>
+        <v>0.607</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01265047439278973</v>
+        <v>0.01264167211626173</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.5764</v>
+        <v>55.7141</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.237</v>
+        <v>56.3773</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6606</v>
+        <v>0.6632</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01188634024514002</v>
+        <v>0.01190362942235449</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6683.15</v>
+        <v>6841.62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6737.49</v>
+        <v>6896.09</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.34</v>
+        <v>54.47</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008130896358752984</v>
+        <v>0.007961564658662714</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7674,48 +7854,48 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.454</v>
+        <v>47.472</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>48.804</v>
+        <v>48.822</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02844860285750411</v>
+        <v>0.02843781597573306</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>54.935</v>
+        <v>55.067</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.498</v>
+        <v>56.633</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.563</v>
+        <v>1.566</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02845180668062255</v>
+        <v>0.02843808451522691</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6580.71</v>
+        <v>6735.53</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6823.81</v>
+        <v>6984.34</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>243.1</v>
+        <v>248.81</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694130268618432</v>
+        <v>0.03693992900335979</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7723,48 +7903,48 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9984</v>
+        <v>48.0158</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6053</v>
+        <v>48.6228</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6069</v>
+        <v>0.607</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264417147238241</v>
+        <v>0.01264167211626173</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.5861</v>
+        <v>55.7155</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.2467</v>
+        <v>56.379</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6606</v>
+        <v>0.6635</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01188426603053641</v>
+        <v>0.01190871481006183</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6685.19</v>
+        <v>6841.95</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6739.53</v>
+        <v>6896.34</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.34</v>
+        <v>54.39</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008128415198371325</v>
+        <v>0.007949488084537304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7772,48 +7952,48 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.8672</v>
+        <v>47.8848</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.8472</v>
+        <v>48.8648</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0.98</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02047330948958786</v>
+        <v>0.02046578454958567</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.4111</v>
+        <v>55.5488</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.5455</v>
+        <v>56.6856</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1344</v>
+        <v>1.1368</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.0204724324187753</v>
+        <v>0.0204648885304453</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6611.86</v>
+        <v>6768.04</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6814.92</v>
+        <v>6976.09</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>203.06</v>
+        <v>208.05</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03071147906942978</v>
+        <v>0.03074006654807005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -7821,48 +8001,48 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.25</v>
+        <v>48.285</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.31</v>
+        <v>48.329</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.06</v>
+        <v>0.044</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.001243523316062176</v>
+        <v>0.0009112560836698767</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.718</v>
+        <v>55.889</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>55.887</v>
+        <v>56.025</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.169</v>
+        <v>0.136</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.003033131124591694</v>
+        <v>0.002433394764622734</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6628.13</v>
+        <v>6798.78</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6713.71</v>
+        <v>6876.17</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>85.58</v>
+        <v>77.39</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01291163571022294</v>
+        <v>0.01138292458352822</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -7870,48 +8050,48 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.218</v>
+        <v>48.2355</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.3648</v>
+        <v>48.382</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1468</v>
+        <v>0.1465</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003044506201003774</v>
+        <v>0.003037182158368837</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.8086</v>
+        <v>55.9469</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>55.9803</v>
+        <v>56.1188</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1717</v>
+        <v>0.1719</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003076586762613647</v>
+        <v>0.003072556298919153</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6673.84</v>
+        <v>6831.7</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6721.1</v>
+        <v>6879.98</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47.26</v>
+        <v>48.28</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007081380434652315</v>
+        <v>0.007067055052183204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -7927,24 +8107,24 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6681.95</v>
+        <v>6780.95</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6877.67</v>
+        <v>6979.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>195.72</v>
+        <v>198.17</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02929085072471359</v>
+        <v>0.02922451868838437</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -7952,48 +8132,48 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.7933</v>
+        <v>47.8217</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.6799</v>
+        <v>48.7085</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8868</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01855071735996468</v>
+        <v>0.01854388279797665</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.3353</v>
+        <v>55.4774</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.3898</v>
+        <v>56.5369</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0545</v>
+        <v>1.0595</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01905655160449117</v>
+        <v>0.01909786687912556</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6617.13</v>
+        <v>6773.34</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7063.22</v>
+        <v>7218.38</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>446.09</v>
+        <v>445.04</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06741442286912906</v>
+        <v>0.06570465973950813</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8001,48 +8181,48 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7514</v>
+        <v>47.7689</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7549</v>
+        <v>48.7723</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0035</v>
+        <v>1.0034</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02101509065702786</v>
+        <v>0.02100529842638202</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.357</v>
+        <v>55.4929</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.367</v>
+        <v>56.5126</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.01</v>
+        <v>1.0197</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01824520837473129</v>
+        <v>0.01837532369005765</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6583.01</v>
+        <v>6742.66</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6835.05</v>
+        <v>6994.99</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>252.04</v>
+        <v>252.33</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03828643735920195</v>
+        <v>0.03742291617848149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8050,48 +8230,48 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6786</v>
+        <v>47.6959</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8336</v>
+        <v>48.8509</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>1.155</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02422470458444669</v>
+        <v>0.02421591793005269</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.1928</v>
+        <v>55.313</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.5298</v>
+        <v>56.667</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.337</v>
+        <v>1.354</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02422417416764506</v>
+        <v>0.02447887476723374</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6604.6</v>
+        <v>6763.4</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6785.71</v>
+        <v>6948.85</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181.11</v>
+        <v>185.45</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02742179692941283</v>
+        <v>0.02741964100895999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8099,48 +8279,48 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.27</v>
+        <v>48.3</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>48.29</v>
+        <v>48.31</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0004143360265175057</v>
+        <v>0.0002070393374741201</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>55.75</v>
+        <v>55.93</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>55.8</v>
+        <v>55.98</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0008968609865470851</v>
+        <v>0.0008939746111210442</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6682.61</v>
+        <v>6846.95</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6690.23</v>
+        <v>6853.22</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>7.62</v>
+        <v>6.27</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.001140273037031938</v>
+        <v>0.0009157362037111415</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8148,48 +8328,48 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.613</v>
+        <v>47.6305</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.5991</v>
+        <v>48.6166</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0.9861</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02071073026274337</v>
+        <v>0.02070312089942369</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.1196</v>
+        <v>55.2585</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.2617</v>
+        <v>56.4031</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1421</v>
+        <v>1.1446</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02072039710012409</v>
+        <v>0.02071355538062018</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6578.23</v>
+        <v>6720.13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6752.43</v>
+        <v>6898.42</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>174.2</v>
+        <v>178.29</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.02648128751959113</v>
+        <v>0.0265307367565806</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8197,28 +8377,28 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>48.1891</v>
+        <v>48.2075</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>48.2759</v>
+        <v>48.2943</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>0.0868</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.001801237209244414</v>
+        <v>0.001800549706995799</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>55.8769</v>
+        <v>55.7929</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>55.9776</v>
+        <v>55.8934</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.1007</v>
+        <v>0.1005</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.001802175854422847</v>
+        <v>0.001801304467055844</v>
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
@@ -8227,10 +8407,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8238,48 +8418,48 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.227</v>
+        <v>48.2443</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2804</v>
+        <v>48.2975</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0534</v>
+        <v>0.0532</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001107263566052211</v>
+        <v>0.001102720943199507</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.8172</v>
+        <v>55.9263</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>55.8979</v>
+        <v>56.0243</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001445790903162466</v>
+        <v>0.00175230616007138</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6662.57</v>
+        <v>6853.96</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6690.94</v>
+        <v>6888.36</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>28.37</v>
+        <v>34.4</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004258116612658479</v>
+        <v>0.005018996317457352</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8287,48 +8467,48 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.265</v>
+        <v>48.304</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.366</v>
+        <v>48.386</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.101</v>
+        <v>0.082</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002092613695224283</v>
+        <v>0.00169758198078834</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.733</v>
+        <v>55.834</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>55.962</v>
+        <v>56.096</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.229</v>
+        <v>0.262</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004108876249259864</v>
+        <v>0.004692481283805566</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6638</v>
+        <v>6817</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6693</v>
+        <v>6868</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.008285628201265442</v>
+        <v>0.007481296758104739</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8336,48 +8516,48 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7615</v>
+        <v>47.7755</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7615</v>
+        <v>48.7755</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093736586999989</v>
+        <v>0.02093123044238156</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.318</v>
+        <v>55.444</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.408</v>
+        <v>56.534</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01970425539607361</v>
+        <v>0.01965947622826636</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6663.22</v>
+        <v>6818.14</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6763.22</v>
+        <v>6918.14</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.0150077590114089</v>
+        <v>0.01466675662277395</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8393,24 +8573,24 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6681.95</v>
+        <v>6780.95</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6863.94</v>
+        <v>6965.19</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>181.99</v>
+        <v>184.24</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02723606132940234</v>
+        <v>0.02717023425921147</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8418,48 +8598,48 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>47.6875</v>
+        <v>47.7045</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>48.9075</v>
+        <v>48.9245</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.02558322411533421</v>
+        <v>0.02557410726451383</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.0919</v>
+        <v>55.2258</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.7489</v>
+        <v>56.8814</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.657</v>
+        <v>1.6556</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03007701676653011</v>
+        <v>0.02997874181994647</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6586.13</v>
+        <v>6741.82</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6784.36</v>
+        <v>6944.4</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>198.23</v>
+        <v>202.58</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03009810009823675</v>
+        <v>0.03004826589852592</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8467,48 +8647,48 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1413</v>
+        <v>48.1907</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.3827</v>
+        <v>48.4081</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2414</v>
+        <v>0.2174</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.005014405510445293</v>
+        <v>0.004511243870705344</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.6806</v>
+        <v>55.8248</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.016</v>
+        <v>56.1611</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3354</v>
+        <v>0.3363</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006023641986616523</v>
+        <v>0.006024204296298419</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6598.67</v>
+        <v>6755.73</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6732.31</v>
+        <v>6892.56</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>133.64</v>
+        <v>136.83</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025256604740046</v>
+        <v>0.02025391778534666</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8516,48 +8696,48 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8518</v>
+        <v>47.8693</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6541</v>
+        <v>48.6711</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8023</v>
+        <v>0.8018</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01676634943722075</v>
+        <v>0.01674977490792637</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.4245</v>
+        <v>55.5596</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.2748</v>
+        <v>56.4105</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8509</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01534159081272722</v>
+        <v>0.0153150850618075</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6611.43</v>
+        <v>6767.92</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6807.72</v>
+        <v>6964.67</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.29</v>
+        <v>196.75</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02968949228835517</v>
+        <v>0.02907097010602962</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8565,48 +8745,48 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1538</v>
+        <v>48.1712</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.357</v>
+        <v>48.3744</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004219812351257845</v>
+        <v>0.004218288105756137</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.7353</v>
+        <v>55.8686</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>55.9599</v>
+        <v>56.0937</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2246</v>
+        <v>0.2251</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004029762107676822</v>
+        <v>0.004029096845097246</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6650.43</v>
+        <v>6806.13</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6703.85</v>
+        <v>6860.8</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>53.42</v>
+        <v>54.67</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.00803256330793648</v>
+        <v>0.008032464851538246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8614,48 +8794,48 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.8946</v>
+        <v>47.9119</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8556</v>
+        <v>48.8729</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02006489249309943</v>
+        <v>0.02005764747380087</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.4653</v>
+        <v>55.6027</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.5673</v>
+        <v>56.7214</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.102</v>
+        <v>1.1187</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.01986827800444602</v>
+        <v>0.02011952656975291</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6617.75</v>
+        <v>6774.91</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6762.35</v>
+        <v>6919.51</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02185032677269465</v>
+        <v>0.02134345696105188</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8663,28 +8843,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.271</v>
+        <v>48.291</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.31</v>
+        <v>48.329</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.000807938513807462</v>
+        <v>0.0007868961090058189</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.772</v>
+        <v>55.902</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>55.875</v>
+        <v>56.013</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.103</v>
+        <v>0.111</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.00184680484831098</v>
+        <v>0.001985617688097027</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8693,10 +8873,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8704,48 +8884,48 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>47.65</v>
+        <v>47.72</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>48.65</v>
+        <v>48.62</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.02098635886673662</v>
+        <v>0.01886001676445935</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.17</v>
+        <v>55.36</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.31</v>
+        <v>56.38</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.02066340402392605</v>
+        <v>0.01842485549132948</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6584.64</v>
+        <v>6748.18</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6786.98</v>
+        <v>6937.84</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>202.34</v>
+        <v>189.66</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.03072909073237109</v>
+        <v>0.02810535581445664</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8753,48 +8933,48 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.8905</v>
+        <v>47.9078</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8593</v>
+        <v>48.877</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.9688</v>
+        <v>0.9692</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02022948183877804</v>
+        <v>0.02023052613561883</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.4241</v>
+        <v>55.5555</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.5454</v>
+        <v>56.6794</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1213</v>
+        <v>1.1239</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023127123399388</v>
+        <v>0.02023022023022023</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6650.94</v>
+        <v>6806.95</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6785.23</v>
+        <v>6944.39</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>134.29</v>
+        <v>137.44</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019113087774059</v>
+        <v>0.02019112818516369</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8802,48 +8982,48 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9384</v>
+        <v>47.9557</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.5906</v>
+        <v>48.6082</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.6522</v>
+        <v>0.6525</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360495969827946</v>
+        <v>0.01360630748795242</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.4326</v>
+        <v>55.562</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.243</v>
+        <v>56.3743</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8104</v>
+        <v>0.8123</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461955600134217</v>
+        <v>0.01461970411432274</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6620.42</v>
+        <v>6776.4</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6754.09</v>
+        <v>6913.23</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>133.67</v>
+        <v>136.83</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019056192809519</v>
+        <v>0.02019213741809811</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -8851,40 +9031,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7683</v>
+        <v>47.7853</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.766</v>
+        <v>48.7835</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9977</v>
+        <v>0.9982</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02088623626966001</v>
+        <v>0.02088926929411346</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.2548</v>
+        <v>55.3938</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.4646</v>
+        <v>56.6063</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2098</v>
+        <v>1.2125</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02189493039518739</v>
+        <v>0.02188873122984883</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6640.01</v>
+        <v>6795.78</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6850.92</v>
+        <v>7011.57</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>210.91</v>
+        <v>215.79</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03176350638026148</v>
+        <v>0.0317535293961841</v>
       </c>
     </row>
   </sheetData>
@@ -8901,7 +9081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N649"/>
+  <dimension ref="A1:N757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41390,6 +41570,5406 @@
       <c r="M649" t="inlineStr"/>
       <c r="N649" s="6" t="n">
         <v>0.4003819444444445</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B650" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C650" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D650" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E650" s="8" t="n">
+        <v>47.519</v>
+      </c>
+      <c r="F650" s="8" t="n">
+        <v>48.869</v>
+      </c>
+      <c r="G650" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H650" s="9" t="n">
+        <v>0.02840968875607652</v>
+      </c>
+      <c r="I650" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J650" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K650" s="54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L650" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M650" t="inlineStr"/>
+      <c r="N650" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B651" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C651" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D651" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E651" s="10" t="n">
+        <v>55.1216</v>
+      </c>
+      <c r="F651" s="10" t="n">
+        <v>56.6876</v>
+      </c>
+      <c r="G651" s="10" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H651" s="11" t="n">
+        <v>0.02840991553220516</v>
+      </c>
+      <c r="I651" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J651" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K651" s="54" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="L651" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M651" t="inlineStr"/>
+      <c r="N651" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B652" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C652" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D652" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E652" s="12" t="n">
+        <v>6691.22</v>
+      </c>
+      <c r="F652" s="12" t="n">
+        <v>6932.9</v>
+      </c>
+      <c r="G652" s="12" t="n">
+        <v>241.68</v>
+      </c>
+      <c r="H652" s="13" t="n">
+        <v>0.03611897381942306</v>
+      </c>
+      <c r="I652" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J652" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K652" s="54" t="n">
+        <v>241.68</v>
+      </c>
+      <c r="L652" s="55" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="M652" t="inlineStr"/>
+      <c r="N652" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B653" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C653" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D653" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E653" s="8" t="n">
+        <v>47.914</v>
+      </c>
+      <c r="F653" s="8" t="n">
+        <v>48.695</v>
+      </c>
+      <c r="G653" s="8" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="H653" s="9" t="n">
+        <v>0.01630003756730809</v>
+      </c>
+      <c r="I653" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J653" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K653" s="54" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L653" s="55" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M653" t="inlineStr"/>
+      <c r="N653" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B654" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C654" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D654" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E654" s="10" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="F654" s="10" t="n">
+        <v>56.496</v>
+      </c>
+      <c r="G654" s="10" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H654" s="11" t="n">
+        <v>0.0164807484706729</v>
+      </c>
+      <c r="I654" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J654" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K654" s="54" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="L654" s="55" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M654" t="inlineStr"/>
+      <c r="N654" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B655" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C655" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D655" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E655" s="12" t="n">
+        <v>6772.16</v>
+      </c>
+      <c r="F655" s="12" t="n">
+        <v>6911.34</v>
+      </c>
+      <c r="G655" s="12" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="H655" s="13" t="n">
+        <v>0.02055178849879507</v>
+      </c>
+      <c r="I655" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J655" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K655" s="54" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="L655" s="55" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="M655" t="inlineStr"/>
+      <c r="N655" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B656" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C656" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D656" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E656" s="8" t="n">
+        <v>48.101</v>
+      </c>
+      <c r="F656" s="8" t="n">
+        <v>48.389</v>
+      </c>
+      <c r="G656" s="8" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="H656" s="9" t="n">
+        <v>0.00598740150932413</v>
+      </c>
+      <c r="I656" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J656" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K656" s="54" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="L656" s="55" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M656" t="inlineStr"/>
+      <c r="N656" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B657" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C657" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D657" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E657" s="10" t="n">
+        <v>55.634</v>
+      </c>
+      <c r="F657" s="10" t="n">
+        <v>56.142</v>
+      </c>
+      <c r="G657" s="10" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="H657" s="11" t="n">
+        <v>0.00913110687708955</v>
+      </c>
+      <c r="I657" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J657" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K657" s="54" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="L657" s="55" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="M657" t="inlineStr"/>
+      <c r="N657" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B658" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C658" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D658" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E658" s="12" t="n">
+        <v>6831.41</v>
+      </c>
+      <c r="F658" s="12" t="n">
+        <v>6899.34</v>
+      </c>
+      <c r="G658" s="12" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="H658" s="13" t="n">
+        <v>0.009943774418458269</v>
+      </c>
+      <c r="I658" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J658" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K658" s="54" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="L658" s="55" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="M658" t="inlineStr"/>
+      <c r="N658" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B659" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C659" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D659" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E659" s="8" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="F659" s="8" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="G659" s="8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H659" s="9" t="n">
+        <v>0.003937007874015748</v>
+      </c>
+      <c r="I659" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J659" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K659" s="54" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L659" s="55" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="M659" t="inlineStr"/>
+      <c r="N659" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B660" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C660" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D660" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E660" s="10" t="n">
+        <v>55.865</v>
+      </c>
+      <c r="F660" s="10" t="n">
+        <v>56.209</v>
+      </c>
+      <c r="G660" s="10" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="H660" s="11" t="n">
+        <v>0.006157701602076435</v>
+      </c>
+      <c r="I660" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J660" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K660" s="54" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="L660" s="55" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M660" t="inlineStr"/>
+      <c r="N660" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B661" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C661" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D661" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E661" s="12" t="n">
+        <v>6773.24</v>
+      </c>
+      <c r="F661" s="12" t="n">
+        <v>6935</v>
+      </c>
+      <c r="G661" s="12" t="n">
+        <v>161.76</v>
+      </c>
+      <c r="H661" s="13" t="n">
+        <v>0.02388221884947233</v>
+      </c>
+      <c r="I661" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J661" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K661" s="54" t="n">
+        <v>161.76</v>
+      </c>
+      <c r="L661" s="55" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="M661" t="inlineStr"/>
+      <c r="N661" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B662" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C662" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D662" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E662" s="8" t="n">
+        <v>47.4706</v>
+      </c>
+      <c r="F662" s="8" t="n">
+        <v>48.747</v>
+      </c>
+      <c r="G662" s="8" t="n">
+        <v>1.2764</v>
+      </c>
+      <c r="H662" s="9" t="n">
+        <v>0.02688822134120909</v>
+      </c>
+      <c r="I662" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J662" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K662" s="54" t="n">
+        <v>1.2764</v>
+      </c>
+      <c r="L662" s="55" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="M662" t="inlineStr"/>
+      <c r="N662" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B663" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C663" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D663" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E663" s="10" t="n">
+        <v>55.1632</v>
+      </c>
+      <c r="F663" s="10" t="n">
+        <v>56.5354</v>
+      </c>
+      <c r="G663" s="10" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="H663" s="11" t="n">
+        <v>0.02487527917162166</v>
+      </c>
+      <c r="I663" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J663" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K663" s="54" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="L663" s="55" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="M663" t="inlineStr"/>
+      <c r="N663" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B664" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C664" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D664" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E664" s="12" t="n">
+        <v>6755.31</v>
+      </c>
+      <c r="F664" s="12" t="n">
+        <v>6913.93</v>
+      </c>
+      <c r="G664" s="12" t="n">
+        <v>158.62</v>
+      </c>
+      <c r="H664" s="13" t="n">
+        <v>0.02348078770626367</v>
+      </c>
+      <c r="I664" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J664" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K664" s="54" t="n">
+        <v>158.63</v>
+      </c>
+      <c r="L664" s="55" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="M664" t="inlineStr"/>
+      <c r="N664" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B665" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C665" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D665" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E665" s="8" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="F665" s="8" t="n">
+        <v>49.243</v>
+      </c>
+      <c r="G665" s="8" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="H665" s="9" t="n">
+        <v>0.04063820794590026</v>
+      </c>
+      <c r="I665" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J665" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K665" s="54" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="L665" s="55" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M665" t="inlineStr"/>
+      <c r="N665" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B666" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C666" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D666" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E666" s="10" t="n">
+        <v>54.896</v>
+      </c>
+      <c r="F666" s="10" t="n">
+        <v>57.131</v>
+      </c>
+      <c r="G666" s="10" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="H666" s="11" t="n">
+        <v>0.04071334887787817</v>
+      </c>
+      <c r="I666" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J666" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K666" s="54" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L666" s="55" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="M666" t="inlineStr"/>
+      <c r="N666" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B667" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C667" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D667" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E667" s="12" t="n">
+        <v>6756.65</v>
+      </c>
+      <c r="F667" s="12" t="n">
+        <v>6950.96</v>
+      </c>
+      <c r="G667" s="12" t="n">
+        <v>194.31</v>
+      </c>
+      <c r="H667" s="13" t="n">
+        <v>0.02875833438168323</v>
+      </c>
+      <c r="I667" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J667" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K667" s="54" t="n">
+        <v>194.31</v>
+      </c>
+      <c r="L667" s="55" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="M667" t="inlineStr"/>
+      <c r="N667" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B668" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C668" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D668" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E668" s="8" t="n">
+        <v>47.5724</v>
+      </c>
+      <c r="F668" s="8" t="n">
+        <v>48.9725</v>
+      </c>
+      <c r="G668" s="8" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="H668" s="9" t="n">
+        <v>0.02943093053955655</v>
+      </c>
+      <c r="I668" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J668" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K668" s="54" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="L668" s="55" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="M668" t="inlineStr"/>
+      <c r="N668" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B669" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C669" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D669" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E669" s="10" t="n">
+        <v>55.1922</v>
+      </c>
+      <c r="F669" s="10" t="n">
+        <v>56.8215</v>
+      </c>
+      <c r="G669" s="10" t="n">
+        <v>1.6293</v>
+      </c>
+      <c r="H669" s="11" t="n">
+        <v>0.02952047571939513</v>
+      </c>
+      <c r="I669" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J669" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K669" s="54" t="n">
+        <v>1.6293</v>
+      </c>
+      <c r="L669" s="55" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="M669" t="inlineStr"/>
+      <c r="N669" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B670" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C670" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D670" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E670" s="12" t="n">
+        <v>6771.17</v>
+      </c>
+      <c r="F670" s="12" t="n">
+        <v>6971.44</v>
+      </c>
+      <c r="G670" s="12" t="n">
+        <v>200.27</v>
+      </c>
+      <c r="H670" s="13" t="n">
+        <v>0.02957686780866527</v>
+      </c>
+      <c r="I670" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J670" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K670" s="54" t="n">
+        <v>200.28</v>
+      </c>
+      <c r="L670" s="55" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="M670" t="inlineStr"/>
+      <c r="N670" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B671" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C671" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D671" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E671" s="8" t="n">
+        <v>48.2418</v>
+      </c>
+      <c r="F671" s="8" t="n">
+        <v>48.2988</v>
+      </c>
+      <c r="G671" s="8" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H671" s="9" t="n">
+        <v>0.001181547952190839</v>
+      </c>
+      <c r="I671" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J671" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K671" s="54" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="L671" s="55" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="M671" t="inlineStr"/>
+      <c r="N671" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B672" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C672" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D672" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E672" s="10" t="n">
+        <v>55.9447</v>
+      </c>
+      <c r="F672" s="10" t="n">
+        <v>56.0327</v>
+      </c>
+      <c r="G672" s="10" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="H672" s="11" t="n">
+        <v>0.001572981891045979</v>
+      </c>
+      <c r="I672" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J672" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K672" s="54" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L672" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M672" t="inlineStr"/>
+      <c r="N672" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B673" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C673" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D673" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E673" s="12" t="n">
+        <v>6822.67</v>
+      </c>
+      <c r="F673" s="12" t="n">
+        <v>6851.87</v>
+      </c>
+      <c r="G673" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H673" s="13" t="n">
+        <v>0.00427984938447851</v>
+      </c>
+      <c r="I673" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J673" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K673" s="54" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L673" s="55" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B674" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C674" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D674" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E674" s="8" t="n">
+        <v>48.2554</v>
+      </c>
+      <c r="F674" s="8" t="n">
+        <v>48.2942</v>
+      </c>
+      <c r="G674" s="8" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="H674" s="9" t="n">
+        <v>0.0008040550902075208</v>
+      </c>
+      <c r="I674" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J674" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K674" s="54" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="L674" s="55" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M674" t="inlineStr"/>
+      <c r="N674" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B675" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C675" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D675" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E675" s="10" t="n">
+        <v>55.9297</v>
+      </c>
+      <c r="F675" s="10" t="n">
+        <v>56.0396</v>
+      </c>
+      <c r="G675" s="10" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="H675" s="11" t="n">
+        <v>0.001964966735026292</v>
+      </c>
+      <c r="I675" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J675" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K675" s="54" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="L675" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B676" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C676" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D676" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E676" s="12" t="n">
+        <v>6819.54</v>
+      </c>
+      <c r="F676" s="12" t="n">
+        <v>6852.53</v>
+      </c>
+      <c r="G676" s="12" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="H676" s="13" t="n">
+        <v>0.004837569689451195</v>
+      </c>
+      <c r="I676" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J676" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K676" s="54" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="L676" s="55" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="M676" t="inlineStr"/>
+      <c r="N676" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B677" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C677" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D677" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E677" s="8" t="n">
+        <v>47.941</v>
+      </c>
+      <c r="F677" s="8" t="n">
+        <v>49.1797</v>
+      </c>
+      <c r="G677" s="8" t="n">
+        <v>1.2387</v>
+      </c>
+      <c r="H677" s="9" t="n">
+        <v>0.02583800921966584</v>
+      </c>
+      <c r="I677" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J677" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K677" s="54" t="n">
+        <v>1.2387</v>
+      </c>
+      <c r="L677" s="55" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="M677" t="inlineStr"/>
+      <c r="N677" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B678" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C678" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D678" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E678" s="10" t="n">
+        <v>55.4817</v>
+      </c>
+      <c r="F678" s="10" t="n">
+        <v>56.772</v>
+      </c>
+      <c r="G678" s="10" t="n">
+        <v>1.2903</v>
+      </c>
+      <c r="H678" s="11" t="n">
+        <v>0.02325631694775034</v>
+      </c>
+      <c r="I678" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J678" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K678" s="54" t="n">
+        <v>1.2904</v>
+      </c>
+      <c r="L678" s="55" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="M678" t="inlineStr"/>
+      <c r="N678" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B679" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C679" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D679" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E679" s="12" t="n">
+        <v>6771.98</v>
+      </c>
+      <c r="F679" s="12" t="n">
+        <v>6882.41</v>
+      </c>
+      <c r="G679" s="12" t="n">
+        <v>110.43</v>
+      </c>
+      <c r="H679" s="13" t="n">
+        <v>0.01630689990224425</v>
+      </c>
+      <c r="I679" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J679" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K679" s="54" t="n">
+        <v>110.43</v>
+      </c>
+      <c r="L679" s="55" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B680" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C680" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D680" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E680" s="8" t="n">
+        <v>47.8645</v>
+      </c>
+      <c r="F680" s="8" t="n">
+        <v>48.7145</v>
+      </c>
+      <c r="G680" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H680" s="9" t="n">
+        <v>0.01775846399732578</v>
+      </c>
+      <c r="I680" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J680" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K680" s="54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L680" s="55" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="M680" t="inlineStr"/>
+      <c r="N680" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B681" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C681" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D681" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E681" s="10" t="n">
+        <v>55.4443</v>
+      </c>
+      <c r="F681" s="10" t="n">
+        <v>56.6033</v>
+      </c>
+      <c r="G681" s="10" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="H681" s="11" t="n">
+        <v>0.02090386207418977</v>
+      </c>
+      <c r="I681" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J681" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K681" s="54" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="L681" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M681" t="inlineStr"/>
+      <c r="N681" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B682" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C682" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D682" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E682" s="12" t="n">
+        <v>6768.67</v>
+      </c>
+      <c r="F682" s="12" t="n">
+        <v>6926.84</v>
+      </c>
+      <c r="G682" s="12" t="n">
+        <v>158.17</v>
+      </c>
+      <c r="H682" s="13" t="n">
+        <v>0.02336795855020262</v>
+      </c>
+      <c r="I682" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J682" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K682" s="54" t="n">
+        <v>158.17</v>
+      </c>
+      <c r="L682" s="55" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="M682" t="inlineStr"/>
+      <c r="N682" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B683" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C683" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D683" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E683" s="8" t="n">
+        <v>48.0158</v>
+      </c>
+      <c r="F683" s="8" t="n">
+        <v>48.6228</v>
+      </c>
+      <c r="G683" s="8" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="H683" s="9" t="n">
+        <v>0.01264167211626173</v>
+      </c>
+      <c r="I683" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J683" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K683" s="54" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L683" s="55" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="M683" t="inlineStr"/>
+      <c r="N683" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B684" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C684" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D684" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E684" s="10" t="n">
+        <v>55.7141</v>
+      </c>
+      <c r="F684" s="10" t="n">
+        <v>56.3773</v>
+      </c>
+      <c r="G684" s="10" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="H684" s="11" t="n">
+        <v>0.01190362942235449</v>
+      </c>
+      <c r="I684" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J684" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K684" s="54" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="L684" s="55" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="M684" t="inlineStr"/>
+      <c r="N684" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B685" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C685" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D685" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E685" s="12" t="n">
+        <v>6841.62</v>
+      </c>
+      <c r="F685" s="12" t="n">
+        <v>6896.09</v>
+      </c>
+      <c r="G685" s="12" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H685" s="13" t="n">
+        <v>0.007961564658662714</v>
+      </c>
+      <c r="I685" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J685" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K685" s="54" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="L685" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M685" t="inlineStr"/>
+      <c r="N685" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B686" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C686" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D686" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E686" s="8" t="n">
+        <v>47.472</v>
+      </c>
+      <c r="F686" s="8" t="n">
+        <v>48.822</v>
+      </c>
+      <c r="G686" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H686" s="9" t="n">
+        <v>0.02843781597573306</v>
+      </c>
+      <c r="I686" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J686" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K686" s="54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L686" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M686" t="inlineStr"/>
+      <c r="N686" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B687" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C687" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D687" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E687" s="10" t="n">
+        <v>55.067</v>
+      </c>
+      <c r="F687" s="10" t="n">
+        <v>56.633</v>
+      </c>
+      <c r="G687" s="10" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H687" s="11" t="n">
+        <v>0.02843808451522691</v>
+      </c>
+      <c r="I687" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J687" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K687" s="54" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="L687" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M687" t="inlineStr"/>
+      <c r="N687" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B688" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C688" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D688" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E688" s="12" t="n">
+        <v>6735.53</v>
+      </c>
+      <c r="F688" s="12" t="n">
+        <v>6984.34</v>
+      </c>
+      <c r="G688" s="12" t="n">
+        <v>248.81</v>
+      </c>
+      <c r="H688" s="13" t="n">
+        <v>0.03693992900335979</v>
+      </c>
+      <c r="I688" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J688" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K688" s="54" t="n">
+        <v>248.81</v>
+      </c>
+      <c r="L688" s="55" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M688" t="inlineStr"/>
+      <c r="N688" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B689" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C689" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D689" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E689" s="8" t="n">
+        <v>48.0158</v>
+      </c>
+      <c r="F689" s="8" t="n">
+        <v>48.6228</v>
+      </c>
+      <c r="G689" s="8" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="H689" s="9" t="n">
+        <v>0.01264167211626173</v>
+      </c>
+      <c r="I689" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J689" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K689" s="54" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L689" s="55" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="M689" t="inlineStr"/>
+      <c r="N689" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B690" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C690" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D690" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E690" s="10" t="n">
+        <v>55.7155</v>
+      </c>
+      <c r="F690" s="10" t="n">
+        <v>56.379</v>
+      </c>
+      <c r="G690" s="10" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="H690" s="11" t="n">
+        <v>0.01190871481006183</v>
+      </c>
+      <c r="I690" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J690" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K690" s="54" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="L690" s="55" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="M690" t="inlineStr"/>
+      <c r="N690" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B691" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C691" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D691" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E691" s="12" t="n">
+        <v>6841.95</v>
+      </c>
+      <c r="F691" s="12" t="n">
+        <v>6896.34</v>
+      </c>
+      <c r="G691" s="12" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="H691" s="13" t="n">
+        <v>0.007949488084537304</v>
+      </c>
+      <c r="I691" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J691" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K691" s="54" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="L691" s="55" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="M691" t="inlineStr"/>
+      <c r="N691" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B692" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C692" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D692" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E692" s="8" t="n">
+        <v>47.8848</v>
+      </c>
+      <c r="F692" s="8" t="n">
+        <v>48.8648</v>
+      </c>
+      <c r="G692" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H692" s="9" t="n">
+        <v>0.02046578454958567</v>
+      </c>
+      <c r="I692" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J692" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K692" s="54" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L692" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M692" t="inlineStr"/>
+      <c r="N692" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B693" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C693" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D693" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E693" s="10" t="n">
+        <v>55.5488</v>
+      </c>
+      <c r="F693" s="10" t="n">
+        <v>56.6856</v>
+      </c>
+      <c r="G693" s="10" t="n">
+        <v>1.1368</v>
+      </c>
+      <c r="H693" s="11" t="n">
+        <v>0.0204648885304453</v>
+      </c>
+      <c r="I693" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J693" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K693" s="54" t="n">
+        <v>1.1368</v>
+      </c>
+      <c r="L693" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M693" t="inlineStr"/>
+      <c r="N693" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B694" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C694" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D694" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E694" s="12" t="n">
+        <v>6768.04</v>
+      </c>
+      <c r="F694" s="12" t="n">
+        <v>6976.09</v>
+      </c>
+      <c r="G694" s="12" t="n">
+        <v>208.05</v>
+      </c>
+      <c r="H694" s="13" t="n">
+        <v>0.03074006654807005</v>
+      </c>
+      <c r="I694" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J694" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K694" s="54" t="n">
+        <v>208.05</v>
+      </c>
+      <c r="L694" s="55" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="M694" t="inlineStr"/>
+      <c r="N694" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B695" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C695" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D695" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E695" s="8" t="n">
+        <v>48.285</v>
+      </c>
+      <c r="F695" s="8" t="n">
+        <v>48.329</v>
+      </c>
+      <c r="G695" s="8" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="H695" s="9" t="n">
+        <v>0.0009112560836698767</v>
+      </c>
+      <c r="I695" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J695" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K695" s="54" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="L695" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M695" t="inlineStr"/>
+      <c r="N695" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B696" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C696" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D696" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E696" s="10" t="n">
+        <v>55.889</v>
+      </c>
+      <c r="F696" s="10" t="n">
+        <v>56.025</v>
+      </c>
+      <c r="G696" s="10" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="H696" s="11" t="n">
+        <v>0.002433394764622734</v>
+      </c>
+      <c r="I696" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J696" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K696" s="54" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="L696" s="55" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="M696" t="inlineStr"/>
+      <c r="N696" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B697" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C697" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D697" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E697" s="12" t="n">
+        <v>6798.78</v>
+      </c>
+      <c r="F697" s="12" t="n">
+        <v>6876.17</v>
+      </c>
+      <c r="G697" s="12" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="H697" s="13" t="n">
+        <v>0.01138292458352822</v>
+      </c>
+      <c r="I697" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J697" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K697" s="54" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="L697" s="55" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="M697" t="inlineStr"/>
+      <c r="N697" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B698" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C698" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D698" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E698" s="8" t="n">
+        <v>48.2355</v>
+      </c>
+      <c r="F698" s="8" t="n">
+        <v>48.382</v>
+      </c>
+      <c r="G698" s="8" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="H698" s="9" t="n">
+        <v>0.003037182158368837</v>
+      </c>
+      <c r="I698" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J698" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K698" s="54" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="L698" s="55" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M698" t="inlineStr"/>
+      <c r="N698" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B699" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C699" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D699" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E699" s="10" t="n">
+        <v>55.9469</v>
+      </c>
+      <c r="F699" s="10" t="n">
+        <v>56.1188</v>
+      </c>
+      <c r="G699" s="10" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="H699" s="11" t="n">
+        <v>0.003072556298919153</v>
+      </c>
+      <c r="I699" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J699" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K699" s="54" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="L699" s="55" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M699" t="inlineStr"/>
+      <c r="N699" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B700" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C700" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D700" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E700" s="12" t="n">
+        <v>6831.7</v>
+      </c>
+      <c r="F700" s="12" t="n">
+        <v>6879.98</v>
+      </c>
+      <c r="G700" s="12" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="H700" s="13" t="n">
+        <v>0.007067055052183204</v>
+      </c>
+      <c r="I700" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J700" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K700" s="54" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="L700" s="55" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="M700" t="inlineStr"/>
+      <c r="N700" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B701" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C701" s="30" t="inlineStr">
+        <is>
+          <t>Hepsipay</t>
+        </is>
+      </c>
+      <c r="D701" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E701" s="12" t="n">
+        <v>6780.95</v>
+      </c>
+      <c r="F701" s="12" t="n">
+        <v>6979.12</v>
+      </c>
+      <c r="G701" s="12" t="n">
+        <v>198.17</v>
+      </c>
+      <c r="H701" s="13" t="n">
+        <v>0.02922451868838437</v>
+      </c>
+      <c r="I701" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J701" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K701" s="54" t="n">
+        <v>198.17</v>
+      </c>
+      <c r="L701" s="55" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="M701" t="inlineStr"/>
+      <c r="N701" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B702" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C702" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D702" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E702" s="8" t="n">
+        <v>47.8217</v>
+      </c>
+      <c r="F702" s="8" t="n">
+        <v>48.7085</v>
+      </c>
+      <c r="G702" s="8" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="H702" s="9" t="n">
+        <v>0.01854388279797665</v>
+      </c>
+      <c r="I702" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J702" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K702" s="54" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="L702" s="55" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="M702" t="inlineStr"/>
+      <c r="N702" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B703" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C703" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D703" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E703" s="10" t="n">
+        <v>55.4774</v>
+      </c>
+      <c r="F703" s="10" t="n">
+        <v>56.5369</v>
+      </c>
+      <c r="G703" s="10" t="n">
+        <v>1.0595</v>
+      </c>
+      <c r="H703" s="11" t="n">
+        <v>0.01909786687912556</v>
+      </c>
+      <c r="I703" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J703" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K703" s="54" t="n">
+        <v>1.0595</v>
+      </c>
+      <c r="L703" s="55" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="M703" t="inlineStr"/>
+      <c r="N703" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B704" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C704" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D704" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E704" s="12" t="n">
+        <v>6773.34</v>
+      </c>
+      <c r="F704" s="12" t="n">
+        <v>7218.38</v>
+      </c>
+      <c r="G704" s="12" t="n">
+        <v>445.04</v>
+      </c>
+      <c r="H704" s="13" t="n">
+        <v>0.06570465973950813</v>
+      </c>
+      <c r="I704" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J704" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K704" s="54" t="n">
+        <v>445.04</v>
+      </c>
+      <c r="L704" s="55" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="M704" t="inlineStr"/>
+      <c r="N704" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B705" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C705" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D705" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E705" s="8" t="n">
+        <v>47.7689</v>
+      </c>
+      <c r="F705" s="8" t="n">
+        <v>48.7723</v>
+      </c>
+      <c r="G705" s="8" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="H705" s="9" t="n">
+        <v>0.02100529842638202</v>
+      </c>
+      <c r="I705" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J705" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K705" s="54" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="L705" s="55" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M705" t="inlineStr"/>
+      <c r="N705" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B706" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C706" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D706" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E706" s="10" t="n">
+        <v>55.4929</v>
+      </c>
+      <c r="F706" s="10" t="n">
+        <v>56.5126</v>
+      </c>
+      <c r="G706" s="10" t="n">
+        <v>1.0197</v>
+      </c>
+      <c r="H706" s="11" t="n">
+        <v>0.01837532369005765</v>
+      </c>
+      <c r="I706" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J706" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K706" s="54" t="n">
+        <v>1.0197</v>
+      </c>
+      <c r="L706" s="55" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B707" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C707" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D707" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E707" s="12" t="n">
+        <v>6742.66</v>
+      </c>
+      <c r="F707" s="12" t="n">
+        <v>6994.99</v>
+      </c>
+      <c r="G707" s="12" t="n">
+        <v>252.33</v>
+      </c>
+      <c r="H707" s="13" t="n">
+        <v>0.03742291617848149</v>
+      </c>
+      <c r="I707" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J707" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K707" s="54" t="n">
+        <v>252.33</v>
+      </c>
+      <c r="L707" s="55" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B708" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C708" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D708" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E708" s="8" t="n">
+        <v>47.6959</v>
+      </c>
+      <c r="F708" s="8" t="n">
+        <v>48.8509</v>
+      </c>
+      <c r="G708" s="8" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="H708" s="9" t="n">
+        <v>0.02421591793005269</v>
+      </c>
+      <c r="I708" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J708" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K708" s="54" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="L708" s="55" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B709" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C709" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D709" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E709" s="10" t="n">
+        <v>55.313</v>
+      </c>
+      <c r="F709" s="10" t="n">
+        <v>56.667</v>
+      </c>
+      <c r="G709" s="10" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="H709" s="11" t="n">
+        <v>0.02447887476723374</v>
+      </c>
+      <c r="I709" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J709" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K709" s="54" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="L709" s="55" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B710" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C710" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D710" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E710" s="12" t="n">
+        <v>6763.4</v>
+      </c>
+      <c r="F710" s="12" t="n">
+        <v>6948.85</v>
+      </c>
+      <c r="G710" s="12" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="H710" s="13" t="n">
+        <v>0.02741964100895999</v>
+      </c>
+      <c r="I710" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J710" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K710" s="54" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="L710" s="55" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B711" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C711" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D711" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E711" s="8" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F711" s="8" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="G711" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H711" s="9" t="n">
+        <v>0.0002070393374741201</v>
+      </c>
+      <c r="I711" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J711" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K711" s="54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L711" s="55" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B712" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C712" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D712" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E712" s="10" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="F712" s="10" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="G712" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H712" s="11" t="n">
+        <v>0.0008939746111210442</v>
+      </c>
+      <c r="I712" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J712" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K712" s="54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L712" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B713" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C713" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D713" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E713" s="12" t="n">
+        <v>6846.95</v>
+      </c>
+      <c r="F713" s="12" t="n">
+        <v>6853.22</v>
+      </c>
+      <c r="G713" s="12" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="H713" s="13" t="n">
+        <v>0.0009157362037111415</v>
+      </c>
+      <c r="I713" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J713" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K713" s="54" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="L713" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B714" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C714" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D714" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E714" s="8" t="n">
+        <v>47.6305</v>
+      </c>
+      <c r="F714" s="8" t="n">
+        <v>48.6166</v>
+      </c>
+      <c r="G714" s="8" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="H714" s="9" t="n">
+        <v>0.02070312089942369</v>
+      </c>
+      <c r="I714" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J714" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K714" s="54" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="L714" s="55" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="M714" t="inlineStr"/>
+      <c r="N714" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B715" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C715" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D715" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E715" s="10" t="n">
+        <v>55.2585</v>
+      </c>
+      <c r="F715" s="10" t="n">
+        <v>56.4031</v>
+      </c>
+      <c r="G715" s="10" t="n">
+        <v>1.1446</v>
+      </c>
+      <c r="H715" s="11" t="n">
+        <v>0.02071355538062018</v>
+      </c>
+      <c r="I715" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J715" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K715" s="54" t="n">
+        <v>1.1446</v>
+      </c>
+      <c r="L715" s="55" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="M715" t="inlineStr"/>
+      <c r="N715" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B716" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C716" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D716" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E716" s="12" t="n">
+        <v>6720.13</v>
+      </c>
+      <c r="F716" s="12" t="n">
+        <v>6898.42</v>
+      </c>
+      <c r="G716" s="12" t="n">
+        <v>178.29</v>
+      </c>
+      <c r="H716" s="13" t="n">
+        <v>0.0265307367565806</v>
+      </c>
+      <c r="I716" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J716" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K716" s="54" t="n">
+        <v>178.29</v>
+      </c>
+      <c r="L716" s="55" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="M716" t="inlineStr"/>
+      <c r="N716" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B717" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C717" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D717" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E717" s="8" t="n">
+        <v>48.2075</v>
+      </c>
+      <c r="F717" s="8" t="n">
+        <v>48.2943</v>
+      </c>
+      <c r="G717" s="8" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="H717" s="9" t="n">
+        <v>0.001800549706995799</v>
+      </c>
+      <c r="I717" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J717" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K717" s="54" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="L717" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M717" t="inlineStr"/>
+      <c r="N717" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B718" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C718" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D718" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E718" s="10" t="n">
+        <v>55.7929</v>
+      </c>
+      <c r="F718" s="10" t="n">
+        <v>55.8934</v>
+      </c>
+      <c r="G718" s="10" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="H718" s="11" t="n">
+        <v>0.001801304467055844</v>
+      </c>
+      <c r="I718" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J718" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K718" s="54" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="L718" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M718" t="inlineStr"/>
+      <c r="N718" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B719" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C719" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D719" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E719" s="8" t="n">
+        <v>48.2443</v>
+      </c>
+      <c r="F719" s="8" t="n">
+        <v>48.2975</v>
+      </c>
+      <c r="G719" s="8" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H719" s="9" t="n">
+        <v>0.001102720943199507</v>
+      </c>
+      <c r="I719" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J719" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K719" s="54" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="L719" s="55" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="M719" t="inlineStr"/>
+      <c r="N719" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B720" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C720" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D720" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E720" s="10" t="n">
+        <v>55.9263</v>
+      </c>
+      <c r="F720" s="10" t="n">
+        <v>56.0243</v>
+      </c>
+      <c r="G720" s="10" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H720" s="11" t="n">
+        <v>0.00175230616007138</v>
+      </c>
+      <c r="I720" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J720" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K720" s="54" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="L720" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M720" t="inlineStr"/>
+      <c r="N720" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B721" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C721" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D721" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E721" s="12" t="n">
+        <v>6853.96</v>
+      </c>
+      <c r="F721" s="12" t="n">
+        <v>6888.36</v>
+      </c>
+      <c r="G721" s="12" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="H721" s="13" t="n">
+        <v>0.005018996317457352</v>
+      </c>
+      <c r="I721" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J721" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K721" s="54" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="L721" s="55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M721" t="inlineStr"/>
+      <c r="N721" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B722" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C722" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D722" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E722" s="8" t="n">
+        <v>48.304</v>
+      </c>
+      <c r="F722" s="8" t="n">
+        <v>48.386</v>
+      </c>
+      <c r="G722" s="8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H722" s="9" t="n">
+        <v>0.00169758198078834</v>
+      </c>
+      <c r="I722" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J722" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K722" s="54" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="L722" s="55" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B723" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C723" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D723" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E723" s="10" t="n">
+        <v>55.834</v>
+      </c>
+      <c r="F723" s="10" t="n">
+        <v>56.096</v>
+      </c>
+      <c r="G723" s="10" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H723" s="11" t="n">
+        <v>0.004692481283805566</v>
+      </c>
+      <c r="I723" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J723" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K723" s="54" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="L723" s="55" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B724" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C724" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D724" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E724" s="12" t="n">
+        <v>6817</v>
+      </c>
+      <c r="F724" s="12" t="n">
+        <v>6868</v>
+      </c>
+      <c r="G724" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="H724" s="13" t="n">
+        <v>0.007481296758104739</v>
+      </c>
+      <c r="I724" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J724" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K724" s="54" t="n">
+        <v>51</v>
+      </c>
+      <c r="L724" s="55" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="M724" t="inlineStr"/>
+      <c r="N724" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B725" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C725" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D725" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E725" s="8" t="n">
+        <v>47.7755</v>
+      </c>
+      <c r="F725" s="8" t="n">
+        <v>48.7755</v>
+      </c>
+      <c r="G725" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H725" s="9" t="n">
+        <v>0.02093123044238156</v>
+      </c>
+      <c r="I725" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J725" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K725" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L725" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M725" t="inlineStr"/>
+      <c r="N725" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B726" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C726" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D726" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E726" s="10" t="n">
+        <v>55.444</v>
+      </c>
+      <c r="F726" s="10" t="n">
+        <v>56.534</v>
+      </c>
+      <c r="G726" s="10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H726" s="11" t="n">
+        <v>0.01965947622826636</v>
+      </c>
+      <c r="I726" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J726" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K726" s="54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L726" s="55" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="M726" t="inlineStr"/>
+      <c r="N726" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B727" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C727" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D727" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E727" s="12" t="n">
+        <v>6818.14</v>
+      </c>
+      <c r="F727" s="12" t="n">
+        <v>6918.14</v>
+      </c>
+      <c r="G727" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H727" s="13" t="n">
+        <v>0.01466675662277395</v>
+      </c>
+      <c r="I727" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J727" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K727" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="L727" s="55" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="M727" t="inlineStr"/>
+      <c r="N727" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B728" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C728" s="40" t="inlineStr">
+        <is>
+          <t>Papara</t>
+        </is>
+      </c>
+      <c r="D728" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E728" s="12" t="n">
+        <v>6780.95</v>
+      </c>
+      <c r="F728" s="12" t="n">
+        <v>6965.19</v>
+      </c>
+      <c r="G728" s="12" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="H728" s="13" t="n">
+        <v>0.02717023425921147</v>
+      </c>
+      <c r="I728" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J728" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K728" s="54" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="L728" s="55" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B729" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C729" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D729" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E729" s="8" t="n">
+        <v>47.7045</v>
+      </c>
+      <c r="F729" s="8" t="n">
+        <v>48.9245</v>
+      </c>
+      <c r="G729" s="8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H729" s="9" t="n">
+        <v>0.02557410726451383</v>
+      </c>
+      <c r="I729" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J729" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K729" s="54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L729" s="55" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B730" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C730" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D730" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E730" s="10" t="n">
+        <v>55.2258</v>
+      </c>
+      <c r="F730" s="10" t="n">
+        <v>56.8814</v>
+      </c>
+      <c r="G730" s="10" t="n">
+        <v>1.6556</v>
+      </c>
+      <c r="H730" s="11" t="n">
+        <v>0.02997874181994647</v>
+      </c>
+      <c r="I730" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J730" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K730" s="54" t="n">
+        <v>1.6556</v>
+      </c>
+      <c r="L730" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B731" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C731" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D731" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E731" s="12" t="n">
+        <v>6741.82</v>
+      </c>
+      <c r="F731" s="12" t="n">
+        <v>6944.4</v>
+      </c>
+      <c r="G731" s="12" t="n">
+        <v>202.58</v>
+      </c>
+      <c r="H731" s="13" t="n">
+        <v>0.03004826589852592</v>
+      </c>
+      <c r="I731" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J731" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K731" s="54" t="n">
+        <v>202.58</v>
+      </c>
+      <c r="L731" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B732" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C732" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D732" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E732" s="8" t="n">
+        <v>48.1907</v>
+      </c>
+      <c r="F732" s="8" t="n">
+        <v>48.4081</v>
+      </c>
+      <c r="G732" s="8" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="H732" s="9" t="n">
+        <v>0.004511243870705344</v>
+      </c>
+      <c r="I732" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J732" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K732" s="54" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="L732" s="55" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B733" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C733" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D733" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E733" s="10" t="n">
+        <v>55.8248</v>
+      </c>
+      <c r="F733" s="10" t="n">
+        <v>56.1611</v>
+      </c>
+      <c r="G733" s="10" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="H733" s="11" t="n">
+        <v>0.006024204296298419</v>
+      </c>
+      <c r="I733" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J733" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K733" s="54" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="L733" s="55" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B734" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C734" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D734" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E734" s="12" t="n">
+        <v>6755.73</v>
+      </c>
+      <c r="F734" s="12" t="n">
+        <v>6892.56</v>
+      </c>
+      <c r="G734" s="12" t="n">
+        <v>136.83</v>
+      </c>
+      <c r="H734" s="13" t="n">
+        <v>0.02025391778534666</v>
+      </c>
+      <c r="I734" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J734" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K734" s="54" t="n">
+        <v>136.82</v>
+      </c>
+      <c r="L734" s="55" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B735" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C735" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D735" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E735" s="8" t="n">
+        <v>47.8693</v>
+      </c>
+      <c r="F735" s="8" t="n">
+        <v>48.6711</v>
+      </c>
+      <c r="G735" s="8" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="H735" s="9" t="n">
+        <v>0.01674977490792637</v>
+      </c>
+      <c r="I735" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J735" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K735" s="54" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="L735" s="55" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B736" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C736" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D736" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E736" s="10" t="n">
+        <v>55.5596</v>
+      </c>
+      <c r="F736" s="10" t="n">
+        <v>56.4105</v>
+      </c>
+      <c r="G736" s="10" t="n">
+        <v>0.8509</v>
+      </c>
+      <c r="H736" s="11" t="n">
+        <v>0.0153150850618075</v>
+      </c>
+      <c r="I736" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J736" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K736" s="54" t="n">
+        <v>0.8509</v>
+      </c>
+      <c r="L736" s="55" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B737" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C737" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D737" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E737" s="12" t="n">
+        <v>6767.92</v>
+      </c>
+      <c r="F737" s="12" t="n">
+        <v>6964.67</v>
+      </c>
+      <c r="G737" s="12" t="n">
+        <v>196.75</v>
+      </c>
+      <c r="H737" s="13" t="n">
+        <v>0.02907097010602962</v>
+      </c>
+      <c r="I737" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J737" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K737" s="54" t="n">
+        <v>196.75</v>
+      </c>
+      <c r="L737" s="55" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B738" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C738" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D738" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E738" s="8" t="n">
+        <v>48.1712</v>
+      </c>
+      <c r="F738" s="8" t="n">
+        <v>48.3744</v>
+      </c>
+      <c r="G738" s="8" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="H738" s="9" t="n">
+        <v>0.004218288105756137</v>
+      </c>
+      <c r="I738" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J738" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K738" s="54" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="L738" s="55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B739" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C739" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D739" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E739" s="10" t="n">
+        <v>55.8686</v>
+      </c>
+      <c r="F739" s="10" t="n">
+        <v>56.0937</v>
+      </c>
+      <c r="G739" s="10" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="H739" s="11" t="n">
+        <v>0.004029096845097246</v>
+      </c>
+      <c r="I739" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J739" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K739" s="54" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="L739" s="55" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B740" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C740" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D740" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E740" s="12" t="n">
+        <v>6806.13</v>
+      </c>
+      <c r="F740" s="12" t="n">
+        <v>6860.8</v>
+      </c>
+      <c r="G740" s="12" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="H740" s="13" t="n">
+        <v>0.008032464851538246</v>
+      </c>
+      <c r="I740" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J740" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K740" s="54" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L740" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B741" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C741" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D741" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E741" s="8" t="n">
+        <v>47.9119</v>
+      </c>
+      <c r="F741" s="8" t="n">
+        <v>48.8729</v>
+      </c>
+      <c r="G741" s="8" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="H741" s="9" t="n">
+        <v>0.02005764747380087</v>
+      </c>
+      <c r="I741" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J741" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K741" s="54" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="L741" s="55" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B742" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C742" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D742" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E742" s="10" t="n">
+        <v>55.6027</v>
+      </c>
+      <c r="F742" s="10" t="n">
+        <v>56.7214</v>
+      </c>
+      <c r="G742" s="10" t="n">
+        <v>1.1187</v>
+      </c>
+      <c r="H742" s="11" t="n">
+        <v>0.02011952656975291</v>
+      </c>
+      <c r="I742" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J742" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K742" s="54" t="n">
+        <v>1.1187</v>
+      </c>
+      <c r="L742" s="55" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B743" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C743" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D743" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E743" s="12" t="n">
+        <v>6774.91</v>
+      </c>
+      <c r="F743" s="12" t="n">
+        <v>6919.51</v>
+      </c>
+      <c r="G743" s="12" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="H743" s="13" t="n">
+        <v>0.02134345696105188</v>
+      </c>
+      <c r="I743" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J743" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K743" s="54" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="L743" s="55" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B744" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C744" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D744" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E744" s="8" t="n">
+        <v>48.291</v>
+      </c>
+      <c r="F744" s="8" t="n">
+        <v>48.329</v>
+      </c>
+      <c r="G744" s="8" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H744" s="9" t="n">
+        <v>0.0007868961090058189</v>
+      </c>
+      <c r="I744" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J744" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K744" s="54" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="L744" s="55" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B745" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C745" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D745" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E745" s="10" t="n">
+        <v>55.902</v>
+      </c>
+      <c r="F745" s="10" t="n">
+        <v>56.013</v>
+      </c>
+      <c r="G745" s="10" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="H745" s="11" t="n">
+        <v>0.001985617688097027</v>
+      </c>
+      <c r="I745" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J745" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K745" s="54" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L745" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B746" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C746" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D746" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E746" s="8" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="F746" s="8" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="G746" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H746" s="9" t="n">
+        <v>0.01886001676445935</v>
+      </c>
+      <c r="I746" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J746" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K746" s="54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L746" s="55" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B747" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C747" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D747" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E747" s="10" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="F747" s="10" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="G747" s="10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H747" s="11" t="n">
+        <v>0.01842485549132948</v>
+      </c>
+      <c r="I747" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J747" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K747" s="54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L747" s="55" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B748" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C748" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D748" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E748" s="12" t="n">
+        <v>6748.18</v>
+      </c>
+      <c r="F748" s="12" t="n">
+        <v>6937.84</v>
+      </c>
+      <c r="G748" s="12" t="n">
+        <v>189.66</v>
+      </c>
+      <c r="H748" s="13" t="n">
+        <v>0.02810535581445664</v>
+      </c>
+      <c r="I748" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J748" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K748" s="54" t="n">
+        <v>189.66</v>
+      </c>
+      <c r="L748" s="55" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="M748" t="inlineStr"/>
+      <c r="N748" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B749" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C749" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D749" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E749" s="8" t="n">
+        <v>47.9078</v>
+      </c>
+      <c r="F749" s="8" t="n">
+        <v>48.877</v>
+      </c>
+      <c r="G749" s="8" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="H749" s="9" t="n">
+        <v>0.02023052613561883</v>
+      </c>
+      <c r="I749" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J749" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K749" s="54" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="L749" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B750" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C750" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D750" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E750" s="10" t="n">
+        <v>55.5555</v>
+      </c>
+      <c r="F750" s="10" t="n">
+        <v>56.6794</v>
+      </c>
+      <c r="G750" s="10" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="H750" s="11" t="n">
+        <v>0.02023022023022023</v>
+      </c>
+      <c r="I750" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J750" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K750" s="54" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="L750" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B751" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C751" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D751" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E751" s="12" t="n">
+        <v>6806.95</v>
+      </c>
+      <c r="F751" s="12" t="n">
+        <v>6944.39</v>
+      </c>
+      <c r="G751" s="12" t="n">
+        <v>137.44</v>
+      </c>
+      <c r="H751" s="13" t="n">
+        <v>0.02019112818516369</v>
+      </c>
+      <c r="I751" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J751" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K751" s="54" t="n">
+        <v>137.44</v>
+      </c>
+      <c r="L751" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B752" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C752" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D752" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E752" s="8" t="n">
+        <v>47.9557</v>
+      </c>
+      <c r="F752" s="8" t="n">
+        <v>48.6082</v>
+      </c>
+      <c r="G752" s="8" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="H752" s="9" t="n">
+        <v>0.01360630748795242</v>
+      </c>
+      <c r="I752" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J752" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K752" s="54" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="L752" s="55" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B753" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C753" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D753" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E753" s="10" t="n">
+        <v>55.562</v>
+      </c>
+      <c r="F753" s="10" t="n">
+        <v>56.3743</v>
+      </c>
+      <c r="G753" s="10" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="H753" s="11" t="n">
+        <v>0.01461970411432274</v>
+      </c>
+      <c r="I753" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J753" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K753" s="54" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="L753" s="55" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B754" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C754" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D754" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E754" s="12" t="n">
+        <v>6776.4</v>
+      </c>
+      <c r="F754" s="12" t="n">
+        <v>6913.23</v>
+      </c>
+      <c r="G754" s="12" t="n">
+        <v>136.83</v>
+      </c>
+      <c r="H754" s="13" t="n">
+        <v>0.02019213741809811</v>
+      </c>
+      <c r="I754" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J754" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K754" s="54" t="n">
+        <v>136.83</v>
+      </c>
+      <c r="L754" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M754" t="inlineStr"/>
+      <c r="N754" s="6" t="n">
+        <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B755" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C755" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D755" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E755" s="8" t="n">
+        <v>47.7853</v>
+      </c>
+      <c r="F755" s="8" t="n">
+        <v>48.7835</v>
+      </c>
+      <c r="G755" s="8" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H755" s="9" t="n">
+        <v>0.02088926929411346</v>
+      </c>
+      <c r="I755" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J755" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K755" s="54" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="L755" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" s="6" t="n">
+        <v>0.5792361111111111</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B756" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C756" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D756" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E756" s="10" t="n">
+        <v>55.3938</v>
+      </c>
+      <c r="F756" s="10" t="n">
+        <v>56.6063</v>
+      </c>
+      <c r="G756" s="10" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="H756" s="11" t="n">
+        <v>0.02188873122984883</v>
+      </c>
+      <c r="I756" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J756" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K756" s="54" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="L756" s="55" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="M756" t="inlineStr"/>
+      <c r="N756" s="6" t="n">
+        <v>0.5793865740740741</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B757" s="6" t="n">
+        <v>0.5790393518518518</v>
+      </c>
+      <c r="C757" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D757" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E757" s="12" t="n">
+        <v>6795.78</v>
+      </c>
+      <c r="F757" s="12" t="n">
+        <v>7011.57</v>
+      </c>
+      <c r="G757" s="12" t="n">
+        <v>215.79</v>
+      </c>
+      <c r="H757" s="13" t="n">
+        <v>0.0317535293961841</v>
+      </c>
+      <c r="I757" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J757" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K757" s="54" t="n">
+        <v>215.79</v>
+      </c>
+      <c r="L757" s="55" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="M757" t="inlineStr"/>
+      <c r="N757" s="6" t="n">
+        <v>0.5795370370370371</v>
       </c>
     </row>
   </sheetData>
@@ -42042,10 +47622,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J647" r:id="rId646"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J648" r:id="rId647"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J698" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J705" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J706" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J707" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J708" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J709" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J710" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J711" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J712" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J713" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J714" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J715" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J716" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J717" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J718" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J719" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J720" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J721" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J722" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J723" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J724" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J725" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J726" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J727" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J728" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J729" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J730" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J731" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J732" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J733" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J734" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J735" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J736" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J737" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J738" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J739" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J740" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J741" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J742" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J743" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J744" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J745" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J746" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J747" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J748" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J749" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J750" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J751" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J752" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J753" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J754" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J755" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J756" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J757" r:id="rId756"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId649"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId757"/>
   </tableParts>
 </worksheet>
 </file>
@@ -42119,7 +47807,7 @@
       </c>
       <c r="B4" s="62" t="n"/>
       <c r="C4" s="63" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D4" s="62" t="n"/>
       <c r="F4" s="1" t="inlineStr">
@@ -42186,7 +47874,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.6215046296296296</v>
+        <v>0.5790393518518518</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -42217,18 +47905,18 @@
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.02022948183877804</v>
+        <v>0.01886001676445935</v>
       </c>
       <c r="O5" s="71" t="inlineStr">
         <is>
-          <t>Ziraat Bankası</t>
+          <t>Yapıkredi</t>
         </is>
       </c>
       <c r="P5" s="72" t="n">
-        <v>47.8905</v>
+        <v>47.72</v>
       </c>
       <c r="Q5" s="72" t="n">
-        <v>48.8593</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="6">
@@ -42270,18 +47958,18 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.02023127123399388</v>
+        <v>0.01842485549132948</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
-          <t>Ziraat Bankası</t>
+          <t>Yapıkredi</t>
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.4241</v>
+        <v>55.36</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.5454</v>
+        <v>56.38</v>
       </c>
     </row>
     <row r="7">
@@ -42300,7 +47988,7 @@
           <t>Ağustos 2026</t>
         </is>
       </c>
-      <c r="G7" s="76" t="inlineStr">
+      <c r="G7" s="71" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
@@ -42314,7 +48002,7 @@
       <c r="J7" s="68" t="n">
         <v>0.0540849048600331</v>
       </c>
-      <c r="L7" s="77" t="inlineStr">
+      <c r="L7" s="76" t="inlineStr">
         <is>
           <t>GRAM ALTIN</t>
         </is>
@@ -42323,18 +48011,18 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019113087774059</v>
-      </c>
-      <c r="O7" s="71" t="inlineStr">
+        <v>0.02019112818516369</v>
+      </c>
+      <c r="O7" s="77" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6650.94</v>
+        <v>6806.95</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6785.23</v>
+        <v>6944.39</v>
       </c>
     </row>
     <row r="8">
@@ -42353,7 +48041,7 @@
           <t>Ağustos 2026</t>
         </is>
       </c>
-      <c r="G8" s="71" t="inlineStr">
+      <c r="G8" s="77" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
@@ -42411,13 +48099,13 @@
         </is>
       </c>
       <c r="H10" s="66" t="n">
-        <v>0.02845400039156511</v>
+        <v>0.02844860558628776</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>0.02846019565754637</v>
+        <v>0.02845282527677321</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>0.03694321012774233</v>
+        <v>0.03694211641961482</v>
       </c>
     </row>
     <row r="11">
@@ -42432,13 +48120,13 @@
         </is>
       </c>
       <c r="H11" s="66" t="n">
-        <v>0.0284261405518742</v>
+        <v>0.02842065661994164</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>0.02847118412784268</v>
+        <v>0.02845076126263018</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>0.03614313031148214</v>
+        <v>0.03613507814746245</v>
       </c>
     </row>
     <row r="12">
@@ -42447,19 +48135,19 @@
           <t>Eylül 2026</t>
         </is>
       </c>
-      <c r="G12" s="76" t="inlineStr">
+      <c r="G12" s="71" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
       </c>
       <c r="H12" s="66" t="n">
-        <v>0.02109574084424381</v>
+        <v>0.02035049948431565</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>0.02046731269055863</v>
+        <v>0.01978649362414892</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>0.03051048704906535</v>
+        <v>0.02970877663752912</v>
       </c>
     </row>
     <row r="13">
@@ -42468,19 +48156,19 @@
           <t>Eylül 2026</t>
         </is>
       </c>
-      <c r="G13" s="71" t="inlineStr">
+      <c r="G13" s="77" t="inlineStr">
         <is>
           <t>Ziraat Bankası</t>
         </is>
       </c>
       <c r="H13" s="66" t="n">
-        <v>0.02023029953768716</v>
+        <v>0.02023037507033105</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>0.02023090916840954</v>
+        <v>0.02023067952234644</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>0.02019194235075064</v>
+        <v>0.02019167096222166</v>
       </c>
     </row>
     <row r="14">
@@ -42495,13 +48183,13 @@
         </is>
       </c>
       <c r="H14" s="66" t="n">
-        <v>0.02422333905778681</v>
+        <v>0.0242208653485421</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>0.02435060197965432</v>
+        <v>0.02439335957551413</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>0.02742927462036698</v>
+        <v>0.02742606341656465</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1"/>
@@ -42707,7 +48395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43031,49 +48719,49 @@
         </is>
       </c>
       <c r="U3" s="55" t="n">
-        <v>0.02845400039156511</v>
+        <v>0.02844860558628776</v>
       </c>
       <c r="V3" s="55" t="n">
-        <v>0.0284261405518742</v>
+        <v>0.02842065661994164</v>
       </c>
       <c r="W3" s="55" t="n">
-        <v>0.02109574084424381</v>
+        <v>0.02035049948431565</v>
       </c>
       <c r="X3" s="55" t="n">
-        <v>0.02023029953768716</v>
+        <v>0.02023037507033105</v>
       </c>
       <c r="Y3" s="55" t="n">
-        <v>0.02422333905778681</v>
+        <v>0.0242208653485421</v>
       </c>
       <c r="Z3" s="55" t="n">
-        <v>0.02846019565754637</v>
+        <v>0.02845282527677321</v>
       </c>
       <c r="AA3" s="55" t="n">
-        <v>0.02847118412784268</v>
+        <v>0.02845076126263018</v>
       </c>
       <c r="AB3" s="55" t="n">
-        <v>0.02046731269055863</v>
+        <v>0.01978649362414892</v>
       </c>
       <c r="AC3" s="55" t="n">
-        <v>0.02023090916840954</v>
+        <v>0.02023067952234644</v>
       </c>
       <c r="AD3" s="55" t="n">
-        <v>0.02435060197965432</v>
+        <v>0.02439335957551413</v>
       </c>
       <c r="AE3" s="55" t="n">
-        <v>0.03694321012774233</v>
+        <v>0.03694211641961482</v>
       </c>
       <c r="AF3" s="55" t="n">
-        <v>0.03614313031148214</v>
+        <v>0.03613507814746245</v>
       </c>
       <c r="AG3" s="55" t="n">
-        <v>0.03051048704906535</v>
+        <v>0.02970877663752912</v>
       </c>
       <c r="AH3" s="55" t="n">
-        <v>0.02019194235075064</v>
+        <v>0.02019167096222166</v>
       </c>
       <c r="AI3" s="55" t="n">
-        <v>0.02742927462036698</v>
+        <v>0.02742606341656465</v>
       </c>
     </row>
     <row r="4">
@@ -43282,6 +48970,58 @@
       </c>
       <c r="P7" s="55" t="n">
         <v>0.02742758272742561</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>03.09</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>0.02843781597573306</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>0.02840968875607652</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>0.01886001676445935</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>0.02023052613561883</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <v>0.02421591793005269</v>
+      </c>
+      <c r="G8" s="55" t="n">
+        <v>0.02843808451522691</v>
+      </c>
+      <c r="H8" s="55" t="n">
+        <v>0.02840991553220516</v>
+      </c>
+      <c r="I8" s="55" t="n">
+        <v>0.01842485549132948</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>0.02023022023022023</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>0.02447887476723374</v>
+      </c>
+      <c r="L8" s="55" t="n">
+        <v>0.03693992900335979</v>
+      </c>
+      <c r="M8" s="55" t="n">
+        <v>0.03611897381942306</v>
+      </c>
+      <c r="N8" s="55" t="n">
+        <v>0.02810535581445664</v>
+      </c>
+      <c r="O8" s="55" t="n">
+        <v>0.02019112818516369</v>
+      </c>
+      <c r="P8" s="55" t="n">
+        <v>0.02741964100895999</v>
       </c>
     </row>
   </sheetData>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -578,9 +578,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -601,16 +601,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$8</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -631,6 +634,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02843781597573306</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02844021235358557</v>
                 </pt>
               </numCache>
             </numRef>
@@ -676,9 +682,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -699,16 +705,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$8</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -729,6 +738,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02840968875607652</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.0284066997727464</v>
                 </pt>
               </numCache>
             </numRef>
@@ -774,9 +786,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -797,16 +809,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$8</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -827,6 +842,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.01886001676445935</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.01907356948228883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -872,9 +890,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -895,16 +913,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$8</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -925,6 +946,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02023052613561883</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02023099065475184</v>
                 </pt>
               </numCache>
             </numRef>
@@ -970,9 +994,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -993,16 +1017,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$8</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -1023,6 +1050,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02421591793005269</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02429357798165137</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1143,9 +1173,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1166,16 +1196,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$8</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -1196,6 +1229,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02840968875607652</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.0284066997727464</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1244,8 +1280,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06361249944535419"/>
-          <min val="0.02254255364119691"/>
+          <max val="0.06361309724202022"/>
+          <min val="0.02253896686120076"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1336,9 +1372,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1359,16 +1395,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$8</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -1389,6 +1428,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02840991553220516</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02849479113841517</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1529,9 +1571,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1552,16 +1594,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$8</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -1582,6 +1627,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.03611897381942306</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.03610505062457936</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1630,8 +1678,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.09493341199430352"/>
-          <min val="0.02631656745694298"/>
+          <max val="0.09493619663327227"/>
+          <min val="0.02629985962313054"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1722,9 +1770,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1745,16 +1793,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$8</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -1775,6 +1826,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.01886001676445935</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.01907356948228883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1915,9 +1969,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1938,16 +1992,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$8</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -1968,6 +2025,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.01842485549132948</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.01857864357864358</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2108,9 +2168,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2131,16 +2191,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$8</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -2161,6 +2224,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02810535581445664</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02799519201839831</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2209,8 +2275,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.0884901149726027"/>
-          <min val="0.01804122928809896"/>
+          <max val="0.08851214773181437"/>
+          <min val="0.01790903273282896"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -2301,9 +2367,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2324,16 +2390,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$8</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -2354,6 +2423,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02023052613561883</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02023099065475184</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2494,9 +2566,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2517,16 +2589,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$8</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -2547,6 +2622,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02023022023022023</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.0202311723225774</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2687,9 +2765,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2710,16 +2788,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$8</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -2740,6 +2821,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02019112818516369</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02019121345887606</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2880,9 +2964,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2903,16 +2987,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$8</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -2933,6 +3020,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02421591793005269</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02429357798165137</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3073,9 +3163,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3096,16 +3186,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$8</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -3126,6 +3219,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02843808451522691</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02842845746609617</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3171,9 +3267,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3194,16 +3290,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$8</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -3224,6 +3323,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02840991553220516</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02849479113841517</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3269,9 +3371,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3292,16 +3394,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$8</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -3322,6 +3427,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.01842485549132948</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.01857864357864358</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3367,9 +3475,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3390,16 +3498,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$8</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -3420,6 +3531,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02023022023022023</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.0202311723225774</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3465,9 +3579,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3488,16 +3602,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$8</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3518,6 +3635,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02447887476723374</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02447024757283306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3638,9 +3758,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3661,16 +3781,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$8</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3691,6 +3814,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02447887476723374</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02447024757283306</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3831,9 +3957,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3854,16 +3980,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$8</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -3884,6 +4013,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02741964100895999</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02742111723366172</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4024,9 +4156,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4047,16 +4179,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$8</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -4077,6 +4212,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.03693992900335979</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.03694098205438084</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4122,9 +4260,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4145,16 +4283,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$8</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -4175,6 +4316,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.03611897381942306</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.03610505062457936</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4220,9 +4364,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4243,16 +4387,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$8</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -4273,6 +4420,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02810535581445664</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02799519201839831</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4318,9 +4468,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4341,16 +4491,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$8</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -4371,6 +4524,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02019112818516369</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02019121345887606</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4416,9 +4572,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4439,16 +4595,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$8</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4469,6 +4628,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02741964100895999</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02742111723366172</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4611,7 +4773,7 @@
                   <v>0.03553378696044311</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02844860558628776</v>
+                  <v>0.02844650727811221</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4679,7 +4841,7 @@
                   <v>0.04311562150687483</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02842065661994164</v>
+                  <v>0.02841716740814283</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4747,7 +4909,7 @@
                   <v>0.03847709584999994</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02035049948431565</v>
+                  <v>0.02003126698380895</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4815,7 +4977,7 @@
                   <v>0.04104187506584386</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023037507033105</v>
+                  <v>0.02023052896643625</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4883,7 +5045,7 @@
                   <v>0.04760750668842017</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.0242208653485421</v>
+                  <v>0.02423904350681942</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4924,8 +5086,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05171407643113354"/>
-          <min val="0.01612380532761768"/>
+          <max val="0.05174394264411185"/>
+          <min val="0.01589483102811727"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5026,7 +5188,7 @@
                   <v>0.03553642841103422</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02845282527677321</v>
+                  <v>0.02844673332410395</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5094,7 +5256,7 @@
                   <v>0.0432699268677014</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02845076126263018</v>
+                  <v>0.02846176873157642</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5162,7 +5324,7 @@
                   <v>0.03535742466332828</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.01978649362414892</v>
+                  <v>0.01948453111277258</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5230,7 +5392,7 @@
                   <v>0.0514487601107881</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023067952234644</v>
+                  <v>0.02023080272240418</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5298,7 +5460,7 @@
                   <v>0.04783493387226885</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02439335957551413</v>
+                  <v>0.02441258157484386</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5339,8 +5501,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05619810008378397"/>
-          <min val="0.01503715365115304"/>
+          <max val="0.05624339446049043"/>
+          <min val="0.01468989676307026"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5441,7 +5603,7 @@
                   <v>0.05383117747984287</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03694211641961482</v>
+                  <v>0.03694183282830633</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5509,7 +5671,7 @@
                   <v>0.06066925394146307</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03613507814746245</v>
+                  <v>0.03612757126674167</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5577,7 +5739,7 @@
                   <v>0.0540849048600331</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02970877663752912</v>
+                  <v>0.02928038048274641</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5645,7 +5807,7 @@
                   <v>0.08301204597474589</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02019167096222166</v>
+                  <v>0.02019155658638526</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5713,7 +5875,7 @@
                   <v>0.1017248276143379</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02742606341656465</v>
+                  <v>0.02742482687083892</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5754,8 +5916,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1139548011121554"/>
-          <min val="0.007961697464404215"/>
+          <max val="0.1139548182685308"/>
+          <min val="0.007961565932192357"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5834,9 +5996,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -5857,16 +6019,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$8</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -5887,6 +6052,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02843781597573306</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02844021235358557</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6027,9 +6195,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6050,16 +6218,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$8</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -6080,6 +6251,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.02843808451522691</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.02842845746609617</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6128,8 +6302,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.04536777025595159"/>
-          <min val="0.02561647022510612"/>
+          <max val="0.04536969566577773"/>
+          <min val="0.02560491776614924"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -6220,9 +6394,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$8</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
               <strCache>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6243,16 +6417,19 @@
                 </pt>
                 <pt idx="6">
                   <v>03.09</v>
+                </pt>
+                <pt idx="7">
+                  <v>04.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$8</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$9</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="7"/>
+                <ptCount val="8"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -6273,6 +6450,9 @@
                 </pt>
                 <pt idx="6">
                   <v>0.03693992900335979</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.03694098205438084</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6845,8 +7025,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N757" headerRowCount="1">
-  <autoFilter ref="A1:N757"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N865" headerRowCount="1">
+  <autoFilter ref="A1:N865"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tarih"/>
     <tableColumn id="2" name="Saat"/>
@@ -7255,10 +7435,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7266,48 +7446,48 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>47.519</v>
+        <v>47.524</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>48.869</v>
+        <v>48.874</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.02840968875607652</v>
+        <v>0.0284066997727464</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>55.1216</v>
+        <v>55.2136</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.6876</v>
+        <v>56.7869</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.566</v>
+        <v>1.5733</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02840991553220516</v>
+        <v>0.02849479113841517</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6691.22</v>
+        <v>6760.55</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>6932.9</v>
+        <v>7004.64</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>241.68</v>
+        <v>244.09</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03611897381942306</v>
+        <v>0.03610505062457936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7315,48 +7495,48 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>47.914</v>
+        <v>48.042</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>48.695</v>
+        <v>48.823</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>0.781</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.01630003756730809</v>
+        <v>0.01625660880063278</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.58</v>
+        <v>55.815</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.496</v>
+        <v>56.728</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.916</v>
+        <v>0.913</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.0164807484706729</v>
+        <v>0.01635760996147989</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6772.16</v>
+        <v>6853.46</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6911.34</v>
+        <v>6993.59</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>139.18</v>
+        <v>140.13</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02055178849879507</v>
+        <v>0.02044660653159134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7364,48 +7544,48 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.101</v>
+        <v>48.23</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.389</v>
+        <v>48.515</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.288</v>
+        <v>0.285</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.00598740150932413</v>
+        <v>0.005909185154468173</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.634</v>
+        <v>55.861</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.142</v>
+        <v>56.377</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.508</v>
+        <v>0.516</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.00913110687708955</v>
+        <v>0.00923721379853565</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6831.41</v>
+        <v>6920.63</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6899.34</v>
+        <v>6990.46</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>67.93000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.009943774418458269</v>
+        <v>0.01009012185306829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7413,48 +7593,48 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.26</v>
+        <v>48.27</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.45</v>
+        <v>48.48</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.003937007874015748</v>
+        <v>0.00435052827843381</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.865</v>
+        <v>55.94</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>56.209</v>
+        <v>56.324</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.344</v>
+        <v>0.384</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006157701602076435</v>
+        <v>0.006864497676081516</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6773.24</v>
+        <v>6842.63</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>6935</v>
+        <v>7015</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>161.76</v>
+        <v>172.37</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02388221884947233</v>
+        <v>0.02519060653579107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7462,48 +7642,48 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.4706</v>
+        <v>47.465</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.747</v>
+        <v>48.7411</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2764</v>
+        <v>1.2761</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.02688822134120909</v>
+        <v>0.0268850732118403</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.1632</v>
+        <v>55.2416</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.5354</v>
+        <v>56.6119</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3722</v>
+        <v>1.3703</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02487527917162166</v>
+        <v>0.02480558130104848</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6755.31</v>
+        <v>6819.63</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6913.93</v>
+        <v>6975.89</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>158.62</v>
+        <v>156.26</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02348078770626367</v>
+        <v>0.02291326655551694</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7511,48 +7691,48 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>47.32</v>
+        <v>47.317</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.243</v>
+        <v>49.24</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>1.923</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04063820794590026</v>
+        <v>0.0406407844960585</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.896</v>
+        <v>54.968</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>57.131</v>
+        <v>57.211</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.235</v>
+        <v>2.243</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04071334887787817</v>
+        <v>0.04080555959831175</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6756.65</v>
+        <v>6821.76</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>6950.96</v>
+        <v>7016.15</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.31</v>
+        <v>194.39</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02875833438168323</v>
+        <v>0.02849557885355099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7560,48 +7740,48 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5724</v>
+        <v>47.5756</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9725</v>
+        <v>48.9757</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1.4001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02943093053955655</v>
+        <v>0.02942895097486947</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.1922</v>
+        <v>55.2594</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.8215</v>
+        <v>56.8905</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6293</v>
+        <v>1.6311</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02952047571939513</v>
+        <v>0.02951715002334444</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6771.17</v>
+        <v>6834.26</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6971.44</v>
+        <v>7036.42</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>200.27</v>
+        <v>202.16</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02957686780866527</v>
+        <v>0.02958037885594051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7609,48 +7789,48 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2418</v>
+        <v>48.2258</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.2988</v>
+        <v>48.301</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.057</v>
+        <v>0.0752</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001181547952190839</v>
+        <v>0.001559331312285125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>55.9447</v>
+        <v>56.0082</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>56.0327</v>
+        <v>56.1124</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1042</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001572981891045979</v>
+        <v>0.001860441863869933</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6822.67</v>
+        <v>6885.98</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6851.87</v>
+        <v>6917.66</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>29.2</v>
+        <v>31.68</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.00427984938447851</v>
+        <v>0.004600652339971943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7658,48 +7838,48 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2554</v>
+        <v>48.2508</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2942</v>
+        <v>48.2891</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.0383</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0008040550902075208</v>
+        <v>0.0007937692224792128</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.9297</v>
+        <v>56.0087</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>56.0396</v>
+        <v>56.1183</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1099</v>
+        <v>0.1096</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.001964966735026292</v>
+        <v>0.001956838848250361</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6819.54</v>
+        <v>6883.87</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6852.53</v>
+        <v>6916.87</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>32.99</v>
+        <v>33</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004837569689451195</v>
+        <v>0.004793815106909341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7707,48 +7887,48 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.941</v>
+        <v>47.9329</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.1797</v>
+        <v>49.172</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2387</v>
+        <v>1.2391</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02583800921966584</v>
+        <v>0.02585072048634654</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.4817</v>
+        <v>55.5946</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.772</v>
+        <v>56.8756</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.2903</v>
+        <v>1.281</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02325631694775034</v>
+        <v>0.02304180621858958</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6771.98</v>
+        <v>6858.32</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6882.41</v>
+        <v>6970.45</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>110.43</v>
+        <v>112.13</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01630689990224425</v>
+        <v>0.01634948500507413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7756,48 +7936,48 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>47.8645</v>
+        <v>47.992</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>48.7145</v>
+        <v>48.842</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>0.85</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.01775846399732578</v>
+        <v>0.01771128521420237</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.4443</v>
+        <v>55.6735</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.6033</v>
+        <v>56.8395</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.159</v>
+        <v>1.166</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.02090386207418977</v>
+        <v>0.0209435368712224</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6768.67</v>
+        <v>6850.3</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6926.84</v>
+        <v>7009.47</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>158.17</v>
+        <v>159.17</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02336795855020262</v>
+        <v>0.02323547873815745</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7805,48 +7985,48 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>48.0158</v>
+        <v>47.9956</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6228</v>
+        <v>48.6215</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6259</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01264167211626173</v>
+        <v>0.01304077873805099</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.7141</v>
+        <v>55.7755</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.3773</v>
+        <v>56.4604</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6632</v>
+        <v>0.6849</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01190362942235449</v>
+        <v>0.01227958512250002</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6841.62</v>
+        <v>6902.96</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6896.09</v>
+        <v>6959.99</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54.47</v>
+        <v>57.03</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.007961564658662714</v>
+        <v>0.008261673253213114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -7854,48 +8034,48 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.472</v>
+        <v>47.468</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>48.822</v>
+        <v>48.818</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>1.35</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02843781597573306</v>
+        <v>0.02844021235358557</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>55.067</v>
+        <v>55.156</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.633</v>
+        <v>56.724</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.566</v>
+        <v>1.568</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02843808451522691</v>
+        <v>0.02842845746609617</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6735.53</v>
+        <v>6801.66</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6984.34</v>
+        <v>7052.92</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>248.81</v>
+        <v>251.26</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03693992900335979</v>
+        <v>0.03694098205438084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -7903,48 +8083,48 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>48.0158</v>
+        <v>47.9956</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6228</v>
+        <v>48.6215</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.607</v>
+        <v>0.6259</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01264167211626173</v>
+        <v>0.01304077873805099</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.7155</v>
+        <v>55.7712</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.379</v>
+        <v>56.4555</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6635</v>
+        <v>0.6843</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01190871481006183</v>
+        <v>0.01226977364661331</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6841.95</v>
+        <v>6904.04</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6896.34</v>
+        <v>6961.05</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>54.39</v>
+        <v>57.01</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.007949488084537304</v>
+        <v>0.008257484023846908</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -7952,48 +8132,48 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.8848</v>
+        <v>47.8822</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.8648</v>
+        <v>48.8623</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.98</v>
+        <v>0.9801</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02046578454958567</v>
+        <v>0.02046898429896705</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.5488</v>
+        <v>55.6343</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.6856</v>
+        <v>56.7731</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1368</v>
+        <v>1.1388</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.0204648885304453</v>
+        <v>0.02046938669130375</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6768.04</v>
+        <v>6834.7</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6976.09</v>
+        <v>7044.54</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>208.05</v>
+        <v>209.84</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03074006654807005</v>
+        <v>0.03070215225247633</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -8001,48 +8181,48 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.285</v>
+        <v>48.268</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.329</v>
+        <v>48.32</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.0009112560836698767</v>
+        <v>0.00107731830612414</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.889</v>
+        <v>55.932</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>56.025</v>
+        <v>56.092</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.136</v>
+        <v>0.16</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.002433394764622734</v>
+        <v>0.002860616462847744</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6798.78</v>
+        <v>6867.73</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6876.17</v>
+        <v>6942.05</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>77.39</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01138292458352822</v>
+        <v>0.01082162519493341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8050,48 +8230,48 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2355</v>
+        <v>48.2431</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.382</v>
+        <v>48.4427</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1465</v>
+        <v>0.1996</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.003037182158368837</v>
+        <v>0.004137379231434132</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.9469</v>
+        <v>56.057</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>56.1188</v>
+        <v>56.2856</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.1719</v>
+        <v>0.2286</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.003072556298919153</v>
+        <v>0.004077992043812548</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6831.7</v>
+        <v>6914.71</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6879.98</v>
+        <v>6963.51</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>48.28</v>
+        <v>48.8</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007067055052183204</v>
+        <v>0.007057418170827121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8107,24 +8287,24 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6780.95</v>
+        <v>6878.46</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6979.12</v>
+        <v>7078.75</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>198.17</v>
+        <v>200.29</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02922451868838437</v>
+        <v>0.02911843639419289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8132,48 +8312,48 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8217</v>
+        <v>47.8078</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.7085</v>
+        <v>48.7116</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.8868</v>
+        <v>0.9038</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01854388279797665</v>
+        <v>0.01890486489652316</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.4774</v>
+        <v>55.5502</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.5369</v>
+        <v>56.6247</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0595</v>
+        <v>1.0745</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01909786687912556</v>
+        <v>0.01934286465215247</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6773.34</v>
+        <v>6807.62</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7218.38</v>
+        <v>7267.06</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>445.04</v>
+        <v>459.44</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06570465973950813</v>
+        <v>0.06748907841507017</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8181,48 +8361,48 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7689</v>
+        <v>47.7612</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7723</v>
+        <v>48.7674</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0034</v>
+        <v>1.0062</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02100529842638202</v>
+        <v>0.02106730986658627</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.4929</v>
+        <v>55.558</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.5126</v>
+        <v>56.5718</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0197</v>
+        <v>1.0138</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01837532369005765</v>
+        <v>0.01824759710572735</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6742.66</v>
+        <v>6806.63</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6994.99</v>
+        <v>7059.58</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>252.33</v>
+        <v>252.95</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03742291617848149</v>
+        <v>0.03716229617299604</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8230,48 +8410,48 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6959</v>
+        <v>47.6875</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.8509</v>
+        <v>48.846</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.155</v>
+        <v>1.1585</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02421591793005269</v>
+        <v>0.02429357798165137</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.313</v>
+        <v>55.3938</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.667</v>
+        <v>56.7493</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.354</v>
+        <v>1.3555</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02447887476723374</v>
+        <v>0.02447024757283306</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6763.4</v>
+        <v>6827.22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6948.85</v>
+        <v>7014.43</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>185.45</v>
+        <v>187.21</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02741964100895999</v>
+        <v>0.02742111723366172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8279,48 +8459,48 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>48.3</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>48.31</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002070393374741201</v>
+        <v>0.0002070822116380203</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>55.93</v>
+        <v>56</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>55.98</v>
+        <v>56.05</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0008939746111210442</v>
+        <v>0.0008928571428571428</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6846.95</v>
+        <v>6913.48</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6853.22</v>
+        <v>6919.76</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.0009157362037111415</v>
+        <v>0.0009083703142266992</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8328,48 +8508,48 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6305</v>
+        <v>47.6242</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.6166</v>
+        <v>48.6133</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9861</v>
+        <v>0.9891</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02070312089942369</v>
+        <v>0.02076885281012594</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.2585</v>
+        <v>55.3388</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.4031</v>
+        <v>56.4887</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1446</v>
+        <v>1.1499</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02071355538062018</v>
+        <v>0.02077927240923186</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6720.13</v>
+        <v>6800.54</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6898.42</v>
+        <v>6980.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>178.29</v>
+        <v>180.42</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.0265307367565806</v>
+        <v>0.0265302461275134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8377,28 +8557,28 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>48.2075</v>
+        <v>48.2238</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>48.2943</v>
+        <v>48.3107</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.0868</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.001800549706995799</v>
+        <v>0.00180201477278854</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>55.7929</v>
+        <v>55.9713</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>55.8934</v>
+        <v>56.0722</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.1005</v>
+        <v>0.1009</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.001801304467055844</v>
+        <v>0.00180270960295723</v>
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
@@ -8407,10 +8587,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8418,48 +8598,48 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2443</v>
+        <v>48.2341</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2975</v>
+        <v>48.2987</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0532</v>
+        <v>0.0646</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001102720943199507</v>
+        <v>0.001339301448560251</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>55.9263</v>
+        <v>56.0351</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>56.0243</v>
+        <v>56.1208</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.098</v>
+        <v>0.0857</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.00175230616007138</v>
+        <v>0.001529398537702262</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6853.96</v>
+        <v>6886.76</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6888.36</v>
+        <v>6915.82</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>34.4</v>
+        <v>29.06</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.005018996317457352</v>
+        <v>0.004219691117448554</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8467,48 +8647,48 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.304</v>
+        <v>48.265</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.386</v>
+        <v>48.381</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.082</v>
+        <v>0.116</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.00169758198078834</v>
+        <v>0.002403397907386305</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.834</v>
+        <v>55.883</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>56.096</v>
+        <v>56.076</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.262</v>
+        <v>0.193</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.004692481283805566</v>
+        <v>0.003453644220961652</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6817</v>
+        <v>6883</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6868</v>
+        <v>6940</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.007481296758104739</v>
+        <v>0.008281272700857184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8516,48 +8696,48 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7755</v>
+        <v>47.7825</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7755</v>
+        <v>48.7825</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02093123044238156</v>
+        <v>0.02092816407680636</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.444</v>
+        <v>55.541</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.534</v>
+        <v>56.631</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>1.09</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01965947622826636</v>
+        <v>0.01962514178714823</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6818.14</v>
+        <v>6892.6</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6918.14</v>
+        <v>6992.6</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01466675662277395</v>
+        <v>0.01450831326349999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8573,24 +8753,24 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6780.95</v>
+        <v>6878.46</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6965.19</v>
+        <v>7064.62</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>184.24</v>
+        <v>186.16</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02717023425921147</v>
+        <v>0.02706419750932621</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8598,48 +8778,48 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>47.7045</v>
+        <v>47.657</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>48.9245</v>
+        <v>48.877</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>1.22</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.02557410726451383</v>
+        <v>0.02559959712109449</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.2258</v>
+        <v>55.2564</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.8814</v>
+        <v>56.9143</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6556</v>
+        <v>1.6579</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.02997874181994647</v>
+        <v>0.03000376426984024</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6741.82</v>
+        <v>6799.9</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6944.4</v>
+        <v>7004.56</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>202.58</v>
+        <v>204.66</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03004826589852592</v>
+        <v>0.03009750143384462</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8647,48 +8827,48 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1907</v>
+        <v>48.2899</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.4081</v>
+        <v>48.5078</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2174</v>
+        <v>0.2179</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.004511243870705344</v>
+        <v>0.004512330735826746</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.8248</v>
+        <v>56.0218</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.1611</v>
+        <v>56.3592</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3363</v>
+        <v>0.3374</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006024204296298419</v>
+        <v>0.006022655466264918</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6755.73</v>
+        <v>6919.66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6892.56</v>
+        <v>7127.25</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>136.83</v>
+        <v>207.59</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.02025391778534666</v>
+        <v>0.0300000289031542</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8696,48 +8876,48 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8693</v>
+        <v>47.8576</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6711</v>
+        <v>48.6678</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8018</v>
+        <v>0.8102</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01674977490792637</v>
+        <v>0.01692939052522483</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.5596</v>
+        <v>55.6424</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.4105</v>
+        <v>56.5036</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8509</v>
+        <v>0.8612</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.0153150850618075</v>
+        <v>0.01547740571937947</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6767.92</v>
+        <v>6834.06</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>6964.67</v>
+        <v>7031.93</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>196.75</v>
+        <v>197.87</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02907097010602962</v>
+        <v>0.02895350640761129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8745,48 +8925,48 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1712</v>
+        <v>48.1706</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3744</v>
+        <v>48.3738</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0.2032</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004218288105756137</v>
+        <v>0.004218340647614936</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.8686</v>
+        <v>55.9582</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>56.0937</v>
+        <v>56.1837</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2251</v>
+        <v>0.2255</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004029096845097246</v>
+        <v>0.004029793667416036</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6806.13</v>
+        <v>6873.88</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6860.8</v>
+        <v>6929.09</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>54.67</v>
+        <v>55.21</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008032464851538246</v>
+        <v>0.008031853916565317</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8794,48 +8974,48 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.9119</v>
+        <v>47.9393</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.8729</v>
+        <v>48.9003</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0.961</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02005764747380087</v>
+        <v>0.02004618340276141</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.6027</v>
+        <v>55.6319</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.7214</v>
+        <v>56.8134</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.1187</v>
+        <v>1.1815</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.02011952656975291</v>
+        <v>0.02123781499463438</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6774.91</v>
+        <v>6840.72</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6919.51</v>
+        <v>6985.32</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>144.6</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.02134345696105188</v>
+        <v>0.0211381258113181</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -8843,28 +9023,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.291</v>
+        <v>48.278</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.329</v>
+        <v>48.318</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.0007868961090058189</v>
+        <v>0.0008285347363188202</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.902</v>
+        <v>55.954</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>56.013</v>
+        <v>56.068</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.111</v>
+        <v>0.114</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.001985617688097027</v>
+        <v>0.002037387854308897</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -8873,10 +9053,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -8884,48 +9064,48 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>48.62</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.01886001676445935</v>
+        <v>0.01907356948228883</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.36</v>
+        <v>55.44</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.38</v>
+        <v>56.47</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.01842485549132948</v>
+        <v>0.01857864357864358</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6748.18</v>
+        <v>6813.67</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6937.84</v>
+        <v>7004.42</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>189.66</v>
+        <v>190.75</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.02810535581445664</v>
+        <v>0.02799519201839831</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -8933,48 +9113,48 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.9078</v>
+        <v>47.9067</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.877</v>
+        <v>48.8759</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.9692</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02023052613561883</v>
+        <v>0.02023099065475184</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.5555</v>
+        <v>55.6468</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.6794</v>
+        <v>56.7726</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1239</v>
+        <v>1.1258</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.02023022023022023</v>
+        <v>0.0202311723225774</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6806.95</v>
+        <v>6898.05</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6944.39</v>
+        <v>7037.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>137.44</v>
+        <v>139.28</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019112818516369</v>
+        <v>0.02019121345887606</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8982,48 +9162,48 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9557</v>
+        <v>47.9546</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.6082</v>
+        <v>48.6071</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0.6525</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360630748795242</v>
+        <v>0.01360661959436634</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.562</v>
+        <v>55.6479</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.3743</v>
+        <v>56.4614</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8123</v>
+        <v>0.8135</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461970411432274</v>
+        <v>0.01461870079553766</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6776.4</v>
+        <v>6859.57</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6913.23</v>
+        <v>6998.07</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>136.83</v>
+        <v>138.5</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019213741809811</v>
+        <v>0.02019076997537747</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -9031,40 +9211,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.7853</v>
+        <v>47.9117</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.7835</v>
+        <v>48.9114</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9982</v>
+        <v>0.9997</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02088926929411346</v>
+        <v>0.02086546709885059</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.3938</v>
+        <v>55.6275</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.6063</v>
+        <v>56.8438</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2125</v>
+        <v>1.2163</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.02188873122984883</v>
+        <v>0.0218650847152937</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6795.78</v>
+        <v>6880.35</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>7011.57</v>
+        <v>7098.77</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>215.79</v>
+        <v>218.42</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.0317535293961841</v>
+        <v>0.03174547806434266</v>
       </c>
     </row>
   </sheetData>
@@ -9081,7 +9261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N757"/>
+  <dimension ref="A1:N865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46970,6 +47150,5406 @@
       <c r="M757" t="inlineStr"/>
       <c r="N757" s="6" t="n">
         <v>0.5795370370370371</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B758" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C758" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D758" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E758" s="8" t="n">
+        <v>47.524</v>
+      </c>
+      <c r="F758" s="8" t="n">
+        <v>48.874</v>
+      </c>
+      <c r="G758" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H758" s="9" t="n">
+        <v>0.0284066997727464</v>
+      </c>
+      <c r="I758" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J758" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K758" s="54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L758" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M758" t="inlineStr"/>
+      <c r="N758" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B759" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C759" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D759" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E759" s="10" t="n">
+        <v>55.2136</v>
+      </c>
+      <c r="F759" s="10" t="n">
+        <v>56.7869</v>
+      </c>
+      <c r="G759" s="10" t="n">
+        <v>1.5733</v>
+      </c>
+      <c r="H759" s="11" t="n">
+        <v>0.02849479113841517</v>
+      </c>
+      <c r="I759" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J759" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K759" s="54" t="n">
+        <v>1.5733</v>
+      </c>
+      <c r="L759" s="55" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="M759" t="inlineStr"/>
+      <c r="N759" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B760" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C760" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D760" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E760" s="12" t="n">
+        <v>6760.55</v>
+      </c>
+      <c r="F760" s="12" t="n">
+        <v>7004.64</v>
+      </c>
+      <c r="G760" s="12" t="n">
+        <v>244.09</v>
+      </c>
+      <c r="H760" s="13" t="n">
+        <v>0.03610505062457936</v>
+      </c>
+      <c r="I760" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J760" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K760" s="54" t="n">
+        <v>244.09</v>
+      </c>
+      <c r="L760" s="55" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="M760" t="inlineStr"/>
+      <c r="N760" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B761" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C761" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D761" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E761" s="8" t="n">
+        <v>48.042</v>
+      </c>
+      <c r="F761" s="8" t="n">
+        <v>48.823</v>
+      </c>
+      <c r="G761" s="8" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="H761" s="9" t="n">
+        <v>0.01625660880063278</v>
+      </c>
+      <c r="I761" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J761" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K761" s="54" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L761" s="55" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M761" t="inlineStr"/>
+      <c r="N761" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B762" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C762" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D762" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E762" s="10" t="n">
+        <v>55.815</v>
+      </c>
+      <c r="F762" s="10" t="n">
+        <v>56.728</v>
+      </c>
+      <c r="G762" s="10" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="H762" s="11" t="n">
+        <v>0.01635760996147989</v>
+      </c>
+      <c r="I762" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J762" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K762" s="54" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L762" s="55" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="M762" t="inlineStr"/>
+      <c r="N762" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B763" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C763" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D763" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E763" s="12" t="n">
+        <v>6853.46</v>
+      </c>
+      <c r="F763" s="12" t="n">
+        <v>6993.59</v>
+      </c>
+      <c r="G763" s="12" t="n">
+        <v>140.13</v>
+      </c>
+      <c r="H763" s="13" t="n">
+        <v>0.02044660653159134</v>
+      </c>
+      <c r="I763" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J763" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K763" s="54" t="n">
+        <v>140.13</v>
+      </c>
+      <c r="L763" s="55" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="M763" t="inlineStr"/>
+      <c r="N763" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B764" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C764" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D764" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E764" s="8" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="F764" s="8" t="n">
+        <v>48.515</v>
+      </c>
+      <c r="G764" s="8" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H764" s="9" t="n">
+        <v>0.005909185154468173</v>
+      </c>
+      <c r="I764" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J764" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K764" s="54" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="L764" s="55" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="M764" t="inlineStr"/>
+      <c r="N764" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B765" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C765" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D765" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E765" s="10" t="n">
+        <v>55.861</v>
+      </c>
+      <c r="F765" s="10" t="n">
+        <v>56.377</v>
+      </c>
+      <c r="G765" s="10" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="H765" s="11" t="n">
+        <v>0.00923721379853565</v>
+      </c>
+      <c r="I765" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J765" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K765" s="54" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="L765" s="55" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="M765" t="inlineStr"/>
+      <c r="N765" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B766" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C766" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D766" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E766" s="12" t="n">
+        <v>6920.63</v>
+      </c>
+      <c r="F766" s="12" t="n">
+        <v>6990.46</v>
+      </c>
+      <c r="G766" s="12" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="H766" s="13" t="n">
+        <v>0.01009012185306829</v>
+      </c>
+      <c r="I766" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J766" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K766" s="54" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="L766" s="55" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="M766" t="inlineStr"/>
+      <c r="N766" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B767" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C767" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D767" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E767" s="8" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="F767" s="8" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="G767" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H767" s="9" t="n">
+        <v>0.00435052827843381</v>
+      </c>
+      <c r="I767" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J767" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K767" s="54" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L767" s="55" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="M767" t="inlineStr"/>
+      <c r="N767" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B768" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C768" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D768" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E768" s="10" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="F768" s="10" t="n">
+        <v>56.324</v>
+      </c>
+      <c r="G768" s="10" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="H768" s="11" t="n">
+        <v>0.006864497676081516</v>
+      </c>
+      <c r="I768" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J768" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K768" s="54" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="L768" s="55" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="M768" t="inlineStr"/>
+      <c r="N768" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B769" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C769" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D769" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E769" s="12" t="n">
+        <v>6842.63</v>
+      </c>
+      <c r="F769" s="12" t="n">
+        <v>7015</v>
+      </c>
+      <c r="G769" s="12" t="n">
+        <v>172.37</v>
+      </c>
+      <c r="H769" s="13" t="n">
+        <v>0.02519060653579107</v>
+      </c>
+      <c r="I769" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J769" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K769" s="54" t="n">
+        <v>172.37</v>
+      </c>
+      <c r="L769" s="55" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="M769" t="inlineStr"/>
+      <c r="N769" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B770" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C770" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D770" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E770" s="8" t="n">
+        <v>47.465</v>
+      </c>
+      <c r="F770" s="8" t="n">
+        <v>48.7411</v>
+      </c>
+      <c r="G770" s="8" t="n">
+        <v>1.2761</v>
+      </c>
+      <c r="H770" s="9" t="n">
+        <v>0.0268850732118403</v>
+      </c>
+      <c r="I770" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J770" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K770" s="54" t="n">
+        <v>1.2761</v>
+      </c>
+      <c r="L770" s="55" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="M770" t="inlineStr"/>
+      <c r="N770" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B771" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C771" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D771" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E771" s="10" t="n">
+        <v>55.2416</v>
+      </c>
+      <c r="F771" s="10" t="n">
+        <v>56.6119</v>
+      </c>
+      <c r="G771" s="10" t="n">
+        <v>1.3703</v>
+      </c>
+      <c r="H771" s="11" t="n">
+        <v>0.02480558130104848</v>
+      </c>
+      <c r="I771" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J771" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K771" s="54" t="n">
+        <v>1.3702</v>
+      </c>
+      <c r="L771" s="55" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="M771" t="inlineStr"/>
+      <c r="N771" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B772" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C772" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D772" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E772" s="12" t="n">
+        <v>6819.63</v>
+      </c>
+      <c r="F772" s="12" t="n">
+        <v>6975.89</v>
+      </c>
+      <c r="G772" s="12" t="n">
+        <v>156.26</v>
+      </c>
+      <c r="H772" s="13" t="n">
+        <v>0.02291326655551694</v>
+      </c>
+      <c r="I772" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J772" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K772" s="54" t="n">
+        <v>156.27</v>
+      </c>
+      <c r="L772" s="55" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="M772" t="inlineStr"/>
+      <c r="N772" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B773" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C773" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D773" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E773" s="8" t="n">
+        <v>47.317</v>
+      </c>
+      <c r="F773" s="8" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="G773" s="8" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="H773" s="9" t="n">
+        <v>0.0406407844960585</v>
+      </c>
+      <c r="I773" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J773" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K773" s="54" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="L773" s="55" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M773" t="inlineStr"/>
+      <c r="N773" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B774" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C774" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D774" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E774" s="10" t="n">
+        <v>54.968</v>
+      </c>
+      <c r="F774" s="10" t="n">
+        <v>57.211</v>
+      </c>
+      <c r="G774" s="10" t="n">
+        <v>2.243</v>
+      </c>
+      <c r="H774" s="11" t="n">
+        <v>0.04080555959831175</v>
+      </c>
+      <c r="I774" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J774" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K774" s="54" t="n">
+        <v>2.243</v>
+      </c>
+      <c r="L774" s="55" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="M774" t="inlineStr"/>
+      <c r="N774" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B775" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C775" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D775" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E775" s="12" t="n">
+        <v>6821.76</v>
+      </c>
+      <c r="F775" s="12" t="n">
+        <v>7016.15</v>
+      </c>
+      <c r="G775" s="12" t="n">
+        <v>194.39</v>
+      </c>
+      <c r="H775" s="13" t="n">
+        <v>0.02849557885355099</v>
+      </c>
+      <c r="I775" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J775" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K775" s="54" t="n">
+        <v>194.39</v>
+      </c>
+      <c r="L775" s="55" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="M775" t="inlineStr"/>
+      <c r="N775" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B776" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C776" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D776" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E776" s="8" t="n">
+        <v>47.5756</v>
+      </c>
+      <c r="F776" s="8" t="n">
+        <v>48.9757</v>
+      </c>
+      <c r="G776" s="8" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="H776" s="9" t="n">
+        <v>0.02942895097486947</v>
+      </c>
+      <c r="I776" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J776" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K776" s="54" t="n">
+        <v>1.4001</v>
+      </c>
+      <c r="L776" s="55" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="M776" t="inlineStr"/>
+      <c r="N776" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B777" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C777" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D777" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E777" s="10" t="n">
+        <v>55.2594</v>
+      </c>
+      <c r="F777" s="10" t="n">
+        <v>56.8905</v>
+      </c>
+      <c r="G777" s="10" t="n">
+        <v>1.6311</v>
+      </c>
+      <c r="H777" s="11" t="n">
+        <v>0.02951715002334444</v>
+      </c>
+      <c r="I777" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J777" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K777" s="54" t="n">
+        <v>1.6311</v>
+      </c>
+      <c r="L777" s="55" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="M777" t="inlineStr"/>
+      <c r="N777" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B778" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C778" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D778" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E778" s="12" t="n">
+        <v>6834.26</v>
+      </c>
+      <c r="F778" s="12" t="n">
+        <v>7036.42</v>
+      </c>
+      <c r="G778" s="12" t="n">
+        <v>202.16</v>
+      </c>
+      <c r="H778" s="13" t="n">
+        <v>0.02958037885594051</v>
+      </c>
+      <c r="I778" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J778" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K778" s="54" t="n">
+        <v>202.17</v>
+      </c>
+      <c r="L778" s="55" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="M778" t="inlineStr"/>
+      <c r="N778" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B779" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C779" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D779" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E779" s="8" t="n">
+        <v>48.2258</v>
+      </c>
+      <c r="F779" s="8" t="n">
+        <v>48.301</v>
+      </c>
+      <c r="G779" s="8" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="H779" s="9" t="n">
+        <v>0.001559331312285125</v>
+      </c>
+      <c r="I779" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J779" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K779" s="54" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="L779" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M779" t="inlineStr"/>
+      <c r="N779" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B780" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C780" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D780" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E780" s="10" t="n">
+        <v>56.0082</v>
+      </c>
+      <c r="F780" s="10" t="n">
+        <v>56.1124</v>
+      </c>
+      <c r="G780" s="10" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="H780" s="11" t="n">
+        <v>0.001860441863869933</v>
+      </c>
+      <c r="I780" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J780" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K780" s="54" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="L780" s="55" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="M780" t="inlineStr"/>
+      <c r="N780" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B781" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C781" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D781" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E781" s="12" t="n">
+        <v>6885.98</v>
+      </c>
+      <c r="F781" s="12" t="n">
+        <v>6917.66</v>
+      </c>
+      <c r="G781" s="12" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="H781" s="13" t="n">
+        <v>0.004600652339971943</v>
+      </c>
+      <c r="I781" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J781" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K781" s="54" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="L781" s="55" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="M781" t="inlineStr"/>
+      <c r="N781" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B782" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C782" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D782" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E782" s="8" t="n">
+        <v>48.2508</v>
+      </c>
+      <c r="F782" s="8" t="n">
+        <v>48.2891</v>
+      </c>
+      <c r="G782" s="8" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="H782" s="9" t="n">
+        <v>0.0007937692224792128</v>
+      </c>
+      <c r="I782" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J782" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K782" s="54" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="L782" s="55" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M782" t="inlineStr"/>
+      <c r="N782" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B783" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C783" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D783" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E783" s="10" t="n">
+        <v>56.0087</v>
+      </c>
+      <c r="F783" s="10" t="n">
+        <v>56.1183</v>
+      </c>
+      <c r="G783" s="10" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="H783" s="11" t="n">
+        <v>0.001956838848250361</v>
+      </c>
+      <c r="I783" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J783" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K783" s="54" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="L783" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M783" t="inlineStr"/>
+      <c r="N783" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B784" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C784" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D784" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E784" s="12" t="n">
+        <v>6883.87</v>
+      </c>
+      <c r="F784" s="12" t="n">
+        <v>6916.87</v>
+      </c>
+      <c r="G784" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H784" s="13" t="n">
+        <v>0.004793815106909341</v>
+      </c>
+      <c r="I784" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J784" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K784" s="54" t="n">
+        <v>33</v>
+      </c>
+      <c r="L784" s="55" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="M784" t="inlineStr"/>
+      <c r="N784" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B785" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C785" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D785" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E785" s="8" t="n">
+        <v>47.9329</v>
+      </c>
+      <c r="F785" s="8" t="n">
+        <v>49.172</v>
+      </c>
+      <c r="G785" s="8" t="n">
+        <v>1.2391</v>
+      </c>
+      <c r="H785" s="9" t="n">
+        <v>0.02585072048634654</v>
+      </c>
+      <c r="I785" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J785" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K785" s="54" t="n">
+        <v>1.2392</v>
+      </c>
+      <c r="L785" s="55" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="M785" t="inlineStr"/>
+      <c r="N785" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B786" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C786" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D786" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E786" s="10" t="n">
+        <v>55.5946</v>
+      </c>
+      <c r="F786" s="10" t="n">
+        <v>56.8756</v>
+      </c>
+      <c r="G786" s="10" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="H786" s="11" t="n">
+        <v>0.02304180621858958</v>
+      </c>
+      <c r="I786" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J786" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K786" s="54" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="L786" s="55" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="M786" t="inlineStr"/>
+      <c r="N786" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B787" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C787" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D787" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E787" s="12" t="n">
+        <v>6858.32</v>
+      </c>
+      <c r="F787" s="12" t="n">
+        <v>6970.45</v>
+      </c>
+      <c r="G787" s="12" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="H787" s="13" t="n">
+        <v>0.01634948500507413</v>
+      </c>
+      <c r="I787" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J787" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K787" s="54" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="L787" s="55" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="M787" t="inlineStr"/>
+      <c r="N787" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B788" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C788" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D788" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E788" s="8" t="n">
+        <v>47.992</v>
+      </c>
+      <c r="F788" s="8" t="n">
+        <v>48.842</v>
+      </c>
+      <c r="G788" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H788" s="9" t="n">
+        <v>0.01771128521420237</v>
+      </c>
+      <c r="I788" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J788" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K788" s="54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L788" s="55" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="M788" t="inlineStr"/>
+      <c r="N788" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B789" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C789" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D789" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E789" s="10" t="n">
+        <v>55.6735</v>
+      </c>
+      <c r="F789" s="10" t="n">
+        <v>56.8395</v>
+      </c>
+      <c r="G789" s="10" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="H789" s="11" t="n">
+        <v>0.0209435368712224</v>
+      </c>
+      <c r="I789" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J789" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K789" s="54" t="n">
+        <v>1.1661</v>
+      </c>
+      <c r="L789" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M789" t="inlineStr"/>
+      <c r="N789" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B790" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C790" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D790" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E790" s="12" t="n">
+        <v>6850.3</v>
+      </c>
+      <c r="F790" s="12" t="n">
+        <v>7009.47</v>
+      </c>
+      <c r="G790" s="12" t="n">
+        <v>159.17</v>
+      </c>
+      <c r="H790" s="13" t="n">
+        <v>0.02323547873815745</v>
+      </c>
+      <c r="I790" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J790" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K790" s="54" t="n">
+        <v>159.17</v>
+      </c>
+      <c r="L790" s="55" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="M790" t="inlineStr"/>
+      <c r="N790" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B791" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C791" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D791" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E791" s="8" t="n">
+        <v>47.9956</v>
+      </c>
+      <c r="F791" s="8" t="n">
+        <v>48.6215</v>
+      </c>
+      <c r="G791" s="8" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="H791" s="9" t="n">
+        <v>0.01304077873805099</v>
+      </c>
+      <c r="I791" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J791" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K791" s="54" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L791" s="55" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M791" t="inlineStr"/>
+      <c r="N791" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B792" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C792" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D792" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E792" s="10" t="n">
+        <v>55.7755</v>
+      </c>
+      <c r="F792" s="10" t="n">
+        <v>56.4604</v>
+      </c>
+      <c r="G792" s="10" t="n">
+        <v>0.6849</v>
+      </c>
+      <c r="H792" s="11" t="n">
+        <v>0.01227958512250002</v>
+      </c>
+      <c r="I792" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J792" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K792" s="54" t="n">
+        <v>0.6849</v>
+      </c>
+      <c r="L792" s="55" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="M792" t="inlineStr"/>
+      <c r="N792" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B793" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C793" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D793" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E793" s="12" t="n">
+        <v>6902.96</v>
+      </c>
+      <c r="F793" s="12" t="n">
+        <v>6959.99</v>
+      </c>
+      <c r="G793" s="12" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="H793" s="13" t="n">
+        <v>0.008261673253213114</v>
+      </c>
+      <c r="I793" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J793" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K793" s="54" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="L793" s="55" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="M793" t="inlineStr"/>
+      <c r="N793" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B794" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C794" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D794" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E794" s="8" t="n">
+        <v>47.468</v>
+      </c>
+      <c r="F794" s="8" t="n">
+        <v>48.818</v>
+      </c>
+      <c r="G794" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H794" s="9" t="n">
+        <v>0.02844021235358557</v>
+      </c>
+      <c r="I794" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J794" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K794" s="54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L794" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M794" t="inlineStr"/>
+      <c r="N794" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B795" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C795" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D795" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E795" s="10" t="n">
+        <v>55.156</v>
+      </c>
+      <c r="F795" s="10" t="n">
+        <v>56.724</v>
+      </c>
+      <c r="G795" s="10" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="H795" s="11" t="n">
+        <v>0.02842845746609617</v>
+      </c>
+      <c r="I795" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J795" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K795" s="54" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="L795" s="55" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="M795" t="inlineStr"/>
+      <c r="N795" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B796" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C796" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D796" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E796" s="12" t="n">
+        <v>6801.66</v>
+      </c>
+      <c r="F796" s="12" t="n">
+        <v>7052.92</v>
+      </c>
+      <c r="G796" s="12" t="n">
+        <v>251.26</v>
+      </c>
+      <c r="H796" s="13" t="n">
+        <v>0.03694098205438084</v>
+      </c>
+      <c r="I796" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J796" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K796" s="54" t="n">
+        <v>251.26</v>
+      </c>
+      <c r="L796" s="55" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M796" t="inlineStr"/>
+      <c r="N796" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B797" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C797" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D797" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E797" s="8" t="n">
+        <v>47.9956</v>
+      </c>
+      <c r="F797" s="8" t="n">
+        <v>48.6215</v>
+      </c>
+      <c r="G797" s="8" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="H797" s="9" t="n">
+        <v>0.01304077873805099</v>
+      </c>
+      <c r="I797" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J797" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K797" s="54" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="L797" s="55" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M797" t="inlineStr"/>
+      <c r="N797" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B798" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C798" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D798" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E798" s="10" t="n">
+        <v>55.7712</v>
+      </c>
+      <c r="F798" s="10" t="n">
+        <v>56.4555</v>
+      </c>
+      <c r="G798" s="10" t="n">
+        <v>0.6843</v>
+      </c>
+      <c r="H798" s="11" t="n">
+        <v>0.01226977364661331</v>
+      </c>
+      <c r="I798" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J798" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K798" s="54" t="n">
+        <v>0.6843</v>
+      </c>
+      <c r="L798" s="55" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="M798" t="inlineStr"/>
+      <c r="N798" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B799" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C799" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D799" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E799" s="12" t="n">
+        <v>6904.04</v>
+      </c>
+      <c r="F799" s="12" t="n">
+        <v>6961.05</v>
+      </c>
+      <c r="G799" s="12" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="H799" s="13" t="n">
+        <v>0.008257484023846908</v>
+      </c>
+      <c r="I799" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J799" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K799" s="54" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="L799" s="55" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="M799" t="inlineStr"/>
+      <c r="N799" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B800" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C800" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D800" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E800" s="8" t="n">
+        <v>47.8822</v>
+      </c>
+      <c r="F800" s="8" t="n">
+        <v>48.8623</v>
+      </c>
+      <c r="G800" s="8" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="H800" s="9" t="n">
+        <v>0.02046898429896705</v>
+      </c>
+      <c r="I800" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J800" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K800" s="54" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="L800" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M800" t="inlineStr"/>
+      <c r="N800" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B801" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C801" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D801" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E801" s="10" t="n">
+        <v>55.6343</v>
+      </c>
+      <c r="F801" s="10" t="n">
+        <v>56.7731</v>
+      </c>
+      <c r="G801" s="10" t="n">
+        <v>1.1388</v>
+      </c>
+      <c r="H801" s="11" t="n">
+        <v>0.02046938669130375</v>
+      </c>
+      <c r="I801" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J801" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K801" s="54" t="n">
+        <v>1.1388</v>
+      </c>
+      <c r="L801" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M801" t="inlineStr"/>
+      <c r="N801" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B802" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C802" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D802" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E802" s="12" t="n">
+        <v>6834.7</v>
+      </c>
+      <c r="F802" s="12" t="n">
+        <v>7044.54</v>
+      </c>
+      <c r="G802" s="12" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="H802" s="13" t="n">
+        <v>0.03070215225247633</v>
+      </c>
+      <c r="I802" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J802" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K802" s="54" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="L802" s="55" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="M802" t="inlineStr"/>
+      <c r="N802" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B803" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C803" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D803" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E803" s="8" t="n">
+        <v>48.268</v>
+      </c>
+      <c r="F803" s="8" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="G803" s="8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H803" s="9" t="n">
+        <v>0.00107731830612414</v>
+      </c>
+      <c r="I803" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J803" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K803" s="54" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L803" s="55" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="M803" t="inlineStr"/>
+      <c r="N803" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B804" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C804" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D804" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E804" s="10" t="n">
+        <v>55.932</v>
+      </c>
+      <c r="F804" s="10" t="n">
+        <v>56.092</v>
+      </c>
+      <c r="G804" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H804" s="11" t="n">
+        <v>0.002860616462847744</v>
+      </c>
+      <c r="I804" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J804" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K804" s="54" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L804" s="55" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="M804" t="inlineStr"/>
+      <c r="N804" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B805" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C805" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D805" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E805" s="12" t="n">
+        <v>6867.73</v>
+      </c>
+      <c r="F805" s="12" t="n">
+        <v>6942.05</v>
+      </c>
+      <c r="G805" s="12" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="H805" s="13" t="n">
+        <v>0.01082162519493341</v>
+      </c>
+      <c r="I805" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J805" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K805" s="54" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="L805" s="55" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="M805" t="inlineStr"/>
+      <c r="N805" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B806" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C806" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D806" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E806" s="8" t="n">
+        <v>48.2431</v>
+      </c>
+      <c r="F806" s="8" t="n">
+        <v>48.4427</v>
+      </c>
+      <c r="G806" s="8" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="H806" s="9" t="n">
+        <v>0.004137379231434132</v>
+      </c>
+      <c r="I806" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J806" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K806" s="54" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="L806" s="55" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="M806" t="inlineStr"/>
+      <c r="N806" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B807" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C807" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D807" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E807" s="10" t="n">
+        <v>56.057</v>
+      </c>
+      <c r="F807" s="10" t="n">
+        <v>56.2856</v>
+      </c>
+      <c r="G807" s="10" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="H807" s="11" t="n">
+        <v>0.004077992043812548</v>
+      </c>
+      <c r="I807" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J807" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K807" s="54" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="L807" s="55" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="M807" t="inlineStr"/>
+      <c r="N807" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B808" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C808" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D808" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E808" s="12" t="n">
+        <v>6914.71</v>
+      </c>
+      <c r="F808" s="12" t="n">
+        <v>6963.51</v>
+      </c>
+      <c r="G808" s="12" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H808" s="13" t="n">
+        <v>0.007057418170827121</v>
+      </c>
+      <c r="I808" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J808" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K808" s="54" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="L808" s="55" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="M808" t="inlineStr"/>
+      <c r="N808" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B809" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C809" s="30" t="inlineStr">
+        <is>
+          <t>Hepsipay</t>
+        </is>
+      </c>
+      <c r="D809" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E809" s="12" t="n">
+        <v>6878.46</v>
+      </c>
+      <c r="F809" s="12" t="n">
+        <v>7078.75</v>
+      </c>
+      <c r="G809" s="12" t="n">
+        <v>200.29</v>
+      </c>
+      <c r="H809" s="13" t="n">
+        <v>0.02911843639419289</v>
+      </c>
+      <c r="I809" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J809" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K809" s="54" t="n">
+        <v>200.29</v>
+      </c>
+      <c r="L809" s="55" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="M809" t="inlineStr"/>
+      <c r="N809" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B810" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C810" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D810" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E810" s="8" t="n">
+        <v>47.8078</v>
+      </c>
+      <c r="F810" s="8" t="n">
+        <v>48.7116</v>
+      </c>
+      <c r="G810" s="8" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="H810" s="9" t="n">
+        <v>0.01890486489652316</v>
+      </c>
+      <c r="I810" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J810" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K810" s="54" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="L810" s="55" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="M810" t="inlineStr"/>
+      <c r="N810" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B811" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C811" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D811" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E811" s="10" t="n">
+        <v>55.5502</v>
+      </c>
+      <c r="F811" s="10" t="n">
+        <v>56.6247</v>
+      </c>
+      <c r="G811" s="10" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="H811" s="11" t="n">
+        <v>0.01934286465215247</v>
+      </c>
+      <c r="I811" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J811" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K811" s="54" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="L811" s="55" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="M811" t="inlineStr"/>
+      <c r="N811" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B812" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C812" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D812" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E812" s="12" t="n">
+        <v>6807.62</v>
+      </c>
+      <c r="F812" s="12" t="n">
+        <v>7267.06</v>
+      </c>
+      <c r="G812" s="12" t="n">
+        <v>459.44</v>
+      </c>
+      <c r="H812" s="13" t="n">
+        <v>0.06748907841507017</v>
+      </c>
+      <c r="I812" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J812" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K812" s="54" t="n">
+        <v>459.44</v>
+      </c>
+      <c r="L812" s="55" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="M812" t="inlineStr"/>
+      <c r="N812" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B813" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C813" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D813" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E813" s="8" t="n">
+        <v>47.7612</v>
+      </c>
+      <c r="F813" s="8" t="n">
+        <v>48.7674</v>
+      </c>
+      <c r="G813" s="8" t="n">
+        <v>1.0062</v>
+      </c>
+      <c r="H813" s="9" t="n">
+        <v>0.02106730986658627</v>
+      </c>
+      <c r="I813" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J813" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K813" s="54" t="n">
+        <v>1.0062</v>
+      </c>
+      <c r="L813" s="55" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="M813" t="inlineStr"/>
+      <c r="N813" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B814" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C814" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D814" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E814" s="10" t="n">
+        <v>55.558</v>
+      </c>
+      <c r="F814" s="10" t="n">
+        <v>56.5718</v>
+      </c>
+      <c r="G814" s="10" t="n">
+        <v>1.0138</v>
+      </c>
+      <c r="H814" s="11" t="n">
+        <v>0.01824759710572735</v>
+      </c>
+      <c r="I814" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J814" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K814" s="54" t="n">
+        <v>1.0138</v>
+      </c>
+      <c r="L814" s="55" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="M814" t="inlineStr"/>
+      <c r="N814" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B815" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C815" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D815" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E815" s="12" t="n">
+        <v>6806.63</v>
+      </c>
+      <c r="F815" s="12" t="n">
+        <v>7059.58</v>
+      </c>
+      <c r="G815" s="12" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="H815" s="13" t="n">
+        <v>0.03716229617299604</v>
+      </c>
+      <c r="I815" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J815" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K815" s="54" t="n">
+        <v>252.96</v>
+      </c>
+      <c r="L815" s="55" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M815" t="inlineStr"/>
+      <c r="N815" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B816" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C816" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D816" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E816" s="8" t="n">
+        <v>47.6875</v>
+      </c>
+      <c r="F816" s="8" t="n">
+        <v>48.846</v>
+      </c>
+      <c r="G816" s="8" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="H816" s="9" t="n">
+        <v>0.02429357798165137</v>
+      </c>
+      <c r="I816" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J816" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K816" s="54" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="L816" s="55" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="M816" t="inlineStr"/>
+      <c r="N816" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B817" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C817" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D817" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E817" s="10" t="n">
+        <v>55.3938</v>
+      </c>
+      <c r="F817" s="10" t="n">
+        <v>56.7493</v>
+      </c>
+      <c r="G817" s="10" t="n">
+        <v>1.3555</v>
+      </c>
+      <c r="H817" s="11" t="n">
+        <v>0.02447024757283306</v>
+      </c>
+      <c r="I817" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J817" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K817" s="54" t="n">
+        <v>1.3555</v>
+      </c>
+      <c r="L817" s="55" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="M817" t="inlineStr"/>
+      <c r="N817" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B818" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C818" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D818" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E818" s="12" t="n">
+        <v>6827.22</v>
+      </c>
+      <c r="F818" s="12" t="n">
+        <v>7014.43</v>
+      </c>
+      <c r="G818" s="12" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="H818" s="13" t="n">
+        <v>0.02742111723366172</v>
+      </c>
+      <c r="I818" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J818" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K818" s="54" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="L818" s="55" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="M818" t="inlineStr"/>
+      <c r="N818" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B819" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C819" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D819" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E819" s="8" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="F819" s="8" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G819" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H819" s="9" t="n">
+        <v>0.0002070822116380203</v>
+      </c>
+      <c r="I819" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J819" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K819" s="54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L819" s="55" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M819" t="inlineStr"/>
+      <c r="N819" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B820" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C820" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D820" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E820" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="F820" s="10" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="G820" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H820" s="11" t="n">
+        <v>0.0008928571428571428</v>
+      </c>
+      <c r="I820" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J820" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K820" s="54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L820" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M820" t="inlineStr"/>
+      <c r="N820" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B821" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C821" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D821" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E821" s="12" t="n">
+        <v>6913.48</v>
+      </c>
+      <c r="F821" s="12" t="n">
+        <v>6919.76</v>
+      </c>
+      <c r="G821" s="12" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H821" s="13" t="n">
+        <v>0.0009083703142266992</v>
+      </c>
+      <c r="I821" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J821" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K821" s="54" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="L821" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M821" t="inlineStr"/>
+      <c r="N821" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B822" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C822" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D822" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E822" s="8" t="n">
+        <v>47.6242</v>
+      </c>
+      <c r="F822" s="8" t="n">
+        <v>48.6133</v>
+      </c>
+      <c r="G822" s="8" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="H822" s="9" t="n">
+        <v>0.02076885281012594</v>
+      </c>
+      <c r="I822" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J822" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K822" s="54" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="L822" s="55" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="M822" t="inlineStr"/>
+      <c r="N822" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B823" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C823" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D823" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E823" s="10" t="n">
+        <v>55.3388</v>
+      </c>
+      <c r="F823" s="10" t="n">
+        <v>56.4887</v>
+      </c>
+      <c r="G823" s="10" t="n">
+        <v>1.1499</v>
+      </c>
+      <c r="H823" s="11" t="n">
+        <v>0.02077927240923186</v>
+      </c>
+      <c r="I823" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J823" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K823" s="54" t="n">
+        <v>1.1498</v>
+      </c>
+      <c r="L823" s="55" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="M823" t="inlineStr"/>
+      <c r="N823" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B824" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C824" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D824" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E824" s="12" t="n">
+        <v>6800.54</v>
+      </c>
+      <c r="F824" s="12" t="n">
+        <v>6980.96</v>
+      </c>
+      <c r="G824" s="12" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="H824" s="13" t="n">
+        <v>0.0265302461275134</v>
+      </c>
+      <c r="I824" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J824" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K824" s="54" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="L824" s="55" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="M824" t="inlineStr"/>
+      <c r="N824" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B825" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C825" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D825" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E825" s="8" t="n">
+        <v>48.2238</v>
+      </c>
+      <c r="F825" s="8" t="n">
+        <v>48.3107</v>
+      </c>
+      <c r="G825" s="8" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="H825" s="9" t="n">
+        <v>0.00180201477278854</v>
+      </c>
+      <c r="I825" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J825" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K825" s="54" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="L825" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M825" t="inlineStr"/>
+      <c r="N825" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B826" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C826" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D826" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E826" s="10" t="n">
+        <v>55.9713</v>
+      </c>
+      <c r="F826" s="10" t="n">
+        <v>56.0722</v>
+      </c>
+      <c r="G826" s="10" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="H826" s="11" t="n">
+        <v>0.00180270960295723</v>
+      </c>
+      <c r="I826" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J826" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K826" s="54" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="L826" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M826" t="inlineStr"/>
+      <c r="N826" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B827" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C827" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D827" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E827" s="8" t="n">
+        <v>48.2341</v>
+      </c>
+      <c r="F827" s="8" t="n">
+        <v>48.2987</v>
+      </c>
+      <c r="G827" s="8" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="H827" s="9" t="n">
+        <v>0.001339301448560251</v>
+      </c>
+      <c r="I827" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J827" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K827" s="54" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="L827" s="55" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="M827" t="inlineStr"/>
+      <c r="N827" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B828" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C828" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D828" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E828" s="10" t="n">
+        <v>56.0351</v>
+      </c>
+      <c r="F828" s="10" t="n">
+        <v>56.1208</v>
+      </c>
+      <c r="G828" s="10" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="H828" s="11" t="n">
+        <v>0.001529398537702262</v>
+      </c>
+      <c r="I828" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J828" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K828" s="54" t="n">
+        <v>0.0858</v>
+      </c>
+      <c r="L828" s="55" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="M828" t="inlineStr"/>
+      <c r="N828" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B829" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C829" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D829" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E829" s="12" t="n">
+        <v>6886.76</v>
+      </c>
+      <c r="F829" s="12" t="n">
+        <v>6915.82</v>
+      </c>
+      <c r="G829" s="12" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H829" s="13" t="n">
+        <v>0.004219691117448554</v>
+      </c>
+      <c r="I829" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J829" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K829" s="54" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="L829" s="55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M829" t="inlineStr"/>
+      <c r="N829" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B830" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C830" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D830" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E830" s="8" t="n">
+        <v>48.265</v>
+      </c>
+      <c r="F830" s="8" t="n">
+        <v>48.381</v>
+      </c>
+      <c r="G830" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="H830" s="9" t="n">
+        <v>0.002403397907386305</v>
+      </c>
+      <c r="I830" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J830" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K830" s="54" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="L830" s="55" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="M830" t="inlineStr"/>
+      <c r="N830" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B831" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C831" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D831" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E831" s="10" t="n">
+        <v>55.883</v>
+      </c>
+      <c r="F831" s="10" t="n">
+        <v>56.076</v>
+      </c>
+      <c r="G831" s="10" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H831" s="11" t="n">
+        <v>0.003453644220961652</v>
+      </c>
+      <c r="I831" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J831" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K831" s="54" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="L831" s="55" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="M831" t="inlineStr"/>
+      <c r="N831" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B832" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C832" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D832" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E832" s="12" t="n">
+        <v>6883</v>
+      </c>
+      <c r="F832" s="12" t="n">
+        <v>6940</v>
+      </c>
+      <c r="G832" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H832" s="13" t="n">
+        <v>0.008281272700857184</v>
+      </c>
+      <c r="I832" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J832" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K832" s="54" t="n">
+        <v>57</v>
+      </c>
+      <c r="L832" s="55" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="M832" t="inlineStr"/>
+      <c r="N832" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B833" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C833" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D833" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E833" s="8" t="n">
+        <v>47.7825</v>
+      </c>
+      <c r="F833" s="8" t="n">
+        <v>48.7825</v>
+      </c>
+      <c r="G833" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H833" s="9" t="n">
+        <v>0.02092816407680636</v>
+      </c>
+      <c r="I833" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J833" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K833" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L833" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M833" t="inlineStr"/>
+      <c r="N833" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B834" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C834" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D834" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E834" s="10" t="n">
+        <v>55.541</v>
+      </c>
+      <c r="F834" s="10" t="n">
+        <v>56.631</v>
+      </c>
+      <c r="G834" s="10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H834" s="11" t="n">
+        <v>0.01962514178714823</v>
+      </c>
+      <c r="I834" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J834" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K834" s="54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L834" s="55" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="M834" t="inlineStr"/>
+      <c r="N834" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B835" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C835" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D835" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E835" s="12" t="n">
+        <v>6892.6</v>
+      </c>
+      <c r="F835" s="12" t="n">
+        <v>6992.6</v>
+      </c>
+      <c r="G835" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H835" s="13" t="n">
+        <v>0.01450831326349999</v>
+      </c>
+      <c r="I835" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J835" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K835" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="L835" s="55" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="M835" t="inlineStr"/>
+      <c r="N835" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B836" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C836" s="40" t="inlineStr">
+        <is>
+          <t>Papara</t>
+        </is>
+      </c>
+      <c r="D836" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E836" s="12" t="n">
+        <v>6878.46</v>
+      </c>
+      <c r="F836" s="12" t="n">
+        <v>7064.62</v>
+      </c>
+      <c r="G836" s="12" t="n">
+        <v>186.16</v>
+      </c>
+      <c r="H836" s="13" t="n">
+        <v>0.02706419750932621</v>
+      </c>
+      <c r="I836" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J836" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K836" s="54" t="n">
+        <v>186.16</v>
+      </c>
+      <c r="L836" s="55" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="M836" t="inlineStr"/>
+      <c r="N836" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B837" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C837" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D837" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E837" s="8" t="n">
+        <v>47.657</v>
+      </c>
+      <c r="F837" s="8" t="n">
+        <v>48.877</v>
+      </c>
+      <c r="G837" s="8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H837" s="9" t="n">
+        <v>0.02559959712109449</v>
+      </c>
+      <c r="I837" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J837" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K837" s="54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L837" s="55" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="M837" t="inlineStr"/>
+      <c r="N837" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B838" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C838" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D838" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E838" s="10" t="n">
+        <v>55.2564</v>
+      </c>
+      <c r="F838" s="10" t="n">
+        <v>56.9143</v>
+      </c>
+      <c r="G838" s="10" t="n">
+        <v>1.6579</v>
+      </c>
+      <c r="H838" s="11" t="n">
+        <v>0.03000376426984024</v>
+      </c>
+      <c r="I838" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J838" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K838" s="54" t="n">
+        <v>1.6579</v>
+      </c>
+      <c r="L838" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M838" t="inlineStr"/>
+      <c r="N838" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B839" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C839" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D839" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E839" s="12" t="n">
+        <v>6799.9</v>
+      </c>
+      <c r="F839" s="12" t="n">
+        <v>7004.56</v>
+      </c>
+      <c r="G839" s="12" t="n">
+        <v>204.66</v>
+      </c>
+      <c r="H839" s="13" t="n">
+        <v>0.03009750143384462</v>
+      </c>
+      <c r="I839" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J839" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K839" s="54" t="n">
+        <v>204.66</v>
+      </c>
+      <c r="L839" s="55" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="M839" t="inlineStr"/>
+      <c r="N839" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B840" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C840" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D840" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E840" s="8" t="n">
+        <v>48.2899</v>
+      </c>
+      <c r="F840" s="8" t="n">
+        <v>48.5078</v>
+      </c>
+      <c r="G840" s="8" t="n">
+        <v>0.2179</v>
+      </c>
+      <c r="H840" s="9" t="n">
+        <v>0.004512330735826746</v>
+      </c>
+      <c r="I840" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J840" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K840" s="54" t="n">
+        <v>0.2179</v>
+      </c>
+      <c r="L840" s="55" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="M840" t="inlineStr"/>
+      <c r="N840" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B841" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C841" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D841" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E841" s="10" t="n">
+        <v>56.0218</v>
+      </c>
+      <c r="F841" s="10" t="n">
+        <v>56.3592</v>
+      </c>
+      <c r="G841" s="10" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="H841" s="11" t="n">
+        <v>0.006022655466264918</v>
+      </c>
+      <c r="I841" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J841" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K841" s="54" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="L841" s="55" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M841" t="inlineStr"/>
+      <c r="N841" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B842" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C842" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D842" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E842" s="12" t="n">
+        <v>6919.66</v>
+      </c>
+      <c r="F842" s="12" t="n">
+        <v>7127.25</v>
+      </c>
+      <c r="G842" s="12" t="n">
+        <v>207.59</v>
+      </c>
+      <c r="H842" s="13" t="n">
+        <v>0.0300000289031542</v>
+      </c>
+      <c r="I842" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J842" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K842" s="54" t="n">
+        <v>207.59</v>
+      </c>
+      <c r="L842" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M842" t="inlineStr"/>
+      <c r="N842" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B843" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C843" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D843" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E843" s="8" t="n">
+        <v>47.8576</v>
+      </c>
+      <c r="F843" s="8" t="n">
+        <v>48.6678</v>
+      </c>
+      <c r="G843" s="8" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="H843" s="9" t="n">
+        <v>0.01692939052522483</v>
+      </c>
+      <c r="I843" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J843" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K843" s="54" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="L843" s="55" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M843" t="inlineStr"/>
+      <c r="N843" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B844" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C844" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D844" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E844" s="10" t="n">
+        <v>55.6424</v>
+      </c>
+      <c r="F844" s="10" t="n">
+        <v>56.5036</v>
+      </c>
+      <c r="G844" s="10" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="H844" s="11" t="n">
+        <v>0.01547740571937947</v>
+      </c>
+      <c r="I844" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J844" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K844" s="54" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="L844" s="55" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="M844" t="inlineStr"/>
+      <c r="N844" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B845" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C845" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D845" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E845" s="12" t="n">
+        <v>6834.06</v>
+      </c>
+      <c r="F845" s="12" t="n">
+        <v>7031.93</v>
+      </c>
+      <c r="G845" s="12" t="n">
+        <v>197.87</v>
+      </c>
+      <c r="H845" s="13" t="n">
+        <v>0.02895350640761129</v>
+      </c>
+      <c r="I845" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J845" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K845" s="54" t="n">
+        <v>197.87</v>
+      </c>
+      <c r="L845" s="55" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M845" t="inlineStr"/>
+      <c r="N845" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B846" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C846" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D846" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E846" s="8" t="n">
+        <v>48.1706</v>
+      </c>
+      <c r="F846" s="8" t="n">
+        <v>48.3738</v>
+      </c>
+      <c r="G846" s="8" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="H846" s="9" t="n">
+        <v>0.004218340647614936</v>
+      </c>
+      <c r="I846" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J846" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K846" s="54" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="L846" s="55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M846" t="inlineStr"/>
+      <c r="N846" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B847" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C847" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D847" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E847" s="10" t="n">
+        <v>55.9582</v>
+      </c>
+      <c r="F847" s="10" t="n">
+        <v>56.1837</v>
+      </c>
+      <c r="G847" s="10" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="H847" s="11" t="n">
+        <v>0.004029793667416036</v>
+      </c>
+      <c r="I847" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J847" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K847" s="54" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="L847" s="55" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M847" t="inlineStr"/>
+      <c r="N847" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B848" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C848" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D848" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E848" s="12" t="n">
+        <v>6873.88</v>
+      </c>
+      <c r="F848" s="12" t="n">
+        <v>6929.09</v>
+      </c>
+      <c r="G848" s="12" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="H848" s="13" t="n">
+        <v>0.008031853916565317</v>
+      </c>
+      <c r="I848" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J848" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K848" s="54" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="L848" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M848" t="inlineStr"/>
+      <c r="N848" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B849" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C849" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D849" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E849" s="8" t="n">
+        <v>47.9393</v>
+      </c>
+      <c r="F849" s="8" t="n">
+        <v>48.9003</v>
+      </c>
+      <c r="G849" s="8" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="H849" s="9" t="n">
+        <v>0.02004618340276141</v>
+      </c>
+      <c r="I849" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J849" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K849" s="54" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="L849" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M849" t="inlineStr"/>
+      <c r="N849" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B850" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C850" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D850" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E850" s="10" t="n">
+        <v>55.6319</v>
+      </c>
+      <c r="F850" s="10" t="n">
+        <v>56.8134</v>
+      </c>
+      <c r="G850" s="10" t="n">
+        <v>1.1815</v>
+      </c>
+      <c r="H850" s="11" t="n">
+        <v>0.02123781499463438</v>
+      </c>
+      <c r="I850" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J850" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K850" s="54" t="n">
+        <v>1.1815</v>
+      </c>
+      <c r="L850" s="55" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="M850" t="inlineStr"/>
+      <c r="N850" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B851" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C851" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D851" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E851" s="12" t="n">
+        <v>6840.72</v>
+      </c>
+      <c r="F851" s="12" t="n">
+        <v>6985.32</v>
+      </c>
+      <c r="G851" s="12" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="H851" s="13" t="n">
+        <v>0.0211381258113181</v>
+      </c>
+      <c r="I851" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J851" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K851" s="54" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="L851" s="55" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="M851" t="inlineStr"/>
+      <c r="N851" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B852" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C852" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D852" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E852" s="8" t="n">
+        <v>48.278</v>
+      </c>
+      <c r="F852" s="8" t="n">
+        <v>48.318</v>
+      </c>
+      <c r="G852" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H852" s="9" t="n">
+        <v>0.0008285347363188202</v>
+      </c>
+      <c r="I852" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J852" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K852" s="54" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L852" s="55" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="M852" t="inlineStr"/>
+      <c r="N852" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B853" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C853" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D853" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E853" s="10" t="n">
+        <v>55.954</v>
+      </c>
+      <c r="F853" s="10" t="n">
+        <v>56.068</v>
+      </c>
+      <c r="G853" s="10" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="H853" s="11" t="n">
+        <v>0.002037387854308897</v>
+      </c>
+      <c r="I853" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J853" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K853" s="54" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="L853" s="55" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M853" t="inlineStr"/>
+      <c r="N853" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B854" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C854" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D854" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E854" s="8" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="F854" s="8" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="G854" s="8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H854" s="9" t="n">
+        <v>0.01907356948228883</v>
+      </c>
+      <c r="I854" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J854" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K854" s="54" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L854" s="55" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="M854" t="inlineStr"/>
+      <c r="N854" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B855" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C855" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D855" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E855" s="10" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="F855" s="10" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="G855" s="10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H855" s="11" t="n">
+        <v>0.01857864357864358</v>
+      </c>
+      <c r="I855" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J855" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K855" s="54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L855" s="55" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="M855" t="inlineStr"/>
+      <c r="N855" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B856" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C856" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D856" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E856" s="12" t="n">
+        <v>6813.67</v>
+      </c>
+      <c r="F856" s="12" t="n">
+        <v>7004.42</v>
+      </c>
+      <c r="G856" s="12" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="H856" s="13" t="n">
+        <v>0.02799519201839831</v>
+      </c>
+      <c r="I856" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J856" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K856" s="54" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="L856" s="55" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="M856" t="inlineStr"/>
+      <c r="N856" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B857" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C857" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D857" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E857" s="8" t="n">
+        <v>47.9067</v>
+      </c>
+      <c r="F857" s="8" t="n">
+        <v>48.8759</v>
+      </c>
+      <c r="G857" s="8" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="H857" s="9" t="n">
+        <v>0.02023099065475184</v>
+      </c>
+      <c r="I857" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J857" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K857" s="54" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="L857" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M857" t="inlineStr"/>
+      <c r="N857" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B858" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C858" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D858" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E858" s="10" t="n">
+        <v>55.6468</v>
+      </c>
+      <c r="F858" s="10" t="n">
+        <v>56.7726</v>
+      </c>
+      <c r="G858" s="10" t="n">
+        <v>1.1258</v>
+      </c>
+      <c r="H858" s="11" t="n">
+        <v>0.0202311723225774</v>
+      </c>
+      <c r="I858" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J858" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K858" s="54" t="n">
+        <v>1.1258</v>
+      </c>
+      <c r="L858" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M858" t="inlineStr"/>
+      <c r="N858" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B859" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C859" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D859" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E859" s="12" t="n">
+        <v>6898.05</v>
+      </c>
+      <c r="F859" s="12" t="n">
+        <v>7037.33</v>
+      </c>
+      <c r="G859" s="12" t="n">
+        <v>139.28</v>
+      </c>
+      <c r="H859" s="13" t="n">
+        <v>0.02019121345887606</v>
+      </c>
+      <c r="I859" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J859" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K859" s="54" t="n">
+        <v>139.28</v>
+      </c>
+      <c r="L859" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M859" t="inlineStr"/>
+      <c r="N859" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B860" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C860" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D860" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E860" s="8" t="n">
+        <v>47.9546</v>
+      </c>
+      <c r="F860" s="8" t="n">
+        <v>48.6071</v>
+      </c>
+      <c r="G860" s="8" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="H860" s="9" t="n">
+        <v>0.01360661959436634</v>
+      </c>
+      <c r="I860" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J860" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K860" s="54" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="L860" s="55" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="M860" t="inlineStr"/>
+      <c r="N860" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B861" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C861" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D861" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E861" s="10" t="n">
+        <v>55.6479</v>
+      </c>
+      <c r="F861" s="10" t="n">
+        <v>56.4614</v>
+      </c>
+      <c r="G861" s="10" t="n">
+        <v>0.8135</v>
+      </c>
+      <c r="H861" s="11" t="n">
+        <v>0.01461870079553766</v>
+      </c>
+      <c r="I861" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J861" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K861" s="54" t="n">
+        <v>0.8135</v>
+      </c>
+      <c r="L861" s="55" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="M861" t="inlineStr"/>
+      <c r="N861" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B862" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C862" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D862" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E862" s="12" t="n">
+        <v>6859.57</v>
+      </c>
+      <c r="F862" s="12" t="n">
+        <v>6998.07</v>
+      </c>
+      <c r="G862" s="12" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="H862" s="13" t="n">
+        <v>0.02019076997537747</v>
+      </c>
+      <c r="I862" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J862" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K862" s="54" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="L862" s="55" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="M862" t="inlineStr"/>
+      <c r="N862" s="6" t="n">
+        <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B863" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C863" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D863" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E863" s="8" t="n">
+        <v>47.9117</v>
+      </c>
+      <c r="F863" s="8" t="n">
+        <v>48.9114</v>
+      </c>
+      <c r="G863" s="8" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H863" s="9" t="n">
+        <v>0.02086546709885059</v>
+      </c>
+      <c r="I863" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J863" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K863" s="54" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="L863" s="55" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M863" t="inlineStr"/>
+      <c r="N863" s="6" t="n">
+        <v>0.5605324074074074</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B864" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C864" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D864" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E864" s="10" t="n">
+        <v>55.6275</v>
+      </c>
+      <c r="F864" s="10" t="n">
+        <v>56.8438</v>
+      </c>
+      <c r="G864" s="10" t="n">
+        <v>1.2163</v>
+      </c>
+      <c r="H864" s="11" t="n">
+        <v>0.0218650847152937</v>
+      </c>
+      <c r="I864" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J864" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K864" s="54" t="n">
+        <v>1.2163</v>
+      </c>
+      <c r="L864" s="55" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="M864" t="inlineStr"/>
+      <c r="N864" s="6" t="n">
+        <v>0.5607523148148148</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B865" s="6" t="n">
+        <v>0.5602777777777778</v>
+      </c>
+      <c r="C865" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D865" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E865" s="12" t="n">
+        <v>6880.35</v>
+      </c>
+      <c r="F865" s="12" t="n">
+        <v>7098.77</v>
+      </c>
+      <c r="G865" s="12" t="n">
+        <v>218.42</v>
+      </c>
+      <c r="H865" s="13" t="n">
+        <v>0.03174547806434266</v>
+      </c>
+      <c r="I865" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J865" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K865" s="54" t="n">
+        <v>218.43</v>
+      </c>
+      <c r="L865" s="55" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="M865" t="inlineStr"/>
+      <c r="N865" s="6" t="n">
+        <v>0.5609375</v>
       </c>
     </row>
   </sheetData>
@@ -47730,10 +53310,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J755" r:id="rId754"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J756" r:id="rId755"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J757" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J758" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J759" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J760" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J761" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J762" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J763" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J764" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J765" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J766" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J767" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J768" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J769" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J770" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J771" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J772" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J773" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J774" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J775" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J776" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J777" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J778" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J779" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J780" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J781" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J782" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J783" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J784" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J785" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J786" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J787" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J788" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J789" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J790" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J791" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J792" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J793" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J794" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J795" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J796" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J797" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J798" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J799" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J800" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J801" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J802" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J803" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J804" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J805" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J806" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J807" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J808" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J809" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J810" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J811" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J812" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J813" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J814" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J815" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J816" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J817" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J818" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J819" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J820" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J821" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J822" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J823" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J824" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J825" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J826" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J827" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J828" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J829" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J830" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J831" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J832" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J833" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J834" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J835" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J836" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J837" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J838" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J839" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J840" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J841" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J842" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J843" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J844" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J845" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J846" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J847" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J848" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J849" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J850" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J851" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J852" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J853" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J854" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J855" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J856" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J857" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J858" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J859" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J860" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J861" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J862" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J863" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J864" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J865" r:id="rId864"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId757"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId865"/>
   </tableParts>
 </worksheet>
 </file>
@@ -47807,7 +53495,7 @@
       </c>
       <c r="B4" s="62" t="n"/>
       <c r="C4" s="63" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D4" s="62" t="n"/>
       <c r="F4" s="1" t="inlineStr">
@@ -47874,7 +53562,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.5790393518518518</v>
+        <v>0.5602777777777778</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -47905,7 +53593,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.01886001676445935</v>
+        <v>0.01907356948228883</v>
       </c>
       <c r="O5" s="71" t="inlineStr">
         <is>
@@ -47913,7 +53601,7 @@
         </is>
       </c>
       <c r="P5" s="72" t="n">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
       <c r="Q5" s="72" t="n">
         <v>48.62</v>
@@ -47958,7 +53646,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.01842485549132948</v>
+        <v>0.01857864357864358</v>
       </c>
       <c r="O6" s="71" t="inlineStr">
         <is>
@@ -47966,10 +53654,10 @@
         </is>
       </c>
       <c r="P6" s="72" t="n">
-        <v>55.36</v>
+        <v>55.44</v>
       </c>
       <c r="Q6" s="72" t="n">
-        <v>56.38</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="7">
@@ -48011,7 +53699,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019112818516369</v>
+        <v>0.02019121345887606</v>
       </c>
       <c r="O7" s="77" t="inlineStr">
         <is>
@@ -48019,10 +53707,10 @@
         </is>
       </c>
       <c r="P7" s="72" t="n">
-        <v>6806.95</v>
+        <v>6898.05</v>
       </c>
       <c r="Q7" s="72" t="n">
-        <v>6944.39</v>
+        <v>7037.33</v>
       </c>
     </row>
     <row r="8">
@@ -48099,13 +53787,13 @@
         </is>
       </c>
       <c r="H10" s="66" t="n">
-        <v>0.02844860558628776</v>
+        <v>0.02844650727811221</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>0.02845282527677321</v>
+        <v>0.02844673332410395</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>0.03694211641961482</v>
+        <v>0.03694183282830633</v>
       </c>
     </row>
     <row r="11">
@@ -48120,13 +53808,13 @@
         </is>
       </c>
       <c r="H11" s="66" t="n">
-        <v>0.02842065661994164</v>
+        <v>0.02841716740814283</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>0.02845076126263018</v>
+        <v>0.02846176873157642</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>0.03613507814746245</v>
+        <v>0.03612757126674167</v>
       </c>
     </row>
     <row r="12">
@@ -48141,13 +53829,13 @@
         </is>
       </c>
       <c r="H12" s="66" t="n">
-        <v>0.02035049948431565</v>
+        <v>0.02003126698380895</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>0.01978649362414892</v>
+        <v>0.01948453111277258</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>0.02970877663752912</v>
+        <v>0.02928038048274641</v>
       </c>
     </row>
     <row r="13">
@@ -48162,13 +53850,13 @@
         </is>
       </c>
       <c r="H13" s="66" t="n">
-        <v>0.02023037507033105</v>
+        <v>0.02023052896643625</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>0.02023067952234644</v>
+        <v>0.02023080272240418</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>0.02019167096222166</v>
+        <v>0.02019155658638526</v>
       </c>
     </row>
     <row r="14">
@@ -48183,13 +53871,13 @@
         </is>
       </c>
       <c r="H14" s="66" t="n">
-        <v>0.0242208653485421</v>
+        <v>0.02423904350681942</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>0.02439335957551413</v>
+        <v>0.02441258157484386</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>0.02742606341656465</v>
+        <v>0.02742482687083892</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1"/>
@@ -48395,7 +54083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48719,49 +54407,49 @@
         </is>
       </c>
       <c r="U3" s="55" t="n">
-        <v>0.02844860558628776</v>
+        <v>0.02844650727811221</v>
       </c>
       <c r="V3" s="55" t="n">
-        <v>0.02842065661994164</v>
+        <v>0.02841716740814283</v>
       </c>
       <c r="W3" s="55" t="n">
-        <v>0.02035049948431565</v>
+        <v>0.02003126698380895</v>
       </c>
       <c r="X3" s="55" t="n">
-        <v>0.02023037507033105</v>
+        <v>0.02023052896643625</v>
       </c>
       <c r="Y3" s="55" t="n">
-        <v>0.0242208653485421</v>
+        <v>0.02423904350681942</v>
       </c>
       <c r="Z3" s="55" t="n">
-        <v>0.02845282527677321</v>
+        <v>0.02844673332410395</v>
       </c>
       <c r="AA3" s="55" t="n">
-        <v>0.02845076126263018</v>
+        <v>0.02846176873157642</v>
       </c>
       <c r="AB3" s="55" t="n">
-        <v>0.01978649362414892</v>
+        <v>0.01948453111277258</v>
       </c>
       <c r="AC3" s="55" t="n">
-        <v>0.02023067952234644</v>
+        <v>0.02023080272240418</v>
       </c>
       <c r="AD3" s="55" t="n">
-        <v>0.02439335957551413</v>
+        <v>0.02441258157484386</v>
       </c>
       <c r="AE3" s="55" t="n">
-        <v>0.03694211641961482</v>
+        <v>0.03694183282830633</v>
       </c>
       <c r="AF3" s="55" t="n">
-        <v>0.03613507814746245</v>
+        <v>0.03612757126674167</v>
       </c>
       <c r="AG3" s="55" t="n">
-        <v>0.02970877663752912</v>
+        <v>0.02928038048274641</v>
       </c>
       <c r="AH3" s="55" t="n">
-        <v>0.02019167096222166</v>
+        <v>0.02019155658638526</v>
       </c>
       <c r="AI3" s="55" t="n">
-        <v>0.02742606341656465</v>
+        <v>0.02742482687083892</v>
       </c>
     </row>
     <row r="4">
@@ -49022,6 +54710,58 @@
       </c>
       <c r="P8" s="55" t="n">
         <v>0.02741964100895999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>04.09</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="n">
+        <v>0.02844021235358557</v>
+      </c>
+      <c r="C9" s="55" t="n">
+        <v>0.0284066997727464</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>0.01907356948228883</v>
+      </c>
+      <c r="E9" s="55" t="n">
+        <v>0.02023099065475184</v>
+      </c>
+      <c r="F9" s="55" t="n">
+        <v>0.02429357798165137</v>
+      </c>
+      <c r="G9" s="55" t="n">
+        <v>0.02842845746609617</v>
+      </c>
+      <c r="H9" s="55" t="n">
+        <v>0.02849479113841517</v>
+      </c>
+      <c r="I9" s="55" t="n">
+        <v>0.01857864357864358</v>
+      </c>
+      <c r="J9" s="55" t="n">
+        <v>0.0202311723225774</v>
+      </c>
+      <c r="K9" s="55" t="n">
+        <v>0.02447024757283306</v>
+      </c>
+      <c r="L9" s="55" t="n">
+        <v>0.03694098205438084</v>
+      </c>
+      <c r="M9" s="55" t="n">
+        <v>0.03610505062457936</v>
+      </c>
+      <c r="N9" s="55" t="n">
+        <v>0.02799519201839831</v>
+      </c>
+      <c r="O9" s="55" t="n">
+        <v>0.02019121345887606</v>
+      </c>
+      <c r="P9" s="55" t="n">
+        <v>0.02742111723366172</v>
       </c>
     </row>
   </sheetData>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -431,13 +431,13 @@
     <xf numFmtId="10" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -578,9 +578,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -604,16 +604,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$9</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -637,6 +640,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02844021235358557</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.0424043252411746</v>
                 </pt>
               </numCache>
             </numRef>
@@ -682,9 +688,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -708,16 +714,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$9</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -741,6 +750,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.0284066997727464</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05750676236927861</v>
                 </pt>
               </numCache>
             </numRef>
@@ -786,9 +798,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -812,16 +824,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$9</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -845,6 +860,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.01907356948228883</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05368555602897316</v>
                 </pt>
               </numCache>
             </numRef>
@@ -890,9 +908,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -916,16 +934,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$9</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -949,6 +970,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02023099065475184</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.06087775948403126</v>
                 </pt>
               </numCache>
             </numRef>
@@ -994,9 +1018,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1020,16 +1044,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$9</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -1053,6 +1080,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02429357798165137</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05549132947976879</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1173,9 +1203,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1199,16 +1229,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$9</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -1232,6 +1265,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.0284066997727464</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05750676236927861</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1372,9 +1408,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1398,16 +1434,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$9</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -1431,6 +1470,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02849479113841517</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05769008566853923</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1571,9 +1613,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1597,16 +1639,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$9</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -1630,6 +1675,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.03610505062457936</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.08487844217912797</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1770,9 +1818,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1796,16 +1844,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$9</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -1829,6 +1880,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.01907356948228883</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05368555602897316</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1969,9 +2023,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1995,16 +2049,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$9</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -2028,6 +2085,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.01857864357864358</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.04793267471642883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2168,9 +2228,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2194,16 +2254,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$9</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -2227,6 +2290,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02799519201839831</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.07654264112083684</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2367,9 +2433,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2393,16 +2459,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$9</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -2426,6 +2495,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02023099065475184</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.06087775948403126</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2566,9 +2638,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2592,16 +2664,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$9</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -2625,6 +2700,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.0202311723225774</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.06087692369686823</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2765,9 +2843,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2791,16 +2869,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$9</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -2824,6 +2905,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02019121345887606</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.1446893533156403</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2964,9 +3048,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2990,16 +3074,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$9</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -3023,6 +3110,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02429357798165137</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05549132947976879</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3071,8 +3161,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06165859703981922"/>
-          <min val="0.01797489899804002"/>
+          <max val="0.06174650991777799"/>
+          <min val="0.01796024685171356"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -3163,9 +3253,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3189,16 +3279,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$9</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -3222,6 +3315,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02842845746609617</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.04240089111261253</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3267,9 +3363,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3293,16 +3389,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$9</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -3326,6 +3425,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02849479113841517</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05769008566853923</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3371,9 +3473,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3397,16 +3499,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$9</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -3430,6 +3535,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.01857864357864358</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.04793267471642883</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3475,9 +3583,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3501,16 +3609,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$9</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -3534,6 +3645,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.0202311723225774</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.06087692369686823</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3579,9 +3693,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3605,16 +3719,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$9</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3638,6 +3755,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02447024757283306</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05558275394670983</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3758,9 +3878,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3784,16 +3904,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$9</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3817,6 +3940,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02447024757283306</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.05558275394670983</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3957,9 +4083,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3983,16 +4109,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$9</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4016,6 +4145,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02742111723366172</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.1264648641618631</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4064,8 +4196,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1462736542993439"/>
-          <min val="0.007610638793896007"/>
+          <max val="0.1462739087924438"/>
+          <min val="0.00761059637837936"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -4156,9 +4288,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4182,16 +4314,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$9</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -4215,6 +4350,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.03694098205438084</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.07067334027581308</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4260,9 +4398,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4286,16 +4424,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$9</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -4319,6 +4460,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.03610505062457936</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.08487844217912797</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4364,9 +4508,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4390,16 +4534,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$9</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -4423,6 +4570,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02799519201839831</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.07654264112083684</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4468,9 +4618,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4494,16 +4644,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$9</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -4527,6 +4680,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02019121345887606</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.1446893533156403</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4572,9 +4728,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4598,16 +4754,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$9</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4631,6 +4790,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02742111723366172</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.1264648641618631</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4773,7 +4935,7 @@
                   <v>0.03553378696044311</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02844650727811221</v>
+                  <v>0.03123807087072469</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4841,7 +5003,7 @@
                   <v>0.04311562150687483</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02841716740814283</v>
+                  <v>0.03423508640036999</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4909,7 +5071,7 @@
                   <v>0.03847709584999994</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02003126698380895</v>
+                  <v>0.02676212479284179</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4977,7 +5139,7 @@
                   <v>0.04104187506584386</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023052896643625</v>
+                  <v>0.02835997506995525</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5045,7 +5207,7 @@
                   <v>0.04760750668842017</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02423904350681942</v>
+                  <v>0.03048950070140929</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5086,8 +5248,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05174394264411185"/>
-          <min val="0.01589483102811727"/>
+          <max val="0.05073431397275693"/>
+          <min val="0.02363531750850503"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5188,7 +5350,7 @@
                   <v>0.03553642841103422</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02844673332410395</v>
+                  <v>0.03123756488180567</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5256,7 +5418,7 @@
                   <v>0.0432699268677014</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02846176873157642</v>
+                  <v>0.03430743211896899</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5324,7 +5486,7 @@
                   <v>0.03535742466332828</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.01948453111277258</v>
+                  <v>0.02517415983350383</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5392,7 +5554,7 @@
                   <v>0.0514487601107881</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02023080272240418</v>
+                  <v>0.02836002691729699</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5460,7 +5622,7 @@
                   <v>0.04783493387226885</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02441258157484386</v>
+                  <v>0.03064661604921706</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5501,8 +5663,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05624339446049043"/>
-          <min val="0.01468989676307026"/>
+          <max val="0.05538995015238074"/>
+          <min val="0.02123296979191119"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5603,7 +5765,7 @@
                   <v>0.05383117747984287</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03694183282830633</v>
+                  <v>0.04368813431780767</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5671,7 +5833,7 @@
                   <v>0.06066925394146307</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03612757126674167</v>
+                  <v>0.04587774544921894</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5739,7 +5901,7 @@
                   <v>0.0540849048600331</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02928038048274641</v>
+                  <v>0.0387328326103645</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5807,7 +5969,7 @@
                   <v>0.08301204597474589</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02019155658638526</v>
+                  <v>0.04509111593223626</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5875,7 +6037,7 @@
                   <v>0.1017248276143379</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02742482687083892</v>
+                  <v>0.04723283432904377</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5916,8 +6078,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1139548182685308"/>
-          <min val="0.007961565932192357"/>
+          <max val="0.111173626864934"/>
+          <min val="0.02928403335976848"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5996,9 +6158,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6022,16 +6184,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$9</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -6055,6 +6220,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02844021235358557</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.0424043252411746</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6195,9 +6363,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6221,16 +6389,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$9</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -6254,6 +6425,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.02842845746609617</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.04240089111261253</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6394,9 +6568,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$9</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
               <strCache>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6420,16 +6594,19 @@
                 </pt>
                 <pt idx="7">
                   <v>04.09</v>
+                </pt>
+                <pt idx="8">
+                  <v>🔵 05.09 Cmt</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$9</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$10</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="8"/>
+                <ptCount val="9"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -6453,6 +6630,9 @@
                 </pt>
                 <pt idx="7">
                   <v>0.03694098205438084</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.07067334027581308</v>
                 </pt>
               </numCache>
             </numRef>
@@ -7025,8 +7205,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N865" headerRowCount="1">
-  <autoFilter ref="A1:N865"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N973" headerRowCount="1">
+  <autoFilter ref="A1:N973"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tarih"/>
     <tableColumn id="2" name="Saat"/>
@@ -7435,10 +7615,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7446,48 +7626,48 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>47.524</v>
+        <v>46.951</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>48.874</v>
+        <v>49.651</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.0284066997727464</v>
+        <v>0.05750676236927861</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>55.2136</v>
+        <v>54.5241</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56.7869</v>
+        <v>57.6696</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1.5733</v>
+        <v>3.1455</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>0.02849479113841517</v>
+        <v>0.05769008566853923</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>6760.55</v>
+        <v>6720.67</v>
       </c>
       <c r="M2" s="12" t="n">
-        <v>7004.64</v>
+        <v>7291.11</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>244.09</v>
+        <v>570.4400000000001</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0.03610505062457936</v>
+        <v>0.08487844217912797</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7495,48 +7675,48 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>48.042</v>
+        <v>47.98</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>48.823</v>
+        <v>48.963</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.781</v>
+        <v>0.983</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.01625660880063278</v>
+        <v>0.0204877032096707</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>55.815</v>
+        <v>55.719</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>56.728</v>
+        <v>56.866</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.913</v>
+        <v>1.147</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.01635760996147989</v>
+        <v>0.02058543764245589</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>6853.46</v>
+        <v>6783.95</v>
       </c>
       <c r="M3" s="12" t="n">
-        <v>6993.59</v>
+        <v>6952.63</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>140.13</v>
+        <v>168.68</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.02044660653159134</v>
+        <v>0.02486457005137125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7544,48 +7724,48 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>48.23</v>
+        <v>46.299</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>48.515</v>
+        <v>50.301</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.285</v>
+        <v>4.002</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.005909185154468173</v>
+        <v>0.08643815201192251</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>55.861</v>
+        <v>53.617</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56.377</v>
+        <v>58.434</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.516</v>
+        <v>4.817</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.00923721379853565</v>
+        <v>0.08984090866702726</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>6920.63</v>
+        <v>6582.3</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>6990.46</v>
+        <v>7179.59</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>69.83</v>
+        <v>597.29</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.01009012185306829</v>
+        <v>0.0907418379593759</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7593,48 +7773,48 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>48.27</v>
+        <v>48.258</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>48.48</v>
+        <v>48.542</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.21</v>
+        <v>0.284</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.00435052827843381</v>
+        <v>0.005885034605661238</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>55.94</v>
+        <v>55.893</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>56.324</v>
+        <v>56.374</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.384</v>
+        <v>0.481</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.006864497676081516</v>
+        <v>0.008605728803249064</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>6842.63</v>
+        <v>6784.36</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>7015</v>
+        <v>6970</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>172.37</v>
+        <v>185.64</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.02519060653579107</v>
+        <v>0.02736293474992483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7642,48 +7822,48 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47.465</v>
+        <v>47.7626</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>48.7411</v>
+        <v>48.8155</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.2761</v>
+        <v>1.0529</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.0268850732118403</v>
+        <v>0.02204444481665571</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>55.2416</v>
+        <v>54.8361</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56.6119</v>
+        <v>57.2538</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1.3703</v>
+        <v>2.4177</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.02480558130104848</v>
+        <v>0.04408956873300617</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>6819.63</v>
+        <v>6242.42</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>6975.89</v>
+        <v>7453.4</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>156.26</v>
+        <v>1210.98</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.02291326655551694</v>
+        <v>0.1939920735868461</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7691,48 +7871,48 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>47.317</v>
+        <v>46.231</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>49.24</v>
+        <v>50.376</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.923</v>
+        <v>4.145</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.0406407844960585</v>
+        <v>0.08965845428392205</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>54.968</v>
+        <v>53.67</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>57.211</v>
+        <v>58.481</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.243</v>
+        <v>4.811</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.04080555959831175</v>
+        <v>0.08964039500652132</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>6821.76</v>
+        <v>5902.36</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>7016.15</v>
+        <v>7899.21</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>194.39</v>
+        <v>1996.85</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.02849557885355099</v>
+        <v>0.3383138270115683</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7740,48 +7920,48 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>47.5756</v>
+        <v>46.8549</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>48.9757</v>
+        <v>49.655</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1.4001</v>
+        <v>2.8001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02942895097486947</v>
+        <v>0.05976109222301189</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>55.2594</v>
+        <v>54.3943</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56.8905</v>
+        <v>57.6499</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1.6311</v>
+        <v>3.2556</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.02951715002334444</v>
+        <v>0.05985185947792324</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6834.26</v>
+        <v>6668.77</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>7036.42</v>
+        <v>7068.95</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>202.16</v>
+        <v>400.18</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.02958037885594051</v>
+        <v>0.06000806745471803</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -7789,48 +7969,48 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>48.2258</v>
+        <v>48.0852</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>48.301</v>
+        <v>48.4354</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0752</v>
+        <v>0.3502</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.001559331312285125</v>
+        <v>0.007282906174872934</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>56.0082</v>
+        <v>55.8259</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>56.1124</v>
+        <v>56.2539</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.1042</v>
+        <v>0.428</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.001860441863869933</v>
+        <v>0.00766669234172669</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>6885.98</v>
+        <v>6805.05</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>6917.66</v>
+        <v>6876.24</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>31.68</v>
+        <v>71.19</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.004600652339971943</v>
+        <v>0.0104613485573214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -7838,48 +8018,48 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2508</v>
+        <v>48.2699</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.2891</v>
+        <v>48.3494</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0795</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.0007937692224792128</v>
+        <v>0.001646989117441718</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>56.0087</v>
+        <v>55.9826</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>56.1183</v>
+        <v>56.1883</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.1096</v>
+        <v>0.2057</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.001956838848250361</v>
+        <v>0.003674355960602044</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6883.87</v>
+        <v>6825.26</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6916.87</v>
+        <v>6866.18</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>33</v>
+        <v>40.92</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.004793815106909341</v>
+        <v>0.005995376000328193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -7887,48 +8067,48 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.9329</v>
+        <v>47.7364</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.172</v>
+        <v>49.7208</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1.2391</v>
+        <v>1.9844</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02585072048634654</v>
+        <v>0.04156995500289087</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.5946</v>
+        <v>55.3526</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>56.8756</v>
+        <v>57.4906</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1.281</v>
+        <v>2.138</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.02304180621858958</v>
+        <v>0.03862510523444247</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>6858.32</v>
+        <v>5805.25</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6970.45</v>
+        <v>7573.31</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>112.13</v>
+        <v>1768.06</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.01634948500507413</v>
+        <v>0.3045622496877826</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -7936,48 +8116,48 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>47.992</v>
+        <v>47.5925</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>48.842</v>
+        <v>49.2925</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.85</v>
+        <v>1.7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.01771128521420237</v>
+        <v>0.03571991385197248</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>55.6735</v>
+        <v>54.9928</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56.8395</v>
+        <v>57.5346</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.166</v>
+        <v>2.5418</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.0209435368712224</v>
+        <v>0.04622059615076883</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>6850.3</v>
+        <v>6707.38</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>7009.47</v>
+        <v>7104.13</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>159.17</v>
+        <v>396.75</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.02323547873815745</v>
+        <v>0.05915126323542128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -7985,48 +8165,48 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>47.9956</v>
+        <v>46.9293</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>48.6215</v>
+        <v>49.9896</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.6259</v>
+        <v>3.0603</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01304077873805099</v>
+        <v>0.06521085974007709</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>55.7755</v>
+        <v>54.2441</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>56.4604</v>
+        <v>58.4498</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.6849</v>
+        <v>4.2057</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.01227958512250002</v>
+        <v>0.0775328561078532</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6902.96</v>
+        <v>6611.27</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6959.99</v>
+        <v>7337.41</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>57.03</v>
+        <v>726.14</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.008261673253213114</v>
+        <v>0.1098336628212129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -8034,48 +8214,48 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.468</v>
+        <v>47.165</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>48.818</v>
+        <v>49.165</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02844021235358557</v>
+        <v>0.0424043252411746</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>55.156</v>
+        <v>54.763</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56.724</v>
+        <v>57.085</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.568</v>
+        <v>2.322</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.02842845746609617</v>
+        <v>0.04240089111261253</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>6801.66</v>
+        <v>6645.08</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>7052.92</v>
+        <v>7114.71</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>251.26</v>
+        <v>469.63</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.03694098205438084</v>
+        <v>0.07067334027581308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -8083,48 +8263,48 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>47.9956</v>
+        <v>46.9293</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>48.6215</v>
+        <v>49.9896</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.6259</v>
+        <v>3.0603</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.01304077873805099</v>
+        <v>0.06521085974007709</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>55.7712</v>
+        <v>54.2441</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>56.4555</v>
+        <v>58.4498</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.6843</v>
+        <v>4.2057</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.01226977364661331</v>
+        <v>0.0775328561078532</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6904.04</v>
+        <v>6611.27</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6961.05</v>
+        <v>7337.4</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>57.01</v>
+        <v>726.13</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.008257484023846908</v>
+        <v>0.1098321502525234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -8132,48 +8312,48 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>47.8822</v>
+        <v>47.1623</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>48.8623</v>
+        <v>49.8623</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.9801</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02046898429896705</v>
+        <v>0.05724911634928746</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>55.6343</v>
+        <v>54.8025</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56.7731</v>
+        <v>57.9399</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.1388</v>
+        <v>3.1374</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.02046938669130375</v>
+        <v>0.05724921308334473</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6834.7</v>
+        <v>6527.6</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>7044.54</v>
+        <v>7423.1</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>209.84</v>
+        <v>895.5</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.03070215225247633</v>
+        <v>0.1371867148722348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -8181,48 +8361,48 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>48.268</v>
+        <v>48.213</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>48.32</v>
+        <v>48.323</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.052</v>
+        <v>0.11</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.00107731830612414</v>
+        <v>0.002281542322610085</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>55.932</v>
+        <v>55.842</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>56.092</v>
+        <v>56.072</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.002860616462847744</v>
+        <v>0.004118763654596898</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6867.73</v>
+        <v>6796.95</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6942.05</v>
+        <v>6888.68</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>74.31999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.01082162519493341</v>
+        <v>0.01349575912725561</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8230,48 +8410,48 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>48.2431</v>
+        <v>47.8265</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.4427</v>
+        <v>48.4543</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1996</v>
+        <v>0.6278</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.004137379231434132</v>
+        <v>0.01312661390651626</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>56.057</v>
+        <v>55.6569</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>56.2856</v>
+        <v>56.2918</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.2286</v>
+        <v>0.6349</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.004077992043812548</v>
+        <v>0.01140739063799816</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6914.71</v>
+        <v>6827.31</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6963.51</v>
+        <v>6969.07</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>48.8</v>
+        <v>141.76</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.007057418170827121</v>
+        <v>0.02076366826759002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8287,24 +8467,24 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6878.46</v>
+        <v>6834.76</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>7078.75</v>
+        <v>7034.29</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>200.29</v>
+        <v>199.53</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02911843639419289</v>
+        <v>0.02919341717924257</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8312,48 +8492,48 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.8078</v>
+        <v>47.5517</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>48.7116</v>
+        <v>49.4789</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.9038</v>
+        <v>1.9272</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.01890486489652316</v>
+        <v>0.04052851948510779</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>55.5502</v>
+        <v>54.7851</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56.6247</v>
+        <v>57.9411</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.0745</v>
+        <v>3.156</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.01934286465215247</v>
+        <v>0.05760690406698171</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6807.62</v>
+        <v>6710.16</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7267.06</v>
+        <v>7363.91</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>459.44</v>
+        <v>653.75</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.06748907841507017</v>
+        <v>0.09742688698928192</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8361,48 +8541,48 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>47.7612</v>
+        <v>47.2028</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>48.7674</v>
+        <v>49.4795</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.0062</v>
+        <v>2.2767</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02106730986658627</v>
+        <v>0.04823230825290025</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>55.558</v>
+        <v>54.8911</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>56.5718</v>
+        <v>57.2139</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.0138</v>
+        <v>2.3228</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.01824759710572735</v>
+        <v>0.04231651397038864</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6806.63</v>
+        <v>6662.76</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>7059.58</v>
+        <v>7078.51</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>252.95</v>
+        <v>415.75</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.03716229617299604</v>
+        <v>0.06239906585258961</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8410,48 +8590,48 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47.6875</v>
+        <v>47.1425</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>48.846</v>
+        <v>49.7585</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.1585</v>
+        <v>2.616</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02429357798165137</v>
+        <v>0.05549132947976879</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>55.3938</v>
+        <v>54.7418</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>56.7493</v>
+        <v>57.7845</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.3555</v>
+        <v>3.0427</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.02447024757283306</v>
+        <v>0.05558275394670983</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6827.22</v>
+        <v>6458.79</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>7014.43</v>
+        <v>7275.6</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>187.21</v>
+        <v>816.8099999999999</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.02742111723366172</v>
+        <v>0.1264648641618631</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8459,48 +8639,48 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>48.29</v>
+        <v>48.25</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>48.3</v>
+        <v>48.26</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.0002070822116380203</v>
+        <v>0.0002072538860103627</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>56.05</v>
+        <v>55.95</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.0008928571428571428</v>
+        <v>0.0008944543828264759</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6913.48</v>
+        <v>6818.04</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6919.76</v>
+        <v>6829.15</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6.28</v>
+        <v>11.11</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.0009083703142266992</v>
+        <v>0.001629500560278321</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8508,48 +8688,48 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>47.6242</v>
+        <v>44.8059</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>48.6133</v>
+        <v>49.2963</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.9891</v>
+        <v>4.4904</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.02076885281012594</v>
+        <v>0.1002189443800928</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>55.3388</v>
+        <v>52.017</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>56.4887</v>
+        <v>57.2734</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.1499</v>
+        <v>5.2564</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.02077927240923186</v>
+        <v>0.1010515792913855</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6800.54</v>
+        <v>6430.53</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6980.96</v>
+        <v>7056.75</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>180.42</v>
+        <v>626.22</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.0265302461275134</v>
+        <v>0.09738233084986775</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8557,28 +8737,28 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>48.2238</v>
+        <v>48.2326</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>48.3107</v>
+        <v>48.3195</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>0.08690000000000001</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.00180201477278854</v>
+        <v>0.001801685996608103</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>55.9713</v>
+        <v>56.0571</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>56.0722</v>
+        <v>56.1581</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.1009</v>
+        <v>0.101</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.00180270960295723</v>
+        <v>0.001801734303058845</v>
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
@@ -8587,10 +8767,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8598,48 +8778,48 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>48.2341</v>
+        <v>48.0452</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>48.2987</v>
+        <v>48.482</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.0646</v>
+        <v>0.4368</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.001339301448560251</v>
+        <v>0.009091438895040504</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>56.0351</v>
+        <v>55.9066</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>56.1208</v>
+        <v>56.3121</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.4055</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.001529398537702262</v>
+        <v>0.007253168677758976</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6886.76</v>
+        <v>6796.19</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6915.82</v>
+        <v>6876.58</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>29.06</v>
+        <v>80.39</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.004219691117448554</v>
+        <v>0.01182868636692029</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8647,48 +8827,48 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>48.265</v>
+        <v>48.239</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>48.381</v>
+        <v>48.382</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.116</v>
+        <v>0.143</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.002403397907386305</v>
+        <v>0.002964406393167354</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>55.883</v>
+        <v>55.851</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>56.076</v>
+        <v>56.093</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.193</v>
+        <v>0.242</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.003453644220961652</v>
+        <v>0.004332957332903619</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6883</v>
+        <v>6813</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6940</v>
+        <v>6879</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.008281272700857184</v>
+        <v>0.009687362395420521</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8696,48 +8876,48 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>47.7825</v>
+        <v>47.3765</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>48.7825</v>
+        <v>49.1765</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.02092816407680636</v>
+        <v>0.0379935199940899</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>55.541</v>
+        <v>54.987</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>56.631</v>
+        <v>57.127</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.01962514178714823</v>
+        <v>0.0389182897775838</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6892.6</v>
+        <v>6700.83</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>6992.6</v>
+        <v>7050.83</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.01450831326349999</v>
+        <v>0.05223233539725676</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8753,24 +8933,24 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6878.46</v>
+        <v>6834.75</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>7064.62</v>
+        <v>7020.24</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>186.16</v>
+        <v>185.49</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02706419750932621</v>
+        <v>0.02713925161856688</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8778,48 +8958,48 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>47.657</v>
+        <v>46.9325</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>48.877</v>
+        <v>49.9525</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1.22</v>
+        <v>3.02</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.02559959712109449</v>
+        <v>0.06434773344697171</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>55.2564</v>
+        <v>53.9523</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>56.9143</v>
+        <v>58.6008</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.6579</v>
+        <v>4.6485</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.03000376426984024</v>
+        <v>0.08615944083940814</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6799.9</v>
+        <v>6553.72</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>7004.56</v>
+        <v>7184.14</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>204.66</v>
+        <v>630.42</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.03009750143384462</v>
+        <v>0.09619269666693114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -8827,48 +9007,48 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.2899</v>
+        <v>48.1299</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.5078</v>
+        <v>48.6747</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.2179</v>
+        <v>0.5448</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.004512330735826746</v>
+        <v>0.01131936696315596</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>56.0218</v>
+        <v>55.6847</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.3592</v>
+        <v>56.5284</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3374</v>
+        <v>0.8437</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.006022655466264918</v>
+        <v>0.01515137910413453</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6919.66</v>
+        <v>6864.2</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>7127.25</v>
+        <v>7379.02</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>207.59</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.0300000289031542</v>
+        <v>0.07500072841700417</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -8876,48 +9056,48 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>47.8576</v>
+        <v>47.7911</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>48.6678</v>
+        <v>48.7367</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.8102</v>
+        <v>0.9456</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.01692939052522483</v>
+        <v>0.01978611080305747</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>55.6424</v>
+        <v>55.532</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>56.5036</v>
+        <v>56.5537</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8612</v>
+        <v>1.0217</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.01547740571937947</v>
+        <v>0.01839840092199092</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6834.06</v>
+        <v>6763.3</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>7031.93</v>
+        <v>6980.72</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>197.87</v>
+        <v>217.42</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.02895350640761129</v>
+        <v>0.03214702881729334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -8925,48 +9105,48 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>48.1706</v>
+        <v>47.9608</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>48.3738</v>
+        <v>48.5704</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.2032</v>
+        <v>0.6096</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.004218340647614936</v>
+        <v>0.01271038014378409</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>55.9582</v>
+        <v>55.6608</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>56.1837</v>
+        <v>56.3368</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2255</v>
+        <v>0.676</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.004029793667416036</v>
+        <v>0.01214499252615845</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6873.88</v>
+        <v>6758.27</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6929.09</v>
+        <v>6922.44</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>55.21</v>
+        <v>164.17</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.008031853916565317</v>
+        <v>0.02429171962647246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -8974,48 +9154,48 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>47.9393</v>
+        <v>47.0674</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>48.9003</v>
+        <v>49.8524</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.961</v>
+        <v>2.785</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.02004618340276141</v>
+        <v>0.05917046618253823</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>55.6319</v>
+        <v>54.591</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>56.8134</v>
+        <v>57.749</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.1815</v>
+        <v>3.158</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.02123781499463438</v>
+        <v>0.05784836328332509</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>6840.72</v>
+        <v>6551.45</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6985.32</v>
+        <v>7449.45</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>144.6</v>
+        <v>898</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.0211381258113181</v>
+        <v>0.1370688931457922</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -9023,28 +9203,28 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>48.278</v>
+        <v>48.227</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>48.318</v>
+        <v>48.356</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.04</v>
+        <v>0.129</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.0008285347363188202</v>
+        <v>0.002674850187654218</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>55.954</v>
+        <v>55.871</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>56.068</v>
+        <v>56.107</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.114</v>
+        <v>0.236</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.002037387854308897</v>
+        <v>0.004224016036942242</v>
       </c>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
@@ -9053,10 +9233,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -9064,48 +9244,48 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>47.71</v>
+        <v>46.94</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>48.62</v>
+        <v>49.46</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.91</v>
+        <v>2.52</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.01907356948228883</v>
+        <v>0.05368555602897316</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>55.44</v>
+        <v>54.66</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>56.47</v>
+        <v>57.28</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.01857864357864358</v>
+        <v>0.04793267471642883</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6813.67</v>
+        <v>6642.18</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>7004.42</v>
+        <v>7150.59</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>190.75</v>
+        <v>508.41</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.02799519201839831</v>
+        <v>0.07654264112083684</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -9113,48 +9293,48 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>47.9067</v>
+        <v>47.0106</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>48.8759</v>
+        <v>49.8725</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.9692</v>
+        <v>2.8619</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.02023099065475184</v>
+        <v>0.06087775948403126</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>55.6468</v>
+        <v>54.5954</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>56.7726</v>
+        <v>57.919</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.1258</v>
+        <v>3.3236</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.0202311723225774</v>
+        <v>0.06087692369686823</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6898.05</v>
+        <v>6616.52</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>7037.33</v>
+        <v>7573.86</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>139.28</v>
+        <v>957.34</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.02019121345887606</v>
+        <v>0.1446893533156403</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9162,48 +9342,48 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>47.9546</v>
+        <v>47.0576</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>48.6071</v>
+        <v>49.5982</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.6525</v>
+        <v>2.5406</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.01360661959436634</v>
+        <v>0.05398915371799667</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>55.6479</v>
+        <v>54.5954</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>56.4614</v>
+        <v>57.6004</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8135</v>
+        <v>3.005</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.01461870079553766</v>
+        <v>0.05504126721298864</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6859.57</v>
+        <v>6583.44</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6998.07</v>
+        <v>7535.99</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>138.5</v>
+        <v>952.55</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.02019076997537747</v>
+        <v>0.1446887949157279</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -9211,40 +9391,40 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>47.9117</v>
+        <v>43.1206</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48.9114</v>
+        <v>53.8029</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.9997</v>
+        <v>10.6823</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02086546709885059</v>
+        <v>0.2477307829668418</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>55.6275</v>
+        <v>50.0454</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>56.8438</v>
+        <v>62.5049</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.2163</v>
+        <v>12.4595</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.0218650847152937</v>
+        <v>0.2489639407418064</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6880.35</v>
+        <v>6131.92</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>7098.77</v>
+        <v>7732.64</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>218.42</v>
+        <v>1600.72</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.03174547806434266</v>
+        <v>0.2610471108559799</v>
       </c>
     </row>
   </sheetData>
@@ -9261,7 +9441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N865"/>
+  <dimension ref="A1:N973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52550,6 +52730,5406 @@
       <c r="M865" t="inlineStr"/>
       <c r="N865" s="6" t="n">
         <v>0.5609375</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B866" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C866" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D866" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E866" s="8" t="n">
+        <v>46.951</v>
+      </c>
+      <c r="F866" s="8" t="n">
+        <v>49.651</v>
+      </c>
+      <c r="G866" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H866" s="9" t="n">
+        <v>0.05750676236927861</v>
+      </c>
+      <c r="I866" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J866" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K866" s="54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L866" s="55" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="M866" t="inlineStr"/>
+      <c r="N866" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B867" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C867" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D867" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E867" s="10" t="n">
+        <v>54.5241</v>
+      </c>
+      <c r="F867" s="10" t="n">
+        <v>57.6696</v>
+      </c>
+      <c r="G867" s="10" t="n">
+        <v>3.1455</v>
+      </c>
+      <c r="H867" s="11" t="n">
+        <v>0.05769008566853923</v>
+      </c>
+      <c r="I867" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J867" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K867" s="54" t="n">
+        <v>3.1455</v>
+      </c>
+      <c r="L867" s="55" t="n">
+        <v>0.05769999999999999</v>
+      </c>
+      <c r="M867" t="inlineStr"/>
+      <c r="N867" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B868" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C868" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D868" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E868" s="12" t="n">
+        <v>6720.67</v>
+      </c>
+      <c r="F868" s="12" t="n">
+        <v>7291.11</v>
+      </c>
+      <c r="G868" s="12" t="n">
+        <v>570.4400000000001</v>
+      </c>
+      <c r="H868" s="13" t="n">
+        <v>0.08487844217912797</v>
+      </c>
+      <c r="I868" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J868" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K868" s="54" t="n">
+        <v>570.4299999999999</v>
+      </c>
+      <c r="L868" s="55" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="M868" t="inlineStr"/>
+      <c r="N868" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B869" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C869" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D869" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E869" s="8" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="F869" s="8" t="n">
+        <v>48.963</v>
+      </c>
+      <c r="G869" s="8" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H869" s="9" t="n">
+        <v>0.0204877032096707</v>
+      </c>
+      <c r="I869" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J869" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K869" s="54" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="L869" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M869" t="inlineStr"/>
+      <c r="N869" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B870" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C870" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D870" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E870" s="10" t="n">
+        <v>55.719</v>
+      </c>
+      <c r="F870" s="10" t="n">
+        <v>56.866</v>
+      </c>
+      <c r="G870" s="10" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="H870" s="11" t="n">
+        <v>0.02058543764245589</v>
+      </c>
+      <c r="I870" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J870" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K870" s="54" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L870" s="55" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="M870" t="inlineStr"/>
+      <c r="N870" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B871" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C871" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D871" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E871" s="12" t="n">
+        <v>6783.95</v>
+      </c>
+      <c r="F871" s="12" t="n">
+        <v>6952.63</v>
+      </c>
+      <c r="G871" s="12" t="n">
+        <v>168.68</v>
+      </c>
+      <c r="H871" s="13" t="n">
+        <v>0.02486457005137125</v>
+      </c>
+      <c r="I871" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J871" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K871" s="54" t="n">
+        <v>168.68</v>
+      </c>
+      <c r="L871" s="55" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="M871" t="inlineStr"/>
+      <c r="N871" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B872" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C872" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D872" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E872" s="8" t="n">
+        <v>46.299</v>
+      </c>
+      <c r="F872" s="8" t="n">
+        <v>50.301</v>
+      </c>
+      <c r="G872" s="8" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="H872" s="9" t="n">
+        <v>0.08643815201192251</v>
+      </c>
+      <c r="I872" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J872" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K872" s="54" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="L872" s="55" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="M872" t="inlineStr"/>
+      <c r="N872" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B873" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C873" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D873" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E873" s="10" t="n">
+        <v>53.617</v>
+      </c>
+      <c r="F873" s="10" t="n">
+        <v>58.434</v>
+      </c>
+      <c r="G873" s="10" t="n">
+        <v>4.817</v>
+      </c>
+      <c r="H873" s="11" t="n">
+        <v>0.08984090866702726</v>
+      </c>
+      <c r="I873" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J873" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K873" s="54" t="n">
+        <v>4.817</v>
+      </c>
+      <c r="L873" s="55" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="M873" t="inlineStr"/>
+      <c r="N873" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B874" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C874" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D874" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E874" s="12" t="n">
+        <v>6582.3</v>
+      </c>
+      <c r="F874" s="12" t="n">
+        <v>7179.59</v>
+      </c>
+      <c r="G874" s="12" t="n">
+        <v>597.29</v>
+      </c>
+      <c r="H874" s="13" t="n">
+        <v>0.0907418379593759</v>
+      </c>
+      <c r="I874" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J874" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K874" s="54" t="n">
+        <v>597.29</v>
+      </c>
+      <c r="L874" s="55" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="M874" t="inlineStr"/>
+      <c r="N874" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B875" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C875" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D875" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E875" s="8" t="n">
+        <v>48.258</v>
+      </c>
+      <c r="F875" s="8" t="n">
+        <v>48.542</v>
+      </c>
+      <c r="G875" s="8" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="H875" s="9" t="n">
+        <v>0.005885034605661238</v>
+      </c>
+      <c r="I875" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J875" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K875" s="54" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="L875" s="55" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="M875" t="inlineStr"/>
+      <c r="N875" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B876" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C876" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D876" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E876" s="10" t="n">
+        <v>55.893</v>
+      </c>
+      <c r="F876" s="10" t="n">
+        <v>56.374</v>
+      </c>
+      <c r="G876" s="10" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="H876" s="11" t="n">
+        <v>0.008605728803249064</v>
+      </c>
+      <c r="I876" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J876" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K876" s="54" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L876" s="55" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="M876" t="inlineStr"/>
+      <c r="N876" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B877" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C877" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D877" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E877" s="12" t="n">
+        <v>6784.36</v>
+      </c>
+      <c r="F877" s="12" t="n">
+        <v>6970</v>
+      </c>
+      <c r="G877" s="12" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="H877" s="13" t="n">
+        <v>0.02736293474992483</v>
+      </c>
+      <c r="I877" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J877" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K877" s="54" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="L877" s="55" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="M877" t="inlineStr"/>
+      <c r="N877" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B878" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C878" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D878" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E878" s="8" t="n">
+        <v>47.7626</v>
+      </c>
+      <c r="F878" s="8" t="n">
+        <v>48.8155</v>
+      </c>
+      <c r="G878" s="8" t="n">
+        <v>1.0529</v>
+      </c>
+      <c r="H878" s="9" t="n">
+        <v>0.02204444481665571</v>
+      </c>
+      <c r="I878" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J878" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K878" s="54" t="n">
+        <v>1.0529</v>
+      </c>
+      <c r="L878" s="55" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="M878" t="inlineStr"/>
+      <c r="N878" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B879" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C879" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D879" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E879" s="10" t="n">
+        <v>54.8361</v>
+      </c>
+      <c r="F879" s="10" t="n">
+        <v>57.2538</v>
+      </c>
+      <c r="G879" s="10" t="n">
+        <v>2.4177</v>
+      </c>
+      <c r="H879" s="11" t="n">
+        <v>0.04408956873300617</v>
+      </c>
+      <c r="I879" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J879" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K879" s="54" t="n">
+        <v>2.4177</v>
+      </c>
+      <c r="L879" s="55" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="M879" t="inlineStr"/>
+      <c r="N879" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B880" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C880" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D880" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E880" s="12" t="n">
+        <v>6242.42</v>
+      </c>
+      <c r="F880" s="12" t="n">
+        <v>7453.4</v>
+      </c>
+      <c r="G880" s="12" t="n">
+        <v>1210.98</v>
+      </c>
+      <c r="H880" s="13" t="n">
+        <v>0.1939920735868461</v>
+      </c>
+      <c r="I880" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J880" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K880" s="54" t="n">
+        <v>1210.98</v>
+      </c>
+      <c r="L880" s="55" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="M880" t="inlineStr"/>
+      <c r="N880" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B881" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C881" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D881" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E881" s="8" t="n">
+        <v>46.231</v>
+      </c>
+      <c r="F881" s="8" t="n">
+        <v>50.376</v>
+      </c>
+      <c r="G881" s="8" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="H881" s="9" t="n">
+        <v>0.08965845428392205</v>
+      </c>
+      <c r="I881" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J881" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K881" s="54" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="L881" s="55" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="M881" t="inlineStr"/>
+      <c r="N881" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B882" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C882" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D882" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E882" s="10" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="F882" s="10" t="n">
+        <v>58.481</v>
+      </c>
+      <c r="G882" s="10" t="n">
+        <v>4.811</v>
+      </c>
+      <c r="H882" s="11" t="n">
+        <v>0.08964039500652132</v>
+      </c>
+      <c r="I882" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J882" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K882" s="54" t="n">
+        <v>4.811</v>
+      </c>
+      <c r="L882" s="55" t="n">
+        <v>0.08960000000000001</v>
+      </c>
+      <c r="M882" t="inlineStr"/>
+      <c r="N882" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B883" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C883" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D883" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E883" s="12" t="n">
+        <v>5902.36</v>
+      </c>
+      <c r="F883" s="12" t="n">
+        <v>7899.21</v>
+      </c>
+      <c r="G883" s="12" t="n">
+        <v>1996.85</v>
+      </c>
+      <c r="H883" s="13" t="n">
+        <v>0.3383138270115683</v>
+      </c>
+      <c r="I883" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J883" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K883" s="54" t="n">
+        <v>1996.85</v>
+      </c>
+      <c r="L883" s="55" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="M883" t="inlineStr"/>
+      <c r="N883" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B884" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C884" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D884" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E884" s="8" t="n">
+        <v>46.8549</v>
+      </c>
+      <c r="F884" s="8" t="n">
+        <v>49.655</v>
+      </c>
+      <c r="G884" s="8" t="n">
+        <v>2.8001</v>
+      </c>
+      <c r="H884" s="9" t="n">
+        <v>0.05976109222301189</v>
+      </c>
+      <c r="I884" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J884" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K884" s="54" t="n">
+        <v>2.8001</v>
+      </c>
+      <c r="L884" s="55" t="n">
+        <v>0.05980000000000001</v>
+      </c>
+      <c r="M884" t="inlineStr"/>
+      <c r="N884" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B885" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C885" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D885" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E885" s="10" t="n">
+        <v>54.3943</v>
+      </c>
+      <c r="F885" s="10" t="n">
+        <v>57.6499</v>
+      </c>
+      <c r="G885" s="10" t="n">
+        <v>3.2556</v>
+      </c>
+      <c r="H885" s="11" t="n">
+        <v>0.05985185947792324</v>
+      </c>
+      <c r="I885" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J885" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K885" s="54" t="n">
+        <v>3.2556</v>
+      </c>
+      <c r="L885" s="55" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="M885" t="inlineStr"/>
+      <c r="N885" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B886" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C886" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D886" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E886" s="12" t="n">
+        <v>6668.77</v>
+      </c>
+      <c r="F886" s="12" t="n">
+        <v>7068.95</v>
+      </c>
+      <c r="G886" s="12" t="n">
+        <v>400.18</v>
+      </c>
+      <c r="H886" s="13" t="n">
+        <v>0.06000806745471803</v>
+      </c>
+      <c r="I886" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J886" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K886" s="54" t="n">
+        <v>400.18</v>
+      </c>
+      <c r="L886" s="55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M886" t="inlineStr"/>
+      <c r="N886" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B887" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C887" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D887" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E887" s="8" t="n">
+        <v>48.0852</v>
+      </c>
+      <c r="F887" s="8" t="n">
+        <v>48.4354</v>
+      </c>
+      <c r="G887" s="8" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="H887" s="9" t="n">
+        <v>0.007282906174872934</v>
+      </c>
+      <c r="I887" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J887" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K887" s="54" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="L887" s="55" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="M887" t="inlineStr"/>
+      <c r="N887" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B888" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C888" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D888" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E888" s="10" t="n">
+        <v>55.8259</v>
+      </c>
+      <c r="F888" s="10" t="n">
+        <v>56.2539</v>
+      </c>
+      <c r="G888" s="10" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="H888" s="11" t="n">
+        <v>0.00766669234172669</v>
+      </c>
+      <c r="I888" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J888" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K888" s="54" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="L888" s="55" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="M888" t="inlineStr"/>
+      <c r="N888" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B889" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C889" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D889" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E889" s="12" t="n">
+        <v>6805.05</v>
+      </c>
+      <c r="F889" s="12" t="n">
+        <v>6876.24</v>
+      </c>
+      <c r="G889" s="12" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="H889" s="13" t="n">
+        <v>0.0104613485573214</v>
+      </c>
+      <c r="I889" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J889" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K889" s="54" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="L889" s="55" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="M889" t="inlineStr"/>
+      <c r="N889" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B890" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C890" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D890" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E890" s="8" t="n">
+        <v>48.2699</v>
+      </c>
+      <c r="F890" s="8" t="n">
+        <v>48.3494</v>
+      </c>
+      <c r="G890" s="8" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="H890" s="9" t="n">
+        <v>0.001646989117441718</v>
+      </c>
+      <c r="I890" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J890" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K890" s="54" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="L890" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M890" t="inlineStr"/>
+      <c r="N890" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B891" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C891" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D891" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E891" s="10" t="n">
+        <v>55.9826</v>
+      </c>
+      <c r="F891" s="10" t="n">
+        <v>56.1883</v>
+      </c>
+      <c r="G891" s="10" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="H891" s="11" t="n">
+        <v>0.003674355960602044</v>
+      </c>
+      <c r="I891" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J891" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K891" s="54" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="L891" s="55" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="M891" t="inlineStr"/>
+      <c r="N891" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B892" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C892" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D892" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E892" s="12" t="n">
+        <v>6825.26</v>
+      </c>
+      <c r="F892" s="12" t="n">
+        <v>6866.18</v>
+      </c>
+      <c r="G892" s="12" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="H892" s="13" t="n">
+        <v>0.005995376000328193</v>
+      </c>
+      <c r="I892" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J892" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K892" s="54" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="L892" s="55" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M892" t="inlineStr"/>
+      <c r="N892" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B893" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C893" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D893" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E893" s="8" t="n">
+        <v>47.7364</v>
+      </c>
+      <c r="F893" s="8" t="n">
+        <v>49.7208</v>
+      </c>
+      <c r="G893" s="8" t="n">
+        <v>1.9844</v>
+      </c>
+      <c r="H893" s="9" t="n">
+        <v>0.04156995500289087</v>
+      </c>
+      <c r="I893" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J893" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K893" s="54" t="n">
+        <v>1.9845</v>
+      </c>
+      <c r="L893" s="55" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="M893" t="inlineStr"/>
+      <c r="N893" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B894" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C894" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D894" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E894" s="10" t="n">
+        <v>55.3526</v>
+      </c>
+      <c r="F894" s="10" t="n">
+        <v>57.4906</v>
+      </c>
+      <c r="G894" s="10" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="H894" s="11" t="n">
+        <v>0.03862510523444247</v>
+      </c>
+      <c r="I894" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J894" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K894" s="54" t="n">
+        <v>2.1381</v>
+      </c>
+      <c r="L894" s="55" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="M894" t="inlineStr"/>
+      <c r="N894" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B895" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C895" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D895" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E895" s="12" t="n">
+        <v>5805.25</v>
+      </c>
+      <c r="F895" s="12" t="n">
+        <v>7573.31</v>
+      </c>
+      <c r="G895" s="12" t="n">
+        <v>1768.06</v>
+      </c>
+      <c r="H895" s="13" t="n">
+        <v>0.3045622496877826</v>
+      </c>
+      <c r="I895" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J895" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K895" s="54" t="n">
+        <v>1768.06</v>
+      </c>
+      <c r="L895" s="55" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="M895" t="inlineStr"/>
+      <c r="N895" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B896" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C896" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D896" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E896" s="8" t="n">
+        <v>47.5925</v>
+      </c>
+      <c r="F896" s="8" t="n">
+        <v>49.2925</v>
+      </c>
+      <c r="G896" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H896" s="9" t="n">
+        <v>0.03571991385197248</v>
+      </c>
+      <c r="I896" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J896" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K896" s="54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L896" s="55" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="M896" t="inlineStr"/>
+      <c r="N896" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B897" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C897" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D897" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E897" s="10" t="n">
+        <v>54.9928</v>
+      </c>
+      <c r="F897" s="10" t="n">
+        <v>57.5346</v>
+      </c>
+      <c r="G897" s="10" t="n">
+        <v>2.5418</v>
+      </c>
+      <c r="H897" s="11" t="n">
+        <v>0.04622059615076883</v>
+      </c>
+      <c r="I897" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J897" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K897" s="54" t="n">
+        <v>2.5418</v>
+      </c>
+      <c r="L897" s="55" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="M897" t="inlineStr"/>
+      <c r="N897" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B898" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C898" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D898" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E898" s="12" t="n">
+        <v>6707.38</v>
+      </c>
+      <c r="F898" s="12" t="n">
+        <v>7104.13</v>
+      </c>
+      <c r="G898" s="12" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="H898" s="13" t="n">
+        <v>0.05915126323542128</v>
+      </c>
+      <c r="I898" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J898" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K898" s="54" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="L898" s="55" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="M898" t="inlineStr"/>
+      <c r="N898" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B899" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C899" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D899" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E899" s="8" t="n">
+        <v>46.9293</v>
+      </c>
+      <c r="F899" s="8" t="n">
+        <v>49.9896</v>
+      </c>
+      <c r="G899" s="8" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="H899" s="9" t="n">
+        <v>0.06521085974007709</v>
+      </c>
+      <c r="I899" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J899" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K899" s="54" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="L899" s="55" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="M899" t="inlineStr"/>
+      <c r="N899" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B900" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C900" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D900" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E900" s="10" t="n">
+        <v>54.2441</v>
+      </c>
+      <c r="F900" s="10" t="n">
+        <v>58.4498</v>
+      </c>
+      <c r="G900" s="10" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="H900" s="11" t="n">
+        <v>0.0775328561078532</v>
+      </c>
+      <c r="I900" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J900" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K900" s="54" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="L900" s="55" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="M900" t="inlineStr"/>
+      <c r="N900" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B901" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C901" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D901" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E901" s="12" t="n">
+        <v>6611.27</v>
+      </c>
+      <c r="F901" s="12" t="n">
+        <v>7337.41</v>
+      </c>
+      <c r="G901" s="12" t="n">
+        <v>726.14</v>
+      </c>
+      <c r="H901" s="13" t="n">
+        <v>0.1098336628212129</v>
+      </c>
+      <c r="I901" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J901" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K901" s="54" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="L901" s="55" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="M901" t="inlineStr"/>
+      <c r="N901" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B902" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C902" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D902" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E902" s="8" t="n">
+        <v>47.165</v>
+      </c>
+      <c r="F902" s="8" t="n">
+        <v>49.165</v>
+      </c>
+      <c r="G902" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H902" s="9" t="n">
+        <v>0.0424043252411746</v>
+      </c>
+      <c r="I902" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J902" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K902" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="L902" s="55" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="M902" t="inlineStr"/>
+      <c r="N902" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B903" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C903" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D903" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E903" s="10" t="n">
+        <v>54.763</v>
+      </c>
+      <c r="F903" s="10" t="n">
+        <v>57.085</v>
+      </c>
+      <c r="G903" s="10" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="H903" s="11" t="n">
+        <v>0.04240089111261253</v>
+      </c>
+      <c r="I903" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J903" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K903" s="54" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="L903" s="55" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="M903" t="inlineStr"/>
+      <c r="N903" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B904" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C904" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D904" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E904" s="12" t="n">
+        <v>6645.08</v>
+      </c>
+      <c r="F904" s="12" t="n">
+        <v>7114.71</v>
+      </c>
+      <c r="G904" s="12" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="H904" s="13" t="n">
+        <v>0.07067334027581308</v>
+      </c>
+      <c r="I904" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J904" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K904" s="54" t="n">
+        <v>469.64</v>
+      </c>
+      <c r="L904" s="55" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="M904" t="inlineStr"/>
+      <c r="N904" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B905" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C905" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D905" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E905" s="8" t="n">
+        <v>46.9293</v>
+      </c>
+      <c r="F905" s="8" t="n">
+        <v>49.9896</v>
+      </c>
+      <c r="G905" s="8" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="H905" s="9" t="n">
+        <v>0.06521085974007709</v>
+      </c>
+      <c r="I905" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J905" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K905" s="54" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="L905" s="55" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="M905" t="inlineStr"/>
+      <c r="N905" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B906" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C906" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D906" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E906" s="10" t="n">
+        <v>54.2441</v>
+      </c>
+      <c r="F906" s="10" t="n">
+        <v>58.4498</v>
+      </c>
+      <c r="G906" s="10" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="H906" s="11" t="n">
+        <v>0.0775328561078532</v>
+      </c>
+      <c r="I906" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J906" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K906" s="54" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="L906" s="55" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="M906" t="inlineStr"/>
+      <c r="N906" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B907" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C907" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D907" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E907" s="12" t="n">
+        <v>6611.27</v>
+      </c>
+      <c r="F907" s="12" t="n">
+        <v>7337.4</v>
+      </c>
+      <c r="G907" s="12" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="H907" s="13" t="n">
+        <v>0.1098321502525234</v>
+      </c>
+      <c r="I907" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J907" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K907" s="54" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="L907" s="55" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="M907" t="inlineStr"/>
+      <c r="N907" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B908" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C908" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D908" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E908" s="8" t="n">
+        <v>47.1623</v>
+      </c>
+      <c r="F908" s="8" t="n">
+        <v>49.8623</v>
+      </c>
+      <c r="G908" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H908" s="9" t="n">
+        <v>0.05724911634928746</v>
+      </c>
+      <c r="I908" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J908" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K908" s="54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L908" s="55" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="M908" t="inlineStr"/>
+      <c r="N908" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B909" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C909" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D909" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E909" s="10" t="n">
+        <v>54.8025</v>
+      </c>
+      <c r="F909" s="10" t="n">
+        <v>57.9399</v>
+      </c>
+      <c r="G909" s="10" t="n">
+        <v>3.1374</v>
+      </c>
+      <c r="H909" s="11" t="n">
+        <v>0.05724921308334473</v>
+      </c>
+      <c r="I909" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J909" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K909" s="54" t="n">
+        <v>3.1374</v>
+      </c>
+      <c r="L909" s="55" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="M909" t="inlineStr"/>
+      <c r="N909" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B910" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C910" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D910" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E910" s="12" t="n">
+        <v>6527.6</v>
+      </c>
+      <c r="F910" s="12" t="n">
+        <v>7423.1</v>
+      </c>
+      <c r="G910" s="12" t="n">
+        <v>895.5</v>
+      </c>
+      <c r="H910" s="13" t="n">
+        <v>0.1371867148722348</v>
+      </c>
+      <c r="I910" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J910" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K910" s="54" t="n">
+        <v>895.5</v>
+      </c>
+      <c r="L910" s="55" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="M910" t="inlineStr"/>
+      <c r="N910" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B911" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C911" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D911" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E911" s="8" t="n">
+        <v>48.213</v>
+      </c>
+      <c r="F911" s="8" t="n">
+        <v>48.323</v>
+      </c>
+      <c r="G911" s="8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H911" s="9" t="n">
+        <v>0.002281542322610085</v>
+      </c>
+      <c r="I911" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J911" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K911" s="54" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L911" s="55" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="M911" t="inlineStr"/>
+      <c r="N911" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B912" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C912" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D912" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E912" s="10" t="n">
+        <v>55.842</v>
+      </c>
+      <c r="F912" s="10" t="n">
+        <v>56.072</v>
+      </c>
+      <c r="G912" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H912" s="11" t="n">
+        <v>0.004118763654596898</v>
+      </c>
+      <c r="I912" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J912" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K912" s="54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L912" s="55" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="M912" t="inlineStr"/>
+      <c r="N912" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B913" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C913" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D913" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E913" s="12" t="n">
+        <v>6796.95</v>
+      </c>
+      <c r="F913" s="12" t="n">
+        <v>6888.68</v>
+      </c>
+      <c r="G913" s="12" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="H913" s="13" t="n">
+        <v>0.01349575912725561</v>
+      </c>
+      <c r="I913" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J913" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K913" s="54" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="L913" s="55" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="M913" t="inlineStr"/>
+      <c r="N913" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B914" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C914" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D914" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E914" s="8" t="n">
+        <v>47.8265</v>
+      </c>
+      <c r="F914" s="8" t="n">
+        <v>48.4543</v>
+      </c>
+      <c r="G914" s="8" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="H914" s="9" t="n">
+        <v>0.01312661390651626</v>
+      </c>
+      <c r="I914" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J914" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K914" s="54" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="L914" s="55" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="M914" t="inlineStr"/>
+      <c r="N914" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B915" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C915" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D915" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E915" s="10" t="n">
+        <v>55.6569</v>
+      </c>
+      <c r="F915" s="10" t="n">
+        <v>56.2918</v>
+      </c>
+      <c r="G915" s="10" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="H915" s="11" t="n">
+        <v>0.01140739063799816</v>
+      </c>
+      <c r="I915" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J915" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K915" s="54" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="L915" s="55" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="M915" t="inlineStr"/>
+      <c r="N915" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B916" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C916" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D916" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E916" s="12" t="n">
+        <v>6827.31</v>
+      </c>
+      <c r="F916" s="12" t="n">
+        <v>6969.07</v>
+      </c>
+      <c r="G916" s="12" t="n">
+        <v>141.76</v>
+      </c>
+      <c r="H916" s="13" t="n">
+        <v>0.02076366826759002</v>
+      </c>
+      <c r="I916" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J916" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K916" s="54" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="L916" s="55" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="M916" t="inlineStr"/>
+      <c r="N916" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B917" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C917" s="30" t="inlineStr">
+        <is>
+          <t>Hepsipay</t>
+        </is>
+      </c>
+      <c r="D917" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E917" s="12" t="n">
+        <v>6834.76</v>
+      </c>
+      <c r="F917" s="12" t="n">
+        <v>7034.29</v>
+      </c>
+      <c r="G917" s="12" t="n">
+        <v>199.53</v>
+      </c>
+      <c r="H917" s="13" t="n">
+        <v>0.02919341717924257</v>
+      </c>
+      <c r="I917" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J917" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K917" s="54" t="n">
+        <v>199.53</v>
+      </c>
+      <c r="L917" s="55" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="M917" t="inlineStr"/>
+      <c r="N917" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B918" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C918" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D918" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E918" s="8" t="n">
+        <v>47.5517</v>
+      </c>
+      <c r="F918" s="8" t="n">
+        <v>49.4789</v>
+      </c>
+      <c r="G918" s="8" t="n">
+        <v>1.9272</v>
+      </c>
+      <c r="H918" s="9" t="n">
+        <v>0.04052851948510779</v>
+      </c>
+      <c r="I918" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J918" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K918" s="54" t="n">
+        <v>1.9272</v>
+      </c>
+      <c r="L918" s="55" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M918" t="inlineStr"/>
+      <c r="N918" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B919" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C919" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D919" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E919" s="10" t="n">
+        <v>54.7851</v>
+      </c>
+      <c r="F919" s="10" t="n">
+        <v>57.9411</v>
+      </c>
+      <c r="G919" s="10" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="H919" s="11" t="n">
+        <v>0.05760690406698171</v>
+      </c>
+      <c r="I919" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J919" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K919" s="54" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="L919" s="55" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="M919" t="inlineStr"/>
+      <c r="N919" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B920" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C920" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D920" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E920" s="12" t="n">
+        <v>6710.16</v>
+      </c>
+      <c r="F920" s="12" t="n">
+        <v>7363.91</v>
+      </c>
+      <c r="G920" s="12" t="n">
+        <v>653.75</v>
+      </c>
+      <c r="H920" s="13" t="n">
+        <v>0.09742688698928192</v>
+      </c>
+      <c r="I920" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J920" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K920" s="54" t="n">
+        <v>653.76</v>
+      </c>
+      <c r="L920" s="55" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="M920" t="inlineStr"/>
+      <c r="N920" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B921" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C921" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D921" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E921" s="8" t="n">
+        <v>47.2028</v>
+      </c>
+      <c r="F921" s="8" t="n">
+        <v>49.4795</v>
+      </c>
+      <c r="G921" s="8" t="n">
+        <v>2.2767</v>
+      </c>
+      <c r="H921" s="9" t="n">
+        <v>0.04823230825290025</v>
+      </c>
+      <c r="I921" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J921" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K921" s="54" t="n">
+        <v>2.2768</v>
+      </c>
+      <c r="L921" s="55" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="M921" t="inlineStr"/>
+      <c r="N921" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B922" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C922" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D922" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E922" s="10" t="n">
+        <v>54.8911</v>
+      </c>
+      <c r="F922" s="10" t="n">
+        <v>57.2139</v>
+      </c>
+      <c r="G922" s="10" t="n">
+        <v>2.3228</v>
+      </c>
+      <c r="H922" s="11" t="n">
+        <v>0.04231651397038864</v>
+      </c>
+      <c r="I922" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J922" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K922" s="54" t="n">
+        <v>2.3228</v>
+      </c>
+      <c r="L922" s="55" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="M922" t="inlineStr"/>
+      <c r="N922" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B923" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C923" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D923" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E923" s="12" t="n">
+        <v>6662.76</v>
+      </c>
+      <c r="F923" s="12" t="n">
+        <v>7078.51</v>
+      </c>
+      <c r="G923" s="12" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="H923" s="13" t="n">
+        <v>0.06239906585258961</v>
+      </c>
+      <c r="I923" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J923" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K923" s="54" t="n">
+        <v>415.74</v>
+      </c>
+      <c r="L923" s="55" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="M923" t="inlineStr"/>
+      <c r="N923" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B924" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C924" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D924" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E924" s="8" t="n">
+        <v>47.1425</v>
+      </c>
+      <c r="F924" s="8" t="n">
+        <v>49.7585</v>
+      </c>
+      <c r="G924" s="8" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="H924" s="9" t="n">
+        <v>0.05549132947976879</v>
+      </c>
+      <c r="I924" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J924" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K924" s="54" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="L924" s="55" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="M924" t="inlineStr"/>
+      <c r="N924" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B925" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C925" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D925" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E925" s="10" t="n">
+        <v>54.7418</v>
+      </c>
+      <c r="F925" s="10" t="n">
+        <v>57.7845</v>
+      </c>
+      <c r="G925" s="10" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="H925" s="11" t="n">
+        <v>0.05558275394670983</v>
+      </c>
+      <c r="I925" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J925" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K925" s="54" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="L925" s="55" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="M925" t="inlineStr"/>
+      <c r="N925" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B926" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C926" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D926" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E926" s="12" t="n">
+        <v>6458.79</v>
+      </c>
+      <c r="F926" s="12" t="n">
+        <v>7275.6</v>
+      </c>
+      <c r="G926" s="12" t="n">
+        <v>816.8099999999999</v>
+      </c>
+      <c r="H926" s="13" t="n">
+        <v>0.1264648641618631</v>
+      </c>
+      <c r="I926" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J926" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K926" s="54" t="n">
+        <v>816.8099999999999</v>
+      </c>
+      <c r="L926" s="55" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="M926" t="inlineStr"/>
+      <c r="N926" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B927" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C927" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D927" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E927" s="8" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="F927" s="8" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="G927" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H927" s="9" t="n">
+        <v>0.0002072538860103627</v>
+      </c>
+      <c r="I927" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J927" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K927" s="54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L927" s="55" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M927" t="inlineStr"/>
+      <c r="N927" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B928" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C928" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D928" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E928" s="10" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F928" s="10" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="G928" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H928" s="11" t="n">
+        <v>0.0008944543828264759</v>
+      </c>
+      <c r="I928" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J928" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K928" s="54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L928" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M928" t="inlineStr"/>
+      <c r="N928" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B929" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C929" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D929" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E929" s="12" t="n">
+        <v>6818.04</v>
+      </c>
+      <c r="F929" s="12" t="n">
+        <v>6829.15</v>
+      </c>
+      <c r="G929" s="12" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="H929" s="13" t="n">
+        <v>0.001629500560278321</v>
+      </c>
+      <c r="I929" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J929" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K929" s="54" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="L929" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M929" t="inlineStr"/>
+      <c r="N929" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B930" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C930" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D930" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E930" s="8" t="n">
+        <v>44.8059</v>
+      </c>
+      <c r="F930" s="8" t="n">
+        <v>49.2963</v>
+      </c>
+      <c r="G930" s="8" t="n">
+        <v>4.4904</v>
+      </c>
+      <c r="H930" s="9" t="n">
+        <v>0.1002189443800928</v>
+      </c>
+      <c r="I930" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J930" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K930" s="54" t="n">
+        <v>4.4904</v>
+      </c>
+      <c r="L930" s="55" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="M930" t="inlineStr"/>
+      <c r="N930" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B931" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C931" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D931" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E931" s="10" t="n">
+        <v>52.017</v>
+      </c>
+      <c r="F931" s="10" t="n">
+        <v>57.2734</v>
+      </c>
+      <c r="G931" s="10" t="n">
+        <v>5.2564</v>
+      </c>
+      <c r="H931" s="11" t="n">
+        <v>0.1010515792913855</v>
+      </c>
+      <c r="I931" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J931" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K931" s="54" t="n">
+        <v>5.2564</v>
+      </c>
+      <c r="L931" s="55" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="M931" t="inlineStr"/>
+      <c r="N931" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B932" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C932" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D932" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E932" s="12" t="n">
+        <v>6430.53</v>
+      </c>
+      <c r="F932" s="12" t="n">
+        <v>7056.75</v>
+      </c>
+      <c r="G932" s="12" t="n">
+        <v>626.22</v>
+      </c>
+      <c r="H932" s="13" t="n">
+        <v>0.09738233084986775</v>
+      </c>
+      <c r="I932" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J932" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K932" s="54" t="n">
+        <v>626.22</v>
+      </c>
+      <c r="L932" s="55" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="M932" t="inlineStr"/>
+      <c r="N932" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B933" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C933" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D933" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E933" s="8" t="n">
+        <v>48.2326</v>
+      </c>
+      <c r="F933" s="8" t="n">
+        <v>48.3195</v>
+      </c>
+      <c r="G933" s="8" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="H933" s="9" t="n">
+        <v>0.001801685996608103</v>
+      </c>
+      <c r="I933" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J933" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K933" s="54" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="L933" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M933" t="inlineStr"/>
+      <c r="N933" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B934" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C934" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D934" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E934" s="10" t="n">
+        <v>56.0571</v>
+      </c>
+      <c r="F934" s="10" t="n">
+        <v>56.1581</v>
+      </c>
+      <c r="G934" s="10" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H934" s="11" t="n">
+        <v>0.001801734303058845</v>
+      </c>
+      <c r="I934" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J934" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K934" s="54" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="L934" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M934" t="inlineStr"/>
+      <c r="N934" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B935" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C935" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D935" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E935" s="8" t="n">
+        <v>48.0452</v>
+      </c>
+      <c r="F935" s="8" t="n">
+        <v>48.482</v>
+      </c>
+      <c r="G935" s="8" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="H935" s="9" t="n">
+        <v>0.009091438895040504</v>
+      </c>
+      <c r="I935" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J935" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K935" s="54" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="L935" s="55" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="M935" t="inlineStr"/>
+      <c r="N935" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B936" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C936" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D936" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E936" s="10" t="n">
+        <v>55.9066</v>
+      </c>
+      <c r="F936" s="10" t="n">
+        <v>56.3121</v>
+      </c>
+      <c r="G936" s="10" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="H936" s="11" t="n">
+        <v>0.007253168677758976</v>
+      </c>
+      <c r="I936" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J936" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K936" s="54" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="L936" s="55" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="M936" t="inlineStr"/>
+      <c r="N936" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B937" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C937" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D937" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E937" s="12" t="n">
+        <v>6796.19</v>
+      </c>
+      <c r="F937" s="12" t="n">
+        <v>6876.58</v>
+      </c>
+      <c r="G937" s="12" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="H937" s="13" t="n">
+        <v>0.01182868636692029</v>
+      </c>
+      <c r="I937" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J937" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K937" s="54" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="L937" s="55" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="M937" t="inlineStr"/>
+      <c r="N937" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B938" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C938" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D938" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E938" s="8" t="n">
+        <v>48.239</v>
+      </c>
+      <c r="F938" s="8" t="n">
+        <v>48.382</v>
+      </c>
+      <c r="G938" s="8" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="H938" s="9" t="n">
+        <v>0.002964406393167354</v>
+      </c>
+      <c r="I938" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J938" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K938" s="54" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="L938" s="55" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M938" t="inlineStr"/>
+      <c r="N938" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B939" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C939" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D939" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E939" s="10" t="n">
+        <v>55.851</v>
+      </c>
+      <c r="F939" s="10" t="n">
+        <v>56.093</v>
+      </c>
+      <c r="G939" s="10" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H939" s="11" t="n">
+        <v>0.004332957332903619</v>
+      </c>
+      <c r="I939" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J939" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K939" s="54" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L939" s="55" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="M939" t="inlineStr"/>
+      <c r="N939" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B940" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C940" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D940" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E940" s="12" t="n">
+        <v>6813</v>
+      </c>
+      <c r="F940" s="12" t="n">
+        <v>6879</v>
+      </c>
+      <c r="G940" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H940" s="13" t="n">
+        <v>0.009687362395420521</v>
+      </c>
+      <c r="I940" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J940" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K940" s="54" t="n">
+        <v>66</v>
+      </c>
+      <c r="L940" s="55" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="M940" t="inlineStr"/>
+      <c r="N940" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B941" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C941" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D941" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E941" s="8" t="n">
+        <v>47.3765</v>
+      </c>
+      <c r="F941" s="8" t="n">
+        <v>49.1765</v>
+      </c>
+      <c r="G941" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H941" s="9" t="n">
+        <v>0.0379935199940899</v>
+      </c>
+      <c r="I941" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J941" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K941" s="54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L941" s="55" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M941" t="inlineStr"/>
+      <c r="N941" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B942" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C942" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D942" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E942" s="10" t="n">
+        <v>54.987</v>
+      </c>
+      <c r="F942" s="10" t="n">
+        <v>57.127</v>
+      </c>
+      <c r="G942" s="10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H942" s="11" t="n">
+        <v>0.0389182897775838</v>
+      </c>
+      <c r="I942" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J942" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K942" s="54" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L942" s="55" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="M942" t="inlineStr"/>
+      <c r="N942" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B943" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C943" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D943" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E943" s="12" t="n">
+        <v>6700.83</v>
+      </c>
+      <c r="F943" s="12" t="n">
+        <v>7050.83</v>
+      </c>
+      <c r="G943" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="H943" s="13" t="n">
+        <v>0.05223233539725676</v>
+      </c>
+      <c r="I943" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J943" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K943" s="54" t="n">
+        <v>350</v>
+      </c>
+      <c r="L943" s="55" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="M943" t="inlineStr"/>
+      <c r="N943" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B944" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C944" s="40" t="inlineStr">
+        <is>
+          <t>Papara</t>
+        </is>
+      </c>
+      <c r="D944" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E944" s="12" t="n">
+        <v>6834.75</v>
+      </c>
+      <c r="F944" s="12" t="n">
+        <v>7020.24</v>
+      </c>
+      <c r="G944" s="12" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="H944" s="13" t="n">
+        <v>0.02713925161856688</v>
+      </c>
+      <c r="I944" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J944" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K944" s="54" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="L944" s="55" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="M944" t="inlineStr"/>
+      <c r="N944" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B945" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C945" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D945" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E945" s="8" t="n">
+        <v>46.9325</v>
+      </c>
+      <c r="F945" s="8" t="n">
+        <v>49.9525</v>
+      </c>
+      <c r="G945" s="8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H945" s="9" t="n">
+        <v>0.06434773344697171</v>
+      </c>
+      <c r="I945" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J945" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K945" s="54" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L945" s="55" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="M945" t="inlineStr"/>
+      <c r="N945" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B946" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C946" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D946" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E946" s="10" t="n">
+        <v>53.9523</v>
+      </c>
+      <c r="F946" s="10" t="n">
+        <v>58.6008</v>
+      </c>
+      <c r="G946" s="10" t="n">
+        <v>4.6485</v>
+      </c>
+      <c r="H946" s="11" t="n">
+        <v>0.08615944083940814</v>
+      </c>
+      <c r="I946" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J946" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K946" s="54" t="n">
+        <v>4.6485</v>
+      </c>
+      <c r="L946" s="55" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="M946" t="inlineStr"/>
+      <c r="N946" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B947" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C947" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D947" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E947" s="12" t="n">
+        <v>6553.72</v>
+      </c>
+      <c r="F947" s="12" t="n">
+        <v>7184.14</v>
+      </c>
+      <c r="G947" s="12" t="n">
+        <v>630.42</v>
+      </c>
+      <c r="H947" s="13" t="n">
+        <v>0.09619269666693114</v>
+      </c>
+      <c r="I947" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J947" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K947" s="54" t="n">
+        <v>630.42</v>
+      </c>
+      <c r="L947" s="55" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="M947" t="inlineStr"/>
+      <c r="N947" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B948" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C948" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D948" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E948" s="8" t="n">
+        <v>48.1299</v>
+      </c>
+      <c r="F948" s="8" t="n">
+        <v>48.6747</v>
+      </c>
+      <c r="G948" s="8" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="H948" s="9" t="n">
+        <v>0.01131936696315596</v>
+      </c>
+      <c r="I948" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J948" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K948" s="54" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="L948" s="55" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="M948" t="inlineStr"/>
+      <c r="N948" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B949" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C949" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D949" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E949" s="10" t="n">
+        <v>55.6847</v>
+      </c>
+      <c r="F949" s="10" t="n">
+        <v>56.5284</v>
+      </c>
+      <c r="G949" s="10" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="H949" s="11" t="n">
+        <v>0.01515137910413453</v>
+      </c>
+      <c r="I949" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J949" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K949" s="54" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="L949" s="55" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="M949" t="inlineStr"/>
+      <c r="N949" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B950" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C950" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D950" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E950" s="12" t="n">
+        <v>6864.2</v>
+      </c>
+      <c r="F950" s="12" t="n">
+        <v>7379.02</v>
+      </c>
+      <c r="G950" s="12" t="n">
+        <v>514.8200000000001</v>
+      </c>
+      <c r="H950" s="13" t="n">
+        <v>0.07500072841700417</v>
+      </c>
+      <c r="I950" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J950" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K950" s="54" t="n">
+        <v>514.8200000000001</v>
+      </c>
+      <c r="L950" s="55" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M950" t="inlineStr"/>
+      <c r="N950" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B951" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C951" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D951" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E951" s="8" t="n">
+        <v>47.7911</v>
+      </c>
+      <c r="F951" s="8" t="n">
+        <v>48.7367</v>
+      </c>
+      <c r="G951" s="8" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="H951" s="9" t="n">
+        <v>0.01978611080305747</v>
+      </c>
+      <c r="I951" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J951" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K951" s="54" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="L951" s="55" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="M951" t="inlineStr"/>
+      <c r="N951" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B952" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C952" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D952" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E952" s="10" t="n">
+        <v>55.532</v>
+      </c>
+      <c r="F952" s="10" t="n">
+        <v>56.5537</v>
+      </c>
+      <c r="G952" s="10" t="n">
+        <v>1.0217</v>
+      </c>
+      <c r="H952" s="11" t="n">
+        <v>0.01839840092199092</v>
+      </c>
+      <c r="I952" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J952" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K952" s="54" t="n">
+        <v>1.0217</v>
+      </c>
+      <c r="L952" s="55" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="M952" t="inlineStr"/>
+      <c r="N952" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B953" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C953" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D953" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E953" s="12" t="n">
+        <v>6763.3</v>
+      </c>
+      <c r="F953" s="12" t="n">
+        <v>6980.72</v>
+      </c>
+      <c r="G953" s="12" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="H953" s="13" t="n">
+        <v>0.03214702881729334</v>
+      </c>
+      <c r="I953" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J953" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K953" s="54" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="L953" s="55" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="M953" t="inlineStr"/>
+      <c r="N953" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B954" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C954" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D954" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E954" s="8" t="n">
+        <v>47.9608</v>
+      </c>
+      <c r="F954" s="8" t="n">
+        <v>48.5704</v>
+      </c>
+      <c r="G954" s="8" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="H954" s="9" t="n">
+        <v>0.01271038014378409</v>
+      </c>
+      <c r="I954" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J954" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K954" s="54" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="L954" s="55" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="M954" t="inlineStr"/>
+      <c r="N954" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B955" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C955" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D955" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E955" s="10" t="n">
+        <v>55.6608</v>
+      </c>
+      <c r="F955" s="10" t="n">
+        <v>56.3368</v>
+      </c>
+      <c r="G955" s="10" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="H955" s="11" t="n">
+        <v>0.01214499252615845</v>
+      </c>
+      <c r="I955" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J955" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K955" s="54" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="L955" s="55" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="M955" t="inlineStr"/>
+      <c r="N955" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B956" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C956" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D956" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E956" s="12" t="n">
+        <v>6758.27</v>
+      </c>
+      <c r="F956" s="12" t="n">
+        <v>6922.44</v>
+      </c>
+      <c r="G956" s="12" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="H956" s="13" t="n">
+        <v>0.02429171962647246</v>
+      </c>
+      <c r="I956" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J956" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K956" s="54" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="L956" s="55" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="M956" t="inlineStr"/>
+      <c r="N956" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B957" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C957" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D957" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E957" s="8" t="n">
+        <v>47.0674</v>
+      </c>
+      <c r="F957" s="8" t="n">
+        <v>49.8524</v>
+      </c>
+      <c r="G957" s="8" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="H957" s="9" t="n">
+        <v>0.05917046618253823</v>
+      </c>
+      <c r="I957" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J957" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K957" s="54" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="L957" s="55" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="M957" t="inlineStr"/>
+      <c r="N957" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B958" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C958" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D958" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E958" s="10" t="n">
+        <v>54.591</v>
+      </c>
+      <c r="F958" s="10" t="n">
+        <v>57.749</v>
+      </c>
+      <c r="G958" s="10" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="H958" s="11" t="n">
+        <v>0.05784836328332509</v>
+      </c>
+      <c r="I958" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J958" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K958" s="54" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="L958" s="55" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="M958" t="inlineStr"/>
+      <c r="N958" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B959" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C959" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D959" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E959" s="12" t="n">
+        <v>6551.45</v>
+      </c>
+      <c r="F959" s="12" t="n">
+        <v>7449.45</v>
+      </c>
+      <c r="G959" s="12" t="n">
+        <v>898</v>
+      </c>
+      <c r="H959" s="13" t="n">
+        <v>0.1370688931457922</v>
+      </c>
+      <c r="I959" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J959" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K959" s="54" t="n">
+        <v>898</v>
+      </c>
+      <c r="L959" s="55" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="M959" t="inlineStr"/>
+      <c r="N959" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B960" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C960" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D960" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E960" s="8" t="n">
+        <v>48.227</v>
+      </c>
+      <c r="F960" s="8" t="n">
+        <v>48.356</v>
+      </c>
+      <c r="G960" s="8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H960" s="9" t="n">
+        <v>0.002674850187654218</v>
+      </c>
+      <c r="I960" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J960" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K960" s="54" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="L960" s="55" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="M960" t="inlineStr"/>
+      <c r="N960" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B961" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C961" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D961" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E961" s="10" t="n">
+        <v>55.871</v>
+      </c>
+      <c r="F961" s="10" t="n">
+        <v>56.107</v>
+      </c>
+      <c r="G961" s="10" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="H961" s="11" t="n">
+        <v>0.004224016036942242</v>
+      </c>
+      <c r="I961" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J961" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K961" s="54" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="L961" s="55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M961" t="inlineStr"/>
+      <c r="N961" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B962" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C962" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D962" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E962" s="8" t="n">
+        <v>46.94</v>
+      </c>
+      <c r="F962" s="8" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="G962" s="8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H962" s="9" t="n">
+        <v>0.05368555602897316</v>
+      </c>
+      <c r="I962" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J962" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K962" s="54" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L962" s="55" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="M962" t="inlineStr"/>
+      <c r="N962" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B963" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C963" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D963" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E963" s="10" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="F963" s="10" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="G963" s="10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H963" s="11" t="n">
+        <v>0.04793267471642883</v>
+      </c>
+      <c r="I963" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J963" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K963" s="54" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L963" s="55" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="M963" t="inlineStr"/>
+      <c r="N963" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B964" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C964" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D964" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E964" s="12" t="n">
+        <v>6642.18</v>
+      </c>
+      <c r="F964" s="12" t="n">
+        <v>7150.59</v>
+      </c>
+      <c r="G964" s="12" t="n">
+        <v>508.41</v>
+      </c>
+      <c r="H964" s="13" t="n">
+        <v>0.07654264112083684</v>
+      </c>
+      <c r="I964" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J964" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K964" s="54" t="n">
+        <v>508.41</v>
+      </c>
+      <c r="L964" s="55" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="M964" t="inlineStr"/>
+      <c r="N964" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B965" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C965" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D965" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E965" s="8" t="n">
+        <v>47.0106</v>
+      </c>
+      <c r="F965" s="8" t="n">
+        <v>49.8725</v>
+      </c>
+      <c r="G965" s="8" t="n">
+        <v>2.8619</v>
+      </c>
+      <c r="H965" s="9" t="n">
+        <v>0.06087775948403126</v>
+      </c>
+      <c r="I965" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J965" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K965" s="54" t="n">
+        <v>2.8619</v>
+      </c>
+      <c r="L965" s="55" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="M965" t="inlineStr"/>
+      <c r="N965" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B966" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C966" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D966" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E966" s="10" t="n">
+        <v>54.5954</v>
+      </c>
+      <c r="F966" s="10" t="n">
+        <v>57.919</v>
+      </c>
+      <c r="G966" s="10" t="n">
+        <v>3.3236</v>
+      </c>
+      <c r="H966" s="11" t="n">
+        <v>0.06087692369686823</v>
+      </c>
+      <c r="I966" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J966" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K966" s="54" t="n">
+        <v>3.3236</v>
+      </c>
+      <c r="L966" s="55" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="M966" t="inlineStr"/>
+      <c r="N966" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B967" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C967" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D967" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E967" s="12" t="n">
+        <v>6616.52</v>
+      </c>
+      <c r="F967" s="12" t="n">
+        <v>7573.86</v>
+      </c>
+      <c r="G967" s="12" t="n">
+        <v>957.34</v>
+      </c>
+      <c r="H967" s="13" t="n">
+        <v>0.1446893533156403</v>
+      </c>
+      <c r="I967" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J967" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K967" s="54" t="n">
+        <v>957.33</v>
+      </c>
+      <c r="L967" s="55" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="M967" t="inlineStr"/>
+      <c r="N967" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B968" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C968" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D968" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E968" s="8" t="n">
+        <v>47.0576</v>
+      </c>
+      <c r="F968" s="8" t="n">
+        <v>49.5982</v>
+      </c>
+      <c r="G968" s="8" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="H968" s="9" t="n">
+        <v>0.05398915371799667</v>
+      </c>
+      <c r="I968" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J968" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K968" s="54" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="L968" s="55" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+      <c r="M968" t="inlineStr"/>
+      <c r="N968" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B969" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C969" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D969" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E969" s="10" t="n">
+        <v>54.5954</v>
+      </c>
+      <c r="F969" s="10" t="n">
+        <v>57.6004</v>
+      </c>
+      <c r="G969" s="10" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="H969" s="11" t="n">
+        <v>0.05504126721298864</v>
+      </c>
+      <c r="I969" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J969" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K969" s="54" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="L969" s="55" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="M969" t="inlineStr"/>
+      <c r="N969" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B970" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C970" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D970" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E970" s="12" t="n">
+        <v>6583.44</v>
+      </c>
+      <c r="F970" s="12" t="n">
+        <v>7535.99</v>
+      </c>
+      <c r="G970" s="12" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="H970" s="13" t="n">
+        <v>0.1446887949157279</v>
+      </c>
+      <c r="I970" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J970" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K970" s="54" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="L970" s="55" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="M970" t="inlineStr"/>
+      <c r="N970" s="6" t="n">
+        <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B971" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C971" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D971" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E971" s="8" t="n">
+        <v>43.1206</v>
+      </c>
+      <c r="F971" s="8" t="n">
+        <v>53.8029</v>
+      </c>
+      <c r="G971" s="8" t="n">
+        <v>10.6823</v>
+      </c>
+      <c r="H971" s="9" t="n">
+        <v>0.2477307829668418</v>
+      </c>
+      <c r="I971" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J971" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K971" s="54" t="n">
+        <v>10.6823</v>
+      </c>
+      <c r="L971" s="55" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="M971" t="inlineStr"/>
+      <c r="N971" s="6" t="n">
+        <v>0.5661689814814815</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B972" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C972" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D972" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E972" s="10" t="n">
+        <v>50.0454</v>
+      </c>
+      <c r="F972" s="10" t="n">
+        <v>62.5049</v>
+      </c>
+      <c r="G972" s="10" t="n">
+        <v>12.4595</v>
+      </c>
+      <c r="H972" s="11" t="n">
+        <v>0.2489639407418064</v>
+      </c>
+      <c r="I972" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J972" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K972" s="54" t="n">
+        <v>12.4595</v>
+      </c>
+      <c r="L972" s="55" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="M972" t="inlineStr"/>
+      <c r="N972" s="6" t="n">
+        <v>0.5663194444444445</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="58" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B973" s="6" t="n">
+        <v>0.5660069444444444</v>
+      </c>
+      <c r="C973" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D973" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E973" s="12" t="n">
+        <v>6131.92</v>
+      </c>
+      <c r="F973" s="12" t="n">
+        <v>7732.64</v>
+      </c>
+      <c r="G973" s="12" t="n">
+        <v>1600.72</v>
+      </c>
+      <c r="H973" s="13" t="n">
+        <v>0.2610471108559799</v>
+      </c>
+      <c r="I973" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J973" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K973" s="54" t="n">
+        <v>1600.72</v>
+      </c>
+      <c r="L973" s="55" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M973" t="inlineStr"/>
+      <c r="N973" s="6" t="n">
+        <v>0.5665162037037037</v>
       </c>
     </row>
   </sheetData>
@@ -53418,10 +58998,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J863" r:id="rId862"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J864" r:id="rId863"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J865" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J866" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J867" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J868" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J869" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J870" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J871" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J872" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J873" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J874" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J875" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J876" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J877" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J878" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J879" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J880" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J881" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J882" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J883" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J884" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J885" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J886" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J887" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J888" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J889" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J890" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J891" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J892" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J893" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J894" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J895" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J896" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J897" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J898" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J899" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J900" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J901" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J902" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J903" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J904" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J905" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J906" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J907" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J908" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J909" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J910" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J911" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J912" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J913" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J914" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J915" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J916" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J917" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J918" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J919" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J920" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J921" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J922" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J923" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J924" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J925" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J926" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J927" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J928" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J929" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J930" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J931" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J932" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J933" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J934" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J935" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J936" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J937" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J938" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J939" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J940" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J941" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J942" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J943" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J944" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J945" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J946" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J947" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J948" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J949" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J950" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J951" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J952" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J953" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J954" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J955" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J956" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J957" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J958" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J959" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J960" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J961" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J962" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J963" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J964" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J965" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J966" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J967" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J968" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J969" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J970" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J971" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J972" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J973" r:id="rId972"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId865"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId973"/>
   </tableParts>
 </worksheet>
 </file>
@@ -53495,7 +59183,7 @@
       </c>
       <c r="B4" s="62" t="n"/>
       <c r="C4" s="63" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D4" s="62" t="n"/>
       <c r="F4" s="1" t="inlineStr">
@@ -53562,7 +59250,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.5602777777777778</v>
+        <v>0.5660069444444444</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -53593,18 +59281,18 @@
         <v>5</v>
       </c>
       <c r="N5" s="70" t="n">
-        <v>0.01907356948228883</v>
-      </c>
-      <c r="O5" s="71" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="P5" s="72" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="Q5" s="72" t="n">
-        <v>48.62</v>
+        <v>0.0424043252411746</v>
+      </c>
+      <c r="O5" s="65" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="P5" s="71" t="n">
+        <v>47.165</v>
+      </c>
+      <c r="Q5" s="71" t="n">
+        <v>49.165</v>
       </c>
     </row>
     <row r="6">
@@ -53614,7 +59302,7 @@
         </is>
       </c>
       <c r="B6" s="62" t="n"/>
-      <c r="C6" s="73" t="n">
+      <c r="C6" s="72" t="n">
         <v>38</v>
       </c>
       <c r="D6" s="62" t="n"/>
@@ -53623,7 +59311,7 @@
           <t>Ağustos 2026</t>
         </is>
       </c>
-      <c r="G6" s="74" t="inlineStr">
+      <c r="G6" s="73" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
@@ -53637,7 +59325,7 @@
       <c r="J6" s="68" t="n">
         <v>0.06066925394146307</v>
       </c>
-      <c r="L6" s="75" t="inlineStr">
+      <c r="L6" s="74" t="inlineStr">
         <is>
           <t>EURO</t>
         </is>
@@ -53646,18 +59334,18 @@
         <v>5</v>
       </c>
       <c r="N6" s="70" t="n">
-        <v>0.01857864357864358</v>
-      </c>
-      <c r="O6" s="71" t="inlineStr">
-        <is>
-          <t>Yapıkredi</t>
-        </is>
-      </c>
-      <c r="P6" s="72" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="Q6" s="72" t="n">
-        <v>56.47</v>
+        <v>0.04240089111261253</v>
+      </c>
+      <c r="O6" s="65" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="P6" s="71" t="n">
+        <v>54.763</v>
+      </c>
+      <c r="Q6" s="71" t="n">
+        <v>57.085</v>
       </c>
     </row>
     <row r="7">
@@ -53667,7 +59355,7 @@
         </is>
       </c>
       <c r="B7" s="62" t="n"/>
-      <c r="C7" s="73" t="n">
+      <c r="C7" s="72" t="n">
         <v>108</v>
       </c>
       <c r="D7" s="62" t="n"/>
@@ -53676,7 +59364,7 @@
           <t>Ağustos 2026</t>
         </is>
       </c>
-      <c r="G7" s="71" t="inlineStr">
+      <c r="G7" s="75" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
@@ -53699,18 +59387,18 @@
         <v>5</v>
       </c>
       <c r="N7" s="70" t="n">
-        <v>0.02019121345887606</v>
-      </c>
-      <c r="O7" s="77" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası</t>
-        </is>
-      </c>
-      <c r="P7" s="72" t="n">
-        <v>6898.05</v>
-      </c>
-      <c r="Q7" s="72" t="n">
-        <v>7037.33</v>
+        <v>0.07067334027581308</v>
+      </c>
+      <c r="O7" s="65" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="P7" s="71" t="n">
+        <v>6645.08</v>
+      </c>
+      <c r="Q7" s="71" t="n">
+        <v>7114.71</v>
       </c>
     </row>
     <row r="8">
@@ -53720,7 +59408,7 @@
         </is>
       </c>
       <c r="B8" s="62" t="n"/>
-      <c r="C8" s="73" t="n">
+      <c r="C8" s="72" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="62" t="n"/>
@@ -53751,7 +59439,7 @@
         </is>
       </c>
       <c r="B9" s="62" t="n"/>
-      <c r="C9" s="73" t="n">
+      <c r="C9" s="72" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="62" t="n"/>
@@ -53787,13 +59475,13 @@
         </is>
       </c>
       <c r="H10" s="66" t="n">
-        <v>0.02844650727811221</v>
+        <v>0.03123807087072469</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>0.02844673332410395</v>
+        <v>0.03123756488180567</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>0.03694183282830633</v>
+        <v>0.04368813431780767</v>
       </c>
     </row>
     <row r="11">
@@ -53802,19 +59490,19 @@
           <t>Eylül 2026</t>
         </is>
       </c>
-      <c r="G11" s="74" t="inlineStr">
+      <c r="G11" s="73" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
       <c r="H11" s="66" t="n">
-        <v>0.02841716740814283</v>
+        <v>0.03423508640036999</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>0.02846176873157642</v>
+        <v>0.03430743211896899</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>0.03612757126674167</v>
+        <v>0.04587774544921894</v>
       </c>
     </row>
     <row r="12">
@@ -53823,19 +59511,19 @@
           <t>Eylül 2026</t>
         </is>
       </c>
-      <c r="G12" s="71" t="inlineStr">
+      <c r="G12" s="75" t="inlineStr">
         <is>
           <t>Yapıkredi</t>
         </is>
       </c>
       <c r="H12" s="66" t="n">
-        <v>0.02003126698380895</v>
+        <v>0.02676212479284179</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>0.01948453111277258</v>
+        <v>0.02517415983350383</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>0.02928038048274641</v>
+        <v>0.0387328326103645</v>
       </c>
     </row>
     <row r="13">
@@ -53850,13 +59538,13 @@
         </is>
       </c>
       <c r="H13" s="66" t="n">
-        <v>0.02023052896643625</v>
+        <v>0.02835997506995525</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>0.02023080272240418</v>
+        <v>0.02836002691729699</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>0.02019155658638526</v>
+        <v>0.04509111593223626</v>
       </c>
     </row>
     <row r="14">
@@ -53871,13 +59559,13 @@
         </is>
       </c>
       <c r="H14" s="66" t="n">
-        <v>0.02423904350681942</v>
+        <v>0.03048950070140929</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>0.02441258157484386</v>
+        <v>0.03064661604921706</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>0.02742482687083892</v>
+        <v>0.04723283432904377</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1"/>
@@ -54083,7 +59771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54407,49 +60095,49 @@
         </is>
       </c>
       <c r="U3" s="55" t="n">
-        <v>0.02844650727811221</v>
+        <v>0.03123807087072469</v>
       </c>
       <c r="V3" s="55" t="n">
-        <v>0.02841716740814283</v>
+        <v>0.03423508640036999</v>
       </c>
       <c r="W3" s="55" t="n">
-        <v>0.02003126698380895</v>
+        <v>0.02676212479284179</v>
       </c>
       <c r="X3" s="55" t="n">
-        <v>0.02023052896643625</v>
+        <v>0.02835997506995525</v>
       </c>
       <c r="Y3" s="55" t="n">
-        <v>0.02423904350681942</v>
+        <v>0.03048950070140929</v>
       </c>
       <c r="Z3" s="55" t="n">
-        <v>0.02844673332410395</v>
+        <v>0.03123756488180567</v>
       </c>
       <c r="AA3" s="55" t="n">
-        <v>0.02846176873157642</v>
+        <v>0.03430743211896899</v>
       </c>
       <c r="AB3" s="55" t="n">
-        <v>0.01948453111277258</v>
+        <v>0.02517415983350383</v>
       </c>
       <c r="AC3" s="55" t="n">
-        <v>0.02023080272240418</v>
+        <v>0.02836002691729699</v>
       </c>
       <c r="AD3" s="55" t="n">
-        <v>0.02441258157484386</v>
+        <v>0.03064661604921706</v>
       </c>
       <c r="AE3" s="55" t="n">
-        <v>0.03694183282830633</v>
+        <v>0.04368813431780767</v>
       </c>
       <c r="AF3" s="55" t="n">
-        <v>0.03612757126674167</v>
+        <v>0.04587774544921894</v>
       </c>
       <c r="AG3" s="55" t="n">
-        <v>0.02928038048274641</v>
+        <v>0.0387328326103645</v>
       </c>
       <c r="AH3" s="55" t="n">
-        <v>0.02019155658638526</v>
+        <v>0.04509111593223626</v>
       </c>
       <c r="AI3" s="55" t="n">
-        <v>0.02742482687083892</v>
+        <v>0.04723283432904377</v>
       </c>
     </row>
     <row r="4">
@@ -54762,6 +60450,58 @@
       </c>
       <c r="P9" s="55" t="n">
         <v>0.02742111723366172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>🔵 05.09 Cmt</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="n">
+        <v>0.0424043252411746</v>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>0.05750676236927861</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>0.05368555602897316</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>0.06087775948403126</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>0.05549132947976879</v>
+      </c>
+      <c r="G10" s="55" t="n">
+        <v>0.04240089111261253</v>
+      </c>
+      <c r="H10" s="55" t="n">
+        <v>0.05769008566853923</v>
+      </c>
+      <c r="I10" s="55" t="n">
+        <v>0.04793267471642883</v>
+      </c>
+      <c r="J10" s="55" t="n">
+        <v>0.06087692369686823</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>0.05558275394670983</v>
+      </c>
+      <c r="L10" s="55" t="n">
+        <v>0.07067334027581308</v>
+      </c>
+      <c r="M10" s="55" t="n">
+        <v>0.08487844217912797</v>
+      </c>
+      <c r="N10" s="55" t="n">
+        <v>0.07654264112083684</v>
+      </c>
+      <c r="O10" s="55" t="n">
+        <v>0.1446893533156403</v>
+      </c>
+      <c r="P10" s="55" t="n">
+        <v>0.1264648641618631</v>
       </c>
     </row>
   </sheetData>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -578,9 +578,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -607,16 +607,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$10</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -642,6 +645,9 @@
                   <v>0.02844021235358557</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.0424043252411746</v>
+                </pt>
+                <pt idx="9">
                   <v>0.0424043252411746</v>
                 </pt>
               </numCache>
@@ -688,9 +694,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -717,16 +723,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$10</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -752,6 +761,9 @@
                   <v>0.0284066997727464</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05750676236927861</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05750676236927861</v>
                 </pt>
               </numCache>
@@ -798,9 +810,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -827,16 +839,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$10</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -863,6 +878,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.05368555602897316</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.05363984674329502</v>
                 </pt>
               </numCache>
             </numRef>
@@ -908,9 +926,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -937,16 +955,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$10</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -972,6 +993,9 @@
                   <v>0.02023099065475184</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.06087775948403126</v>
+                </pt>
+                <pt idx="9">
                   <v>0.06087775948403126</v>
                 </pt>
               </numCache>
@@ -1018,9 +1042,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1047,16 +1071,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$10</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -1082,6 +1109,9 @@
                   <v>0.02429357798165137</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05549132947976879</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05549132947976879</v>
                 </pt>
               </numCache>
@@ -1203,9 +1233,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1232,16 +1262,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$10</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -1267,6 +1300,9 @@
                   <v>0.0284066997727464</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05750676236927861</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05750676236927861</v>
                 </pt>
               </numCache>
@@ -1408,9 +1444,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1437,16 +1473,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$10</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -1472,6 +1511,9 @@
                   <v>0.02849479113841517</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05769008566853923</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05769008566853923</v>
                 </pt>
               </numCache>
@@ -1613,9 +1655,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1642,16 +1684,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$10</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -1677,6 +1722,9 @@
                   <v>0.03610505062457936</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.08487844217912797</v>
+                </pt>
+                <pt idx="9">
                   <v>0.08487844217912797</v>
                 </pt>
               </numCache>
@@ -1818,9 +1866,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1847,16 +1895,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$10</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -1883,6 +1934,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.05368555602897316</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.05363984674329502</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2023,9 +2077,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2052,16 +2106,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$10</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -2088,6 +2145,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.04793267471642883</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.04769736842105263</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2228,9 +2288,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2257,16 +2317,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$10</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -2293,6 +2356,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.07654264112083684</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.07642550554801916</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2433,9 +2499,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2462,16 +2528,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$10</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -2497,6 +2566,9 @@
                   <v>0.02023099065475184</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.06087775948403126</v>
+                </pt>
+                <pt idx="9">
                   <v>0.06087775948403126</v>
                 </pt>
               </numCache>
@@ -2638,9 +2710,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2667,16 +2739,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$10</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -2702,6 +2777,9 @@
                   <v>0.0202311723225774</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.06087692369686823</v>
+                </pt>
+                <pt idx="9">
                   <v>0.06087692369686823</v>
                 </pt>
               </numCache>
@@ -2843,9 +2921,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -2872,16 +2950,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$10</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -2907,6 +2988,9 @@
                   <v>0.02019121345887606</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.1446893533156403</v>
+                </pt>
+                <pt idx="9">
                   <v>0.1446893533156403</v>
                 </pt>
               </numCache>
@@ -3048,9 +3132,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3077,16 +3161,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$10</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -3112,6 +3199,9 @@
                   <v>0.02429357798165137</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05549132947976879</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05549132947976879</v>
                 </pt>
               </numCache>
@@ -3253,9 +3343,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3282,16 +3372,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$10</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -3317,6 +3410,9 @@
                   <v>0.02842845746609617</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.04240089111261253</v>
+                </pt>
+                <pt idx="9">
                   <v>0.04240089111261253</v>
                 </pt>
               </numCache>
@@ -3363,9 +3459,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3392,16 +3488,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$H$2:$H$10</f>
+              <f>'GRAFIK_VERILERI'!$H$2:$H$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0285090304898068</v>
                 </pt>
@@ -3427,6 +3526,9 @@
                   <v>0.02849479113841517</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05769008566853923</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05769008566853923</v>
                 </pt>
               </numCache>
@@ -3473,9 +3575,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3502,16 +3604,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$I$2:$I$10</f>
+              <f>'GRAFIK_VERILERI'!$I$2:$I$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02058504875406284</v>
                 </pt>
@@ -3538,6 +3643,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.04793267471642883</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.04769736842105263</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3583,9 +3691,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3612,16 +3720,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$J$2:$J$10</f>
+              <f>'GRAFIK_VERILERI'!$J$2:$J$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02023002817773203</v>
                 </pt>
@@ -3647,6 +3758,9 @@
                   <v>0.0202311723225774</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.06087692369686823</v>
+                </pt>
+                <pt idx="9">
                   <v>0.06087692369686823</v>
                 </pt>
               </numCache>
@@ -3693,9 +3807,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3722,16 +3836,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$10</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3757,6 +3874,9 @@
                   <v>0.02447024757283306</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05558275394670983</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05558275394670983</v>
                 </pt>
               </numCache>
@@ -3878,9 +3998,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -3907,16 +4027,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$K$2:$K$10</f>
+              <f>'GRAFIK_VERILERI'!$K$2:$K$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02445509246121618</v>
                 </pt>
@@ -3942,6 +4065,9 @@
                   <v>0.02447024757283306</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.05558275394670983</v>
+                </pt>
+                <pt idx="9">
                   <v>0.05558275394670983</v>
                 </pt>
               </numCache>
@@ -4083,9 +4209,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4112,16 +4238,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$10</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4147,6 +4276,9 @@
                   <v>0.02742111723366172</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.1264648641618631</v>
+                </pt>
+                <pt idx="9">
                   <v>0.1264648641618631</v>
                 </pt>
               </numCache>
@@ -4288,9 +4420,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4317,16 +4449,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$10</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -4352,6 +4487,9 @@
                   <v>0.03694098205438084</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.07067334027581308</v>
+                </pt>
+                <pt idx="9">
                   <v>0.07067334027581308</v>
                 </pt>
               </numCache>
@@ -4398,9 +4536,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4427,16 +4565,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$M$2:$M$10</f>
+              <f>'GRAFIK_VERILERI'!$M$2:$M$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.03623508807809576</v>
                 </pt>
@@ -4462,6 +4603,9 @@
                   <v>0.03610505062457936</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.08487844217912797</v>
+                </pt>
+                <pt idx="9">
                   <v>0.08487844217912797</v>
                 </pt>
               </numCache>
@@ -4508,9 +4652,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4537,16 +4681,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$N$2:$N$10</f>
+              <f>'GRAFIK_VERILERI'!$N$2:$N$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02941852054231659</v>
                 </pt>
@@ -4573,6 +4720,9 @@
                 </pt>
                 <pt idx="8">
                   <v>0.07654264112083684</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.07642550554801916</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4618,9 +4768,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4647,16 +4797,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$O$2:$O$10</f>
+              <f>'GRAFIK_VERILERI'!$O$2:$O$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.020191203292302</v>
                 </pt>
@@ -4682,6 +4835,9 @@
                   <v>0.02019121345887606</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.1446893533156403</v>
+                </pt>
+                <pt idx="9">
                   <v>0.1446893533156403</v>
                 </pt>
               </numCache>
@@ -4728,9 +4884,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -4757,16 +4913,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$P$2:$P$10</f>
+              <f>'GRAFIK_VERILERI'!$P$2:$P$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02750535420451208</v>
                 </pt>
@@ -4792,6 +4951,9 @@
                   <v>0.02742111723366172</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.1264648641618631</v>
+                </pt>
+                <pt idx="9">
                   <v>0.1264648641618631</v>
                 </pt>
               </numCache>
@@ -4935,7 +5097,7 @@
                   <v>0.03553378696044311</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03123807087072469</v>
+                  <v>0.03309911326579967</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5003,7 +5165,7 @@
                   <v>0.04311562150687483</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03423508640036999</v>
+                  <v>0.03811369906185476</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5071,7 +5233,7 @@
                   <v>0.03847709584999994</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02676212479284179</v>
+                  <v>0.03124174511791733</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5139,7 +5301,7 @@
                   <v>0.04104187506584386</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02835997506995525</v>
+                  <v>0.03377960580563458</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5207,7 +5369,7 @@
                   <v>0.04760750668842017</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03048950070140929</v>
+                  <v>0.03465647216446921</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5248,8 +5410,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05073431397275693"/>
-          <min val="0.02363531750850503"/>
+          <max val="0.0500623709239956"/>
+          <min val="0.02878688088234191"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5350,7 +5512,7 @@
                   <v>0.03553642841103422</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03123756488180567</v>
+                  <v>0.03309811925360681</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5418,7 +5580,7 @@
                   <v>0.0432699268677014</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03430743211896899</v>
+                  <v>0.03820454104389736</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5486,7 +5648,7 @@
                   <v>0.03535742466332828</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02517415983350383</v>
+                  <v>0.02892802793142863</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5554,7 +5716,7 @@
                   <v>0.0514487601107881</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.02836002691729699</v>
+                  <v>0.03377950971389219</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5622,7 +5784,7 @@
                   <v>0.04783493387226885</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.03064661604921706</v>
+                  <v>0.03480263903213252</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5663,8 +5825,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.05538995015238074"/>
-          <min val="0.02123296979191119"/>
+          <max val="0.05482686993769201"/>
+          <min val="0.02554991810452471"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -5765,7 +5927,7 @@
                   <v>0.05383117747984287</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.04368813431780767</v>
+                  <v>0.04818566864414191</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5833,7 +5995,7 @@
                   <v>0.06066925394146307</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.04587774544921894</v>
+                  <v>0.05237786157087044</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5901,7 +6063,7 @@
                   <v>0.0540849048600331</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.0387328326103645</v>
+                  <v>0.04501494476664027</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5969,7 +6131,7 @@
                   <v>0.08301204597474589</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.04509111593223626</v>
+                  <v>0.06169082216280359</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6037,7 +6199,7 @@
                   <v>0.1017248276143379</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.04723283432904377</v>
+                  <v>0.06043817263451366</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6078,8 +6240,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.111173626864934"/>
-          <min val="0.02928403335976848"/>
+          <max val="0.1102313100414926"/>
+          <min val="0.03650846233948563"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -6158,9 +6320,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6187,16 +6349,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$10</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -6222,6 +6387,9 @@
                   <v>0.02844021235358557</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.0424043252411746</v>
+                </pt>
+                <pt idx="9">
                   <v>0.0424043252411746</v>
                 </pt>
               </numCache>
@@ -6363,9 +6531,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6392,16 +6560,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$G$2:$G$10</f>
+              <f>'GRAFIK_VERILERI'!$G$2:$G$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.02853823251760947</v>
                 </pt>
@@ -6427,6 +6598,9 @@
                   <v>0.02842845746609617</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.04240089111261253</v>
+                </pt>
+                <pt idx="9">
                   <v>0.04240089111261253</v>
                 </pt>
               </numCache>
@@ -6568,9 +6742,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$10</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -6597,16 +6771,19 @@
                 </pt>
                 <pt idx="8">
                   <v>🔵 05.09 Cmt</v>
+                </pt>
+                <pt idx="9">
+                  <v>🔴 06.09 Paz</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$L$2:$L$10</f>
+              <f>'GRAFIK_VERILERI'!$L$2:$L$11</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>0.0369612266397948</v>
                 </pt>
@@ -6632,6 +6809,9 @@
                   <v>0.03694098205438084</v>
                 </pt>
                 <pt idx="8">
+                  <v>0.07067334027581308</v>
+                </pt>
+                <pt idx="9">
                   <v>0.07067334027581308</v>
                 </pt>
               </numCache>
@@ -7205,8 +7385,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N973" headerRowCount="1">
-  <autoFilter ref="A1:N973"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GecmisTable" displayName="GecmisTable" ref="A1:N1081" headerRowCount="1">
+  <autoFilter ref="A1:N1081"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tarih"/>
     <tableColumn id="2" name="Saat"/>
@@ -7615,10 +7795,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -7664,10 +7844,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7713,10 +7893,10 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
@@ -7762,10 +7942,10 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7811,10 +7991,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
@@ -7860,10 +8040,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
@@ -7909,10 +8089,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
@@ -7958,10 +8138,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
@@ -8007,10 +8187,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -8018,48 +8198,48 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>48.2699</v>
+        <v>48.3137</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48.3494</v>
+        <v>48.3933</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0795</v>
+        <v>0.0796</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.001646989117441718</v>
+        <v>0.001647565804316374</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>55.9826</v>
+        <v>56.0357</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>56.1883</v>
+        <v>56.2416</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.2057</v>
+        <v>0.2059</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.003674355960602044</v>
+        <v>0.003674443256709562</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>6825.26</v>
+        <v>6831.46</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>6866.18</v>
+        <v>6872.41</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>40.92</v>
+        <v>40.95</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.005995376000328193</v>
+        <v>0.00599432624944009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -8067,48 +8247,48 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>47.7364</v>
+        <v>47.7363</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>49.7208</v>
+        <v>49.7207</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>1.9844</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.04156995500289087</v>
+        <v>0.04157004208537319</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>55.3526</v>
+        <v>55.3525</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>57.4906</v>
+        <v>57.4905</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>2.138</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.03862510523444247</v>
+        <v>0.03862517501467865</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>5805.25</v>
+        <v>5805.24</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>7573.31</v>
+        <v>7573.29</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1768.06</v>
+        <v>1768.05</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.3045622496877826</v>
+        <v>0.304561051739463</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -8154,10 +8334,10 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
@@ -8203,10 +8383,10 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
@@ -8252,10 +8432,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
@@ -8301,10 +8481,10 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -8350,10 +8530,10 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
@@ -8399,10 +8579,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
@@ -8410,48 +8590,48 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>47.8265</v>
+        <v>47.8264</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>48.4543</v>
+        <v>48.4542</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0.6278</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.01312661390651626</v>
+        <v>0.01312664135289296</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>55.6569</v>
+        <v>55.6568</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>56.2918</v>
+        <v>56.2917</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>0.6349</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.01140739063799816</v>
+        <v>0.01140741113394949</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6827.31</v>
+        <v>6827.3</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>6969.07</v>
+        <v>6969.05</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>141.76</v>
+        <v>141.75</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.02076366826759002</v>
+        <v>0.0207622339724342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
@@ -8467,24 +8647,24 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n">
-        <v>6834.76</v>
+        <v>6834.62</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>7034.29</v>
+        <v>7034.06</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>199.53</v>
+        <v>199.44</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.02919341717924257</v>
+        <v>0.02918084692345734</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -8492,48 +8672,48 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>47.5517</v>
+        <v>47.5991</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>49.4789</v>
+        <v>49.5206</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1.9272</v>
+        <v>1.9215</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.04052851948510779</v>
+        <v>0.04036841032708602</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>54.7851</v>
+        <v>54.8418</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>57.9411</v>
+        <v>57.9922</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>3.156</v>
+        <v>3.1504</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.05760690406698171</v>
+        <v>0.05744523338037774</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>6710.16</v>
+        <v>6717.61</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7363.91</v>
+        <v>7370.64</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>653.75</v>
+        <v>653.03</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.09742688698928192</v>
+        <v>0.09721165712210146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -8553,16 +8733,16 @@
         <v>0.04823230825290025</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>54.8911</v>
+        <v>54.8132</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>57.2139</v>
+        <v>57.4618</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2.3228</v>
+        <v>2.6486</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.04231651397038864</v>
+        <v>0.04832047754920347</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>6662.76</v>
@@ -8579,10 +8759,10 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -8628,10 +8808,10 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
@@ -8677,10 +8857,10 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
@@ -8688,48 +8868,48 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>44.8059</v>
+        <v>44.8474</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>49.2963</v>
+        <v>49.3407</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>4.4904</v>
+        <v>4.4933</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.1002189443800928</v>
+        <v>0.1001908694818429</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>52.017</v>
+        <v>52.0651</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>57.2734</v>
+        <v>57.325</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>5.2564</v>
+        <v>5.2599</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.1010515792913855</v>
+        <v>0.1010254469884817</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6430.53</v>
+        <v>6435.95</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>7056.75</v>
+        <v>7063.67</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>626.22</v>
+        <v>627.72</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.09738233084986775</v>
+        <v>0.09753338667951118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
@@ -8767,10 +8947,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
@@ -8816,10 +8996,10 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
@@ -8865,10 +9045,10 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -8914,10 +9094,10 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
@@ -8933,24 +9113,24 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="12" t="n">
-        <v>6834.75</v>
+        <v>6834.62</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>7020.24</v>
+        <v>7020.02</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>185.49</v>
+        <v>185.4</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.02713925161856688</v>
+        <v>0.02712659957686016</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
@@ -8996,10 +9176,10 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
@@ -9007,48 +9187,48 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>48.1299</v>
+        <v>48.1293</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>48.6747</v>
+        <v>48.6741</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0.5448</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.01131936696315596</v>
+        <v>0.01131950807512264</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>55.6847</v>
+        <v>55.684</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>56.5284</v>
+        <v>56.5277</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.8437</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.01515137910413453</v>
+        <v>0.0151515695711515</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6864.2</v>
+        <v>6864.09</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>7379.02</v>
+        <v>7378.9</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>514.8200000000001</v>
+        <v>514.8099999999999</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.07500072841700417</v>
+        <v>0.07500047347864029</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
@@ -9094,10 +9274,10 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -9143,10 +9323,10 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
@@ -9192,10 +9372,10 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C35" s="46" t="inlineStr">
         <is>
@@ -9233,10 +9413,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
@@ -9244,48 +9424,48 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>46.94</v>
+        <v>46.98</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>49.46</v>
+        <v>49.5</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>2.52</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.05368555602897316</v>
+        <v>0.05363984674329502</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>54.66</v>
+        <v>54.72</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>57.28</v>
+        <v>57.33</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.04793267471642883</v>
+        <v>0.04769736842105263</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6642.18</v>
+        <v>6649.22</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>7150.59</v>
+        <v>7157.39</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>508.41</v>
+        <v>508.17</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.07654264112083684</v>
+        <v>0.07642550554801916</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -9331,10 +9511,10 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -9380,10 +9560,10 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
@@ -9441,7 +9621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N973"/>
+  <dimension ref="A1:N1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58130,6 +58310,5406 @@
       <c r="M973" t="inlineStr"/>
       <c r="N973" s="6" t="n">
         <v>0.5665162037037037</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B974" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C974" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D974" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E974" s="8" t="n">
+        <v>46.951</v>
+      </c>
+      <c r="F974" s="8" t="n">
+        <v>49.651</v>
+      </c>
+      <c r="G974" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H974" s="9" t="n">
+        <v>0.05750676236927861</v>
+      </c>
+      <c r="I974" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J974" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K974" s="54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L974" s="55" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="M974" t="inlineStr"/>
+      <c r="N974" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B975" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C975" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D975" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E975" s="10" t="n">
+        <v>54.5241</v>
+      </c>
+      <c r="F975" s="10" t="n">
+        <v>57.6696</v>
+      </c>
+      <c r="G975" s="10" t="n">
+        <v>3.1455</v>
+      </c>
+      <c r="H975" s="11" t="n">
+        <v>0.05769008566853923</v>
+      </c>
+      <c r="I975" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J975" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K975" s="54" t="n">
+        <v>3.1455</v>
+      </c>
+      <c r="L975" s="55" t="n">
+        <v>0.05769999999999999</v>
+      </c>
+      <c r="M975" t="inlineStr"/>
+      <c r="N975" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B976" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C976" s="7" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D976" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E976" s="12" t="n">
+        <v>6720.67</v>
+      </c>
+      <c r="F976" s="12" t="n">
+        <v>7291.11</v>
+      </c>
+      <c r="G976" s="12" t="n">
+        <v>570.4400000000001</v>
+      </c>
+      <c r="H976" s="13" t="n">
+        <v>0.08487844217912797</v>
+      </c>
+      <c r="I976" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J976" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K976" s="54" t="n">
+        <v>570.4299999999999</v>
+      </c>
+      <c r="L976" s="55" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="M976" t="inlineStr"/>
+      <c r="N976" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B977" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C977" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D977" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E977" s="8" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="F977" s="8" t="n">
+        <v>48.963</v>
+      </c>
+      <c r="G977" s="8" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H977" s="9" t="n">
+        <v>0.0204877032096707</v>
+      </c>
+      <c r="I977" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J977" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K977" s="54" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="L977" s="55" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="M977" t="inlineStr"/>
+      <c r="N977" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B978" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C978" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D978" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E978" s="10" t="n">
+        <v>55.719</v>
+      </c>
+      <c r="F978" s="10" t="n">
+        <v>56.866</v>
+      </c>
+      <c r="G978" s="10" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="H978" s="11" t="n">
+        <v>0.02058543764245589</v>
+      </c>
+      <c r="I978" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J978" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K978" s="54" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L978" s="55" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="M978" t="inlineStr"/>
+      <c r="N978" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B979" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C979" s="14" t="inlineStr">
+        <is>
+          <t>Albaraka Türk</t>
+        </is>
+      </c>
+      <c r="D979" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E979" s="12" t="n">
+        <v>6783.95</v>
+      </c>
+      <c r="F979" s="12" t="n">
+        <v>6952.63</v>
+      </c>
+      <c r="G979" s="12" t="n">
+        <v>168.68</v>
+      </c>
+      <c r="H979" s="13" t="n">
+        <v>0.02486457005137125</v>
+      </c>
+      <c r="I979" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J979" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K979" s="54" t="n">
+        <v>168.68</v>
+      </c>
+      <c r="L979" s="55" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="M979" t="inlineStr"/>
+      <c r="N979" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B980" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C980" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D980" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E980" s="8" t="n">
+        <v>46.299</v>
+      </c>
+      <c r="F980" s="8" t="n">
+        <v>50.301</v>
+      </c>
+      <c r="G980" s="8" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="H980" s="9" t="n">
+        <v>0.08643815201192251</v>
+      </c>
+      <c r="I980" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J980" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K980" s="54" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="L980" s="55" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="M980" t="inlineStr"/>
+      <c r="N980" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B981" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C981" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D981" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E981" s="10" t="n">
+        <v>53.617</v>
+      </c>
+      <c r="F981" s="10" t="n">
+        <v>58.434</v>
+      </c>
+      <c r="G981" s="10" t="n">
+        <v>4.817</v>
+      </c>
+      <c r="H981" s="11" t="n">
+        <v>0.08984090866702726</v>
+      </c>
+      <c r="I981" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J981" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K981" s="54" t="n">
+        <v>4.817</v>
+      </c>
+      <c r="L981" s="55" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="M981" t="inlineStr"/>
+      <c r="N981" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B982" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C982" s="15" t="inlineStr">
+        <is>
+          <t>Alternatif Bank</t>
+        </is>
+      </c>
+      <c r="D982" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E982" s="12" t="n">
+        <v>6582.3</v>
+      </c>
+      <c r="F982" s="12" t="n">
+        <v>7179.59</v>
+      </c>
+      <c r="G982" s="12" t="n">
+        <v>597.29</v>
+      </c>
+      <c r="H982" s="13" t="n">
+        <v>0.0907418379593759</v>
+      </c>
+      <c r="I982" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J982" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K982" s="54" t="n">
+        <v>597.29</v>
+      </c>
+      <c r="L982" s="55" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="M982" t="inlineStr"/>
+      <c r="N982" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B983" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C983" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D983" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E983" s="8" t="n">
+        <v>48.258</v>
+      </c>
+      <c r="F983" s="8" t="n">
+        <v>48.542</v>
+      </c>
+      <c r="G983" s="8" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="H983" s="9" t="n">
+        <v>0.005885034605661238</v>
+      </c>
+      <c r="I983" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J983" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K983" s="54" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="L983" s="55" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="M983" t="inlineStr"/>
+      <c r="N983" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B984" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C984" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D984" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E984" s="10" t="n">
+        <v>55.893</v>
+      </c>
+      <c r="F984" s="10" t="n">
+        <v>56.374</v>
+      </c>
+      <c r="G984" s="10" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="H984" s="11" t="n">
+        <v>0.008605728803249064</v>
+      </c>
+      <c r="I984" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J984" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K984" s="54" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L984" s="55" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="M984" t="inlineStr"/>
+      <c r="N984" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B985" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C985" s="16" t="inlineStr">
+        <is>
+          <t>Altınkaynak</t>
+        </is>
+      </c>
+      <c r="D985" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E985" s="12" t="n">
+        <v>6784.36</v>
+      </c>
+      <c r="F985" s="12" t="n">
+        <v>6970</v>
+      </c>
+      <c r="G985" s="12" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="H985" s="13" t="n">
+        <v>0.02736293474992483</v>
+      </c>
+      <c r="I985" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J985" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K985" s="54" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="L985" s="55" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="M985" t="inlineStr"/>
+      <c r="N985" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B986" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C986" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D986" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E986" s="8" t="n">
+        <v>47.7626</v>
+      </c>
+      <c r="F986" s="8" t="n">
+        <v>48.8155</v>
+      </c>
+      <c r="G986" s="8" t="n">
+        <v>1.0529</v>
+      </c>
+      <c r="H986" s="9" t="n">
+        <v>0.02204444481665571</v>
+      </c>
+      <c r="I986" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J986" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K986" s="54" t="n">
+        <v>1.0529</v>
+      </c>
+      <c r="L986" s="55" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="M986" t="inlineStr"/>
+      <c r="N986" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B987" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C987" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D987" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E987" s="10" t="n">
+        <v>54.8361</v>
+      </c>
+      <c r="F987" s="10" t="n">
+        <v>57.2538</v>
+      </c>
+      <c r="G987" s="10" t="n">
+        <v>2.4177</v>
+      </c>
+      <c r="H987" s="11" t="n">
+        <v>0.04408956873300617</v>
+      </c>
+      <c r="I987" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J987" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K987" s="54" t="n">
+        <v>2.4177</v>
+      </c>
+      <c r="L987" s="55" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="M987" t="inlineStr"/>
+      <c r="N987" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B988" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C988" s="17" t="inlineStr">
+        <is>
+          <t>Anadolubank</t>
+        </is>
+      </c>
+      <c r="D988" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E988" s="12" t="n">
+        <v>6242.42</v>
+      </c>
+      <c r="F988" s="12" t="n">
+        <v>7453.4</v>
+      </c>
+      <c r="G988" s="12" t="n">
+        <v>1210.98</v>
+      </c>
+      <c r="H988" s="13" t="n">
+        <v>0.1939920735868461</v>
+      </c>
+      <c r="I988" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J988" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K988" s="54" t="n">
+        <v>1210.98</v>
+      </c>
+      <c r="L988" s="55" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="M988" t="inlineStr"/>
+      <c r="N988" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B989" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C989" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D989" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E989" s="8" t="n">
+        <v>46.231</v>
+      </c>
+      <c r="F989" s="8" t="n">
+        <v>50.376</v>
+      </c>
+      <c r="G989" s="8" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="H989" s="9" t="n">
+        <v>0.08965845428392205</v>
+      </c>
+      <c r="I989" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J989" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K989" s="54" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="L989" s="55" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="M989" t="inlineStr"/>
+      <c r="N989" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B990" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C990" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D990" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E990" s="10" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="F990" s="10" t="n">
+        <v>58.481</v>
+      </c>
+      <c r="G990" s="10" t="n">
+        <v>4.811</v>
+      </c>
+      <c r="H990" s="11" t="n">
+        <v>0.08964039500652132</v>
+      </c>
+      <c r="I990" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J990" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K990" s="54" t="n">
+        <v>4.811</v>
+      </c>
+      <c r="L990" s="55" t="n">
+        <v>0.08960000000000001</v>
+      </c>
+      <c r="M990" t="inlineStr"/>
+      <c r="N990" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B991" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C991" s="18" t="inlineStr">
+        <is>
+          <t>CEPTETEB</t>
+        </is>
+      </c>
+      <c r="D991" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E991" s="12" t="n">
+        <v>5902.36</v>
+      </c>
+      <c r="F991" s="12" t="n">
+        <v>7899.21</v>
+      </c>
+      <c r="G991" s="12" t="n">
+        <v>1996.85</v>
+      </c>
+      <c r="H991" s="13" t="n">
+        <v>0.3383138270115683</v>
+      </c>
+      <c r="I991" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J991" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K991" s="54" t="n">
+        <v>1996.85</v>
+      </c>
+      <c r="L991" s="55" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="M991" t="inlineStr"/>
+      <c r="N991" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B992" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C992" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D992" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E992" s="8" t="n">
+        <v>46.8549</v>
+      </c>
+      <c r="F992" s="8" t="n">
+        <v>49.655</v>
+      </c>
+      <c r="G992" s="8" t="n">
+        <v>2.8001</v>
+      </c>
+      <c r="H992" s="9" t="n">
+        <v>0.05976109222301189</v>
+      </c>
+      <c r="I992" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J992" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K992" s="54" t="n">
+        <v>2.8001</v>
+      </c>
+      <c r="L992" s="55" t="n">
+        <v>0.05980000000000001</v>
+      </c>
+      <c r="M992" t="inlineStr"/>
+      <c r="N992" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B993" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C993" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D993" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E993" s="10" t="n">
+        <v>54.3943</v>
+      </c>
+      <c r="F993" s="10" t="n">
+        <v>57.6499</v>
+      </c>
+      <c r="G993" s="10" t="n">
+        <v>3.2556</v>
+      </c>
+      <c r="H993" s="11" t="n">
+        <v>0.05985185947792324</v>
+      </c>
+      <c r="I993" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J993" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K993" s="54" t="n">
+        <v>3.2556</v>
+      </c>
+      <c r="L993" s="55" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="M993" t="inlineStr"/>
+      <c r="N993" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B994" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C994" s="19" t="inlineStr">
+        <is>
+          <t>Denizbank</t>
+        </is>
+      </c>
+      <c r="D994" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E994" s="12" t="n">
+        <v>6668.77</v>
+      </c>
+      <c r="F994" s="12" t="n">
+        <v>7068.95</v>
+      </c>
+      <c r="G994" s="12" t="n">
+        <v>400.18</v>
+      </c>
+      <c r="H994" s="13" t="n">
+        <v>0.06000806745471803</v>
+      </c>
+      <c r="I994" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J994" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K994" s="54" t="n">
+        <v>400.18</v>
+      </c>
+      <c r="L994" s="55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M994" t="inlineStr"/>
+      <c r="N994" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B995" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C995" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D995" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E995" s="8" t="n">
+        <v>48.0852</v>
+      </c>
+      <c r="F995" s="8" t="n">
+        <v>48.4354</v>
+      </c>
+      <c r="G995" s="8" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="H995" s="9" t="n">
+        <v>0.007282906174872934</v>
+      </c>
+      <c r="I995" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J995" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K995" s="54" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="L995" s="55" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="M995" t="inlineStr"/>
+      <c r="N995" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B996" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C996" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D996" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E996" s="10" t="n">
+        <v>55.8259</v>
+      </c>
+      <c r="F996" s="10" t="n">
+        <v>56.2539</v>
+      </c>
+      <c r="G996" s="10" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="H996" s="11" t="n">
+        <v>0.00766669234172669</v>
+      </c>
+      <c r="I996" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J996" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K996" s="54" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="L996" s="55" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="M996" t="inlineStr"/>
+      <c r="N996" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B997" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C997" s="20" t="inlineStr">
+        <is>
+          <t>DestekBank</t>
+        </is>
+      </c>
+      <c r="D997" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E997" s="12" t="n">
+        <v>6805.05</v>
+      </c>
+      <c r="F997" s="12" t="n">
+        <v>6876.24</v>
+      </c>
+      <c r="G997" s="12" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="H997" s="13" t="n">
+        <v>0.0104613485573214</v>
+      </c>
+      <c r="I997" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J997" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K997" s="54" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="L997" s="55" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="M997" t="inlineStr"/>
+      <c r="N997" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B998" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C998" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D998" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E998" s="8" t="n">
+        <v>48.3137</v>
+      </c>
+      <c r="F998" s="8" t="n">
+        <v>48.3933</v>
+      </c>
+      <c r="G998" s="8" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="H998" s="9" t="n">
+        <v>0.001647565804316374</v>
+      </c>
+      <c r="I998" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J998" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K998" s="54" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="L998" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M998" t="inlineStr"/>
+      <c r="N998" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B999" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C999" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D999" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E999" s="10" t="n">
+        <v>56.0357</v>
+      </c>
+      <c r="F999" s="10" t="n">
+        <v>56.2416</v>
+      </c>
+      <c r="G999" s="10" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="H999" s="11" t="n">
+        <v>0.003674443256709562</v>
+      </c>
+      <c r="I999" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J999" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K999" s="54" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="L999" s="55" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="M999" t="inlineStr"/>
+      <c r="N999" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1000" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1000" s="21" t="inlineStr">
+        <is>
+          <t>Dünya Katılım</t>
+        </is>
+      </c>
+      <c r="D1000" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1000" s="12" t="n">
+        <v>6831.46</v>
+      </c>
+      <c r="F1000" s="12" t="n">
+        <v>6872.41</v>
+      </c>
+      <c r="G1000" s="12" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="H1000" s="13" t="n">
+        <v>0.00599432624944009</v>
+      </c>
+      <c r="I1000" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1000" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1000" s="54" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="L1000" s="55" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M1000" t="inlineStr"/>
+      <c r="N1000" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1001" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1001" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D1001" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1001" s="8" t="n">
+        <v>47.7363</v>
+      </c>
+      <c r="F1001" s="8" t="n">
+        <v>49.7207</v>
+      </c>
+      <c r="G1001" s="8" t="n">
+        <v>1.9844</v>
+      </c>
+      <c r="H1001" s="9" t="n">
+        <v>0.04157004208537319</v>
+      </c>
+      <c r="I1001" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1001" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1001" s="54" t="n">
+        <v>1.9845</v>
+      </c>
+      <c r="L1001" s="55" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="M1001" t="inlineStr"/>
+      <c r="N1001" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1002" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1002" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D1002" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1002" s="10" t="n">
+        <v>55.3525</v>
+      </c>
+      <c r="F1002" s="10" t="n">
+        <v>57.4905</v>
+      </c>
+      <c r="G1002" s="10" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="H1002" s="11" t="n">
+        <v>0.03862517501467865</v>
+      </c>
+      <c r="I1002" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1002" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1002" s="54" t="n">
+        <v>2.1381</v>
+      </c>
+      <c r="L1002" s="55" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="M1002" t="inlineStr"/>
+      <c r="N1002" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1003" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1003" s="22" t="inlineStr">
+        <is>
+          <t>Emlak Katılım</t>
+        </is>
+      </c>
+      <c r="D1003" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1003" s="12" t="n">
+        <v>5805.24</v>
+      </c>
+      <c r="F1003" s="12" t="n">
+        <v>7573.29</v>
+      </c>
+      <c r="G1003" s="12" t="n">
+        <v>1768.05</v>
+      </c>
+      <c r="H1003" s="13" t="n">
+        <v>0.304561051739463</v>
+      </c>
+      <c r="I1003" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1003" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1003" s="54" t="n">
+        <v>1768.05</v>
+      </c>
+      <c r="L1003" s="55" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="M1003" t="inlineStr"/>
+      <c r="N1003" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1004" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1004" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D1004" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1004" s="8" t="n">
+        <v>47.5925</v>
+      </c>
+      <c r="F1004" s="8" t="n">
+        <v>49.2925</v>
+      </c>
+      <c r="G1004" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H1004" s="9" t="n">
+        <v>0.03571991385197248</v>
+      </c>
+      <c r="I1004" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1004" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1004" s="54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L1004" s="55" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="M1004" t="inlineStr"/>
+      <c r="N1004" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1005" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1005" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D1005" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1005" s="10" t="n">
+        <v>54.9928</v>
+      </c>
+      <c r="F1005" s="10" t="n">
+        <v>57.5346</v>
+      </c>
+      <c r="G1005" s="10" t="n">
+        <v>2.5418</v>
+      </c>
+      <c r="H1005" s="11" t="n">
+        <v>0.04622059615076883</v>
+      </c>
+      <c r="I1005" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1005" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1005" s="54" t="n">
+        <v>2.5418</v>
+      </c>
+      <c r="L1005" s="55" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="M1005" t="inlineStr"/>
+      <c r="N1005" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1006" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1006" s="23" t="inlineStr">
+        <is>
+          <t>Enpara</t>
+        </is>
+      </c>
+      <c r="D1006" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1006" s="12" t="n">
+        <v>6707.38</v>
+      </c>
+      <c r="F1006" s="12" t="n">
+        <v>7104.13</v>
+      </c>
+      <c r="G1006" s="12" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="H1006" s="13" t="n">
+        <v>0.05915126323542128</v>
+      </c>
+      <c r="I1006" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1006" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1006" s="54" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="L1006" s="55" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="M1006" t="inlineStr"/>
+      <c r="N1006" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1007" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1007" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D1007" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1007" s="8" t="n">
+        <v>46.9293</v>
+      </c>
+      <c r="F1007" s="8" t="n">
+        <v>49.9896</v>
+      </c>
+      <c r="G1007" s="8" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="H1007" s="9" t="n">
+        <v>0.06521085974007709</v>
+      </c>
+      <c r="I1007" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1007" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1007" s="54" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="L1007" s="55" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="M1007" t="inlineStr"/>
+      <c r="N1007" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1008" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1008" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D1008" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1008" s="10" t="n">
+        <v>54.2441</v>
+      </c>
+      <c r="F1008" s="10" t="n">
+        <v>58.4498</v>
+      </c>
+      <c r="G1008" s="10" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="H1008" s="11" t="n">
+        <v>0.0775328561078532</v>
+      </c>
+      <c r="I1008" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1008" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1008" s="54" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="L1008" s="55" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="M1008" t="inlineStr"/>
+      <c r="N1008" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1009" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1009" s="24" t="inlineStr">
+        <is>
+          <t>Fibabanka</t>
+        </is>
+      </c>
+      <c r="D1009" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1009" s="12" t="n">
+        <v>6611.27</v>
+      </c>
+      <c r="F1009" s="12" t="n">
+        <v>7337.41</v>
+      </c>
+      <c r="G1009" s="12" t="n">
+        <v>726.14</v>
+      </c>
+      <c r="H1009" s="13" t="n">
+        <v>0.1098336628212129</v>
+      </c>
+      <c r="I1009" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1009" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1009" s="54" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="L1009" s="55" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="M1009" t="inlineStr"/>
+      <c r="N1009" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1010" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1010" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D1010" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1010" s="8" t="n">
+        <v>47.165</v>
+      </c>
+      <c r="F1010" s="8" t="n">
+        <v>49.165</v>
+      </c>
+      <c r="G1010" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1010" s="9" t="n">
+        <v>0.0424043252411746</v>
+      </c>
+      <c r="I1010" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1010" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1010" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1010" s="55" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="M1010" t="inlineStr"/>
+      <c r="N1010" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1011" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1011" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D1011" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1011" s="10" t="n">
+        <v>54.763</v>
+      </c>
+      <c r="F1011" s="10" t="n">
+        <v>57.085</v>
+      </c>
+      <c r="G1011" s="10" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="H1011" s="11" t="n">
+        <v>0.04240089111261253</v>
+      </c>
+      <c r="I1011" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1011" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1011" s="54" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="L1011" s="55" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="M1011" t="inlineStr"/>
+      <c r="N1011" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1012" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1012" s="25" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D1012" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1012" s="12" t="n">
+        <v>6645.08</v>
+      </c>
+      <c r="F1012" s="12" t="n">
+        <v>7114.71</v>
+      </c>
+      <c r="G1012" s="12" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="H1012" s="13" t="n">
+        <v>0.07067334027581308</v>
+      </c>
+      <c r="I1012" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1012" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1012" s="54" t="n">
+        <v>469.64</v>
+      </c>
+      <c r="L1012" s="55" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="M1012" t="inlineStr"/>
+      <c r="N1012" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1013" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1013" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D1013" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1013" s="8" t="n">
+        <v>46.9293</v>
+      </c>
+      <c r="F1013" s="8" t="n">
+        <v>49.9896</v>
+      </c>
+      <c r="G1013" s="8" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="H1013" s="9" t="n">
+        <v>0.06521085974007709</v>
+      </c>
+      <c r="I1013" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1013" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1013" s="54" t="n">
+        <v>3.0603</v>
+      </c>
+      <c r="L1013" s="55" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="M1013" t="inlineStr"/>
+      <c r="N1013" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1014" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1014" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D1014" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1014" s="10" t="n">
+        <v>54.2441</v>
+      </c>
+      <c r="F1014" s="10" t="n">
+        <v>58.4498</v>
+      </c>
+      <c r="G1014" s="10" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="H1014" s="11" t="n">
+        <v>0.0775328561078532</v>
+      </c>
+      <c r="I1014" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1014" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1014" s="54" t="n">
+        <v>4.2057</v>
+      </c>
+      <c r="L1014" s="55" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="M1014" t="inlineStr"/>
+      <c r="N1014" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1015" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1015" s="26" t="inlineStr">
+        <is>
+          <t>Getirfinans</t>
+        </is>
+      </c>
+      <c r="D1015" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1015" s="12" t="n">
+        <v>6611.27</v>
+      </c>
+      <c r="F1015" s="12" t="n">
+        <v>7337.4</v>
+      </c>
+      <c r="G1015" s="12" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="H1015" s="13" t="n">
+        <v>0.1098321502525234</v>
+      </c>
+      <c r="I1015" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1015" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1015" s="54" t="n">
+        <v>726.13</v>
+      </c>
+      <c r="L1015" s="55" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="M1015" t="inlineStr"/>
+      <c r="N1015" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1016" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1016" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D1016" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1016" s="8" t="n">
+        <v>47.1623</v>
+      </c>
+      <c r="F1016" s="8" t="n">
+        <v>49.8623</v>
+      </c>
+      <c r="G1016" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1016" s="9" t="n">
+        <v>0.05724911634928746</v>
+      </c>
+      <c r="I1016" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1016" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1016" s="54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L1016" s="55" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="M1016" t="inlineStr"/>
+      <c r="N1016" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1017" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1017" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D1017" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1017" s="10" t="n">
+        <v>54.8025</v>
+      </c>
+      <c r="F1017" s="10" t="n">
+        <v>57.9399</v>
+      </c>
+      <c r="G1017" s="10" t="n">
+        <v>3.1374</v>
+      </c>
+      <c r="H1017" s="11" t="n">
+        <v>0.05724921308334473</v>
+      </c>
+      <c r="I1017" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1017" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1017" s="54" t="n">
+        <v>3.1374</v>
+      </c>
+      <c r="L1017" s="55" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="M1017" t="inlineStr"/>
+      <c r="N1017" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1018" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1018" s="27" t="inlineStr">
+        <is>
+          <t>Halkbank</t>
+        </is>
+      </c>
+      <c r="D1018" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1018" s="12" t="n">
+        <v>6527.6</v>
+      </c>
+      <c r="F1018" s="12" t="n">
+        <v>7423.1</v>
+      </c>
+      <c r="G1018" s="12" t="n">
+        <v>895.5</v>
+      </c>
+      <c r="H1018" s="13" t="n">
+        <v>0.1371867148722348</v>
+      </c>
+      <c r="I1018" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1018" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1018" s="54" t="n">
+        <v>895.5</v>
+      </c>
+      <c r="L1018" s="55" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="M1018" t="inlineStr"/>
+      <c r="N1018" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1019" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1019" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D1019" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1019" s="8" t="n">
+        <v>48.213</v>
+      </c>
+      <c r="F1019" s="8" t="n">
+        <v>48.323</v>
+      </c>
+      <c r="G1019" s="8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H1019" s="9" t="n">
+        <v>0.002281542322610085</v>
+      </c>
+      <c r="I1019" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1019" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1019" s="54" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L1019" s="55" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="M1019" t="inlineStr"/>
+      <c r="N1019" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1020" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1020" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D1020" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1020" s="10" t="n">
+        <v>55.842</v>
+      </c>
+      <c r="F1020" s="10" t="n">
+        <v>56.072</v>
+      </c>
+      <c r="G1020" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H1020" s="11" t="n">
+        <v>0.004118763654596898</v>
+      </c>
+      <c r="I1020" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1020" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1020" s="54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L1020" s="55" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="M1020" t="inlineStr"/>
+      <c r="N1020" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1021" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1021" s="28" t="inlineStr">
+        <is>
+          <t>Harem</t>
+        </is>
+      </c>
+      <c r="D1021" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1021" s="12" t="n">
+        <v>6796.95</v>
+      </c>
+      <c r="F1021" s="12" t="n">
+        <v>6888.68</v>
+      </c>
+      <c r="G1021" s="12" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="H1021" s="13" t="n">
+        <v>0.01349575912725561</v>
+      </c>
+      <c r="I1021" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1021" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1021" s="54" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="L1021" s="55" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="M1021" t="inlineStr"/>
+      <c r="N1021" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1022" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1022" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D1022" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1022" s="8" t="n">
+        <v>47.8264</v>
+      </c>
+      <c r="F1022" s="8" t="n">
+        <v>48.4542</v>
+      </c>
+      <c r="G1022" s="8" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="H1022" s="9" t="n">
+        <v>0.01312664135289296</v>
+      </c>
+      <c r="I1022" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1022" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1022" s="54" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="L1022" s="55" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="M1022" t="inlineStr"/>
+      <c r="N1022" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1023" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1023" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D1023" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1023" s="10" t="n">
+        <v>55.6568</v>
+      </c>
+      <c r="F1023" s="10" t="n">
+        <v>56.2917</v>
+      </c>
+      <c r="G1023" s="10" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="H1023" s="11" t="n">
+        <v>0.01140741113394949</v>
+      </c>
+      <c r="I1023" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1023" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1023" s="54" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="L1023" s="55" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="M1023" t="inlineStr"/>
+      <c r="N1023" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1024" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1024" s="29" t="inlineStr">
+        <is>
+          <t>Hayat Finans</t>
+        </is>
+      </c>
+      <c r="D1024" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1024" s="12" t="n">
+        <v>6827.3</v>
+      </c>
+      <c r="F1024" s="12" t="n">
+        <v>6969.05</v>
+      </c>
+      <c r="G1024" s="12" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="H1024" s="13" t="n">
+        <v>0.0207622339724342</v>
+      </c>
+      <c r="I1024" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1024" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1024" s="54" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="L1024" s="55" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="M1024" t="inlineStr"/>
+      <c r="N1024" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1025" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1025" s="30" t="inlineStr">
+        <is>
+          <t>Hepsipay</t>
+        </is>
+      </c>
+      <c r="D1025" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1025" s="12" t="n">
+        <v>6834.62</v>
+      </c>
+      <c r="F1025" s="12" t="n">
+        <v>7034.06</v>
+      </c>
+      <c r="G1025" s="12" t="n">
+        <v>199.44</v>
+      </c>
+      <c r="H1025" s="13" t="n">
+        <v>0.02918084692345734</v>
+      </c>
+      <c r="I1025" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1025" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1025" s="54" t="n">
+        <v>199.44</v>
+      </c>
+      <c r="L1025" s="55" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="M1025" t="inlineStr"/>
+      <c r="N1025" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1026" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1026" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D1026" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1026" s="8" t="n">
+        <v>47.5991</v>
+      </c>
+      <c r="F1026" s="8" t="n">
+        <v>49.5206</v>
+      </c>
+      <c r="G1026" s="8" t="n">
+        <v>1.9215</v>
+      </c>
+      <c r="H1026" s="9" t="n">
+        <v>0.04036841032708602</v>
+      </c>
+      <c r="I1026" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1026" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1026" s="54" t="n">
+        <v>1.9215</v>
+      </c>
+      <c r="L1026" s="55" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="M1026" t="inlineStr"/>
+      <c r="N1026" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1027" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1027" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D1027" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1027" s="10" t="n">
+        <v>54.8418</v>
+      </c>
+      <c r="F1027" s="10" t="n">
+        <v>57.9922</v>
+      </c>
+      <c r="G1027" s="10" t="n">
+        <v>3.1504</v>
+      </c>
+      <c r="H1027" s="11" t="n">
+        <v>0.05744523338037774</v>
+      </c>
+      <c r="I1027" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1027" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1027" s="54" t="n">
+        <v>3.1504</v>
+      </c>
+      <c r="L1027" s="55" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="M1027" t="inlineStr"/>
+      <c r="N1027" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1028" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1028" s="31" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D1028" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1028" s="12" t="n">
+        <v>6717.61</v>
+      </c>
+      <c r="F1028" s="12" t="n">
+        <v>7370.64</v>
+      </c>
+      <c r="G1028" s="12" t="n">
+        <v>653.03</v>
+      </c>
+      <c r="H1028" s="13" t="n">
+        <v>0.09721165712210146</v>
+      </c>
+      <c r="I1028" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1028" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1028" s="54" t="n">
+        <v>653.03</v>
+      </c>
+      <c r="L1028" s="55" t="n">
+        <v>0.09720000000000001</v>
+      </c>
+      <c r="M1028" t="inlineStr"/>
+      <c r="N1028" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1029" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1029" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D1029" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1029" s="8" t="n">
+        <v>47.2028</v>
+      </c>
+      <c r="F1029" s="8" t="n">
+        <v>49.4795</v>
+      </c>
+      <c r="G1029" s="8" t="n">
+        <v>2.2767</v>
+      </c>
+      <c r="H1029" s="9" t="n">
+        <v>0.04823230825290025</v>
+      </c>
+      <c r="I1029" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1029" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1029" s="54" t="n">
+        <v>2.2768</v>
+      </c>
+      <c r="L1029" s="55" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="M1029" t="inlineStr"/>
+      <c r="N1029" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1030" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1030" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D1030" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1030" s="10" t="n">
+        <v>54.8132</v>
+      </c>
+      <c r="F1030" s="10" t="n">
+        <v>57.4618</v>
+      </c>
+      <c r="G1030" s="10" t="n">
+        <v>2.6486</v>
+      </c>
+      <c r="H1030" s="11" t="n">
+        <v>0.04832047754920347</v>
+      </c>
+      <c r="I1030" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1030" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1030" s="54" t="n">
+        <v>2.6486</v>
+      </c>
+      <c r="L1030" s="55" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="M1030" t="inlineStr"/>
+      <c r="N1030" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1031" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1031" s="32" t="inlineStr">
+        <is>
+          <t>ING Bank</t>
+        </is>
+      </c>
+      <c r="D1031" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1031" s="12" t="n">
+        <v>6662.76</v>
+      </c>
+      <c r="F1031" s="12" t="n">
+        <v>7078.51</v>
+      </c>
+      <c r="G1031" s="12" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="H1031" s="13" t="n">
+        <v>0.06239906585258961</v>
+      </c>
+      <c r="I1031" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1031" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1031" s="54" t="n">
+        <v>415.74</v>
+      </c>
+      <c r="L1031" s="55" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="M1031" t="inlineStr"/>
+      <c r="N1031" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1032" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1032" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D1032" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1032" s="8" t="n">
+        <v>47.1425</v>
+      </c>
+      <c r="F1032" s="8" t="n">
+        <v>49.7585</v>
+      </c>
+      <c r="G1032" s="8" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="H1032" s="9" t="n">
+        <v>0.05549132947976879</v>
+      </c>
+      <c r="I1032" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1032" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1032" s="54" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="L1032" s="55" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="M1032" t="inlineStr"/>
+      <c r="N1032" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1033" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1033" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D1033" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1033" s="10" t="n">
+        <v>54.7418</v>
+      </c>
+      <c r="F1033" s="10" t="n">
+        <v>57.7845</v>
+      </c>
+      <c r="G1033" s="10" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="H1033" s="11" t="n">
+        <v>0.05558275394670983</v>
+      </c>
+      <c r="I1033" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1033" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1033" s="54" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="L1033" s="55" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="M1033" t="inlineStr"/>
+      <c r="N1033" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1034" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1034" s="33" t="inlineStr">
+        <is>
+          <t>İş Bankası</t>
+        </is>
+      </c>
+      <c r="D1034" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1034" s="12" t="n">
+        <v>6458.79</v>
+      </c>
+      <c r="F1034" s="12" t="n">
+        <v>7275.6</v>
+      </c>
+      <c r="G1034" s="12" t="n">
+        <v>816.8099999999999</v>
+      </c>
+      <c r="H1034" s="13" t="n">
+        <v>0.1264648641618631</v>
+      </c>
+      <c r="I1034" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1034" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1034" s="54" t="n">
+        <v>816.8099999999999</v>
+      </c>
+      <c r="L1034" s="55" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="M1034" t="inlineStr"/>
+      <c r="N1034" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1035" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1035" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D1035" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1035" s="8" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="F1035" s="8" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="G1035" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H1035" s="9" t="n">
+        <v>0.0002072538860103627</v>
+      </c>
+      <c r="I1035" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1035" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1035" s="54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L1035" s="55" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="M1035" t="inlineStr"/>
+      <c r="N1035" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1036" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1036" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D1036" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1036" s="10" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F1036" s="10" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="G1036" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1036" s="11" t="n">
+        <v>0.0008944543828264759</v>
+      </c>
+      <c r="I1036" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1036" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1036" s="54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L1036" s="55" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="M1036" t="inlineStr"/>
+      <c r="N1036" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1037" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1037" s="34" t="inlineStr">
+        <is>
+          <t>Kapalıçarşı</t>
+        </is>
+      </c>
+      <c r="D1037" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1037" s="12" t="n">
+        <v>6818.04</v>
+      </c>
+      <c r="F1037" s="12" t="n">
+        <v>6829.15</v>
+      </c>
+      <c r="G1037" s="12" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="H1037" s="13" t="n">
+        <v>0.001629500560278321</v>
+      </c>
+      <c r="I1037" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1037" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1037" s="54" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="L1037" s="55" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="M1037" t="inlineStr"/>
+      <c r="N1037" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1038" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1038" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D1038" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1038" s="8" t="n">
+        <v>44.8474</v>
+      </c>
+      <c r="F1038" s="8" t="n">
+        <v>49.3407</v>
+      </c>
+      <c r="G1038" s="8" t="n">
+        <v>4.4933</v>
+      </c>
+      <c r="H1038" s="9" t="n">
+        <v>0.1001908694818429</v>
+      </c>
+      <c r="I1038" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1038" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1038" s="54" t="n">
+        <v>4.4933</v>
+      </c>
+      <c r="L1038" s="55" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="M1038" t="inlineStr"/>
+      <c r="N1038" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1039" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1039" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D1039" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1039" s="10" t="n">
+        <v>52.0651</v>
+      </c>
+      <c r="F1039" s="10" t="n">
+        <v>57.325</v>
+      </c>
+      <c r="G1039" s="10" t="n">
+        <v>5.2599</v>
+      </c>
+      <c r="H1039" s="11" t="n">
+        <v>0.1010254469884817</v>
+      </c>
+      <c r="I1039" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1039" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1039" s="54" t="n">
+        <v>5.2599</v>
+      </c>
+      <c r="L1039" s="55" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="M1039" t="inlineStr"/>
+      <c r="N1039" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1040" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1040" s="35" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk</t>
+        </is>
+      </c>
+      <c r="D1040" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1040" s="12" t="n">
+        <v>6435.95</v>
+      </c>
+      <c r="F1040" s="12" t="n">
+        <v>7063.67</v>
+      </c>
+      <c r="G1040" s="12" t="n">
+        <v>627.72</v>
+      </c>
+      <c r="H1040" s="13" t="n">
+        <v>0.09753338667951118</v>
+      </c>
+      <c r="I1040" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1040" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1040" s="54" t="n">
+        <v>627.71</v>
+      </c>
+      <c r="L1040" s="55" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="M1040" t="inlineStr"/>
+      <c r="N1040" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1041" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1041" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D1041" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1041" s="8" t="n">
+        <v>48.2326</v>
+      </c>
+      <c r="F1041" s="8" t="n">
+        <v>48.3195</v>
+      </c>
+      <c r="G1041" s="8" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="H1041" s="9" t="n">
+        <v>0.001801685996608103</v>
+      </c>
+      <c r="I1041" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1041" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1041" s="54" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="L1041" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M1041" t="inlineStr"/>
+      <c r="N1041" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1042" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1042" s="36" t="inlineStr">
+        <is>
+          <t>Merkez Bankası</t>
+        </is>
+      </c>
+      <c r="D1042" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1042" s="10" t="n">
+        <v>56.0571</v>
+      </c>
+      <c r="F1042" s="10" t="n">
+        <v>56.1581</v>
+      </c>
+      <c r="G1042" s="10" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H1042" s="11" t="n">
+        <v>0.001801734303058845</v>
+      </c>
+      <c r="I1042" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1042" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1042" s="54" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="L1042" s="55" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="M1042" t="inlineStr"/>
+      <c r="N1042" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1043" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1043" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D1043" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1043" s="8" t="n">
+        <v>48.0452</v>
+      </c>
+      <c r="F1043" s="8" t="n">
+        <v>48.482</v>
+      </c>
+      <c r="G1043" s="8" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="H1043" s="9" t="n">
+        <v>0.009091438895040504</v>
+      </c>
+      <c r="I1043" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1043" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1043" s="54" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="L1043" s="55" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="M1043" t="inlineStr"/>
+      <c r="N1043" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1044" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1044" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D1044" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1044" s="10" t="n">
+        <v>55.9066</v>
+      </c>
+      <c r="F1044" s="10" t="n">
+        <v>56.3121</v>
+      </c>
+      <c r="G1044" s="10" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="H1044" s="11" t="n">
+        <v>0.007253168677758976</v>
+      </c>
+      <c r="I1044" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1044" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1044" s="54" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="L1044" s="55" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="M1044" t="inlineStr"/>
+      <c r="N1044" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1045" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1045" s="37" t="inlineStr">
+        <is>
+          <t>Misyon Bank</t>
+        </is>
+      </c>
+      <c r="D1045" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1045" s="12" t="n">
+        <v>6796.19</v>
+      </c>
+      <c r="F1045" s="12" t="n">
+        <v>6876.58</v>
+      </c>
+      <c r="G1045" s="12" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="H1045" s="13" t="n">
+        <v>0.01182868636692029</v>
+      </c>
+      <c r="I1045" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1045" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1045" s="54" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="L1045" s="55" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="M1045" t="inlineStr"/>
+      <c r="N1045" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1046" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1046" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D1046" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1046" s="8" t="n">
+        <v>48.239</v>
+      </c>
+      <c r="F1046" s="8" t="n">
+        <v>48.382</v>
+      </c>
+      <c r="G1046" s="8" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="H1046" s="9" t="n">
+        <v>0.002964406393167354</v>
+      </c>
+      <c r="I1046" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1046" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1046" s="54" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="L1046" s="55" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M1046" t="inlineStr"/>
+      <c r="N1046" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1047" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1047" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D1047" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1047" s="10" t="n">
+        <v>55.851</v>
+      </c>
+      <c r="F1047" s="10" t="n">
+        <v>56.093</v>
+      </c>
+      <c r="G1047" s="10" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H1047" s="11" t="n">
+        <v>0.004332957332903619</v>
+      </c>
+      <c r="I1047" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1047" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1047" s="54" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L1047" s="55" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="M1047" t="inlineStr"/>
+      <c r="N1047" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1048" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1048" s="38" t="inlineStr">
+        <is>
+          <t>Odacı</t>
+        </is>
+      </c>
+      <c r="D1048" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1048" s="12" t="n">
+        <v>6813</v>
+      </c>
+      <c r="F1048" s="12" t="n">
+        <v>6879</v>
+      </c>
+      <c r="G1048" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H1048" s="13" t="n">
+        <v>0.009687362395420521</v>
+      </c>
+      <c r="I1048" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1048" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1048" s="54" t="n">
+        <v>66</v>
+      </c>
+      <c r="L1048" s="55" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="M1048" t="inlineStr"/>
+      <c r="N1048" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1049" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1049" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D1049" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1049" s="8" t="n">
+        <v>47.3765</v>
+      </c>
+      <c r="F1049" s="8" t="n">
+        <v>49.1765</v>
+      </c>
+      <c r="G1049" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1049" s="9" t="n">
+        <v>0.0379935199940899</v>
+      </c>
+      <c r="I1049" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1049" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1049" s="54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L1049" s="55" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M1049" t="inlineStr"/>
+      <c r="N1049" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1050" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1050" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D1050" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1050" s="10" t="n">
+        <v>54.987</v>
+      </c>
+      <c r="F1050" s="10" t="n">
+        <v>57.127</v>
+      </c>
+      <c r="G1050" s="10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H1050" s="11" t="n">
+        <v>0.0389182897775838</v>
+      </c>
+      <c r="I1050" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1050" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1050" s="54" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L1050" s="55" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="M1050" t="inlineStr"/>
+      <c r="N1050" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1051" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1051" s="39" t="inlineStr">
+        <is>
+          <t>Odeabank</t>
+        </is>
+      </c>
+      <c r="D1051" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1051" s="12" t="n">
+        <v>6700.83</v>
+      </c>
+      <c r="F1051" s="12" t="n">
+        <v>7050.83</v>
+      </c>
+      <c r="G1051" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="H1051" s="13" t="n">
+        <v>0.05223233539725676</v>
+      </c>
+      <c r="I1051" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1051" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1051" s="54" t="n">
+        <v>350</v>
+      </c>
+      <c r="L1051" s="55" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="M1051" t="inlineStr"/>
+      <c r="N1051" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1052" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1052" s="40" t="inlineStr">
+        <is>
+          <t>Papara</t>
+        </is>
+      </c>
+      <c r="D1052" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1052" s="12" t="n">
+        <v>6834.62</v>
+      </c>
+      <c r="F1052" s="12" t="n">
+        <v>7020.02</v>
+      </c>
+      <c r="G1052" s="12" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="H1052" s="13" t="n">
+        <v>0.02712659957686016</v>
+      </c>
+      <c r="I1052" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1052" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1052" s="54" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="L1052" s="55" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="M1052" t="inlineStr"/>
+      <c r="N1052" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1053" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1053" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D1053" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1053" s="8" t="n">
+        <v>46.9325</v>
+      </c>
+      <c r="F1053" s="8" t="n">
+        <v>49.9525</v>
+      </c>
+      <c r="G1053" s="8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H1053" s="9" t="n">
+        <v>0.06434773344697171</v>
+      </c>
+      <c r="I1053" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1053" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1053" s="54" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L1053" s="55" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="M1053" t="inlineStr"/>
+      <c r="N1053" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1054" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1054" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D1054" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1054" s="10" t="n">
+        <v>53.9523</v>
+      </c>
+      <c r="F1054" s="10" t="n">
+        <v>58.6008</v>
+      </c>
+      <c r="G1054" s="10" t="n">
+        <v>4.6485</v>
+      </c>
+      <c r="H1054" s="11" t="n">
+        <v>0.08615944083940814</v>
+      </c>
+      <c r="I1054" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1054" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1054" s="54" t="n">
+        <v>4.6485</v>
+      </c>
+      <c r="L1054" s="55" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="M1054" t="inlineStr"/>
+      <c r="N1054" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1055" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1055" s="41" t="inlineStr">
+        <is>
+          <t>QNB Finansbank</t>
+        </is>
+      </c>
+      <c r="D1055" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1055" s="12" t="n">
+        <v>6553.72</v>
+      </c>
+      <c r="F1055" s="12" t="n">
+        <v>7184.14</v>
+      </c>
+      <c r="G1055" s="12" t="n">
+        <v>630.42</v>
+      </c>
+      <c r="H1055" s="13" t="n">
+        <v>0.09619269666693114</v>
+      </c>
+      <c r="I1055" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1055" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1055" s="54" t="n">
+        <v>630.42</v>
+      </c>
+      <c r="L1055" s="55" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="M1055" t="inlineStr"/>
+      <c r="N1055" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1056" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1056" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D1056" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1056" s="8" t="n">
+        <v>48.1293</v>
+      </c>
+      <c r="F1056" s="8" t="n">
+        <v>48.6741</v>
+      </c>
+      <c r="G1056" s="8" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="H1056" s="9" t="n">
+        <v>0.01131950807512264</v>
+      </c>
+      <c r="I1056" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1056" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1056" s="54" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="L1056" s="55" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="M1056" t="inlineStr"/>
+      <c r="N1056" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1057" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1057" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D1057" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1057" s="10" t="n">
+        <v>55.684</v>
+      </c>
+      <c r="F1057" s="10" t="n">
+        <v>56.5277</v>
+      </c>
+      <c r="G1057" s="10" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="H1057" s="11" t="n">
+        <v>0.0151515695711515</v>
+      </c>
+      <c r="I1057" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1057" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1057" s="54" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="L1057" s="55" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="M1057" t="inlineStr"/>
+      <c r="N1057" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1058" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1058" s="42" t="inlineStr">
+        <is>
+          <t>TOM Bank Hadi</t>
+        </is>
+      </c>
+      <c r="D1058" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1058" s="12" t="n">
+        <v>6864.09</v>
+      </c>
+      <c r="F1058" s="12" t="n">
+        <v>7378.9</v>
+      </c>
+      <c r="G1058" s="12" t="n">
+        <v>514.8099999999999</v>
+      </c>
+      <c r="H1058" s="13" t="n">
+        <v>0.07500047347864029</v>
+      </c>
+      <c r="I1058" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1058" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1058" s="54" t="n">
+        <v>514.8099999999999</v>
+      </c>
+      <c r="L1058" s="55" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M1058" t="inlineStr"/>
+      <c r="N1058" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1059" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1059" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D1059" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1059" s="8" t="n">
+        <v>47.7911</v>
+      </c>
+      <c r="F1059" s="8" t="n">
+        <v>48.7367</v>
+      </c>
+      <c r="G1059" s="8" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="H1059" s="9" t="n">
+        <v>0.01978611080305747</v>
+      </c>
+      <c r="I1059" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1059" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1059" s="54" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="L1059" s="55" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="M1059" t="inlineStr"/>
+      <c r="N1059" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1060" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1060" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D1060" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1060" s="10" t="n">
+        <v>55.532</v>
+      </c>
+      <c r="F1060" s="10" t="n">
+        <v>56.5537</v>
+      </c>
+      <c r="G1060" s="10" t="n">
+        <v>1.0217</v>
+      </c>
+      <c r="H1060" s="11" t="n">
+        <v>0.01839840092199092</v>
+      </c>
+      <c r="I1060" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1060" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1060" s="54" t="n">
+        <v>1.0217</v>
+      </c>
+      <c r="L1060" s="55" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="M1060" t="inlineStr"/>
+      <c r="N1060" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1061" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1061" s="43" t="inlineStr">
+        <is>
+          <t>Türkiye Finans</t>
+        </is>
+      </c>
+      <c r="D1061" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1061" s="12" t="n">
+        <v>6763.3</v>
+      </c>
+      <c r="F1061" s="12" t="n">
+        <v>6980.72</v>
+      </c>
+      <c r="G1061" s="12" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="H1061" s="13" t="n">
+        <v>0.03214702881729334</v>
+      </c>
+      <c r="I1061" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1061" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1061" s="54" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="L1061" s="55" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="M1061" t="inlineStr"/>
+      <c r="N1061" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1062" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1062" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D1062" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1062" s="8" t="n">
+        <v>47.9608</v>
+      </c>
+      <c r="F1062" s="8" t="n">
+        <v>48.5704</v>
+      </c>
+      <c r="G1062" s="8" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="H1062" s="9" t="n">
+        <v>0.01271038014378409</v>
+      </c>
+      <c r="I1062" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1062" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1062" s="54" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="L1062" s="55" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="M1062" t="inlineStr"/>
+      <c r="N1062" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1063" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1063" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D1063" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1063" s="10" t="n">
+        <v>55.6608</v>
+      </c>
+      <c r="F1063" s="10" t="n">
+        <v>56.3368</v>
+      </c>
+      <c r="G1063" s="10" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="H1063" s="11" t="n">
+        <v>0.01214499252615845</v>
+      </c>
+      <c r="I1063" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1063" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1063" s="54" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="L1063" s="55" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="M1063" t="inlineStr"/>
+      <c r="N1063" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1064" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1064" s="44" t="inlineStr">
+        <is>
+          <t>Vakıf Katılım</t>
+        </is>
+      </c>
+      <c r="D1064" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1064" s="12" t="n">
+        <v>6758.27</v>
+      </c>
+      <c r="F1064" s="12" t="n">
+        <v>6922.44</v>
+      </c>
+      <c r="G1064" s="12" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="H1064" s="13" t="n">
+        <v>0.02429171962647246</v>
+      </c>
+      <c r="I1064" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1064" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1064" s="54" t="n">
+        <v>164.17</v>
+      </c>
+      <c r="L1064" s="55" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="M1064" t="inlineStr"/>
+      <c r="N1064" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1065" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1065" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D1065" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1065" s="8" t="n">
+        <v>47.0674</v>
+      </c>
+      <c r="F1065" s="8" t="n">
+        <v>49.8524</v>
+      </c>
+      <c r="G1065" s="8" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="H1065" s="9" t="n">
+        <v>0.05917046618253823</v>
+      </c>
+      <c r="I1065" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1065" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1065" s="54" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="L1065" s="55" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="M1065" t="inlineStr"/>
+      <c r="N1065" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1066" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1066" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D1066" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1066" s="10" t="n">
+        <v>54.591</v>
+      </c>
+      <c r="F1066" s="10" t="n">
+        <v>57.749</v>
+      </c>
+      <c r="G1066" s="10" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="H1066" s="11" t="n">
+        <v>0.05784836328332509</v>
+      </c>
+      <c r="I1066" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1066" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1066" s="54" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="L1066" s="55" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="M1066" t="inlineStr"/>
+      <c r="N1066" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1067" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1067" s="45" t="inlineStr">
+        <is>
+          <t>Vakıfbank</t>
+        </is>
+      </c>
+      <c r="D1067" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1067" s="12" t="n">
+        <v>6551.45</v>
+      </c>
+      <c r="F1067" s="12" t="n">
+        <v>7449.45</v>
+      </c>
+      <c r="G1067" s="12" t="n">
+        <v>898</v>
+      </c>
+      <c r="H1067" s="13" t="n">
+        <v>0.1370688931457922</v>
+      </c>
+      <c r="I1067" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1067" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1067" s="54" t="n">
+        <v>898</v>
+      </c>
+      <c r="L1067" s="55" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="M1067" t="inlineStr"/>
+      <c r="N1067" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1068" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1068" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D1068" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1068" s="8" t="n">
+        <v>48.227</v>
+      </c>
+      <c r="F1068" s="8" t="n">
+        <v>48.356</v>
+      </c>
+      <c r="G1068" s="8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H1068" s="9" t="n">
+        <v>0.002674850187654218</v>
+      </c>
+      <c r="I1068" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1068" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1068" s="54" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="L1068" s="55" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="M1068" t="inlineStr"/>
+      <c r="N1068" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1069" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1069" s="46" t="inlineStr">
+        <is>
+          <t>Venüs</t>
+        </is>
+      </c>
+      <c r="D1069" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1069" s="10" t="n">
+        <v>55.871</v>
+      </c>
+      <c r="F1069" s="10" t="n">
+        <v>56.107</v>
+      </c>
+      <c r="G1069" s="10" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="H1069" s="11" t="n">
+        <v>0.004224016036942242</v>
+      </c>
+      <c r="I1069" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1069" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1069" s="54" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="L1069" s="55" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="M1069" t="inlineStr"/>
+      <c r="N1069" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1070" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1070" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D1070" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1070" s="8" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="F1070" s="8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G1070" s="8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H1070" s="9" t="n">
+        <v>0.05363984674329502</v>
+      </c>
+      <c r="I1070" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1070" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1070" s="54" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L1070" s="55" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="M1070" t="inlineStr"/>
+      <c r="N1070" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1071" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1071" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D1071" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1071" s="10" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="F1071" s="10" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="G1071" s="10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H1071" s="11" t="n">
+        <v>0.04769736842105263</v>
+      </c>
+      <c r="I1071" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1071" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1071" s="54" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L1071" s="55" t="n">
+        <v>0.04769999999999999</v>
+      </c>
+      <c r="M1071" t="inlineStr"/>
+      <c r="N1071" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1072" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1072" s="47" t="inlineStr">
+        <is>
+          <t>Yapıkredi</t>
+        </is>
+      </c>
+      <c r="D1072" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1072" s="12" t="n">
+        <v>6649.22</v>
+      </c>
+      <c r="F1072" s="12" t="n">
+        <v>7157.39</v>
+      </c>
+      <c r="G1072" s="12" t="n">
+        <v>508.17</v>
+      </c>
+      <c r="H1072" s="13" t="n">
+        <v>0.07642550554801916</v>
+      </c>
+      <c r="I1072" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1072" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1072" s="54" t="n">
+        <v>508.17</v>
+      </c>
+      <c r="L1072" s="55" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="M1072" t="inlineStr"/>
+      <c r="N1072" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1073" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1073" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D1073" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1073" s="8" t="n">
+        <v>47.0106</v>
+      </c>
+      <c r="F1073" s="8" t="n">
+        <v>49.8725</v>
+      </c>
+      <c r="G1073" s="8" t="n">
+        <v>2.8619</v>
+      </c>
+      <c r="H1073" s="9" t="n">
+        <v>0.06087775948403126</v>
+      </c>
+      <c r="I1073" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1073" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1073" s="54" t="n">
+        <v>2.8619</v>
+      </c>
+      <c r="L1073" s="55" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="M1073" t="inlineStr"/>
+      <c r="N1073" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1074" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1074" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D1074" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1074" s="10" t="n">
+        <v>54.5954</v>
+      </c>
+      <c r="F1074" s="10" t="n">
+        <v>57.919</v>
+      </c>
+      <c r="G1074" s="10" t="n">
+        <v>3.3236</v>
+      </c>
+      <c r="H1074" s="11" t="n">
+        <v>0.06087692369686823</v>
+      </c>
+      <c r="I1074" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1074" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1074" s="54" t="n">
+        <v>3.3236</v>
+      </c>
+      <c r="L1074" s="55" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="M1074" t="inlineStr"/>
+      <c r="N1074" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1075" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1075" s="48" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası</t>
+        </is>
+      </c>
+      <c r="D1075" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1075" s="12" t="n">
+        <v>6616.52</v>
+      </c>
+      <c r="F1075" s="12" t="n">
+        <v>7573.86</v>
+      </c>
+      <c r="G1075" s="12" t="n">
+        <v>957.34</v>
+      </c>
+      <c r="H1075" s="13" t="n">
+        <v>0.1446893533156403</v>
+      </c>
+      <c r="I1075" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1075" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1075" s="54" t="n">
+        <v>957.33</v>
+      </c>
+      <c r="L1075" s="55" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="M1075" t="inlineStr"/>
+      <c r="N1075" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1076" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1076" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D1076" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1076" s="8" t="n">
+        <v>47.0576</v>
+      </c>
+      <c r="F1076" s="8" t="n">
+        <v>49.5982</v>
+      </c>
+      <c r="G1076" s="8" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="H1076" s="9" t="n">
+        <v>0.05398915371799667</v>
+      </c>
+      <c r="I1076" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1076" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1076" s="54" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="L1076" s="55" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+      <c r="M1076" t="inlineStr"/>
+      <c r="N1076" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1077" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1077" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D1077" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1077" s="10" t="n">
+        <v>54.5954</v>
+      </c>
+      <c r="F1077" s="10" t="n">
+        <v>57.6004</v>
+      </c>
+      <c r="G1077" s="10" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="H1077" s="11" t="n">
+        <v>0.05504126721298864</v>
+      </c>
+      <c r="I1077" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1077" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1077" s="54" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="L1077" s="55" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="M1077" t="inlineStr"/>
+      <c r="N1077" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1078" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1078" s="49" t="inlineStr">
+        <is>
+          <t>Ziraat Dinamik</t>
+        </is>
+      </c>
+      <c r="D1078" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1078" s="12" t="n">
+        <v>6583.44</v>
+      </c>
+      <c r="F1078" s="12" t="n">
+        <v>7535.99</v>
+      </c>
+      <c r="G1078" s="12" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="H1078" s="13" t="n">
+        <v>0.1446887949157279</v>
+      </c>
+      <c r="I1078" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1078" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1078" s="54" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="L1078" s="55" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="M1078" t="inlineStr"/>
+      <c r="N1078" s="6" t="n">
+        <v>0.5811111111111111</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1079" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1079" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D1079" s="51" t="inlineStr">
+        <is>
+          <t>DOLAR</t>
+        </is>
+      </c>
+      <c r="E1079" s="8" t="n">
+        <v>43.1206</v>
+      </c>
+      <c r="F1079" s="8" t="n">
+        <v>53.8029</v>
+      </c>
+      <c r="G1079" s="8" t="n">
+        <v>10.6823</v>
+      </c>
+      <c r="H1079" s="9" t="n">
+        <v>0.2477307829668418</v>
+      </c>
+      <c r="I1079" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1079" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/amerikan-dolari</t>
+        </is>
+      </c>
+      <c r="K1079" s="54" t="n">
+        <v>10.6823</v>
+      </c>
+      <c r="L1079" s="55" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="M1079" t="inlineStr"/>
+      <c r="N1079" s="6" t="n">
+        <v>0.5807175925925926</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1080" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1080" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D1080" s="56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="E1080" s="10" t="n">
+        <v>50.0454</v>
+      </c>
+      <c r="F1080" s="10" t="n">
+        <v>62.5049</v>
+      </c>
+      <c r="G1080" s="10" t="n">
+        <v>12.4595</v>
+      </c>
+      <c r="H1080" s="11" t="n">
+        <v>0.2489639407418064</v>
+      </c>
+      <c r="I1080" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1080" s="53" t="inlineStr">
+        <is>
+          <t>https://kur.doviz.com/serbest-piyasa/euro</t>
+        </is>
+      </c>
+      <c r="K1080" s="54" t="n">
+        <v>12.4595</v>
+      </c>
+      <c r="L1080" s="55" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="M1080" t="inlineStr"/>
+      <c r="N1080" s="6" t="n">
+        <v>0.5809027777777778</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="58" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1081" s="6" t="n">
+        <v>0.5805092592592592</v>
+      </c>
+      <c r="C1081" s="50" t="inlineStr">
+        <is>
+          <t>Ziraat Katılım</t>
+        </is>
+      </c>
+      <c r="D1081" s="57" t="inlineStr">
+        <is>
+          <t>GRAM_ALTIN</t>
+        </is>
+      </c>
+      <c r="E1081" s="12" t="n">
+        <v>6131.92</v>
+      </c>
+      <c r="F1081" s="12" t="n">
+        <v>7732.64</v>
+      </c>
+      <c r="G1081" s="12" t="n">
+        <v>1600.72</v>
+      </c>
+      <c r="H1081" s="13" t="n">
+        <v>0.2610471108559799</v>
+      </c>
+      <c r="I1081" s="52" t="inlineStr">
+        <is>
+          <t>DOĞRU</t>
+        </is>
+      </c>
+      <c r="J1081" s="53" t="inlineStr">
+        <is>
+          <t>https://altin.doviz.com/gram-altin</t>
+        </is>
+      </c>
+      <c r="K1081" s="54" t="n">
+        <v>1600.72</v>
+      </c>
+      <c r="L1081" s="55" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M1081" t="inlineStr"/>
+      <c r="N1081" s="6" t="n">
+        <v>0.5811111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -59106,10 +64686,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J971" r:id="rId970"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J972" r:id="rId971"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J973" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J974" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J975" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J976" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J977" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J978" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J979" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J980" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J981" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J982" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J983" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J984" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J985" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J986" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J987" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J988" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J989" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J990" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J991" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J992" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J993" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J994" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J995" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J996" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J997" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J998" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J999" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1000" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1001" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1002" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1003" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1004" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1005" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1006" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1007" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1008" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1009" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1010" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1011" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1012" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1013" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1014" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1015" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1016" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1017" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1018" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1019" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1020" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1021" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1022" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1023" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1024" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1025" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1026" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1027" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1028" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1029" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1030" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1031" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1032" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1033" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1034" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1035" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1036" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1037" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1038" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1039" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1040" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1041" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1042" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1043" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1044" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1045" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1046" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1047" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1048" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1049" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1050" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1051" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1052" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1053" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1054" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1055" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1056" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1057" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1058" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1059" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1060" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1061" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1062" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1063" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1064" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1065" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1066" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1067" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1068" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1069" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1070" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1071" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1072" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1073" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1074" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1075" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1076" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1077" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1078" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1079" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1080" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1081" r:id="rId1080"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId973"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1081"/>
   </tableParts>
 </worksheet>
 </file>
@@ -59183,7 +64871,7 @@
       </c>
       <c r="B4" s="62" t="n"/>
       <c r="C4" s="63" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D4" s="62" t="n"/>
       <c r="F4" s="1" t="inlineStr">
@@ -59250,7 +64938,7 @@
       </c>
       <c r="B5" s="62" t="n"/>
       <c r="C5" s="64" t="n">
-        <v>0.5660069444444444</v>
+        <v>0.5805092592592592</v>
       </c>
       <c r="D5" s="62" t="n"/>
       <c r="F5" s="62" t="inlineStr">
@@ -59475,13 +65163,13 @@
         </is>
       </c>
       <c r="H10" s="66" t="n">
-        <v>0.03123807087072469</v>
+        <v>0.03309911326579967</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>0.03123756488180567</v>
+        <v>0.03309811925360681</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>0.04368813431780767</v>
+        <v>0.04818566864414191</v>
       </c>
     </row>
     <row r="11">
@@ -59496,13 +65184,13 @@
         </is>
       </c>
       <c r="H11" s="66" t="n">
-        <v>0.03423508640036999</v>
+        <v>0.03811369906185476</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>0.03430743211896899</v>
+        <v>0.03820454104389736</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>0.04587774544921894</v>
+        <v>0.05237786157087044</v>
       </c>
     </row>
     <row r="12">
@@ -59517,13 +65205,13 @@
         </is>
       </c>
       <c r="H12" s="66" t="n">
-        <v>0.02676212479284179</v>
+        <v>0.03124174511791733</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>0.02517415983350383</v>
+        <v>0.02892802793142863</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>0.0387328326103645</v>
+        <v>0.04501494476664027</v>
       </c>
     </row>
     <row r="13">
@@ -59538,13 +65226,13 @@
         </is>
       </c>
       <c r="H13" s="66" t="n">
-        <v>0.02835997506995525</v>
+        <v>0.03377960580563458</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>0.02836002691729699</v>
+        <v>0.03377950971389219</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>0.04509111593223626</v>
+        <v>0.06169082216280359</v>
       </c>
     </row>
     <row r="14">
@@ -59559,13 +65247,13 @@
         </is>
       </c>
       <c r="H14" s="66" t="n">
-        <v>0.03048950070140929</v>
+        <v>0.03465647216446921</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>0.03064661604921706</v>
+        <v>0.03480263903213252</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>0.04723283432904377</v>
+        <v>0.06043817263451366</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1"/>
@@ -59771,7 +65459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60095,49 +65783,49 @@
         </is>
       </c>
       <c r="U3" s="55" t="n">
-        <v>0.03123807087072469</v>
+        <v>0.03309911326579967</v>
       </c>
       <c r="V3" s="55" t="n">
-        <v>0.03423508640036999</v>
+        <v>0.03811369906185476</v>
       </c>
       <c r="W3" s="55" t="n">
-        <v>0.02676212479284179</v>
+        <v>0.03124174511791733</v>
       </c>
       <c r="X3" s="55" t="n">
-        <v>0.02835997506995525</v>
+        <v>0.03377960580563458</v>
       </c>
       <c r="Y3" s="55" t="n">
-        <v>0.03048950070140929</v>
+        <v>0.03465647216446921</v>
       </c>
       <c r="Z3" s="55" t="n">
-        <v>0.03123756488180567</v>
+        <v>0.03309811925360681</v>
       </c>
       <c r="AA3" s="55" t="n">
-        <v>0.03430743211896899</v>
+        <v>0.03820454104389736</v>
       </c>
       <c r="AB3" s="55" t="n">
-        <v>0.02517415983350383</v>
+        <v>0.02892802793142863</v>
       </c>
       <c r="AC3" s="55" t="n">
-        <v>0.02836002691729699</v>
+        <v>0.03377950971389219</v>
       </c>
       <c r="AD3" s="55" t="n">
-        <v>0.03064661604921706</v>
+        <v>0.03480263903213252</v>
       </c>
       <c r="AE3" s="55" t="n">
-        <v>0.04368813431780767</v>
+        <v>0.04818566864414191</v>
       </c>
       <c r="AF3" s="55" t="n">
-        <v>0.04587774544921894</v>
+        <v>0.05237786157087044</v>
       </c>
       <c r="AG3" s="55" t="n">
-        <v>0.0387328326103645</v>
+        <v>0.04501494476664027</v>
       </c>
       <c r="AH3" s="55" t="n">
-        <v>0.04509111593223626</v>
+        <v>0.06169082216280359</v>
       </c>
       <c r="AI3" s="55" t="n">
-        <v>0.04723283432904377</v>
+        <v>0.06043817263451366</v>
       </c>
     </row>
     <row r="4">
@@ -60501,6 +66189,58 @@
         <v>0.1446893533156403</v>
       </c>
       <c r="P10" s="55" t="n">
+        <v>0.1264648641618631</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>🔴 06.09 Paz</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="n">
+        <v>0.0424043252411746</v>
+      </c>
+      <c r="C11" s="55" t="n">
+        <v>0.05750676236927861</v>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>0.05363984674329502</v>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>0.06087775948403126</v>
+      </c>
+      <c r="F11" s="55" t="n">
+        <v>0.05549132947976879</v>
+      </c>
+      <c r="G11" s="55" t="n">
+        <v>0.04240089111261253</v>
+      </c>
+      <c r="H11" s="55" t="n">
+        <v>0.05769008566853923</v>
+      </c>
+      <c r="I11" s="55" t="n">
+        <v>0.04769736842105263</v>
+      </c>
+      <c r="J11" s="55" t="n">
+        <v>0.06087692369686823</v>
+      </c>
+      <c r="K11" s="55" t="n">
+        <v>0.05558275394670983</v>
+      </c>
+      <c r="L11" s="55" t="n">
+        <v>0.07067334027581308</v>
+      </c>
+      <c r="M11" s="55" t="n">
+        <v>0.08487844217912797</v>
+      </c>
+      <c r="N11" s="55" t="n">
+        <v>0.07642550554801916</v>
+      </c>
+      <c r="O11" s="55" t="n">
+        <v>0.1446893533156403</v>
+      </c>
+      <c r="P11" s="55" t="n">
         <v>0.1264648641618631</v>
       </c>
     </row>

--- a/output/banka_kurlari.xlsx
+++ b/output/banka_kurlari.xlsx
@@ -431,6 +431,7 @@
     <xf numFmtId="10" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -439,7 +440,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -578,9 +578,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -610,16 +610,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$B$2:$B$11</f>
+              <f>'GRAFIK_VERILERI'!$B$2:$B$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.02853217795625066</v>
                 </pt>
@@ -649,6 +652,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.0424043252411746</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02836730405547384</v>
                 </pt>
               </numCache>
             </numRef>
@@ -694,9 +700,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -726,16 +732,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$11</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -765,6 +774,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.05750676236927861</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02833931607783866</v>
                 </pt>
               </numCache>
             </numRef>
@@ -810,9 +822,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -842,16 +854,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$D$2:$D$11</f>
+              <f>'GRAFIK_VERILERI'!$D$2:$D$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.0212363330529857</v>
                 </pt>
@@ -881,6 +896,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.05363984674329502</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02092487968194183</v>
                 </pt>
               </numCache>
             </numRef>
@@ -926,9 +944,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -958,16 +976,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$E$2:$E$11</f>
+              <f>'GRAFIK_VERILERI'!$E$2:$E$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.02022862958363784</v>
                 </pt>
@@ -997,6 +1018,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.06087775948403126</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02023091899095272</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1042,9 +1066,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1074,16 +1098,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$F$2:$F$11</f>
+              <f>'GRAFIK_VERILERI'!$F$2:$F$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.024367308299148</v>
                 </pt>
@@ -1113,6 +1140,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.05549132947976879</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02421338397570505</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1233,9 +1263,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1265,16 +1295,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GRAFIK_VERILERI'!$C$2:$C$11</f>
+              <f>'GRAFIK_VERILERI'!$C$2:$C$12</f>
               <numCache>
                 <formatCode>0.00%</formatCode>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>0.02850867930903408</v>
                 </pt>
@@ -1304,6 +1337,9 @@
                 </pt>
                 <pt idx="9">
                   <v>0.05750676236927861</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.02833931607783866</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1352,8 +1388,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.06361309724202022"/>
-          <min val="0.02253896686120076"/>
+          <max val="0.06362657398100176"/>
+          <min val="0.02245810642731147"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -1444,9 +1480,9 @@
           </marker>
           <cat>
             <strRef>
-              <f>'GRAFIK_VERILERI'!$A$2:$A$11</f>
+              <f>'GRAFIK_VERILERI'!$A$2:$A$12</f>
               <strCache>
-                <ptCount val="10"/>
+                <ptCount val="11"/>
                 <pt idx="0">
                   <v>28.08</v>
                 </pt>
@@ -1476,16 +1512,19 @@
                 </pt>
                 <pt idx="9">
                   <v>🔴 06.09 Paz</v>
+                </pt>
+                <pt idx="10">
+                  <v>07.09</v>
                 </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'GR